--- a/A061_典当与资金台账/A061_典当登记表.xlsx
+++ b/A061_典当与资金台账/A061_典当登记表.xlsx
@@ -14,10 +14,11 @@
     <sheet name="金辉典当" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="明道典当" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="个人典当" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="查询表" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="查询表（新）" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="查询表" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId11"/>
+    <externalReference r:id="rId12"/>
   </externalReferences>
   <definedNames>
     <definedName name="日滞纳金率">资料!$L$4</definedName>
@@ -35,9 +36,8 @@
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
 <metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="2">
+  <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-    <metadataType name="XLRICHVALUE" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1"/>
   </metadataTypes>
   <futureMetadata name="XLDAPR" count="1">
     <bk>
@@ -48,34 +48,21 @@
       </extLst>
     </bk>
   </futureMetadata>
-  <futureMetadata name="XLRICHVALUE" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{3e2802c4-a4d2-4d8b-9148-e3be6c30e623}">
-          <xlrd:rvb i="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
   <cellMetadata count="1">
     <bk>
       <rc t="1" v="0"/>
     </bk>
   </cellMetadata>
-  <valueMetadata count="1">
-    <bk>
-      <rc t="2" v="0"/>
-    </bk>
-  </valueMetadata>
 </metadata>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.0000"/>
     <numFmt numFmtId="165" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="yyyy-mm-dd;;;@"/>
   </numFmts>
   <fonts count="17">
     <font>
@@ -297,7 +284,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -382,22 +369,31 @@
     <xf numFmtId="4" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="166" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="49" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -406,14 +402,11 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="3">
     <dxf>
       <font>
         <b val="1"/>
@@ -428,6 +421,19 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="00FFD7D7"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <name val="微软雅黑"/>
+        <b val="1"/>
+        <color rgb="00FFFFFF"/>
+        <sz val="10"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C00000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -507,7 +513,7 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames count="1">
+    <sheetNames>
       <sheetName val="数据录入"/>
     </sheetNames>
     <sheetDataSet>
@@ -807,7 +813,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -829,7 +835,7 @@
     <row r="3" ht="24" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>一、七张表，各管一段</t>
+          <t>一、八张表，各管一段</t>
         </is>
       </c>
       <c r="B3" s="2" t="n"/>
@@ -965,63 +971,63 @@
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
         <is>
+          <t>查询表（新）</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>查客户</t>
+        </is>
+      </c>
+      <c r="C11" s="7" t="inlineStr">
+        <is>
+          <t>★ 主用这张。第 1 行输姓名（同名才补身份证号），左边典当明细、右边资金收付并排看，下面是不动产。</t>
+        </is>
+      </c>
+      <c r="D11" s="3" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
           <t>查询表</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B12" s="6" t="inlineStr">
         <is>
           <t>查客户</t>
         </is>
       </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>输入客户姓名，一次拉出他的典当记录、不动产记录、资金收付流水。</t>
-        </is>
-      </c>
-      <c r="D11" s="3" t="n"/>
-    </row>
-    <row r="13" ht="24" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="C12" s="7" t="inlineStr">
+        <is>
+          <t>旧版，三块竖着排，内容一样，保留备用。不想要可以右键删掉。</t>
+        </is>
+      </c>
+      <c r="D12" s="3" t="n"/>
+    </row>
+    <row r="14" ht="24" customHeight="1">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>二、三张子表是怎么自动拆出来的</t>
         </is>
       </c>
-      <c r="B13" s="2" t="n"/>
-      <c r="C13" s="2" t="n"/>
-      <c r="D13" s="3" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
-        <is>
-          <t>公式</t>
-        </is>
-      </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>FILTER</t>
-        </is>
-      </c>
-      <c r="C14" s="7" t="inlineStr">
-        <is>
-          <t>每张子表的 A4 是一条 FILTER：把表2里「抵押机构 = 本表名字」的行整块搬过来。</t>
-        </is>
-      </c>
+      <c r="B14" s="2" t="n"/>
+      <c r="C14" s="2" t="n"/>
       <c r="D14" s="3" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="5" t="inlineStr">
         <is>
-          <t>所以</t>
+          <t>公式</t>
         </is>
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>别在子表里打字</t>
+          <t>FILTER</t>
         </is>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>子表整块是一条公式的结果，手动输入会把公式顶掉。要改去表2改。</t>
+          <t>每张子表的 A4 是一条 FILTER：把表2里「抵押机构 = 本表名字」的行整块搬过来。</t>
         </is>
       </c>
       <c r="D15" s="3" t="n"/>
@@ -1029,63 +1035,63 @@
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
+          <t>所以</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>别在子表里打字</t>
+        </is>
+      </c>
+      <c r="C16" s="7" t="inlineStr">
+        <is>
+          <t>子表整块是一条公式的结果，手动输入会把公式顶掉。要改去表2改。</t>
+        </is>
+      </c>
+      <c r="D16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="inlineStr">
+        <is>
           <t>新增机构</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B17" s="6" t="inlineStr">
         <is>
           <t>两步</t>
         </is>
       </c>
-      <c r="C16" s="7" t="inlineStr">
+      <c r="C17" s="7" t="inlineStr">
         <is>
           <t>① 在【资料】A 列加机构名；② 复制一张子表，把 B2 改成新机构名即可。</t>
         </is>
       </c>
-      <c r="D16" s="3" t="n"/>
-    </row>
-    <row r="18" ht="24" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
-        <is>
-          <t>三、查询表怎么用</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n"/>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="3" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>第 1 步</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="inlineStr">
-        <is>
-          <t>打开两个文件</t>
-        </is>
-      </c>
-      <c r="C19" s="7" t="inlineStr">
-        <is>
-          <t>《A061_典当登记表.xlsx》和《A061_资金台账.xlsx》都要打开。</t>
-        </is>
-      </c>
+      <c r="D17" s="3" t="n"/>
+    </row>
+    <row r="19" ht="24" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>三、【查询表（新）】怎么用</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="n"/>
+      <c r="C19" s="2" t="n"/>
       <c r="D19" s="3" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>第 2 步</t>
+          <t>第 1 步</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>B3 选客户</t>
+          <t>打开两个文件</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>B3 那格选（或直接打）客户姓名，下面三块和上面的汇总条全部自动跳出来。</t>
+          <t>《A061_典当登记表.xlsx》和《A061_资金台账.xlsx》都要打开。</t>
         </is>
       </c>
       <c r="D20" s="3" t="n"/>
@@ -1093,17 +1099,17 @@
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
         <is>
-          <t>为什么要都打开</t>
+          <t>第 2 步</t>
         </is>
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>Excel 的规矩</t>
+          <t>B1 选姓名</t>
         </is>
       </c>
       <c r="C21" s="7" t="inlineStr">
         <is>
-          <t>FILTER、SUMIF 这类公式读不了「关着的」工作簿，只能读打开着的。关着的时候第三块会显示取不到数，把资金台账打开就好了。</t>
+          <t>第 1 行 B1 那格选（或直接打）客户姓名，三块明细和汇总条全部自动跳出来。</t>
         </is>
       </c>
       <c r="D21" s="3" t="n"/>
@@ -1111,119 +1117,143 @@
     <row r="22">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>两个文件要放一起</t>
+          <t>第 3 步（一般用不上）</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>同一个文件夹</t>
+          <t>E1 填身份证号</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>文件名一个字都不能改。从聊天里下载重名会变成「(1)」，要把括号那段删掉。</t>
+          <t>只有碰到同名客户才要填。B1 右边的黄条会提示：「这个姓名下登了 N 个不同的身份证号」，看到了再去 E1 填身份证号，左边典当那块就只剩这个人的。没同名就别填。</t>
         </is>
       </c>
       <c r="D22" s="3" t="n"/>
     </row>
-    <row r="24" ht="24" customHeight="1">
-      <c r="A24" s="4" t="inlineStr">
-        <is>
-          <t>四、颜色和符号</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n"/>
-      <c r="C24" s="2" t="n"/>
+    <row r="23">
+      <c r="A23" s="5" t="inlineStr">
+        <is>
+          <t>身份证号从哪来</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>表2 的 F 列</t>
+        </is>
+      </c>
+      <c r="C23" s="7" t="inlineStr">
+        <is>
+          <t>在【表2客户典当登记】的「身份证号」列登。表1 不动产和资金台账里没有这一列，那两块只能按姓名查——黄条里也写着。</t>
+        </is>
+      </c>
+      <c r="D23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>为什么要都打开</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>Excel 的规矩</t>
+        </is>
+      </c>
+      <c r="C24" s="7" t="inlineStr">
+        <is>
+          <t>FILTER、SUMIF 这类公式读不了「关着的」工作簿，只能读打开着的。关着的时候右边那块会显示「取不到数」，把资金台账打开就回来了。</t>
+        </is>
+      </c>
       <c r="D24" s="3" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="5" t="inlineStr">
         <is>
+          <t>两个文件要放一起</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>同一个文件夹</t>
+        </is>
+      </c>
+      <c r="C25" s="7" t="inlineStr">
+        <is>
+          <t>文件名一个字都不能改。从聊天里下载重名会变成「(1)」，要把括号那段删掉。</t>
+        </is>
+      </c>
+      <c r="D25" s="3" t="n"/>
+    </row>
+    <row r="27" ht="24" customHeight="1">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>四、颜色和符号</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="n"/>
+      <c r="C27" s="2" t="n"/>
+      <c r="D27" s="3" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
           <t>淡黄色格子</t>
         </is>
       </c>
-      <c r="B25" s="6" t="inlineStr">
+      <c r="B28" s="6" t="inlineStr">
         <is>
           <t>请填写</t>
         </is>
       </c>
-      <c r="C25" s="7" t="inlineStr">
+      <c r="C28" s="7" t="inlineStr">
         <is>
           <t>这是要人填的。</t>
         </is>
       </c>
-      <c r="D25" s="3" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="D28" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>灰色格子</t>
         </is>
       </c>
-      <c r="B26" s="6" t="inlineStr">
+      <c r="B29" s="6" t="inlineStr">
         <is>
           <t>公式自动算</t>
         </is>
       </c>
-      <c r="C26" s="7" t="inlineStr">
+      <c r="C29" s="7" t="inlineStr">
         <is>
           <t>别手动改。</t>
         </is>
       </c>
-      <c r="D26" s="3" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="D29" s="3" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>※ 开头的红字</t>
         </is>
       </c>
-      <c r="B27" s="6" t="inlineStr">
+      <c r="B30" s="6" t="inlineStr">
         <is>
           <t>有问题</t>
         </is>
       </c>
-      <c r="C27" s="7" t="inlineStr">
-        <is>
-          <t>「核对」列会自己挑毛病：机构/状态不在名单、已还本金大于典当金额、到期日早于当票日期、利息跟「在当×月利率」对不上。</t>
-        </is>
-      </c>
-      <c r="D27" s="3" t="n"/>
-    </row>
-    <row r="29" ht="24" customHeight="1">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>「核对」列会自己挑毛病：机构/状态不在名单、已还本金大于典当金额、到期日早于当票日期、当票号重复。</t>
+        </is>
+      </c>
+      <c r="D30" s="3" t="n"/>
+    </row>
+    <row r="32" ht="24" customHeight="1">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>五、这次从原表搬过来的</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n"/>
-      <c r="C29" s="2" t="n"/>
-      <c r="D29" s="3" t="n"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>· 表2（原 Sheet2）201 行全部搬过来，「个人借款」统一改名「个人典当」（134 笔），金辉典当 67 笔。</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="3" t="n"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>· 表1（原 Sheet1）67 行全部搬过来。</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="3" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>· 新加了「身份证号」「客户电话」两列（空着，你自己补），查询表按姓名查，身份证号自动带出来。</t>
         </is>
       </c>
       <c r="B32" s="2" t="n"/>
@@ -1233,7 +1263,7 @@
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>· 新加了「当前在当」列 = 典当金额 − 已还本金，自动算。</t>
+          <t>· 表2（原 Sheet2）201 行全部搬过来，「个人借款」统一改名「个人典当」（134 笔），金辉典当 67 笔。</t>
         </is>
       </c>
       <c r="B33" s="2" t="n"/>
@@ -1243,7 +1273,7 @@
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>· 新加了「核对」列，逐行挑毛病。</t>
+          <t>· 表1（原 Sheet1）67 行全部搬过来。</t>
         </is>
       </c>
       <c r="B34" s="2" t="n"/>
@@ -1253,7 +1283,7 @@
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t>· 原来「应收金额」改叫「应收利息」，位置挪到「典当系统费率」后面，看起来更顺。</t>
+          <t>· 新加了「身份证号」「客户电话」两列（空着，你自己补），查询表按姓名查，身份证号自动带出来。</t>
         </is>
       </c>
       <c r="B35" s="2" t="n"/>
@@ -1263,7 +1293,7 @@
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>· ⚠ 查过了：【表1】那 67 行，跟【表2】里机构=金辉典当的 67 行是同一批当（姓名+金额+当票号 66 行完全一致）。</t>
+          <t>· 新加了「当前在当」列 = 典当金额 − 已还本金，自动算。</t>
         </is>
       </c>
       <c r="B36" s="2" t="n"/>
@@ -1273,7 +1303,7 @@
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 表1 多出来的是收款拆分（对公/林总/建行民生/微信）、违约金、滞纳金。所以两张表的金额**不能相加**，</t>
+          <t>· 新加了「核对」列，逐行挑毛病。</t>
         </is>
       </c>
       <c r="B37" s="2" t="n"/>
@@ -1283,7 +1313,7 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 查询表里也分成两块单独列，就是这个原因。</t>
+          <t>· 原来「应收金额」改叫「应收利息」，位置挪到「典当系统费率」后面，看起来更顺。</t>
         </is>
       </c>
       <c r="B38" s="2" t="n"/>
@@ -1293,7 +1323,7 @@
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t>· 「典当系统费率」这一列各行口径不一样（有的按月、有的按日），所以没拿它去反推利息对错，</t>
+          <t>· ⚠ 查过了：【表1】那 67 行，跟【表2】里机构=金辉典当的 67 行是同一批当（姓名+金额+当票号 66 行完全一致）。</t>
         </is>
       </c>
       <c r="B39" s="2" t="n"/>
@@ -1303,50 +1333,83 @@
     <row r="40">
       <c r="A40" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">　 免得整屏报警。要核利息请直接看「应收利息」那一列。</t>
+          <t xml:space="preserve">　 表1 多出来的是收款拆分（对公/林总/建行民生/微信）、违约金、滞纳金。所以两张表的金额**不能相加**，</t>
         </is>
       </c>
       <c r="B40" s="2" t="n"/>
       <c r="C40" s="2" t="n"/>
       <c r="D40" s="3" t="n"/>
     </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 查询表里也分成两块单独列，就是这个原因。</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="n"/>
+      <c r="C41" s="2" t="n"/>
+      <c r="D41" s="3" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>· 「典当系统费率」这一列各行口径不一样（有的按月、有的按日），所以没拿它去反推利息对错，</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="n"/>
+      <c r="C42" s="2" t="n"/>
+      <c r="D42" s="3" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">　 免得整屏报警。要核利息请直接看「应收利息」那一列。</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="n"/>
+      <c r="C43" s="2" t="n"/>
+      <c r="D43" s="3" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="35">
+  <mergeCells count="38">
     <mergeCell ref="C6:D6"/>
+    <mergeCell ref="C24:D24"/>
+    <mergeCell ref="C30:D30"/>
     <mergeCell ref="C15:D15"/>
     <mergeCell ref="A35:D35"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="C26:D26"/>
-    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A43:D43"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="A40:D40"/>
-    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="C29:D29"/>
     <mergeCell ref="C10:D10"/>
     <mergeCell ref="C16:D16"/>
     <mergeCell ref="A34:D34"/>
     <mergeCell ref="C25:D25"/>
-    <mergeCell ref="A30:D30"/>
     <mergeCell ref="A39:D39"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="A24:D24"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="A36:D36"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="C12:D12"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="C27:D27"/>
+    <mergeCell ref="A41:D41"/>
+    <mergeCell ref="C17:D17"/>
+    <mergeCell ref="C23:D23"/>
     <mergeCell ref="C8:D8"/>
     <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A27:D27"/>
     <mergeCell ref="C7:D7"/>
     <mergeCell ref="A3:D3"/>
-    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="C28:D28"/>
     <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A42:D42"/>
     <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4034,7 +4097,7 @@
       <c r="Y4" s="12" t="n"/>
       <c r="Z4" s="20" t="n"/>
       <c r="AA4" s="18">
-        <f>IF($D4="","",IF(AND($C4&lt;&gt;"",ISNA(MATCH($C4,状态表,0))),"※状态不在【资料】里",IF(AND($G4&lt;&gt;"",$H4&lt;&gt;"",$H4&lt;$G4),"※到期日早于当票日期",IF(AND($F4&lt;&gt;"",COUNTIF($F$4:$F$123,$F4)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U4)&gt;0,N($T4)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D4="","",IF(AND($C4&lt;&gt;"",ISNA(MATCH($C4,状态表,0))),"※状态不在【资料】里",IF(AND($G4&lt;&gt;"",$H4&lt;&gt;"",$H4&lt;$G4),"※到期日早于当票日期",IF(AND($F4&lt;&gt;"",COUNTIF($F$4:$F$123,$F4)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U4)&gt;0,N($T4)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -4116,7 +4179,7 @@
       <c r="Y5" s="12" t="n"/>
       <c r="Z5" s="20" t="n"/>
       <c r="AA5" s="18">
-        <f>IF($D5="","",IF(AND($C5&lt;&gt;"",ISNA(MATCH($C5,状态表,0))),"※状态不在【资料】里",IF(AND($G5&lt;&gt;"",$H5&lt;&gt;"",$H5&lt;$G5),"※到期日早于当票日期",IF(AND($F5&lt;&gt;"",COUNTIF($F$4:$F$123,$F5)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U5)&gt;0,N($T5)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D5="","",IF(AND($C5&lt;&gt;"",ISNA(MATCH($C5,状态表,0))),"※状态不在【资料】里",IF(AND($G5&lt;&gt;"",$H5&lt;&gt;"",$H5&lt;$G5),"※到期日早于当票日期",IF(AND($F5&lt;&gt;"",COUNTIF($F$4:$F$123,$F5)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U5)&gt;0,N($T5)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -4198,7 +4261,7 @@
       <c r="Y6" s="12" t="n"/>
       <c r="Z6" s="20" t="n"/>
       <c r="AA6" s="18">
-        <f>IF($D6="","",IF(AND($C6&lt;&gt;"",ISNA(MATCH($C6,状态表,0))),"※状态不在【资料】里",IF(AND($G6&lt;&gt;"",$H6&lt;&gt;"",$H6&lt;$G6),"※到期日早于当票日期",IF(AND($F6&lt;&gt;"",COUNTIF($F$4:$F$123,$F6)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U6)&gt;0,N($T6)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D6="","",IF(AND($C6&lt;&gt;"",ISNA(MATCH($C6,状态表,0))),"※状态不在【资料】里",IF(AND($G6&lt;&gt;"",$H6&lt;&gt;"",$H6&lt;$G6),"※到期日早于当票日期",IF(AND($F6&lt;&gt;"",COUNTIF($F$4:$F$123,$F6)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U6)&gt;0,N($T6)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -4280,7 +4343,7 @@
       <c r="Y7" s="12" t="n"/>
       <c r="Z7" s="20" t="n"/>
       <c r="AA7" s="18">
-        <f>IF($D7="","",IF(AND($C7&lt;&gt;"",ISNA(MATCH($C7,状态表,0))),"※状态不在【资料】里",IF(AND($G7&lt;&gt;"",$H7&lt;&gt;"",$H7&lt;$G7),"※到期日早于当票日期",IF(AND($F7&lt;&gt;"",COUNTIF($F$4:$F$123,$F7)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U7)&gt;0,N($T7)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D7="","",IF(AND($C7&lt;&gt;"",ISNA(MATCH($C7,状态表,0))),"※状态不在【资料】里",IF(AND($G7&lt;&gt;"",$H7&lt;&gt;"",$H7&lt;$G7),"※到期日早于当票日期",IF(AND($F7&lt;&gt;"",COUNTIF($F$4:$F$123,$F7)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U7)&gt;0,N($T7)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -4362,7 +4425,7 @@
       <c r="Y8" s="12" t="n"/>
       <c r="Z8" s="20" t="n"/>
       <c r="AA8" s="18">
-        <f>IF($D8="","",IF(AND($C8&lt;&gt;"",ISNA(MATCH($C8,状态表,0))),"※状态不在【资料】里",IF(AND($G8&lt;&gt;"",$H8&lt;&gt;"",$H8&lt;$G8),"※到期日早于当票日期",IF(AND($F8&lt;&gt;"",COUNTIF($F$4:$F$123,$F8)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U8)&gt;0,N($T8)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D8="","",IF(AND($C8&lt;&gt;"",ISNA(MATCH($C8,状态表,0))),"※状态不在【资料】里",IF(AND($G8&lt;&gt;"",$H8&lt;&gt;"",$H8&lt;$G8),"※到期日早于当票日期",IF(AND($F8&lt;&gt;"",COUNTIF($F$4:$F$123,$F8)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U8)&gt;0,N($T8)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -4444,7 +4507,7 @@
       <c r="Y9" s="12" t="n"/>
       <c r="Z9" s="20" t="n"/>
       <c r="AA9" s="18">
-        <f>IF($D9="","",IF(AND($C9&lt;&gt;"",ISNA(MATCH($C9,状态表,0))),"※状态不在【资料】里",IF(AND($G9&lt;&gt;"",$H9&lt;&gt;"",$H9&lt;$G9),"※到期日早于当票日期",IF(AND($F9&lt;&gt;"",COUNTIF($F$4:$F$123,$F9)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U9)&gt;0,N($T9)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D9="","",IF(AND($C9&lt;&gt;"",ISNA(MATCH($C9,状态表,0))),"※状态不在【资料】里",IF(AND($G9&lt;&gt;"",$H9&lt;&gt;"",$H9&lt;$G9),"※到期日早于当票日期",IF(AND($F9&lt;&gt;"",COUNTIF($F$4:$F$123,$F9)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U9)&gt;0,N($T9)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -4526,7 +4589,7 @@
       <c r="Y10" s="12" t="n"/>
       <c r="Z10" s="20" t="n"/>
       <c r="AA10" s="18">
-        <f>IF($D10="","",IF(AND($C10&lt;&gt;"",ISNA(MATCH($C10,状态表,0))),"※状态不在【资料】里",IF(AND($G10&lt;&gt;"",$H10&lt;&gt;"",$H10&lt;$G10),"※到期日早于当票日期",IF(AND($F10&lt;&gt;"",COUNTIF($F$4:$F$123,$F10)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U10)&gt;0,N($T10)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D10="","",IF(AND($C10&lt;&gt;"",ISNA(MATCH($C10,状态表,0))),"※状态不在【资料】里",IF(AND($G10&lt;&gt;"",$H10&lt;&gt;"",$H10&lt;$G10),"※到期日早于当票日期",IF(AND($F10&lt;&gt;"",COUNTIF($F$4:$F$123,$F10)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U10)&gt;0,N($T10)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -4608,7 +4671,7 @@
       </c>
       <c r="Z11" s="20" t="n"/>
       <c r="AA11" s="18">
-        <f>IF($D11="","",IF(AND($C11&lt;&gt;"",ISNA(MATCH($C11,状态表,0))),"※状态不在【资料】里",IF(AND($G11&lt;&gt;"",$H11&lt;&gt;"",$H11&lt;$G11),"※到期日早于当票日期",IF(AND($F11&lt;&gt;"",COUNTIF($F$4:$F$123,$F11)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U11)&gt;0,N($T11)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D11="","",IF(AND($C11&lt;&gt;"",ISNA(MATCH($C11,状态表,0))),"※状态不在【资料】里",IF(AND($G11&lt;&gt;"",$H11&lt;&gt;"",$H11&lt;$G11),"※到期日早于当票日期",IF(AND($F11&lt;&gt;"",COUNTIF($F$4:$F$123,$F11)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U11)&gt;0,N($T11)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -4690,7 +4753,7 @@
       <c r="Y12" s="12" t="n"/>
       <c r="Z12" s="20" t="n"/>
       <c r="AA12" s="18">
-        <f>IF($D12="","",IF(AND($C12&lt;&gt;"",ISNA(MATCH($C12,状态表,0))),"※状态不在【资料】里",IF(AND($G12&lt;&gt;"",$H12&lt;&gt;"",$H12&lt;$G12),"※到期日早于当票日期",IF(AND($F12&lt;&gt;"",COUNTIF($F$4:$F$123,$F12)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U12)&gt;0,N($T12)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D12="","",IF(AND($C12&lt;&gt;"",ISNA(MATCH($C12,状态表,0))),"※状态不在【资料】里",IF(AND($G12&lt;&gt;"",$H12&lt;&gt;"",$H12&lt;$G12),"※到期日早于当票日期",IF(AND($F12&lt;&gt;"",COUNTIF($F$4:$F$123,$F12)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U12)&gt;0,N($T12)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -4772,7 +4835,7 @@
       <c r="Y13" s="12" t="n"/>
       <c r="Z13" s="20" t="n"/>
       <c r="AA13" s="18">
-        <f>IF($D13="","",IF(AND($C13&lt;&gt;"",ISNA(MATCH($C13,状态表,0))),"※状态不在【资料】里",IF(AND($G13&lt;&gt;"",$H13&lt;&gt;"",$H13&lt;$G13),"※到期日早于当票日期",IF(AND($F13&lt;&gt;"",COUNTIF($F$4:$F$123,$F13)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U13)&gt;0,N($T13)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D13="","",IF(AND($C13&lt;&gt;"",ISNA(MATCH($C13,状态表,0))),"※状态不在【资料】里",IF(AND($G13&lt;&gt;"",$H13&lt;&gt;"",$H13&lt;$G13),"※到期日早于当票日期",IF(AND($F13&lt;&gt;"",COUNTIF($F$4:$F$123,$F13)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U13)&gt;0,N($T13)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -4850,7 +4913,7 @@
       <c r="Y14" s="12" t="n"/>
       <c r="Z14" s="20" t="n"/>
       <c r="AA14" s="18">
-        <f>IF($D14="","",IF(AND($C14&lt;&gt;"",ISNA(MATCH($C14,状态表,0))),"※状态不在【资料】里",IF(AND($G14&lt;&gt;"",$H14&lt;&gt;"",$H14&lt;$G14),"※到期日早于当票日期",IF(AND($F14&lt;&gt;"",COUNTIF($F$4:$F$123,$F14)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U14)&gt;0,N($T14)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D14="","",IF(AND($C14&lt;&gt;"",ISNA(MATCH($C14,状态表,0))),"※状态不在【资料】里",IF(AND($G14&lt;&gt;"",$H14&lt;&gt;"",$H14&lt;$G14),"※到期日早于当票日期",IF(AND($F14&lt;&gt;"",COUNTIF($F$4:$F$123,$F14)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U14)&gt;0,N($T14)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -4928,7 +4991,7 @@
       <c r="Y15" s="12" t="n"/>
       <c r="Z15" s="20" t="n"/>
       <c r="AA15" s="18">
-        <f>IF($D15="","",IF(AND($C15&lt;&gt;"",ISNA(MATCH($C15,状态表,0))),"※状态不在【资料】里",IF(AND($G15&lt;&gt;"",$H15&lt;&gt;"",$H15&lt;$G15),"※到期日早于当票日期",IF(AND($F15&lt;&gt;"",COUNTIF($F$4:$F$123,$F15)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U15)&gt;0,N($T15)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D15="","",IF(AND($C15&lt;&gt;"",ISNA(MATCH($C15,状态表,0))),"※状态不在【资料】里",IF(AND($G15&lt;&gt;"",$H15&lt;&gt;"",$H15&lt;$G15),"※到期日早于当票日期",IF(AND($F15&lt;&gt;"",COUNTIF($F$4:$F$123,$F15)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U15)&gt;0,N($T15)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -5006,7 +5069,7 @@
       <c r="Y16" s="12" t="n"/>
       <c r="Z16" s="20" t="n"/>
       <c r="AA16" s="18">
-        <f>IF($D16="","",IF(AND($C16&lt;&gt;"",ISNA(MATCH($C16,状态表,0))),"※状态不在【资料】里",IF(AND($G16&lt;&gt;"",$H16&lt;&gt;"",$H16&lt;$G16),"※到期日早于当票日期",IF(AND($F16&lt;&gt;"",COUNTIF($F$4:$F$123,$F16)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U16)&gt;0,N($T16)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D16="","",IF(AND($C16&lt;&gt;"",ISNA(MATCH($C16,状态表,0))),"※状态不在【资料】里",IF(AND($G16&lt;&gt;"",$H16&lt;&gt;"",$H16&lt;$G16),"※到期日早于当票日期",IF(AND($F16&lt;&gt;"",COUNTIF($F$4:$F$123,$F16)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U16)&gt;0,N($T16)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -5084,7 +5147,7 @@
       <c r="Y17" s="12" t="n"/>
       <c r="Z17" s="20" t="n"/>
       <c r="AA17" s="18">
-        <f>IF($D17="","",IF(AND($C17&lt;&gt;"",ISNA(MATCH($C17,状态表,0))),"※状态不在【资料】里",IF(AND($G17&lt;&gt;"",$H17&lt;&gt;"",$H17&lt;$G17),"※到期日早于当票日期",IF(AND($F17&lt;&gt;"",COUNTIF($F$4:$F$123,$F17)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U17)&gt;0,N($T17)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D17="","",IF(AND($C17&lt;&gt;"",ISNA(MATCH($C17,状态表,0))),"※状态不在【资料】里",IF(AND($G17&lt;&gt;"",$H17&lt;&gt;"",$H17&lt;$G17),"※到期日早于当票日期",IF(AND($F17&lt;&gt;"",COUNTIF($F$4:$F$123,$F17)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U17)&gt;0,N($T17)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -5162,7 +5225,7 @@
       <c r="Y18" s="12" t="n"/>
       <c r="Z18" s="20" t="n"/>
       <c r="AA18" s="18">
-        <f>IF($D18="","",IF(AND($C18&lt;&gt;"",ISNA(MATCH($C18,状态表,0))),"※状态不在【资料】里",IF(AND($G18&lt;&gt;"",$H18&lt;&gt;"",$H18&lt;$G18),"※到期日早于当票日期",IF(AND($F18&lt;&gt;"",COUNTIF($F$4:$F$123,$F18)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U18)&gt;0,N($T18)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D18="","",IF(AND($C18&lt;&gt;"",ISNA(MATCH($C18,状态表,0))),"※状态不在【资料】里",IF(AND($G18&lt;&gt;"",$H18&lt;&gt;"",$H18&lt;$G18),"※到期日早于当票日期",IF(AND($F18&lt;&gt;"",COUNTIF($F$4:$F$123,$F18)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U18)&gt;0,N($T18)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -5240,7 +5303,7 @@
       <c r="Y19" s="12" t="n"/>
       <c r="Z19" s="20" t="n"/>
       <c r="AA19" s="18">
-        <f>IF($D19="","",IF(AND($C19&lt;&gt;"",ISNA(MATCH($C19,状态表,0))),"※状态不在【资料】里",IF(AND($G19&lt;&gt;"",$H19&lt;&gt;"",$H19&lt;$G19),"※到期日早于当票日期",IF(AND($F19&lt;&gt;"",COUNTIF($F$4:$F$123,$F19)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U19)&gt;0,N($T19)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D19="","",IF(AND($C19&lt;&gt;"",ISNA(MATCH($C19,状态表,0))),"※状态不在【资料】里",IF(AND($G19&lt;&gt;"",$H19&lt;&gt;"",$H19&lt;$G19),"※到期日早于当票日期",IF(AND($F19&lt;&gt;"",COUNTIF($F$4:$F$123,$F19)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U19)&gt;0,N($T19)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -5318,7 +5381,7 @@
       <c r="Y20" s="12" t="n"/>
       <c r="Z20" s="20" t="n"/>
       <c r="AA20" s="18">
-        <f>IF($D20="","",IF(AND($C20&lt;&gt;"",ISNA(MATCH($C20,状态表,0))),"※状态不在【资料】里",IF(AND($G20&lt;&gt;"",$H20&lt;&gt;"",$H20&lt;$G20),"※到期日早于当票日期",IF(AND($F20&lt;&gt;"",COUNTIF($F$4:$F$123,$F20)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U20)&gt;0,N($T20)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D20="","",IF(AND($C20&lt;&gt;"",ISNA(MATCH($C20,状态表,0))),"※状态不在【资料】里",IF(AND($G20&lt;&gt;"",$H20&lt;&gt;"",$H20&lt;$G20),"※到期日早于当票日期",IF(AND($F20&lt;&gt;"",COUNTIF($F$4:$F$123,$F20)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U20)&gt;0,N($T20)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -5396,7 +5459,7 @@
       <c r="Y21" s="12" t="n"/>
       <c r="Z21" s="20" t="n"/>
       <c r="AA21" s="18">
-        <f>IF($D21="","",IF(AND($C21&lt;&gt;"",ISNA(MATCH($C21,状态表,0))),"※状态不在【资料】里",IF(AND($G21&lt;&gt;"",$H21&lt;&gt;"",$H21&lt;$G21),"※到期日早于当票日期",IF(AND($F21&lt;&gt;"",COUNTIF($F$4:$F$123,$F21)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U21)&gt;0,N($T21)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D21="","",IF(AND($C21&lt;&gt;"",ISNA(MATCH($C21,状态表,0))),"※状态不在【资料】里",IF(AND($G21&lt;&gt;"",$H21&lt;&gt;"",$H21&lt;$G21),"※到期日早于当票日期",IF(AND($F21&lt;&gt;"",COUNTIF($F$4:$F$123,$F21)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U21)&gt;0,N($T21)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -5478,7 +5541,7 @@
       <c r="Y22" s="12" t="n"/>
       <c r="Z22" s="20" t="n"/>
       <c r="AA22" s="18">
-        <f>IF($D22="","",IF(AND($C22&lt;&gt;"",ISNA(MATCH($C22,状态表,0))),"※状态不在【资料】里",IF(AND($G22&lt;&gt;"",$H22&lt;&gt;"",$H22&lt;$G22),"※到期日早于当票日期",IF(AND($F22&lt;&gt;"",COUNTIF($F$4:$F$123,$F22)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U22)&gt;0,N($T22)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D22="","",IF(AND($C22&lt;&gt;"",ISNA(MATCH($C22,状态表,0))),"※状态不在【资料】里",IF(AND($G22&lt;&gt;"",$H22&lt;&gt;"",$H22&lt;$G22),"※到期日早于当票日期",IF(AND($F22&lt;&gt;"",COUNTIF($F$4:$F$123,$F22)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U22)&gt;0,N($T22)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -5564,7 +5627,7 @@
       </c>
       <c r="Z23" s="20" t="n"/>
       <c r="AA23" s="18">
-        <f>IF($D23="","",IF(AND($C23&lt;&gt;"",ISNA(MATCH($C23,状态表,0))),"※状态不在【资料】里",IF(AND($G23&lt;&gt;"",$H23&lt;&gt;"",$H23&lt;$G23),"※到期日早于当票日期",IF(AND($F23&lt;&gt;"",COUNTIF($F$4:$F$123,$F23)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U23)&gt;0,N($T23)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D23="","",IF(AND($C23&lt;&gt;"",ISNA(MATCH($C23,状态表,0))),"※状态不在【资料】里",IF(AND($G23&lt;&gt;"",$H23&lt;&gt;"",$H23&lt;$G23),"※到期日早于当票日期",IF(AND($F23&lt;&gt;"",COUNTIF($F$4:$F$123,$F23)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U23)&gt;0,N($T23)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -5644,7 +5707,7 @@
       <c r="Y24" s="12" t="n"/>
       <c r="Z24" s="20" t="n"/>
       <c r="AA24" s="18">
-        <f>IF($D24="","",IF(AND($C24&lt;&gt;"",ISNA(MATCH($C24,状态表,0))),"※状态不在【资料】里",IF(AND($G24&lt;&gt;"",$H24&lt;&gt;"",$H24&lt;$G24),"※到期日早于当票日期",IF(AND($F24&lt;&gt;"",COUNTIF($F$4:$F$123,$F24)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U24)&gt;0,N($T24)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D24="","",IF(AND($C24&lt;&gt;"",ISNA(MATCH($C24,状态表,0))),"※状态不在【资料】里",IF(AND($G24&lt;&gt;"",$H24&lt;&gt;"",$H24&lt;$G24),"※到期日早于当票日期",IF(AND($F24&lt;&gt;"",COUNTIF($F$4:$F$123,$F24)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U24)&gt;0,N($T24)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -5720,7 +5783,7 @@
       <c r="Y25" s="12" t="n"/>
       <c r="Z25" s="20" t="n"/>
       <c r="AA25" s="18">
-        <f>IF($D25="","",IF(AND($C25&lt;&gt;"",ISNA(MATCH($C25,状态表,0))),"※状态不在【资料】里",IF(AND($G25&lt;&gt;"",$H25&lt;&gt;"",$H25&lt;$G25),"※到期日早于当票日期",IF(AND($F25&lt;&gt;"",COUNTIF($F$4:$F$123,$F25)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U25)&gt;0,N($T25)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D25="","",IF(AND($C25&lt;&gt;"",ISNA(MATCH($C25,状态表,0))),"※状态不在【资料】里",IF(AND($G25&lt;&gt;"",$H25&lt;&gt;"",$H25&lt;$G25),"※到期日早于当票日期",IF(AND($F25&lt;&gt;"",COUNTIF($F$4:$F$123,$F25)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U25)&gt;0,N($T25)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -5802,7 +5865,7 @@
       <c r="Y26" s="12" t="n"/>
       <c r="Z26" s="20" t="n"/>
       <c r="AA26" s="18">
-        <f>IF($D26="","",IF(AND($C26&lt;&gt;"",ISNA(MATCH($C26,状态表,0))),"※状态不在【资料】里",IF(AND($G26&lt;&gt;"",$H26&lt;&gt;"",$H26&lt;$G26),"※到期日早于当票日期",IF(AND($F26&lt;&gt;"",COUNTIF($F$4:$F$123,$F26)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U26)&gt;0,N($T26)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D26="","",IF(AND($C26&lt;&gt;"",ISNA(MATCH($C26,状态表,0))),"※状态不在【资料】里",IF(AND($G26&lt;&gt;"",$H26&lt;&gt;"",$H26&lt;$G26),"※到期日早于当票日期",IF(AND($F26&lt;&gt;"",COUNTIF($F$4:$F$123,$F26)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U26)&gt;0,N($T26)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -5878,7 +5941,7 @@
       <c r="Y27" s="12" t="n"/>
       <c r="Z27" s="20" t="n"/>
       <c r="AA27" s="18">
-        <f>IF($D27="","",IF(AND($C27&lt;&gt;"",ISNA(MATCH($C27,状态表,0))),"※状态不在【资料】里",IF(AND($G27&lt;&gt;"",$H27&lt;&gt;"",$H27&lt;$G27),"※到期日早于当票日期",IF(AND($F27&lt;&gt;"",COUNTIF($F$4:$F$123,$F27)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U27)&gt;0,N($T27)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D27="","",IF(AND($C27&lt;&gt;"",ISNA(MATCH($C27,状态表,0))),"※状态不在【资料】里",IF(AND($G27&lt;&gt;"",$H27&lt;&gt;"",$H27&lt;$G27),"※到期日早于当票日期",IF(AND($F27&lt;&gt;"",COUNTIF($F$4:$F$123,$F27)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U27)&gt;0,N($T27)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -5960,7 +6023,7 @@
       <c r="Y28" s="12" t="n"/>
       <c r="Z28" s="20" t="n"/>
       <c r="AA28" s="18">
-        <f>IF($D28="","",IF(AND($C28&lt;&gt;"",ISNA(MATCH($C28,状态表,0))),"※状态不在【资料】里",IF(AND($G28&lt;&gt;"",$H28&lt;&gt;"",$H28&lt;$G28),"※到期日早于当票日期",IF(AND($F28&lt;&gt;"",COUNTIF($F$4:$F$123,$F28)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U28)&gt;0,N($T28)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D28="","",IF(AND($C28&lt;&gt;"",ISNA(MATCH($C28,状态表,0))),"※状态不在【资料】里",IF(AND($G28&lt;&gt;"",$H28&lt;&gt;"",$H28&lt;$G28),"※到期日早于当票日期",IF(AND($F28&lt;&gt;"",COUNTIF($F$4:$F$123,$F28)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U28)&gt;0,N($T28)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -6036,7 +6099,7 @@
       </c>
       <c r="Z29" s="20" t="n"/>
       <c r="AA29" s="18">
-        <f>IF($D29="","",IF(AND($C29&lt;&gt;"",ISNA(MATCH($C29,状态表,0))),"※状态不在【资料】里",IF(AND($G29&lt;&gt;"",$H29&lt;&gt;"",$H29&lt;$G29),"※到期日早于当票日期",IF(AND($F29&lt;&gt;"",COUNTIF($F$4:$F$123,$F29)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U29)&gt;0,N($T29)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D29="","",IF(AND($C29&lt;&gt;"",ISNA(MATCH($C29,状态表,0))),"※状态不在【资料】里",IF(AND($G29&lt;&gt;"",$H29&lt;&gt;"",$H29&lt;$G29),"※到期日早于当票日期",IF(AND($F29&lt;&gt;"",COUNTIF($F$4:$F$123,$F29)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U29)&gt;0,N($T29)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -6116,7 +6179,7 @@
       <c r="Y30" s="12" t="n"/>
       <c r="Z30" s="20" t="n"/>
       <c r="AA30" s="18">
-        <f>IF($D30="","",IF(AND($C30&lt;&gt;"",ISNA(MATCH($C30,状态表,0))),"※状态不在【资料】里",IF(AND($G30&lt;&gt;"",$H30&lt;&gt;"",$H30&lt;$G30),"※到期日早于当票日期",IF(AND($F30&lt;&gt;"",COUNTIF($F$4:$F$123,$F30)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U30)&gt;0,N($T30)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D30="","",IF(AND($C30&lt;&gt;"",ISNA(MATCH($C30,状态表,0))),"※状态不在【资料】里",IF(AND($G30&lt;&gt;"",$H30&lt;&gt;"",$H30&lt;$G30),"※到期日早于当票日期",IF(AND($F30&lt;&gt;"",COUNTIF($F$4:$F$123,$F30)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U30)&gt;0,N($T30)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -6198,7 +6261,7 @@
       <c r="Y31" s="12" t="n"/>
       <c r="Z31" s="20" t="n"/>
       <c r="AA31" s="18">
-        <f>IF($D31="","",IF(AND($C31&lt;&gt;"",ISNA(MATCH($C31,状态表,0))),"※状态不在【资料】里",IF(AND($G31&lt;&gt;"",$H31&lt;&gt;"",$H31&lt;$G31),"※到期日早于当票日期",IF(AND($F31&lt;&gt;"",COUNTIF($F$4:$F$123,$F31)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U31)&gt;0,N($T31)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D31="","",IF(AND($C31&lt;&gt;"",ISNA(MATCH($C31,状态表,0))),"※状态不在【资料】里",IF(AND($G31&lt;&gt;"",$H31&lt;&gt;"",$H31&lt;$G31),"※到期日早于当票日期",IF(AND($F31&lt;&gt;"",COUNTIF($F$4:$F$123,$F31)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U31)&gt;0,N($T31)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -6278,7 +6341,7 @@
       <c r="Y32" s="12" t="n"/>
       <c r="Z32" s="20" t="n"/>
       <c r="AA32" s="18">
-        <f>IF($D32="","",IF(AND($C32&lt;&gt;"",ISNA(MATCH($C32,状态表,0))),"※状态不在【资料】里",IF(AND($G32&lt;&gt;"",$H32&lt;&gt;"",$H32&lt;$G32),"※到期日早于当票日期",IF(AND($F32&lt;&gt;"",COUNTIF($F$4:$F$123,$F32)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U32)&gt;0,N($T32)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D32="","",IF(AND($C32&lt;&gt;"",ISNA(MATCH($C32,状态表,0))),"※状态不在【资料】里",IF(AND($G32&lt;&gt;"",$H32&lt;&gt;"",$H32&lt;$G32),"※到期日早于当票日期",IF(AND($F32&lt;&gt;"",COUNTIF($F$4:$F$123,$F32)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U32)&gt;0,N($T32)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -6360,7 +6423,7 @@
       <c r="Y33" s="12" t="n"/>
       <c r="Z33" s="20" t="n"/>
       <c r="AA33" s="18">
-        <f>IF($D33="","",IF(AND($C33&lt;&gt;"",ISNA(MATCH($C33,状态表,0))),"※状态不在【资料】里",IF(AND($G33&lt;&gt;"",$H33&lt;&gt;"",$H33&lt;$G33),"※到期日早于当票日期",IF(AND($F33&lt;&gt;"",COUNTIF($F$4:$F$123,$F33)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U33)&gt;0,N($T33)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D33="","",IF(AND($C33&lt;&gt;"",ISNA(MATCH($C33,状态表,0))),"※状态不在【资料】里",IF(AND($G33&lt;&gt;"",$H33&lt;&gt;"",$H33&lt;$G33),"※到期日早于当票日期",IF(AND($F33&lt;&gt;"",COUNTIF($F$4:$F$123,$F33)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U33)&gt;0,N($T33)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -6440,7 +6503,7 @@
       <c r="Y34" s="12" t="n"/>
       <c r="Z34" s="20" t="n"/>
       <c r="AA34" s="18">
-        <f>IF($D34="","",IF(AND($C34&lt;&gt;"",ISNA(MATCH($C34,状态表,0))),"※状态不在【资料】里",IF(AND($G34&lt;&gt;"",$H34&lt;&gt;"",$H34&lt;$G34),"※到期日早于当票日期",IF(AND($F34&lt;&gt;"",COUNTIF($F$4:$F$123,$F34)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U34)&gt;0,N($T34)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D34="","",IF(AND($C34&lt;&gt;"",ISNA(MATCH($C34,状态表,0))),"※状态不在【资料】里",IF(AND($G34&lt;&gt;"",$H34&lt;&gt;"",$H34&lt;$G34),"※到期日早于当票日期",IF(AND($F34&lt;&gt;"",COUNTIF($F$4:$F$123,$F34)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U34)&gt;0,N($T34)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -6520,7 +6583,7 @@
       <c r="Y35" s="12" t="n"/>
       <c r="Z35" s="20" t="n"/>
       <c r="AA35" s="18">
-        <f>IF($D35="","",IF(AND($C35&lt;&gt;"",ISNA(MATCH($C35,状态表,0))),"※状态不在【资料】里",IF(AND($G35&lt;&gt;"",$H35&lt;&gt;"",$H35&lt;$G35),"※到期日早于当票日期",IF(AND($F35&lt;&gt;"",COUNTIF($F$4:$F$123,$F35)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U35)&gt;0,N($T35)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D35="","",IF(AND($C35&lt;&gt;"",ISNA(MATCH($C35,状态表,0))),"※状态不在【资料】里",IF(AND($G35&lt;&gt;"",$H35&lt;&gt;"",$H35&lt;$G35),"※到期日早于当票日期",IF(AND($F35&lt;&gt;"",COUNTIF($F$4:$F$123,$F35)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U35)&gt;0,N($T35)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -6600,7 +6663,7 @@
       <c r="Y36" s="12" t="n"/>
       <c r="Z36" s="20" t="n"/>
       <c r="AA36" s="18">
-        <f>IF($D36="","",IF(AND($C36&lt;&gt;"",ISNA(MATCH($C36,状态表,0))),"※状态不在【资料】里",IF(AND($G36&lt;&gt;"",$H36&lt;&gt;"",$H36&lt;$G36),"※到期日早于当票日期",IF(AND($F36&lt;&gt;"",COUNTIF($F$4:$F$123,$F36)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U36)&gt;0,N($T36)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D36="","",IF(AND($C36&lt;&gt;"",ISNA(MATCH($C36,状态表,0))),"※状态不在【资料】里",IF(AND($G36&lt;&gt;"",$H36&lt;&gt;"",$H36&lt;$G36),"※到期日早于当票日期",IF(AND($F36&lt;&gt;"",COUNTIF($F$4:$F$123,$F36)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U36)&gt;0,N($T36)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -6680,7 +6743,7 @@
       <c r="Y37" s="12" t="n"/>
       <c r="Z37" s="20" t="n"/>
       <c r="AA37" s="18">
-        <f>IF($D37="","",IF(AND($C37&lt;&gt;"",ISNA(MATCH($C37,状态表,0))),"※状态不在【资料】里",IF(AND($G37&lt;&gt;"",$H37&lt;&gt;"",$H37&lt;$G37),"※到期日早于当票日期",IF(AND($F37&lt;&gt;"",COUNTIF($F$4:$F$123,$F37)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U37)&gt;0,N($T37)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D37="","",IF(AND($C37&lt;&gt;"",ISNA(MATCH($C37,状态表,0))),"※状态不在【资料】里",IF(AND($G37&lt;&gt;"",$H37&lt;&gt;"",$H37&lt;$G37),"※到期日早于当票日期",IF(AND($F37&lt;&gt;"",COUNTIF($F$4:$F$123,$F37)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U37)&gt;0,N($T37)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -6762,7 +6825,7 @@
       <c r="Y38" s="12" t="n"/>
       <c r="Z38" s="20" t="n"/>
       <c r="AA38" s="18">
-        <f>IF($D38="","",IF(AND($C38&lt;&gt;"",ISNA(MATCH($C38,状态表,0))),"※状态不在【资料】里",IF(AND($G38&lt;&gt;"",$H38&lt;&gt;"",$H38&lt;$G38),"※到期日早于当票日期",IF(AND($F38&lt;&gt;"",COUNTIF($F$4:$F$123,$F38)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U38)&gt;0,N($T38)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D38="","",IF(AND($C38&lt;&gt;"",ISNA(MATCH($C38,状态表,0))),"※状态不在【资料】里",IF(AND($G38&lt;&gt;"",$H38&lt;&gt;"",$H38&lt;$G38),"※到期日早于当票日期",IF(AND($F38&lt;&gt;"",COUNTIF($F$4:$F$123,$F38)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U38)&gt;0,N($T38)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -6834,7 +6897,7 @@
       <c r="Y39" s="12" t="n"/>
       <c r="Z39" s="20" t="n"/>
       <c r="AA39" s="18">
-        <f>IF($D39="","",IF(AND($C39&lt;&gt;"",ISNA(MATCH($C39,状态表,0))),"※状态不在【资料】里",IF(AND($G39&lt;&gt;"",$H39&lt;&gt;"",$H39&lt;$G39),"※到期日早于当票日期",IF(AND($F39&lt;&gt;"",COUNTIF($F$4:$F$123,$F39)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U39)&gt;0,N($T39)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D39="","",IF(AND($C39&lt;&gt;"",ISNA(MATCH($C39,状态表,0))),"※状态不在【资料】里",IF(AND($G39&lt;&gt;"",$H39&lt;&gt;"",$H39&lt;$G39),"※到期日早于当票日期",IF(AND($F39&lt;&gt;"",COUNTIF($F$4:$F$123,$F39)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U39)&gt;0,N($T39)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -6914,7 +6977,7 @@
       <c r="Y40" s="12" t="n"/>
       <c r="Z40" s="20" t="n"/>
       <c r="AA40" s="18">
-        <f>IF($D40="","",IF(AND($C40&lt;&gt;"",ISNA(MATCH($C40,状态表,0))),"※状态不在【资料】里",IF(AND($G40&lt;&gt;"",$H40&lt;&gt;"",$H40&lt;$G40),"※到期日早于当票日期",IF(AND($F40&lt;&gt;"",COUNTIF($F$4:$F$123,$F40)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U40)&gt;0,N($T40)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D40="","",IF(AND($C40&lt;&gt;"",ISNA(MATCH($C40,状态表,0))),"※状态不在【资料】里",IF(AND($G40&lt;&gt;"",$H40&lt;&gt;"",$H40&lt;$G40),"※到期日早于当票日期",IF(AND($F40&lt;&gt;"",COUNTIF($F$4:$F$123,$F40)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U40)&gt;0,N($T40)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -6988,7 +7051,7 @@
       <c r="Y41" s="12" t="n"/>
       <c r="Z41" s="20" t="n"/>
       <c r="AA41" s="18">
-        <f>IF($D41="","",IF(AND($C41&lt;&gt;"",ISNA(MATCH($C41,状态表,0))),"※状态不在【资料】里",IF(AND($G41&lt;&gt;"",$H41&lt;&gt;"",$H41&lt;$G41),"※到期日早于当票日期",IF(AND($F41&lt;&gt;"",COUNTIF($F$4:$F$123,$F41)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U41)&gt;0,N($T41)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D41="","",IF(AND($C41&lt;&gt;"",ISNA(MATCH($C41,状态表,0))),"※状态不在【资料】里",IF(AND($G41&lt;&gt;"",$H41&lt;&gt;"",$H41&lt;$G41),"※到期日早于当票日期",IF(AND($F41&lt;&gt;"",COUNTIF($F$4:$F$123,$F41)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U41)&gt;0,N($T41)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -7064,7 +7127,7 @@
       <c r="Y42" s="12" t="n"/>
       <c r="Z42" s="20" t="n"/>
       <c r="AA42" s="18">
-        <f>IF($D42="","",IF(AND($C42&lt;&gt;"",ISNA(MATCH($C42,状态表,0))),"※状态不在【资料】里",IF(AND($G42&lt;&gt;"",$H42&lt;&gt;"",$H42&lt;$G42),"※到期日早于当票日期",IF(AND($F42&lt;&gt;"",COUNTIF($F$4:$F$123,$F42)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U42)&gt;0,N($T42)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D42="","",IF(AND($C42&lt;&gt;"",ISNA(MATCH($C42,状态表,0))),"※状态不在【资料】里",IF(AND($G42&lt;&gt;"",$H42&lt;&gt;"",$H42&lt;$G42),"※到期日早于当票日期",IF(AND($F42&lt;&gt;"",COUNTIF($F$4:$F$123,$F42)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U42)&gt;0,N($T42)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -7140,7 +7203,7 @@
       <c r="Y43" s="12" t="n"/>
       <c r="Z43" s="20" t="n"/>
       <c r="AA43" s="18">
-        <f>IF($D43="","",IF(AND($C43&lt;&gt;"",ISNA(MATCH($C43,状态表,0))),"※状态不在【资料】里",IF(AND($G43&lt;&gt;"",$H43&lt;&gt;"",$H43&lt;$G43),"※到期日早于当票日期",IF(AND($F43&lt;&gt;"",COUNTIF($F$4:$F$123,$F43)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U43)&gt;0,N($T43)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D43="","",IF(AND($C43&lt;&gt;"",ISNA(MATCH($C43,状态表,0))),"※状态不在【资料】里",IF(AND($G43&lt;&gt;"",$H43&lt;&gt;"",$H43&lt;$G43),"※到期日早于当票日期",IF(AND($F43&lt;&gt;"",COUNTIF($F$4:$F$123,$F43)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U43)&gt;0,N($T43)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -7216,7 +7279,7 @@
       <c r="Y44" s="12" t="n"/>
       <c r="Z44" s="20" t="n"/>
       <c r="AA44" s="18">
-        <f>IF($D44="","",IF(AND($C44&lt;&gt;"",ISNA(MATCH($C44,状态表,0))),"※状态不在【资料】里",IF(AND($G44&lt;&gt;"",$H44&lt;&gt;"",$H44&lt;$G44),"※到期日早于当票日期",IF(AND($F44&lt;&gt;"",COUNTIF($F$4:$F$123,$F44)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U44)&gt;0,N($T44)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D44="","",IF(AND($C44&lt;&gt;"",ISNA(MATCH($C44,状态表,0))),"※状态不在【资料】里",IF(AND($G44&lt;&gt;"",$H44&lt;&gt;"",$H44&lt;$G44),"※到期日早于当票日期",IF(AND($F44&lt;&gt;"",COUNTIF($F$4:$F$123,$F44)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U44)&gt;0,N($T44)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -7290,7 +7353,7 @@
       <c r="Y45" s="12" t="n"/>
       <c r="Z45" s="20" t="n"/>
       <c r="AA45" s="18">
-        <f>IF($D45="","",IF(AND($C45&lt;&gt;"",ISNA(MATCH($C45,状态表,0))),"※状态不在【资料】里",IF(AND($G45&lt;&gt;"",$H45&lt;&gt;"",$H45&lt;$G45),"※到期日早于当票日期",IF(AND($F45&lt;&gt;"",COUNTIF($F$4:$F$123,$F45)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U45)&gt;0,N($T45)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D45="","",IF(AND($C45&lt;&gt;"",ISNA(MATCH($C45,状态表,0))),"※状态不在【资料】里",IF(AND($G45&lt;&gt;"",$H45&lt;&gt;"",$H45&lt;$G45),"※到期日早于当票日期",IF(AND($F45&lt;&gt;"",COUNTIF($F$4:$F$123,$F45)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U45)&gt;0,N($T45)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -7366,7 +7429,7 @@
       <c r="Y46" s="12" t="n"/>
       <c r="Z46" s="20" t="n"/>
       <c r="AA46" s="18">
-        <f>IF($D46="","",IF(AND($C46&lt;&gt;"",ISNA(MATCH($C46,状态表,0))),"※状态不在【资料】里",IF(AND($G46&lt;&gt;"",$H46&lt;&gt;"",$H46&lt;$G46),"※到期日早于当票日期",IF(AND($F46&lt;&gt;"",COUNTIF($F$4:$F$123,$F46)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U46)&gt;0,N($T46)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D46="","",IF(AND($C46&lt;&gt;"",ISNA(MATCH($C46,状态表,0))),"※状态不在【资料】里",IF(AND($G46&lt;&gt;"",$H46&lt;&gt;"",$H46&lt;$G46),"※到期日早于当票日期",IF(AND($F46&lt;&gt;"",COUNTIF($F$4:$F$123,$F46)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U46)&gt;0,N($T46)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -7440,7 +7503,7 @@
       <c r="Y47" s="12" t="n"/>
       <c r="Z47" s="20" t="n"/>
       <c r="AA47" s="18">
-        <f>IF($D47="","",IF(AND($C47&lt;&gt;"",ISNA(MATCH($C47,状态表,0))),"※状态不在【资料】里",IF(AND($G47&lt;&gt;"",$H47&lt;&gt;"",$H47&lt;$G47),"※到期日早于当票日期",IF(AND($F47&lt;&gt;"",COUNTIF($F$4:$F$123,$F47)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U47)&gt;0,N($T47)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D47="","",IF(AND($C47&lt;&gt;"",ISNA(MATCH($C47,状态表,0))),"※状态不在【资料】里",IF(AND($G47&lt;&gt;"",$H47&lt;&gt;"",$H47&lt;$G47),"※到期日早于当票日期",IF(AND($F47&lt;&gt;"",COUNTIF($F$4:$F$123,$F47)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U47)&gt;0,N($T47)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -7518,7 +7581,7 @@
       <c r="Y48" s="12" t="n"/>
       <c r="Z48" s="20" t="n"/>
       <c r="AA48" s="18">
-        <f>IF($D48="","",IF(AND($C48&lt;&gt;"",ISNA(MATCH($C48,状态表,0))),"※状态不在【资料】里",IF(AND($G48&lt;&gt;"",$H48&lt;&gt;"",$H48&lt;$G48),"※到期日早于当票日期",IF(AND($F48&lt;&gt;"",COUNTIF($F$4:$F$123,$F48)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U48)&gt;0,N($T48)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D48="","",IF(AND($C48&lt;&gt;"",ISNA(MATCH($C48,状态表,0))),"※状态不在【资料】里",IF(AND($G48&lt;&gt;"",$H48&lt;&gt;"",$H48&lt;$G48),"※到期日早于当票日期",IF(AND($F48&lt;&gt;"",COUNTIF($F$4:$F$123,$F48)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U48)&gt;0,N($T48)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -7594,7 +7657,7 @@
       <c r="Y49" s="12" t="n"/>
       <c r="Z49" s="20" t="n"/>
       <c r="AA49" s="18">
-        <f>IF($D49="","",IF(AND($C49&lt;&gt;"",ISNA(MATCH($C49,状态表,0))),"※状态不在【资料】里",IF(AND($G49&lt;&gt;"",$H49&lt;&gt;"",$H49&lt;$G49),"※到期日早于当票日期",IF(AND($F49&lt;&gt;"",COUNTIF($F$4:$F$123,$F49)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U49)&gt;0,N($T49)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D49="","",IF(AND($C49&lt;&gt;"",ISNA(MATCH($C49,状态表,0))),"※状态不在【资料】里",IF(AND($G49&lt;&gt;"",$H49&lt;&gt;"",$H49&lt;$G49),"※到期日早于当票日期",IF(AND($F49&lt;&gt;"",COUNTIF($F$4:$F$123,$F49)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U49)&gt;0,N($T49)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -7670,7 +7733,7 @@
       <c r="Y50" s="12" t="n"/>
       <c r="Z50" s="20" t="n"/>
       <c r="AA50" s="18">
-        <f>IF($D50="","",IF(AND($C50&lt;&gt;"",ISNA(MATCH($C50,状态表,0))),"※状态不在【资料】里",IF(AND($G50&lt;&gt;"",$H50&lt;&gt;"",$H50&lt;$G50),"※到期日早于当票日期",IF(AND($F50&lt;&gt;"",COUNTIF($F$4:$F$123,$F50)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U50)&gt;0,N($T50)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D50="","",IF(AND($C50&lt;&gt;"",ISNA(MATCH($C50,状态表,0))),"※状态不在【资料】里",IF(AND($G50&lt;&gt;"",$H50&lt;&gt;"",$H50&lt;$G50),"※到期日早于当票日期",IF(AND($F50&lt;&gt;"",COUNTIF($F$4:$F$123,$F50)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U50)&gt;0,N($T50)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -7746,7 +7809,7 @@
       <c r="Y51" s="12" t="n"/>
       <c r="Z51" s="20" t="n"/>
       <c r="AA51" s="18">
-        <f>IF($D51="","",IF(AND($C51&lt;&gt;"",ISNA(MATCH($C51,状态表,0))),"※状态不在【资料】里",IF(AND($G51&lt;&gt;"",$H51&lt;&gt;"",$H51&lt;$G51),"※到期日早于当票日期",IF(AND($F51&lt;&gt;"",COUNTIF($F$4:$F$123,$F51)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U51)&gt;0,N($T51)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D51="","",IF(AND($C51&lt;&gt;"",ISNA(MATCH($C51,状态表,0))),"※状态不在【资料】里",IF(AND($G51&lt;&gt;"",$H51&lt;&gt;"",$H51&lt;$G51),"※到期日早于当票日期",IF(AND($F51&lt;&gt;"",COUNTIF($F$4:$F$123,$F51)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U51)&gt;0,N($T51)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -7824,7 +7887,7 @@
       <c r="Y52" s="12" t="n"/>
       <c r="Z52" s="20" t="n"/>
       <c r="AA52" s="18">
-        <f>IF($D52="","",IF(AND($C52&lt;&gt;"",ISNA(MATCH($C52,状态表,0))),"※状态不在【资料】里",IF(AND($G52&lt;&gt;"",$H52&lt;&gt;"",$H52&lt;$G52),"※到期日早于当票日期",IF(AND($F52&lt;&gt;"",COUNTIF($F$4:$F$123,$F52)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U52)&gt;0,N($T52)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D52="","",IF(AND($C52&lt;&gt;"",ISNA(MATCH($C52,状态表,0))),"※状态不在【资料】里",IF(AND($G52&lt;&gt;"",$H52&lt;&gt;"",$H52&lt;$G52),"※到期日早于当票日期",IF(AND($F52&lt;&gt;"",COUNTIF($F$4:$F$123,$F52)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U52)&gt;0,N($T52)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -7902,7 +7965,7 @@
       <c r="Y53" s="12" t="n"/>
       <c r="Z53" s="20" t="n"/>
       <c r="AA53" s="18">
-        <f>IF($D53="","",IF(AND($C53&lt;&gt;"",ISNA(MATCH($C53,状态表,0))),"※状态不在【资料】里",IF(AND($G53&lt;&gt;"",$H53&lt;&gt;"",$H53&lt;$G53),"※到期日早于当票日期",IF(AND($F53&lt;&gt;"",COUNTIF($F$4:$F$123,$F53)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U53)&gt;0,N($T53)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D53="","",IF(AND($C53&lt;&gt;"",ISNA(MATCH($C53,状态表,0))),"※状态不在【资料】里",IF(AND($G53&lt;&gt;"",$H53&lt;&gt;"",$H53&lt;$G53),"※到期日早于当票日期",IF(AND($F53&lt;&gt;"",COUNTIF($F$4:$F$123,$F53)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U53)&gt;0,N($T53)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -7974,7 +8037,7 @@
       <c r="Y54" s="12" t="n"/>
       <c r="Z54" s="20" t="n"/>
       <c r="AA54" s="18">
-        <f>IF($D54="","",IF(AND($C54&lt;&gt;"",ISNA(MATCH($C54,状态表,0))),"※状态不在【资料】里",IF(AND($G54&lt;&gt;"",$H54&lt;&gt;"",$H54&lt;$G54),"※到期日早于当票日期",IF(AND($F54&lt;&gt;"",COUNTIF($F$4:$F$123,$F54)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U54)&gt;0,N($T54)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D54="","",IF(AND($C54&lt;&gt;"",ISNA(MATCH($C54,状态表,0))),"※状态不在【资料】里",IF(AND($G54&lt;&gt;"",$H54&lt;&gt;"",$H54&lt;$G54),"※到期日早于当票日期",IF(AND($F54&lt;&gt;"",COUNTIF($F$4:$F$123,$F54)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U54)&gt;0,N($T54)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -8052,7 +8115,7 @@
       <c r="Y55" s="12" t="n"/>
       <c r="Z55" s="20" t="n"/>
       <c r="AA55" s="18">
-        <f>IF($D55="","",IF(AND($C55&lt;&gt;"",ISNA(MATCH($C55,状态表,0))),"※状态不在【资料】里",IF(AND($G55&lt;&gt;"",$H55&lt;&gt;"",$H55&lt;$G55),"※到期日早于当票日期",IF(AND($F55&lt;&gt;"",COUNTIF($F$4:$F$123,$F55)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U55)&gt;0,N($T55)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D55="","",IF(AND($C55&lt;&gt;"",ISNA(MATCH($C55,状态表,0))),"※状态不在【资料】里",IF(AND($G55&lt;&gt;"",$H55&lt;&gt;"",$H55&lt;$G55),"※到期日早于当票日期",IF(AND($F55&lt;&gt;"",COUNTIF($F$4:$F$123,$F55)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U55)&gt;0,N($T55)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -8130,7 +8193,7 @@
       <c r="Y56" s="12" t="n"/>
       <c r="Z56" s="20" t="n"/>
       <c r="AA56" s="18">
-        <f>IF($D56="","",IF(AND($C56&lt;&gt;"",ISNA(MATCH($C56,状态表,0))),"※状态不在【资料】里",IF(AND($G56&lt;&gt;"",$H56&lt;&gt;"",$H56&lt;$G56),"※到期日早于当票日期",IF(AND($F56&lt;&gt;"",COUNTIF($F$4:$F$123,$F56)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U56)&gt;0,N($T56)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D56="","",IF(AND($C56&lt;&gt;"",ISNA(MATCH($C56,状态表,0))),"※状态不在【资料】里",IF(AND($G56&lt;&gt;"",$H56&lt;&gt;"",$H56&lt;$G56),"※到期日早于当票日期",IF(AND($F56&lt;&gt;"",COUNTIF($F$4:$F$123,$F56)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U56)&gt;0,N($T56)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -8206,7 +8269,7 @@
       <c r="Y57" s="12" t="n"/>
       <c r="Z57" s="20" t="n"/>
       <c r="AA57" s="18">
-        <f>IF($D57="","",IF(AND($C57&lt;&gt;"",ISNA(MATCH($C57,状态表,0))),"※状态不在【资料】里",IF(AND($G57&lt;&gt;"",$H57&lt;&gt;"",$H57&lt;$G57),"※到期日早于当票日期",IF(AND($F57&lt;&gt;"",COUNTIF($F$4:$F$123,$F57)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U57)&gt;0,N($T57)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D57="","",IF(AND($C57&lt;&gt;"",ISNA(MATCH($C57,状态表,0))),"※状态不在【资料】里",IF(AND($G57&lt;&gt;"",$H57&lt;&gt;"",$H57&lt;$G57),"※到期日早于当票日期",IF(AND($F57&lt;&gt;"",COUNTIF($F$4:$F$123,$F57)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U57)&gt;0,N($T57)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -8286,7 +8349,7 @@
       <c r="Y58" s="12" t="n"/>
       <c r="Z58" s="20" t="n"/>
       <c r="AA58" s="18">
-        <f>IF($D58="","",IF(AND($C58&lt;&gt;"",ISNA(MATCH($C58,状态表,0))),"※状态不在【资料】里",IF(AND($G58&lt;&gt;"",$H58&lt;&gt;"",$H58&lt;$G58),"※到期日早于当票日期",IF(AND($F58&lt;&gt;"",COUNTIF($F$4:$F$123,$F58)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U58)&gt;0,N($T58)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D58="","",IF(AND($C58&lt;&gt;"",ISNA(MATCH($C58,状态表,0))),"※状态不在【资料】里",IF(AND($G58&lt;&gt;"",$H58&lt;&gt;"",$H58&lt;$G58),"※到期日早于当票日期",IF(AND($F58&lt;&gt;"",COUNTIF($F$4:$F$123,$F58)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U58)&gt;0,N($T58)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -8364,7 +8427,7 @@
       <c r="Y59" s="12" t="n"/>
       <c r="Z59" s="20" t="n"/>
       <c r="AA59" s="18">
-        <f>IF($D59="","",IF(AND($C59&lt;&gt;"",ISNA(MATCH($C59,状态表,0))),"※状态不在【资料】里",IF(AND($G59&lt;&gt;"",$H59&lt;&gt;"",$H59&lt;$G59),"※到期日早于当票日期",IF(AND($F59&lt;&gt;"",COUNTIF($F$4:$F$123,$F59)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U59)&gt;0,N($T59)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D59="","",IF(AND($C59&lt;&gt;"",ISNA(MATCH($C59,状态表,0))),"※状态不在【资料】里",IF(AND($G59&lt;&gt;"",$H59&lt;&gt;"",$H59&lt;$G59),"※到期日早于当票日期",IF(AND($F59&lt;&gt;"",COUNTIF($F$4:$F$123,$F59)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U59)&gt;0,N($T59)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -8442,7 +8505,7 @@
       <c r="Y60" s="12" t="n"/>
       <c r="Z60" s="20" t="n"/>
       <c r="AA60" s="18">
-        <f>IF($D60="","",IF(AND($C60&lt;&gt;"",ISNA(MATCH($C60,状态表,0))),"※状态不在【资料】里",IF(AND($G60&lt;&gt;"",$H60&lt;&gt;"",$H60&lt;$G60),"※到期日早于当票日期",IF(AND($F60&lt;&gt;"",COUNTIF($F$4:$F$123,$F60)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U60)&gt;0,N($T60)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D60="","",IF(AND($C60&lt;&gt;"",ISNA(MATCH($C60,状态表,0))),"※状态不在【资料】里",IF(AND($G60&lt;&gt;"",$H60&lt;&gt;"",$H60&lt;$G60),"※到期日早于当票日期",IF(AND($F60&lt;&gt;"",COUNTIF($F$4:$F$123,$F60)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U60)&gt;0,N($T60)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -8518,7 +8581,7 @@
       <c r="Y61" s="12" t="n"/>
       <c r="Z61" s="20" t="n"/>
       <c r="AA61" s="18">
-        <f>IF($D61="","",IF(AND($C61&lt;&gt;"",ISNA(MATCH($C61,状态表,0))),"※状态不在【资料】里",IF(AND($G61&lt;&gt;"",$H61&lt;&gt;"",$H61&lt;$G61),"※到期日早于当票日期",IF(AND($F61&lt;&gt;"",COUNTIF($F$4:$F$123,$F61)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U61)&gt;0,N($T61)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D61="","",IF(AND($C61&lt;&gt;"",ISNA(MATCH($C61,状态表,0))),"※状态不在【资料】里",IF(AND($G61&lt;&gt;"",$H61&lt;&gt;"",$H61&lt;$G61),"※到期日早于当票日期",IF(AND($F61&lt;&gt;"",COUNTIF($F$4:$F$123,$F61)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U61)&gt;0,N($T61)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -8590,7 +8653,7 @@
       <c r="Y62" s="12" t="n"/>
       <c r="Z62" s="20" t="n"/>
       <c r="AA62" s="18">
-        <f>IF($D62="","",IF(AND($C62&lt;&gt;"",ISNA(MATCH($C62,状态表,0))),"※状态不在【资料】里",IF(AND($G62&lt;&gt;"",$H62&lt;&gt;"",$H62&lt;$G62),"※到期日早于当票日期",IF(AND($F62&lt;&gt;"",COUNTIF($F$4:$F$123,$F62)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U62)&gt;0,N($T62)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D62="","",IF(AND($C62&lt;&gt;"",ISNA(MATCH($C62,状态表,0))),"※状态不在【资料】里",IF(AND($G62&lt;&gt;"",$H62&lt;&gt;"",$H62&lt;$G62),"※到期日早于当票日期",IF(AND($F62&lt;&gt;"",COUNTIF($F$4:$F$123,$F62)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U62)&gt;0,N($T62)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -8662,7 +8725,7 @@
       <c r="Y63" s="12" t="n"/>
       <c r="Z63" s="20" t="n"/>
       <c r="AA63" s="18">
-        <f>IF($D63="","",IF(AND($C63&lt;&gt;"",ISNA(MATCH($C63,状态表,0))),"※状态不在【资料】里",IF(AND($G63&lt;&gt;"",$H63&lt;&gt;"",$H63&lt;$G63),"※到期日早于当票日期",IF(AND($F63&lt;&gt;"",COUNTIF($F$4:$F$123,$F63)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U63)&gt;0,N($T63)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D63="","",IF(AND($C63&lt;&gt;"",ISNA(MATCH($C63,状态表,0))),"※状态不在【资料】里",IF(AND($G63&lt;&gt;"",$H63&lt;&gt;"",$H63&lt;$G63),"※到期日早于当票日期",IF(AND($F63&lt;&gt;"",COUNTIF($F$4:$F$123,$F63)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U63)&gt;0,N($T63)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -8738,7 +8801,7 @@
       <c r="Y64" s="12" t="n"/>
       <c r="Z64" s="20" t="n"/>
       <c r="AA64" s="18">
-        <f>IF($D64="","",IF(AND($C64&lt;&gt;"",ISNA(MATCH($C64,状态表,0))),"※状态不在【资料】里",IF(AND($G64&lt;&gt;"",$H64&lt;&gt;"",$H64&lt;$G64),"※到期日早于当票日期",IF(AND($F64&lt;&gt;"",COUNTIF($F$4:$F$123,$F64)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U64)&gt;0,N($T64)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D64="","",IF(AND($C64&lt;&gt;"",ISNA(MATCH($C64,状态表,0))),"※状态不在【资料】里",IF(AND($G64&lt;&gt;"",$H64&lt;&gt;"",$H64&lt;$G64),"※到期日早于当票日期",IF(AND($F64&lt;&gt;"",COUNTIF($F$4:$F$123,$F64)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U64)&gt;0,N($T64)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -8818,7 +8881,7 @@
       <c r="Y65" s="12" t="n"/>
       <c r="Z65" s="20" t="n"/>
       <c r="AA65" s="18">
-        <f>IF($D65="","",IF(AND($C65&lt;&gt;"",ISNA(MATCH($C65,状态表,0))),"※状态不在【资料】里",IF(AND($G65&lt;&gt;"",$H65&lt;&gt;"",$H65&lt;$G65),"※到期日早于当票日期",IF(AND($F65&lt;&gt;"",COUNTIF($F$4:$F$123,$F65)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U65)&gt;0,N($T65)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D65="","",IF(AND($C65&lt;&gt;"",ISNA(MATCH($C65,状态表,0))),"※状态不在【资料】里",IF(AND($G65&lt;&gt;"",$H65&lt;&gt;"",$H65&lt;$G65),"※到期日早于当票日期",IF(AND($F65&lt;&gt;"",COUNTIF($F$4:$F$123,$F65)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U65)&gt;0,N($T65)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -8894,7 +8957,7 @@
       <c r="Y66" s="12" t="n"/>
       <c r="Z66" s="20" t="n"/>
       <c r="AA66" s="18">
-        <f>IF($D66="","",IF(AND($C66&lt;&gt;"",ISNA(MATCH($C66,状态表,0))),"※状态不在【资料】里",IF(AND($G66&lt;&gt;"",$H66&lt;&gt;"",$H66&lt;$G66),"※到期日早于当票日期",IF(AND($F66&lt;&gt;"",COUNTIF($F$4:$F$123,$F66)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U66)&gt;0,N($T66)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D66="","",IF(AND($C66&lt;&gt;"",ISNA(MATCH($C66,状态表,0))),"※状态不在【资料】里",IF(AND($G66&lt;&gt;"",$H66&lt;&gt;"",$H66&lt;$G66),"※到期日早于当票日期",IF(AND($F66&lt;&gt;"",COUNTIF($F$4:$F$123,$F66)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U66)&gt;0,N($T66)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -8970,7 +9033,7 @@
       <c r="Y67" s="12" t="n"/>
       <c r="Z67" s="20" t="n"/>
       <c r="AA67" s="18">
-        <f>IF($D67="","",IF(AND($C67&lt;&gt;"",ISNA(MATCH($C67,状态表,0))),"※状态不在【资料】里",IF(AND($G67&lt;&gt;"",$H67&lt;&gt;"",$H67&lt;$G67),"※到期日早于当票日期",IF(AND($F67&lt;&gt;"",COUNTIF($F$4:$F$123,$F67)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U67)&gt;0,N($T67)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D67="","",IF(AND($C67&lt;&gt;"",ISNA(MATCH($C67,状态表,0))),"※状态不在【资料】里",IF(AND($G67&lt;&gt;"",$H67&lt;&gt;"",$H67&lt;$G67),"※到期日早于当票日期",IF(AND($F67&lt;&gt;"",COUNTIF($F$4:$F$123,$F67)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U67)&gt;0,N($T67)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9050,7 +9113,7 @@
       <c r="Y68" s="12" t="n"/>
       <c r="Z68" s="20" t="n"/>
       <c r="AA68" s="18">
-        <f>IF($D68="","",IF(AND($C68&lt;&gt;"",ISNA(MATCH($C68,状态表,0))),"※状态不在【资料】里",IF(AND($G68&lt;&gt;"",$H68&lt;&gt;"",$H68&lt;$G68),"※到期日早于当票日期",IF(AND($F68&lt;&gt;"",COUNTIF($F$4:$F$123,$F68)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U68)&gt;0,N($T68)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D68="","",IF(AND($C68&lt;&gt;"",ISNA(MATCH($C68,状态表,0))),"※状态不在【资料】里",IF(AND($G68&lt;&gt;"",$H68&lt;&gt;"",$H68&lt;$G68),"※到期日早于当票日期",IF(AND($F68&lt;&gt;"",COUNTIF($F$4:$F$123,$F68)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U68)&gt;0,N($T68)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9130,7 +9193,7 @@
       <c r="Y69" s="12" t="n"/>
       <c r="Z69" s="20" t="n"/>
       <c r="AA69" s="18">
-        <f>IF($D69="","",IF(AND($C69&lt;&gt;"",ISNA(MATCH($C69,状态表,0))),"※状态不在【资料】里",IF(AND($G69&lt;&gt;"",$H69&lt;&gt;"",$H69&lt;$G69),"※到期日早于当票日期",IF(AND($F69&lt;&gt;"",COUNTIF($F$4:$F$123,$F69)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U69)&gt;0,N($T69)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D69="","",IF(AND($C69&lt;&gt;"",ISNA(MATCH($C69,状态表,0))),"※状态不在【资料】里",IF(AND($G69&lt;&gt;"",$H69&lt;&gt;"",$H69&lt;$G69),"※到期日早于当票日期",IF(AND($F69&lt;&gt;"",COUNTIF($F$4:$F$123,$F69)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U69)&gt;0,N($T69)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9210,7 +9273,7 @@
       <c r="Y70" s="12" t="n"/>
       <c r="Z70" s="20" t="n"/>
       <c r="AA70" s="18">
-        <f>IF($D70="","",IF(AND($C70&lt;&gt;"",ISNA(MATCH($C70,状态表,0))),"※状态不在【资料】里",IF(AND($G70&lt;&gt;"",$H70&lt;&gt;"",$H70&lt;$G70),"※到期日早于当票日期",IF(AND($F70&lt;&gt;"",COUNTIF($F$4:$F$123,$F70)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U70)&gt;0,N($T70)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D70="","",IF(AND($C70&lt;&gt;"",ISNA(MATCH($C70,状态表,0))),"※状态不在【资料】里",IF(AND($G70&lt;&gt;"",$H70&lt;&gt;"",$H70&lt;$G70),"※到期日早于当票日期",IF(AND($F70&lt;&gt;"",COUNTIF($F$4:$F$123,$F70)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U70)&gt;0,N($T70)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9254,7 +9317,7 @@
       <c r="Y71" s="12" t="n"/>
       <c r="Z71" s="20" t="n"/>
       <c r="AA71" s="18">
-        <f>IF($D71="","",IF(AND($C71&lt;&gt;"",ISNA(MATCH($C71,状态表,0))),"※状态不在【资料】里",IF(AND($G71&lt;&gt;"",$H71&lt;&gt;"",$H71&lt;$G71),"※到期日早于当票日期",IF(AND($F71&lt;&gt;"",COUNTIF($F$4:$F$123,$F71)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U71)&gt;0,N($T71)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D71="","",IF(AND($C71&lt;&gt;"",ISNA(MATCH($C71,状态表,0))),"※状态不在【资料】里",IF(AND($G71&lt;&gt;"",$H71&lt;&gt;"",$H71&lt;$G71),"※到期日早于当票日期",IF(AND($F71&lt;&gt;"",COUNTIF($F$4:$F$123,$F71)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U71)&gt;0,N($T71)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9298,7 +9361,7 @@
       <c r="Y72" s="12" t="n"/>
       <c r="Z72" s="20" t="n"/>
       <c r="AA72" s="18">
-        <f>IF($D72="","",IF(AND($C72&lt;&gt;"",ISNA(MATCH($C72,状态表,0))),"※状态不在【资料】里",IF(AND($G72&lt;&gt;"",$H72&lt;&gt;"",$H72&lt;$G72),"※到期日早于当票日期",IF(AND($F72&lt;&gt;"",COUNTIF($F$4:$F$123,$F72)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U72)&gt;0,N($T72)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D72="","",IF(AND($C72&lt;&gt;"",ISNA(MATCH($C72,状态表,0))),"※状态不在【资料】里",IF(AND($G72&lt;&gt;"",$H72&lt;&gt;"",$H72&lt;$G72),"※到期日早于当票日期",IF(AND($F72&lt;&gt;"",COUNTIF($F$4:$F$123,$F72)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U72)&gt;0,N($T72)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9342,7 +9405,7 @@
       <c r="Y73" s="12" t="n"/>
       <c r="Z73" s="20" t="n"/>
       <c r="AA73" s="18">
-        <f>IF($D73="","",IF(AND($C73&lt;&gt;"",ISNA(MATCH($C73,状态表,0))),"※状态不在【资料】里",IF(AND($G73&lt;&gt;"",$H73&lt;&gt;"",$H73&lt;$G73),"※到期日早于当票日期",IF(AND($F73&lt;&gt;"",COUNTIF($F$4:$F$123,$F73)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U73)&gt;0,N($T73)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D73="","",IF(AND($C73&lt;&gt;"",ISNA(MATCH($C73,状态表,0))),"※状态不在【资料】里",IF(AND($G73&lt;&gt;"",$H73&lt;&gt;"",$H73&lt;$G73),"※到期日早于当票日期",IF(AND($F73&lt;&gt;"",COUNTIF($F$4:$F$123,$F73)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U73)&gt;0,N($T73)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9386,7 +9449,7 @@
       <c r="Y74" s="12" t="n"/>
       <c r="Z74" s="20" t="n"/>
       <c r="AA74" s="18">
-        <f>IF($D74="","",IF(AND($C74&lt;&gt;"",ISNA(MATCH($C74,状态表,0))),"※状态不在【资料】里",IF(AND($G74&lt;&gt;"",$H74&lt;&gt;"",$H74&lt;$G74),"※到期日早于当票日期",IF(AND($F74&lt;&gt;"",COUNTIF($F$4:$F$123,$F74)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U74)&gt;0,N($T74)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D74="","",IF(AND($C74&lt;&gt;"",ISNA(MATCH($C74,状态表,0))),"※状态不在【资料】里",IF(AND($G74&lt;&gt;"",$H74&lt;&gt;"",$H74&lt;$G74),"※到期日早于当票日期",IF(AND($F74&lt;&gt;"",COUNTIF($F$4:$F$123,$F74)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U74)&gt;0,N($T74)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9430,7 +9493,7 @@
       <c r="Y75" s="12" t="n"/>
       <c r="Z75" s="20" t="n"/>
       <c r="AA75" s="18">
-        <f>IF($D75="","",IF(AND($C75&lt;&gt;"",ISNA(MATCH($C75,状态表,0))),"※状态不在【资料】里",IF(AND($G75&lt;&gt;"",$H75&lt;&gt;"",$H75&lt;$G75),"※到期日早于当票日期",IF(AND($F75&lt;&gt;"",COUNTIF($F$4:$F$123,$F75)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U75)&gt;0,N($T75)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D75="","",IF(AND($C75&lt;&gt;"",ISNA(MATCH($C75,状态表,0))),"※状态不在【资料】里",IF(AND($G75&lt;&gt;"",$H75&lt;&gt;"",$H75&lt;$G75),"※到期日早于当票日期",IF(AND($F75&lt;&gt;"",COUNTIF($F$4:$F$123,$F75)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U75)&gt;0,N($T75)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9474,7 +9537,7 @@
       <c r="Y76" s="12" t="n"/>
       <c r="Z76" s="20" t="n"/>
       <c r="AA76" s="18">
-        <f>IF($D76="","",IF(AND($C76&lt;&gt;"",ISNA(MATCH($C76,状态表,0))),"※状态不在【资料】里",IF(AND($G76&lt;&gt;"",$H76&lt;&gt;"",$H76&lt;$G76),"※到期日早于当票日期",IF(AND($F76&lt;&gt;"",COUNTIF($F$4:$F$123,$F76)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U76)&gt;0,N($T76)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D76="","",IF(AND($C76&lt;&gt;"",ISNA(MATCH($C76,状态表,0))),"※状态不在【资料】里",IF(AND($G76&lt;&gt;"",$H76&lt;&gt;"",$H76&lt;$G76),"※到期日早于当票日期",IF(AND($F76&lt;&gt;"",COUNTIF($F$4:$F$123,$F76)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U76)&gt;0,N($T76)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9518,7 +9581,7 @@
       <c r="Y77" s="12" t="n"/>
       <c r="Z77" s="20" t="n"/>
       <c r="AA77" s="18">
-        <f>IF($D77="","",IF(AND($C77&lt;&gt;"",ISNA(MATCH($C77,状态表,0))),"※状态不在【资料】里",IF(AND($G77&lt;&gt;"",$H77&lt;&gt;"",$H77&lt;$G77),"※到期日早于当票日期",IF(AND($F77&lt;&gt;"",COUNTIF($F$4:$F$123,$F77)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U77)&gt;0,N($T77)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D77="","",IF(AND($C77&lt;&gt;"",ISNA(MATCH($C77,状态表,0))),"※状态不在【资料】里",IF(AND($G77&lt;&gt;"",$H77&lt;&gt;"",$H77&lt;$G77),"※到期日早于当票日期",IF(AND($F77&lt;&gt;"",COUNTIF($F$4:$F$123,$F77)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U77)&gt;0,N($T77)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9562,7 +9625,7 @@
       <c r="Y78" s="12" t="n"/>
       <c r="Z78" s="20" t="n"/>
       <c r="AA78" s="18">
-        <f>IF($D78="","",IF(AND($C78&lt;&gt;"",ISNA(MATCH($C78,状态表,0))),"※状态不在【资料】里",IF(AND($G78&lt;&gt;"",$H78&lt;&gt;"",$H78&lt;$G78),"※到期日早于当票日期",IF(AND($F78&lt;&gt;"",COUNTIF($F$4:$F$123,$F78)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U78)&gt;0,N($T78)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D78="","",IF(AND($C78&lt;&gt;"",ISNA(MATCH($C78,状态表,0))),"※状态不在【资料】里",IF(AND($G78&lt;&gt;"",$H78&lt;&gt;"",$H78&lt;$G78),"※到期日早于当票日期",IF(AND($F78&lt;&gt;"",COUNTIF($F$4:$F$123,$F78)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U78)&gt;0,N($T78)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9606,7 +9669,7 @@
       <c r="Y79" s="12" t="n"/>
       <c r="Z79" s="20" t="n"/>
       <c r="AA79" s="18">
-        <f>IF($D79="","",IF(AND($C79&lt;&gt;"",ISNA(MATCH($C79,状态表,0))),"※状态不在【资料】里",IF(AND($G79&lt;&gt;"",$H79&lt;&gt;"",$H79&lt;$G79),"※到期日早于当票日期",IF(AND($F79&lt;&gt;"",COUNTIF($F$4:$F$123,$F79)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U79)&gt;0,N($T79)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D79="","",IF(AND($C79&lt;&gt;"",ISNA(MATCH($C79,状态表,0))),"※状态不在【资料】里",IF(AND($G79&lt;&gt;"",$H79&lt;&gt;"",$H79&lt;$G79),"※到期日早于当票日期",IF(AND($F79&lt;&gt;"",COUNTIF($F$4:$F$123,$F79)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U79)&gt;0,N($T79)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9650,7 +9713,7 @@
       <c r="Y80" s="12" t="n"/>
       <c r="Z80" s="20" t="n"/>
       <c r="AA80" s="18">
-        <f>IF($D80="","",IF(AND($C80&lt;&gt;"",ISNA(MATCH($C80,状态表,0))),"※状态不在【资料】里",IF(AND($G80&lt;&gt;"",$H80&lt;&gt;"",$H80&lt;$G80),"※到期日早于当票日期",IF(AND($F80&lt;&gt;"",COUNTIF($F$4:$F$123,$F80)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U80)&gt;0,N($T80)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D80="","",IF(AND($C80&lt;&gt;"",ISNA(MATCH($C80,状态表,0))),"※状态不在【资料】里",IF(AND($G80&lt;&gt;"",$H80&lt;&gt;"",$H80&lt;$G80),"※到期日早于当票日期",IF(AND($F80&lt;&gt;"",COUNTIF($F$4:$F$123,$F80)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U80)&gt;0,N($T80)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9694,7 +9757,7 @@
       <c r="Y81" s="12" t="n"/>
       <c r="Z81" s="20" t="n"/>
       <c r="AA81" s="18">
-        <f>IF($D81="","",IF(AND($C81&lt;&gt;"",ISNA(MATCH($C81,状态表,0))),"※状态不在【资料】里",IF(AND($G81&lt;&gt;"",$H81&lt;&gt;"",$H81&lt;$G81),"※到期日早于当票日期",IF(AND($F81&lt;&gt;"",COUNTIF($F$4:$F$123,$F81)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U81)&gt;0,N($T81)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D81="","",IF(AND($C81&lt;&gt;"",ISNA(MATCH($C81,状态表,0))),"※状态不在【资料】里",IF(AND($G81&lt;&gt;"",$H81&lt;&gt;"",$H81&lt;$G81),"※到期日早于当票日期",IF(AND($F81&lt;&gt;"",COUNTIF($F$4:$F$123,$F81)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U81)&gt;0,N($T81)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9738,7 +9801,7 @@
       <c r="Y82" s="12" t="n"/>
       <c r="Z82" s="20" t="n"/>
       <c r="AA82" s="18">
-        <f>IF($D82="","",IF(AND($C82&lt;&gt;"",ISNA(MATCH($C82,状态表,0))),"※状态不在【资料】里",IF(AND($G82&lt;&gt;"",$H82&lt;&gt;"",$H82&lt;$G82),"※到期日早于当票日期",IF(AND($F82&lt;&gt;"",COUNTIF($F$4:$F$123,$F82)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U82)&gt;0,N($T82)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D82="","",IF(AND($C82&lt;&gt;"",ISNA(MATCH($C82,状态表,0))),"※状态不在【资料】里",IF(AND($G82&lt;&gt;"",$H82&lt;&gt;"",$H82&lt;$G82),"※到期日早于当票日期",IF(AND($F82&lt;&gt;"",COUNTIF($F$4:$F$123,$F82)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U82)&gt;0,N($T82)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9782,7 +9845,7 @@
       <c r="Y83" s="12" t="n"/>
       <c r="Z83" s="20" t="n"/>
       <c r="AA83" s="18">
-        <f>IF($D83="","",IF(AND($C83&lt;&gt;"",ISNA(MATCH($C83,状态表,0))),"※状态不在【资料】里",IF(AND($G83&lt;&gt;"",$H83&lt;&gt;"",$H83&lt;$G83),"※到期日早于当票日期",IF(AND($F83&lt;&gt;"",COUNTIF($F$4:$F$123,$F83)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U83)&gt;0,N($T83)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D83="","",IF(AND($C83&lt;&gt;"",ISNA(MATCH($C83,状态表,0))),"※状态不在【资料】里",IF(AND($G83&lt;&gt;"",$H83&lt;&gt;"",$H83&lt;$G83),"※到期日早于当票日期",IF(AND($F83&lt;&gt;"",COUNTIF($F$4:$F$123,$F83)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U83)&gt;0,N($T83)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9826,7 +9889,7 @@
       <c r="Y84" s="12" t="n"/>
       <c r="Z84" s="20" t="n"/>
       <c r="AA84" s="18">
-        <f>IF($D84="","",IF(AND($C84&lt;&gt;"",ISNA(MATCH($C84,状态表,0))),"※状态不在【资料】里",IF(AND($G84&lt;&gt;"",$H84&lt;&gt;"",$H84&lt;$G84),"※到期日早于当票日期",IF(AND($F84&lt;&gt;"",COUNTIF($F$4:$F$123,$F84)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U84)&gt;0,N($T84)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D84="","",IF(AND($C84&lt;&gt;"",ISNA(MATCH($C84,状态表,0))),"※状态不在【资料】里",IF(AND($G84&lt;&gt;"",$H84&lt;&gt;"",$H84&lt;$G84),"※到期日早于当票日期",IF(AND($F84&lt;&gt;"",COUNTIF($F$4:$F$123,$F84)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U84)&gt;0,N($T84)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9870,7 +9933,7 @@
       <c r="Y85" s="12" t="n"/>
       <c r="Z85" s="20" t="n"/>
       <c r="AA85" s="18">
-        <f>IF($D85="","",IF(AND($C85&lt;&gt;"",ISNA(MATCH($C85,状态表,0))),"※状态不在【资料】里",IF(AND($G85&lt;&gt;"",$H85&lt;&gt;"",$H85&lt;$G85),"※到期日早于当票日期",IF(AND($F85&lt;&gt;"",COUNTIF($F$4:$F$123,$F85)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U85)&gt;0,N($T85)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D85="","",IF(AND($C85&lt;&gt;"",ISNA(MATCH($C85,状态表,0))),"※状态不在【资料】里",IF(AND($G85&lt;&gt;"",$H85&lt;&gt;"",$H85&lt;$G85),"※到期日早于当票日期",IF(AND($F85&lt;&gt;"",COUNTIF($F$4:$F$123,$F85)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U85)&gt;0,N($T85)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9914,7 +9977,7 @@
       <c r="Y86" s="12" t="n"/>
       <c r="Z86" s="20" t="n"/>
       <c r="AA86" s="18">
-        <f>IF($D86="","",IF(AND($C86&lt;&gt;"",ISNA(MATCH($C86,状态表,0))),"※状态不在【资料】里",IF(AND($G86&lt;&gt;"",$H86&lt;&gt;"",$H86&lt;$G86),"※到期日早于当票日期",IF(AND($F86&lt;&gt;"",COUNTIF($F$4:$F$123,$F86)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U86)&gt;0,N($T86)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D86="","",IF(AND($C86&lt;&gt;"",ISNA(MATCH($C86,状态表,0))),"※状态不在【资料】里",IF(AND($G86&lt;&gt;"",$H86&lt;&gt;"",$H86&lt;$G86),"※到期日早于当票日期",IF(AND($F86&lt;&gt;"",COUNTIF($F$4:$F$123,$F86)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U86)&gt;0,N($T86)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -9958,7 +10021,7 @@
       <c r="Y87" s="12" t="n"/>
       <c r="Z87" s="20" t="n"/>
       <c r="AA87" s="18">
-        <f>IF($D87="","",IF(AND($C87&lt;&gt;"",ISNA(MATCH($C87,状态表,0))),"※状态不在【资料】里",IF(AND($G87&lt;&gt;"",$H87&lt;&gt;"",$H87&lt;$G87),"※到期日早于当票日期",IF(AND($F87&lt;&gt;"",COUNTIF($F$4:$F$123,$F87)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U87)&gt;0,N($T87)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D87="","",IF(AND($C87&lt;&gt;"",ISNA(MATCH($C87,状态表,0))),"※状态不在【资料】里",IF(AND($G87&lt;&gt;"",$H87&lt;&gt;"",$H87&lt;$G87),"※到期日早于当票日期",IF(AND($F87&lt;&gt;"",COUNTIF($F$4:$F$123,$F87)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U87)&gt;0,N($T87)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10002,7 +10065,7 @@
       <c r="Y88" s="12" t="n"/>
       <c r="Z88" s="20" t="n"/>
       <c r="AA88" s="18">
-        <f>IF($D88="","",IF(AND($C88&lt;&gt;"",ISNA(MATCH($C88,状态表,0))),"※状态不在【资料】里",IF(AND($G88&lt;&gt;"",$H88&lt;&gt;"",$H88&lt;$G88),"※到期日早于当票日期",IF(AND($F88&lt;&gt;"",COUNTIF($F$4:$F$123,$F88)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U88)&gt;0,N($T88)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D88="","",IF(AND($C88&lt;&gt;"",ISNA(MATCH($C88,状态表,0))),"※状态不在【资料】里",IF(AND($G88&lt;&gt;"",$H88&lt;&gt;"",$H88&lt;$G88),"※到期日早于当票日期",IF(AND($F88&lt;&gt;"",COUNTIF($F$4:$F$123,$F88)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U88)&gt;0,N($T88)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10046,7 +10109,7 @@
       <c r="Y89" s="12" t="n"/>
       <c r="Z89" s="20" t="n"/>
       <c r="AA89" s="18">
-        <f>IF($D89="","",IF(AND($C89&lt;&gt;"",ISNA(MATCH($C89,状态表,0))),"※状态不在【资料】里",IF(AND($G89&lt;&gt;"",$H89&lt;&gt;"",$H89&lt;$G89),"※到期日早于当票日期",IF(AND($F89&lt;&gt;"",COUNTIF($F$4:$F$123,$F89)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U89)&gt;0,N($T89)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D89="","",IF(AND($C89&lt;&gt;"",ISNA(MATCH($C89,状态表,0))),"※状态不在【资料】里",IF(AND($G89&lt;&gt;"",$H89&lt;&gt;"",$H89&lt;$G89),"※到期日早于当票日期",IF(AND($F89&lt;&gt;"",COUNTIF($F$4:$F$123,$F89)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U89)&gt;0,N($T89)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10090,7 +10153,7 @@
       <c r="Y90" s="12" t="n"/>
       <c r="Z90" s="20" t="n"/>
       <c r="AA90" s="18">
-        <f>IF($D90="","",IF(AND($C90&lt;&gt;"",ISNA(MATCH($C90,状态表,0))),"※状态不在【资料】里",IF(AND($G90&lt;&gt;"",$H90&lt;&gt;"",$H90&lt;$G90),"※到期日早于当票日期",IF(AND($F90&lt;&gt;"",COUNTIF($F$4:$F$123,$F90)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U90)&gt;0,N($T90)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D90="","",IF(AND($C90&lt;&gt;"",ISNA(MATCH($C90,状态表,0))),"※状态不在【资料】里",IF(AND($G90&lt;&gt;"",$H90&lt;&gt;"",$H90&lt;$G90),"※到期日早于当票日期",IF(AND($F90&lt;&gt;"",COUNTIF($F$4:$F$123,$F90)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U90)&gt;0,N($T90)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10134,7 +10197,7 @@
       <c r="Y91" s="12" t="n"/>
       <c r="Z91" s="20" t="n"/>
       <c r="AA91" s="18">
-        <f>IF($D91="","",IF(AND($C91&lt;&gt;"",ISNA(MATCH($C91,状态表,0))),"※状态不在【资料】里",IF(AND($G91&lt;&gt;"",$H91&lt;&gt;"",$H91&lt;$G91),"※到期日早于当票日期",IF(AND($F91&lt;&gt;"",COUNTIF($F$4:$F$123,$F91)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U91)&gt;0,N($T91)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D91="","",IF(AND($C91&lt;&gt;"",ISNA(MATCH($C91,状态表,0))),"※状态不在【资料】里",IF(AND($G91&lt;&gt;"",$H91&lt;&gt;"",$H91&lt;$G91),"※到期日早于当票日期",IF(AND($F91&lt;&gt;"",COUNTIF($F$4:$F$123,$F91)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U91)&gt;0,N($T91)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10178,7 +10241,7 @@
       <c r="Y92" s="12" t="n"/>
       <c r="Z92" s="20" t="n"/>
       <c r="AA92" s="18">
-        <f>IF($D92="","",IF(AND($C92&lt;&gt;"",ISNA(MATCH($C92,状态表,0))),"※状态不在【资料】里",IF(AND($G92&lt;&gt;"",$H92&lt;&gt;"",$H92&lt;$G92),"※到期日早于当票日期",IF(AND($F92&lt;&gt;"",COUNTIF($F$4:$F$123,$F92)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U92)&gt;0,N($T92)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D92="","",IF(AND($C92&lt;&gt;"",ISNA(MATCH($C92,状态表,0))),"※状态不在【资料】里",IF(AND($G92&lt;&gt;"",$H92&lt;&gt;"",$H92&lt;$G92),"※到期日早于当票日期",IF(AND($F92&lt;&gt;"",COUNTIF($F$4:$F$123,$F92)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U92)&gt;0,N($T92)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10222,7 +10285,7 @@
       <c r="Y93" s="12" t="n"/>
       <c r="Z93" s="20" t="n"/>
       <c r="AA93" s="18">
-        <f>IF($D93="","",IF(AND($C93&lt;&gt;"",ISNA(MATCH($C93,状态表,0))),"※状态不在【资料】里",IF(AND($G93&lt;&gt;"",$H93&lt;&gt;"",$H93&lt;$G93),"※到期日早于当票日期",IF(AND($F93&lt;&gt;"",COUNTIF($F$4:$F$123,$F93)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U93)&gt;0,N($T93)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D93="","",IF(AND($C93&lt;&gt;"",ISNA(MATCH($C93,状态表,0))),"※状态不在【资料】里",IF(AND($G93&lt;&gt;"",$H93&lt;&gt;"",$H93&lt;$G93),"※到期日早于当票日期",IF(AND($F93&lt;&gt;"",COUNTIF($F$4:$F$123,$F93)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U93)&gt;0,N($T93)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10266,7 +10329,7 @@
       <c r="Y94" s="12" t="n"/>
       <c r="Z94" s="20" t="n"/>
       <c r="AA94" s="18">
-        <f>IF($D94="","",IF(AND($C94&lt;&gt;"",ISNA(MATCH($C94,状态表,0))),"※状态不在【资料】里",IF(AND($G94&lt;&gt;"",$H94&lt;&gt;"",$H94&lt;$G94),"※到期日早于当票日期",IF(AND($F94&lt;&gt;"",COUNTIF($F$4:$F$123,$F94)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U94)&gt;0,N($T94)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D94="","",IF(AND($C94&lt;&gt;"",ISNA(MATCH($C94,状态表,0))),"※状态不在【资料】里",IF(AND($G94&lt;&gt;"",$H94&lt;&gt;"",$H94&lt;$G94),"※到期日早于当票日期",IF(AND($F94&lt;&gt;"",COUNTIF($F$4:$F$123,$F94)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U94)&gt;0,N($T94)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10310,7 +10373,7 @@
       <c r="Y95" s="12" t="n"/>
       <c r="Z95" s="20" t="n"/>
       <c r="AA95" s="18">
-        <f>IF($D95="","",IF(AND($C95&lt;&gt;"",ISNA(MATCH($C95,状态表,0))),"※状态不在【资料】里",IF(AND($G95&lt;&gt;"",$H95&lt;&gt;"",$H95&lt;$G95),"※到期日早于当票日期",IF(AND($F95&lt;&gt;"",COUNTIF($F$4:$F$123,$F95)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U95)&gt;0,N($T95)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D95="","",IF(AND($C95&lt;&gt;"",ISNA(MATCH($C95,状态表,0))),"※状态不在【资料】里",IF(AND($G95&lt;&gt;"",$H95&lt;&gt;"",$H95&lt;$G95),"※到期日早于当票日期",IF(AND($F95&lt;&gt;"",COUNTIF($F$4:$F$123,$F95)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U95)&gt;0,N($T95)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10354,7 +10417,7 @@
       <c r="Y96" s="12" t="n"/>
       <c r="Z96" s="20" t="n"/>
       <c r="AA96" s="18">
-        <f>IF($D96="","",IF(AND($C96&lt;&gt;"",ISNA(MATCH($C96,状态表,0))),"※状态不在【资料】里",IF(AND($G96&lt;&gt;"",$H96&lt;&gt;"",$H96&lt;$G96),"※到期日早于当票日期",IF(AND($F96&lt;&gt;"",COUNTIF($F$4:$F$123,$F96)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U96)&gt;0,N($T96)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D96="","",IF(AND($C96&lt;&gt;"",ISNA(MATCH($C96,状态表,0))),"※状态不在【资料】里",IF(AND($G96&lt;&gt;"",$H96&lt;&gt;"",$H96&lt;$G96),"※到期日早于当票日期",IF(AND($F96&lt;&gt;"",COUNTIF($F$4:$F$123,$F96)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U96)&gt;0,N($T96)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10398,7 +10461,7 @@
       <c r="Y97" s="12" t="n"/>
       <c r="Z97" s="20" t="n"/>
       <c r="AA97" s="18">
-        <f>IF($D97="","",IF(AND($C97&lt;&gt;"",ISNA(MATCH($C97,状态表,0))),"※状态不在【资料】里",IF(AND($G97&lt;&gt;"",$H97&lt;&gt;"",$H97&lt;$G97),"※到期日早于当票日期",IF(AND($F97&lt;&gt;"",COUNTIF($F$4:$F$123,$F97)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U97)&gt;0,N($T97)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D97="","",IF(AND($C97&lt;&gt;"",ISNA(MATCH($C97,状态表,0))),"※状态不在【资料】里",IF(AND($G97&lt;&gt;"",$H97&lt;&gt;"",$H97&lt;$G97),"※到期日早于当票日期",IF(AND($F97&lt;&gt;"",COUNTIF($F$4:$F$123,$F97)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U97)&gt;0,N($T97)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10442,7 +10505,7 @@
       <c r="Y98" s="12" t="n"/>
       <c r="Z98" s="20" t="n"/>
       <c r="AA98" s="18">
-        <f>IF($D98="","",IF(AND($C98&lt;&gt;"",ISNA(MATCH($C98,状态表,0))),"※状态不在【资料】里",IF(AND($G98&lt;&gt;"",$H98&lt;&gt;"",$H98&lt;$G98),"※到期日早于当票日期",IF(AND($F98&lt;&gt;"",COUNTIF($F$4:$F$123,$F98)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U98)&gt;0,N($T98)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D98="","",IF(AND($C98&lt;&gt;"",ISNA(MATCH($C98,状态表,0))),"※状态不在【资料】里",IF(AND($G98&lt;&gt;"",$H98&lt;&gt;"",$H98&lt;$G98),"※到期日早于当票日期",IF(AND($F98&lt;&gt;"",COUNTIF($F$4:$F$123,$F98)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U98)&gt;0,N($T98)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10486,7 +10549,7 @@
       <c r="Y99" s="12" t="n"/>
       <c r="Z99" s="20" t="n"/>
       <c r="AA99" s="18">
-        <f>IF($D99="","",IF(AND($C99&lt;&gt;"",ISNA(MATCH($C99,状态表,0))),"※状态不在【资料】里",IF(AND($G99&lt;&gt;"",$H99&lt;&gt;"",$H99&lt;$G99),"※到期日早于当票日期",IF(AND($F99&lt;&gt;"",COUNTIF($F$4:$F$123,$F99)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U99)&gt;0,N($T99)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D99="","",IF(AND($C99&lt;&gt;"",ISNA(MATCH($C99,状态表,0))),"※状态不在【资料】里",IF(AND($G99&lt;&gt;"",$H99&lt;&gt;"",$H99&lt;$G99),"※到期日早于当票日期",IF(AND($F99&lt;&gt;"",COUNTIF($F$4:$F$123,$F99)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U99)&gt;0,N($T99)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10530,7 +10593,7 @@
       <c r="Y100" s="12" t="n"/>
       <c r="Z100" s="20" t="n"/>
       <c r="AA100" s="18">
-        <f>IF($D100="","",IF(AND($C100&lt;&gt;"",ISNA(MATCH($C100,状态表,0))),"※状态不在【资料】里",IF(AND($G100&lt;&gt;"",$H100&lt;&gt;"",$H100&lt;$G100),"※到期日早于当票日期",IF(AND($F100&lt;&gt;"",COUNTIF($F$4:$F$123,$F100)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U100)&gt;0,N($T100)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D100="","",IF(AND($C100&lt;&gt;"",ISNA(MATCH($C100,状态表,0))),"※状态不在【资料】里",IF(AND($G100&lt;&gt;"",$H100&lt;&gt;"",$H100&lt;$G100),"※到期日早于当票日期",IF(AND($F100&lt;&gt;"",COUNTIF($F$4:$F$123,$F100)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U100)&gt;0,N($T100)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10574,7 +10637,7 @@
       <c r="Y101" s="12" t="n"/>
       <c r="Z101" s="20" t="n"/>
       <c r="AA101" s="18">
-        <f>IF($D101="","",IF(AND($C101&lt;&gt;"",ISNA(MATCH($C101,状态表,0))),"※状态不在【资料】里",IF(AND($G101&lt;&gt;"",$H101&lt;&gt;"",$H101&lt;$G101),"※到期日早于当票日期",IF(AND($F101&lt;&gt;"",COUNTIF($F$4:$F$123,$F101)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U101)&gt;0,N($T101)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D101="","",IF(AND($C101&lt;&gt;"",ISNA(MATCH($C101,状态表,0))),"※状态不在【资料】里",IF(AND($G101&lt;&gt;"",$H101&lt;&gt;"",$H101&lt;$G101),"※到期日早于当票日期",IF(AND($F101&lt;&gt;"",COUNTIF($F$4:$F$123,$F101)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U101)&gt;0,N($T101)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10618,7 +10681,7 @@
       <c r="Y102" s="12" t="n"/>
       <c r="Z102" s="20" t="n"/>
       <c r="AA102" s="18">
-        <f>IF($D102="","",IF(AND($C102&lt;&gt;"",ISNA(MATCH($C102,状态表,0))),"※状态不在【资料】里",IF(AND($G102&lt;&gt;"",$H102&lt;&gt;"",$H102&lt;$G102),"※到期日早于当票日期",IF(AND($F102&lt;&gt;"",COUNTIF($F$4:$F$123,$F102)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U102)&gt;0,N($T102)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D102="","",IF(AND($C102&lt;&gt;"",ISNA(MATCH($C102,状态表,0))),"※状态不在【资料】里",IF(AND($G102&lt;&gt;"",$H102&lt;&gt;"",$H102&lt;$G102),"※到期日早于当票日期",IF(AND($F102&lt;&gt;"",COUNTIF($F$4:$F$123,$F102)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U102)&gt;0,N($T102)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10662,7 +10725,7 @@
       <c r="Y103" s="12" t="n"/>
       <c r="Z103" s="20" t="n"/>
       <c r="AA103" s="18">
-        <f>IF($D103="","",IF(AND($C103&lt;&gt;"",ISNA(MATCH($C103,状态表,0))),"※状态不在【资料】里",IF(AND($G103&lt;&gt;"",$H103&lt;&gt;"",$H103&lt;$G103),"※到期日早于当票日期",IF(AND($F103&lt;&gt;"",COUNTIF($F$4:$F$123,$F103)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U103)&gt;0,N($T103)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D103="","",IF(AND($C103&lt;&gt;"",ISNA(MATCH($C103,状态表,0))),"※状态不在【资料】里",IF(AND($G103&lt;&gt;"",$H103&lt;&gt;"",$H103&lt;$G103),"※到期日早于当票日期",IF(AND($F103&lt;&gt;"",COUNTIF($F$4:$F$123,$F103)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U103)&gt;0,N($T103)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10706,7 +10769,7 @@
       <c r="Y104" s="12" t="n"/>
       <c r="Z104" s="20" t="n"/>
       <c r="AA104" s="18">
-        <f>IF($D104="","",IF(AND($C104&lt;&gt;"",ISNA(MATCH($C104,状态表,0))),"※状态不在【资料】里",IF(AND($G104&lt;&gt;"",$H104&lt;&gt;"",$H104&lt;$G104),"※到期日早于当票日期",IF(AND($F104&lt;&gt;"",COUNTIF($F$4:$F$123,$F104)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U104)&gt;0,N($T104)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D104="","",IF(AND($C104&lt;&gt;"",ISNA(MATCH($C104,状态表,0))),"※状态不在【资料】里",IF(AND($G104&lt;&gt;"",$H104&lt;&gt;"",$H104&lt;$G104),"※到期日早于当票日期",IF(AND($F104&lt;&gt;"",COUNTIF($F$4:$F$123,$F104)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U104)&gt;0,N($T104)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10750,7 +10813,7 @@
       <c r="Y105" s="12" t="n"/>
       <c r="Z105" s="20" t="n"/>
       <c r="AA105" s="18">
-        <f>IF($D105="","",IF(AND($C105&lt;&gt;"",ISNA(MATCH($C105,状态表,0))),"※状态不在【资料】里",IF(AND($G105&lt;&gt;"",$H105&lt;&gt;"",$H105&lt;$G105),"※到期日早于当票日期",IF(AND($F105&lt;&gt;"",COUNTIF($F$4:$F$123,$F105)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U105)&gt;0,N($T105)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D105="","",IF(AND($C105&lt;&gt;"",ISNA(MATCH($C105,状态表,0))),"※状态不在【资料】里",IF(AND($G105&lt;&gt;"",$H105&lt;&gt;"",$H105&lt;$G105),"※到期日早于当票日期",IF(AND($F105&lt;&gt;"",COUNTIF($F$4:$F$123,$F105)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U105)&gt;0,N($T105)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10794,7 +10857,7 @@
       <c r="Y106" s="12" t="n"/>
       <c r="Z106" s="20" t="n"/>
       <c r="AA106" s="18">
-        <f>IF($D106="","",IF(AND($C106&lt;&gt;"",ISNA(MATCH($C106,状态表,0))),"※状态不在【资料】里",IF(AND($G106&lt;&gt;"",$H106&lt;&gt;"",$H106&lt;$G106),"※到期日早于当票日期",IF(AND($F106&lt;&gt;"",COUNTIF($F$4:$F$123,$F106)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U106)&gt;0,N($T106)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D106="","",IF(AND($C106&lt;&gt;"",ISNA(MATCH($C106,状态表,0))),"※状态不在【资料】里",IF(AND($G106&lt;&gt;"",$H106&lt;&gt;"",$H106&lt;$G106),"※到期日早于当票日期",IF(AND($F106&lt;&gt;"",COUNTIF($F$4:$F$123,$F106)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U106)&gt;0,N($T106)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10838,7 +10901,7 @@
       <c r="Y107" s="12" t="n"/>
       <c r="Z107" s="20" t="n"/>
       <c r="AA107" s="18">
-        <f>IF($D107="","",IF(AND($C107&lt;&gt;"",ISNA(MATCH($C107,状态表,0))),"※状态不在【资料】里",IF(AND($G107&lt;&gt;"",$H107&lt;&gt;"",$H107&lt;$G107),"※到期日早于当票日期",IF(AND($F107&lt;&gt;"",COUNTIF($F$4:$F$123,$F107)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U107)&gt;0,N($T107)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D107="","",IF(AND($C107&lt;&gt;"",ISNA(MATCH($C107,状态表,0))),"※状态不在【资料】里",IF(AND($G107&lt;&gt;"",$H107&lt;&gt;"",$H107&lt;$G107),"※到期日早于当票日期",IF(AND($F107&lt;&gt;"",COUNTIF($F$4:$F$123,$F107)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U107)&gt;0,N($T107)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10882,7 +10945,7 @@
       <c r="Y108" s="12" t="n"/>
       <c r="Z108" s="20" t="n"/>
       <c r="AA108" s="18">
-        <f>IF($D108="","",IF(AND($C108&lt;&gt;"",ISNA(MATCH($C108,状态表,0))),"※状态不在【资料】里",IF(AND($G108&lt;&gt;"",$H108&lt;&gt;"",$H108&lt;$G108),"※到期日早于当票日期",IF(AND($F108&lt;&gt;"",COUNTIF($F$4:$F$123,$F108)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U108)&gt;0,N($T108)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D108="","",IF(AND($C108&lt;&gt;"",ISNA(MATCH($C108,状态表,0))),"※状态不在【资料】里",IF(AND($G108&lt;&gt;"",$H108&lt;&gt;"",$H108&lt;$G108),"※到期日早于当票日期",IF(AND($F108&lt;&gt;"",COUNTIF($F$4:$F$123,$F108)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U108)&gt;0,N($T108)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10926,7 +10989,7 @@
       <c r="Y109" s="12" t="n"/>
       <c r="Z109" s="20" t="n"/>
       <c r="AA109" s="18">
-        <f>IF($D109="","",IF(AND($C109&lt;&gt;"",ISNA(MATCH($C109,状态表,0))),"※状态不在【资料】里",IF(AND($G109&lt;&gt;"",$H109&lt;&gt;"",$H109&lt;$G109),"※到期日早于当票日期",IF(AND($F109&lt;&gt;"",COUNTIF($F$4:$F$123,$F109)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U109)&gt;0,N($T109)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D109="","",IF(AND($C109&lt;&gt;"",ISNA(MATCH($C109,状态表,0))),"※状态不在【资料】里",IF(AND($G109&lt;&gt;"",$H109&lt;&gt;"",$H109&lt;$G109),"※到期日早于当票日期",IF(AND($F109&lt;&gt;"",COUNTIF($F$4:$F$123,$F109)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U109)&gt;0,N($T109)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -10970,7 +11033,7 @@
       <c r="Y110" s="12" t="n"/>
       <c r="Z110" s="20" t="n"/>
       <c r="AA110" s="18">
-        <f>IF($D110="","",IF(AND($C110&lt;&gt;"",ISNA(MATCH($C110,状态表,0))),"※状态不在【资料】里",IF(AND($G110&lt;&gt;"",$H110&lt;&gt;"",$H110&lt;$G110),"※到期日早于当票日期",IF(AND($F110&lt;&gt;"",COUNTIF($F$4:$F$123,$F110)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U110)&gt;0,N($T110)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D110="","",IF(AND($C110&lt;&gt;"",ISNA(MATCH($C110,状态表,0))),"※状态不在【资料】里",IF(AND($G110&lt;&gt;"",$H110&lt;&gt;"",$H110&lt;$G110),"※到期日早于当票日期",IF(AND($F110&lt;&gt;"",COUNTIF($F$4:$F$123,$F110)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U110)&gt;0,N($T110)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -11014,7 +11077,7 @@
       <c r="Y111" s="12" t="n"/>
       <c r="Z111" s="20" t="n"/>
       <c r="AA111" s="18">
-        <f>IF($D111="","",IF(AND($C111&lt;&gt;"",ISNA(MATCH($C111,状态表,0))),"※状态不在【资料】里",IF(AND($G111&lt;&gt;"",$H111&lt;&gt;"",$H111&lt;$G111),"※到期日早于当票日期",IF(AND($F111&lt;&gt;"",COUNTIF($F$4:$F$123,$F111)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U111)&gt;0,N($T111)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D111="","",IF(AND($C111&lt;&gt;"",ISNA(MATCH($C111,状态表,0))),"※状态不在【资料】里",IF(AND($G111&lt;&gt;"",$H111&lt;&gt;"",$H111&lt;$G111),"※到期日早于当票日期",IF(AND($F111&lt;&gt;"",COUNTIF($F$4:$F$123,$F111)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U111)&gt;0,N($T111)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -11058,7 +11121,7 @@
       <c r="Y112" s="12" t="n"/>
       <c r="Z112" s="20" t="n"/>
       <c r="AA112" s="18">
-        <f>IF($D112="","",IF(AND($C112&lt;&gt;"",ISNA(MATCH($C112,状态表,0))),"※状态不在【资料】里",IF(AND($G112&lt;&gt;"",$H112&lt;&gt;"",$H112&lt;$G112),"※到期日早于当票日期",IF(AND($F112&lt;&gt;"",COUNTIF($F$4:$F$123,$F112)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U112)&gt;0,N($T112)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D112="","",IF(AND($C112&lt;&gt;"",ISNA(MATCH($C112,状态表,0))),"※状态不在【资料】里",IF(AND($G112&lt;&gt;"",$H112&lt;&gt;"",$H112&lt;$G112),"※到期日早于当票日期",IF(AND($F112&lt;&gt;"",COUNTIF($F$4:$F$123,$F112)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U112)&gt;0,N($T112)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -11102,7 +11165,7 @@
       <c r="Y113" s="12" t="n"/>
       <c r="Z113" s="20" t="n"/>
       <c r="AA113" s="18">
-        <f>IF($D113="","",IF(AND($C113&lt;&gt;"",ISNA(MATCH($C113,状态表,0))),"※状态不在【资料】里",IF(AND($G113&lt;&gt;"",$H113&lt;&gt;"",$H113&lt;$G113),"※到期日早于当票日期",IF(AND($F113&lt;&gt;"",COUNTIF($F$4:$F$123,$F113)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U113)&gt;0,N($T113)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D113="","",IF(AND($C113&lt;&gt;"",ISNA(MATCH($C113,状态表,0))),"※状态不在【资料】里",IF(AND($G113&lt;&gt;"",$H113&lt;&gt;"",$H113&lt;$G113),"※到期日早于当票日期",IF(AND($F113&lt;&gt;"",COUNTIF($F$4:$F$123,$F113)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U113)&gt;0,N($T113)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -11146,7 +11209,7 @@
       <c r="Y114" s="12" t="n"/>
       <c r="Z114" s="20" t="n"/>
       <c r="AA114" s="18">
-        <f>IF($D114="","",IF(AND($C114&lt;&gt;"",ISNA(MATCH($C114,状态表,0))),"※状态不在【资料】里",IF(AND($G114&lt;&gt;"",$H114&lt;&gt;"",$H114&lt;$G114),"※到期日早于当票日期",IF(AND($F114&lt;&gt;"",COUNTIF($F$4:$F$123,$F114)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U114)&gt;0,N($T114)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D114="","",IF(AND($C114&lt;&gt;"",ISNA(MATCH($C114,状态表,0))),"※状态不在【资料】里",IF(AND($G114&lt;&gt;"",$H114&lt;&gt;"",$H114&lt;$G114),"※到期日早于当票日期",IF(AND($F114&lt;&gt;"",COUNTIF($F$4:$F$123,$F114)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U114)&gt;0,N($T114)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -11190,7 +11253,7 @@
       <c r="Y115" s="12" t="n"/>
       <c r="Z115" s="20" t="n"/>
       <c r="AA115" s="18">
-        <f>IF($D115="","",IF(AND($C115&lt;&gt;"",ISNA(MATCH($C115,状态表,0))),"※状态不在【资料】里",IF(AND($G115&lt;&gt;"",$H115&lt;&gt;"",$H115&lt;$G115),"※到期日早于当票日期",IF(AND($F115&lt;&gt;"",COUNTIF($F$4:$F$123,$F115)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U115)&gt;0,N($T115)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D115="","",IF(AND($C115&lt;&gt;"",ISNA(MATCH($C115,状态表,0))),"※状态不在【资料】里",IF(AND($G115&lt;&gt;"",$H115&lt;&gt;"",$H115&lt;$G115),"※到期日早于当票日期",IF(AND($F115&lt;&gt;"",COUNTIF($F$4:$F$123,$F115)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U115)&gt;0,N($T115)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -11234,7 +11297,7 @@
       <c r="Y116" s="12" t="n"/>
       <c r="Z116" s="20" t="n"/>
       <c r="AA116" s="18">
-        <f>IF($D116="","",IF(AND($C116&lt;&gt;"",ISNA(MATCH($C116,状态表,0))),"※状态不在【资料】里",IF(AND($G116&lt;&gt;"",$H116&lt;&gt;"",$H116&lt;$G116),"※到期日早于当票日期",IF(AND($F116&lt;&gt;"",COUNTIF($F$4:$F$123,$F116)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U116)&gt;0,N($T116)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D116="","",IF(AND($C116&lt;&gt;"",ISNA(MATCH($C116,状态表,0))),"※状态不在【资料】里",IF(AND($G116&lt;&gt;"",$H116&lt;&gt;"",$H116&lt;$G116),"※到期日早于当票日期",IF(AND($F116&lt;&gt;"",COUNTIF($F$4:$F$123,$F116)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U116)&gt;0,N($T116)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -11278,7 +11341,7 @@
       <c r="Y117" s="12" t="n"/>
       <c r="Z117" s="20" t="n"/>
       <c r="AA117" s="18">
-        <f>IF($D117="","",IF(AND($C117&lt;&gt;"",ISNA(MATCH($C117,状态表,0))),"※状态不在【资料】里",IF(AND($G117&lt;&gt;"",$H117&lt;&gt;"",$H117&lt;$G117),"※到期日早于当票日期",IF(AND($F117&lt;&gt;"",COUNTIF($F$4:$F$123,$F117)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U117)&gt;0,N($T117)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D117="","",IF(AND($C117&lt;&gt;"",ISNA(MATCH($C117,状态表,0))),"※状态不在【资料】里",IF(AND($G117&lt;&gt;"",$H117&lt;&gt;"",$H117&lt;$G117),"※到期日早于当票日期",IF(AND($F117&lt;&gt;"",COUNTIF($F$4:$F$123,$F117)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U117)&gt;0,N($T117)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -11322,7 +11385,7 @@
       <c r="Y118" s="12" t="n"/>
       <c r="Z118" s="20" t="n"/>
       <c r="AA118" s="18">
-        <f>IF($D118="","",IF(AND($C118&lt;&gt;"",ISNA(MATCH($C118,状态表,0))),"※状态不在【资料】里",IF(AND($G118&lt;&gt;"",$H118&lt;&gt;"",$H118&lt;$G118),"※到期日早于当票日期",IF(AND($F118&lt;&gt;"",COUNTIF($F$4:$F$123,$F118)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U118)&gt;0,N($T118)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D118="","",IF(AND($C118&lt;&gt;"",ISNA(MATCH($C118,状态表,0))),"※状态不在【资料】里",IF(AND($G118&lt;&gt;"",$H118&lt;&gt;"",$H118&lt;$G118),"※到期日早于当票日期",IF(AND($F118&lt;&gt;"",COUNTIF($F$4:$F$123,$F118)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U118)&gt;0,N($T118)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -11366,7 +11429,7 @@
       <c r="Y119" s="12" t="n"/>
       <c r="Z119" s="20" t="n"/>
       <c r="AA119" s="18">
-        <f>IF($D119="","",IF(AND($C119&lt;&gt;"",ISNA(MATCH($C119,状态表,0))),"※状态不在【资料】里",IF(AND($G119&lt;&gt;"",$H119&lt;&gt;"",$H119&lt;$G119),"※到期日早于当票日期",IF(AND($F119&lt;&gt;"",COUNTIF($F$4:$F$123,$F119)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U119)&gt;0,N($T119)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D119="","",IF(AND($C119&lt;&gt;"",ISNA(MATCH($C119,状态表,0))),"※状态不在【资料】里",IF(AND($G119&lt;&gt;"",$H119&lt;&gt;"",$H119&lt;$G119),"※到期日早于当票日期",IF(AND($F119&lt;&gt;"",COUNTIF($F$4:$F$123,$F119)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U119)&gt;0,N($T119)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -11410,7 +11473,7 @@
       <c r="Y120" s="12" t="n"/>
       <c r="Z120" s="20" t="n"/>
       <c r="AA120" s="18">
-        <f>IF($D120="","",IF(AND($C120&lt;&gt;"",ISNA(MATCH($C120,状态表,0))),"※状态不在【资料】里",IF(AND($G120&lt;&gt;"",$H120&lt;&gt;"",$H120&lt;$G120),"※到期日早于当票日期",IF(AND($F120&lt;&gt;"",COUNTIF($F$4:$F$123,$F120)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U120)&gt;0,N($T120)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D120="","",IF(AND($C120&lt;&gt;"",ISNA(MATCH($C120,状态表,0))),"※状态不在【资料】里",IF(AND($G120&lt;&gt;"",$H120&lt;&gt;"",$H120&lt;$G120),"※到期日早于当票日期",IF(AND($F120&lt;&gt;"",COUNTIF($F$4:$F$123,$F120)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U120)&gt;0,N($T120)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -11454,7 +11517,7 @@
       <c r="Y121" s="12" t="n"/>
       <c r="Z121" s="20" t="n"/>
       <c r="AA121" s="18">
-        <f>IF($D121="","",IF(AND($C121&lt;&gt;"",ISNA(MATCH($C121,状态表,0))),"※状态不在【资料】里",IF(AND($G121&lt;&gt;"",$H121&lt;&gt;"",$H121&lt;$G121),"※到期日早于当票日期",IF(AND($F121&lt;&gt;"",COUNTIF($F$4:$F$123,$F121)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U121)&gt;0,N($T121)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D121="","",IF(AND($C121&lt;&gt;"",ISNA(MATCH($C121,状态表,0))),"※状态不在【资料】里",IF(AND($G121&lt;&gt;"",$H121&lt;&gt;"",$H121&lt;$G121),"※到期日早于当票日期",IF(AND($F121&lt;&gt;"",COUNTIF($F$4:$F$123,$F121)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U121)&gt;0,N($T121)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -11498,7 +11561,7 @@
       <c r="Y122" s="12" t="n"/>
       <c r="Z122" s="20" t="n"/>
       <c r="AA122" s="18">
-        <f>IF($D122="","",IF(AND($C122&lt;&gt;"",ISNA(MATCH($C122,状态表,0))),"※状态不在【资料】里",IF(AND($G122&lt;&gt;"",$H122&lt;&gt;"",$H122&lt;$G122),"※到期日早于当票日期",IF(AND($F122&lt;&gt;"",COUNTIF($F$4:$F$123,$F122)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U122)&gt;0,N($T122)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D122="","",IF(AND($C122&lt;&gt;"",ISNA(MATCH($C122,状态表,0))),"※状态不在【资料】里",IF(AND($G122&lt;&gt;"",$H122&lt;&gt;"",$H122&lt;$G122),"※到期日早于当票日期",IF(AND($F122&lt;&gt;"",COUNTIF($F$4:$F$123,$F122)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U122)&gt;0,N($T122)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -11542,7 +11605,7 @@
       <c r="Y123" s="12" t="n"/>
       <c r="Z123" s="20" t="n"/>
       <c r="AA123" s="18">
-        <f>IF($D123="","",IF(AND($C123&lt;&gt;"",ISNA(MATCH($C123,状态表,0))),"※状态不在【资料】里",IF(AND($G123&lt;&gt;"",$H123&lt;&gt;"",$H123&lt;$G123),"※到期日早于当票日期",IF(AND($F123&lt;&gt;"",COUNTIF($F$4:$F$123,$F123)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U123)&gt;0,N($T123)=0),"※填了实际付息日但没填应付息日","")))</f>
+        <f>IF($D123="","",IF(AND($C123&lt;&gt;"",ISNA(MATCH($C123,状态表,0))),"※状态不在【资料】里",IF(AND($G123&lt;&gt;"",$H123&lt;&gt;"",$H123&lt;$G123),"※到期日早于当票日期",IF(AND($F123&lt;&gt;"",COUNTIF($F$4:$F$123,$F123)&gt;1),"※当票号在本表里出现了不止一次",IF(AND(N($U123)&gt;0,N($T123)=0),"※填了实际付息日但没填应付息日","")))))</f>
         <v/>
       </c>
     </row>
@@ -11803,7 +11866,7 @@
       <c r="V4" s="12" t="n"/>
       <c r="W4" s="12" t="n"/>
       <c r="X4" s="18">
-        <f>IF($E4="","",IF(AND($B4&lt;&gt;"",ISNA(MATCH($B4,机构表,0))),"※机构不在【资料】里",IF(AND($D4&lt;&gt;"",ISNA(MATCH($D4,状态表,0))),"※状态不在【资料】里",IF(N($M4)&gt;N($L4),"※已还本金大于典当金额",IF(AND($I4&lt;&gt;"",$J4&lt;&gt;"",$J4&lt;$I4),"※到期日早于当票日期",IF(AND($H4&lt;&gt;"",COUNTIF($H$4:$H$403,$H4)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L4&lt;&gt;"",$E4=""),"※有金额没写客户","")))))</f>
+        <f>IF($E4="","",IF(AND($B4&lt;&gt;"",ISNA(MATCH($B4,机构表,0))),"※机构不在【资料】里",IF(AND($D4&lt;&gt;"",ISNA(MATCH($D4,状态表,0))),"※状态不在【资料】里",IF(N($M4)&gt;N($L4),"※已还本金大于典当金额",IF(AND($I4&lt;&gt;"",$J4&lt;&gt;"",$J4&lt;$I4),"※到期日早于当票日期",IF(AND($H4&lt;&gt;"",COUNTIF($H$4:$H$403,$H4)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L4&lt;&gt;"",$E4=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -11868,7 +11931,7 @@
       <c r="V5" s="12" t="n"/>
       <c r="W5" s="12" t="n"/>
       <c r="X5" s="18">
-        <f>IF($E5="","",IF(AND($B5&lt;&gt;"",ISNA(MATCH($B5,机构表,0))),"※机构不在【资料】里",IF(AND($D5&lt;&gt;"",ISNA(MATCH($D5,状态表,0))),"※状态不在【资料】里",IF(N($M5)&gt;N($L5),"※已还本金大于典当金额",IF(AND($I5&lt;&gt;"",$J5&lt;&gt;"",$J5&lt;$I5),"※到期日早于当票日期",IF(AND($H5&lt;&gt;"",COUNTIF($H$4:$H$403,$H5)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L5&lt;&gt;"",$E5=""),"※有金额没写客户","")))))</f>
+        <f>IF($E5="","",IF(AND($B5&lt;&gt;"",ISNA(MATCH($B5,机构表,0))),"※机构不在【资料】里",IF(AND($D5&lt;&gt;"",ISNA(MATCH($D5,状态表,0))),"※状态不在【资料】里",IF(N($M5)&gt;N($L5),"※已还本金大于典当金额",IF(AND($I5&lt;&gt;"",$J5&lt;&gt;"",$J5&lt;$I5),"※到期日早于当票日期",IF(AND($H5&lt;&gt;"",COUNTIF($H$4:$H$403,$H5)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L5&lt;&gt;"",$E5=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -11931,7 +11994,7 @@
       <c r="V6" s="12" t="n"/>
       <c r="W6" s="12" t="n"/>
       <c r="X6" s="18">
-        <f>IF($E6="","",IF(AND($B6&lt;&gt;"",ISNA(MATCH($B6,机构表,0))),"※机构不在【资料】里",IF(AND($D6&lt;&gt;"",ISNA(MATCH($D6,状态表,0))),"※状态不在【资料】里",IF(N($M6)&gt;N($L6),"※已还本金大于典当金额",IF(AND($I6&lt;&gt;"",$J6&lt;&gt;"",$J6&lt;$I6),"※到期日早于当票日期",IF(AND($H6&lt;&gt;"",COUNTIF($H$4:$H$403,$H6)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L6&lt;&gt;"",$E6=""),"※有金额没写客户","")))))</f>
+        <f>IF($E6="","",IF(AND($B6&lt;&gt;"",ISNA(MATCH($B6,机构表,0))),"※机构不在【资料】里",IF(AND($D6&lt;&gt;"",ISNA(MATCH($D6,状态表,0))),"※状态不在【资料】里",IF(N($M6)&gt;N($L6),"※已还本金大于典当金额",IF(AND($I6&lt;&gt;"",$J6&lt;&gt;"",$J6&lt;$I6),"※到期日早于当票日期",IF(AND($H6&lt;&gt;"",COUNTIF($H$4:$H$403,$H6)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L6&lt;&gt;"",$E6=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -11994,7 +12057,7 @@
       <c r="V7" s="12" t="n"/>
       <c r="W7" s="12" t="n"/>
       <c r="X7" s="18">
-        <f>IF($E7="","",IF(AND($B7&lt;&gt;"",ISNA(MATCH($B7,机构表,0))),"※机构不在【资料】里",IF(AND($D7&lt;&gt;"",ISNA(MATCH($D7,状态表,0))),"※状态不在【资料】里",IF(N($M7)&gt;N($L7),"※已还本金大于典当金额",IF(AND($I7&lt;&gt;"",$J7&lt;&gt;"",$J7&lt;$I7),"※到期日早于当票日期",IF(AND($H7&lt;&gt;"",COUNTIF($H$4:$H$403,$H7)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L7&lt;&gt;"",$E7=""),"※有金额没写客户","")))))</f>
+        <f>IF($E7="","",IF(AND($B7&lt;&gt;"",ISNA(MATCH($B7,机构表,0))),"※机构不在【资料】里",IF(AND($D7&lt;&gt;"",ISNA(MATCH($D7,状态表,0))),"※状态不在【资料】里",IF(N($M7)&gt;N($L7),"※已还本金大于典当金额",IF(AND($I7&lt;&gt;"",$J7&lt;&gt;"",$J7&lt;$I7),"※到期日早于当票日期",IF(AND($H7&lt;&gt;"",COUNTIF($H$4:$H$403,$H7)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L7&lt;&gt;"",$E7=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -12067,7 +12130,7 @@
       <c r="V8" s="12" t="n"/>
       <c r="W8" s="12" t="n"/>
       <c r="X8" s="18">
-        <f>IF($E8="","",IF(AND($B8&lt;&gt;"",ISNA(MATCH($B8,机构表,0))),"※机构不在【资料】里",IF(AND($D8&lt;&gt;"",ISNA(MATCH($D8,状态表,0))),"※状态不在【资料】里",IF(N($M8)&gt;N($L8),"※已还本金大于典当金额",IF(AND($I8&lt;&gt;"",$J8&lt;&gt;"",$J8&lt;$I8),"※到期日早于当票日期",IF(AND($H8&lt;&gt;"",COUNTIF($H$4:$H$403,$H8)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L8&lt;&gt;"",$E8=""),"※有金额没写客户","")))))</f>
+        <f>IF($E8="","",IF(AND($B8&lt;&gt;"",ISNA(MATCH($B8,机构表,0))),"※机构不在【资料】里",IF(AND($D8&lt;&gt;"",ISNA(MATCH($D8,状态表,0))),"※状态不在【资料】里",IF(N($M8)&gt;N($L8),"※已还本金大于典当金额",IF(AND($I8&lt;&gt;"",$J8&lt;&gt;"",$J8&lt;$I8),"※到期日早于当票日期",IF(AND($H8&lt;&gt;"",COUNTIF($H$4:$H$403,$H8)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L8&lt;&gt;"",$E8=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -12132,7 +12195,7 @@
       <c r="V9" s="12" t="n"/>
       <c r="W9" s="12" t="n"/>
       <c r="X9" s="18">
-        <f>IF($E9="","",IF(AND($B9&lt;&gt;"",ISNA(MATCH($B9,机构表,0))),"※机构不在【资料】里",IF(AND($D9&lt;&gt;"",ISNA(MATCH($D9,状态表,0))),"※状态不在【资料】里",IF(N($M9)&gt;N($L9),"※已还本金大于典当金额",IF(AND($I9&lt;&gt;"",$J9&lt;&gt;"",$J9&lt;$I9),"※到期日早于当票日期",IF(AND($H9&lt;&gt;"",COUNTIF($H$4:$H$403,$H9)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L9&lt;&gt;"",$E9=""),"※有金额没写客户","")))))</f>
+        <f>IF($E9="","",IF(AND($B9&lt;&gt;"",ISNA(MATCH($B9,机构表,0))),"※机构不在【资料】里",IF(AND($D9&lt;&gt;"",ISNA(MATCH($D9,状态表,0))),"※状态不在【资料】里",IF(N($M9)&gt;N($L9),"※已还本金大于典当金额",IF(AND($I9&lt;&gt;"",$J9&lt;&gt;"",$J9&lt;$I9),"※到期日早于当票日期",IF(AND($H9&lt;&gt;"",COUNTIF($H$4:$H$403,$H9)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L9&lt;&gt;"",$E9=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -12193,7 +12256,7 @@
       <c r="V10" s="12" t="n"/>
       <c r="W10" s="12" t="n"/>
       <c r="X10" s="18">
-        <f>IF($E10="","",IF(AND($B10&lt;&gt;"",ISNA(MATCH($B10,机构表,0))),"※机构不在【资料】里",IF(AND($D10&lt;&gt;"",ISNA(MATCH($D10,状态表,0))),"※状态不在【资料】里",IF(N($M10)&gt;N($L10),"※已还本金大于典当金额",IF(AND($I10&lt;&gt;"",$J10&lt;&gt;"",$J10&lt;$I10),"※到期日早于当票日期",IF(AND($H10&lt;&gt;"",COUNTIF($H$4:$H$403,$H10)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L10&lt;&gt;"",$E10=""),"※有金额没写客户","")))))</f>
+        <f>IF($E10="","",IF(AND($B10&lt;&gt;"",ISNA(MATCH($B10,机构表,0))),"※机构不在【资料】里",IF(AND($D10&lt;&gt;"",ISNA(MATCH($D10,状态表,0))),"※状态不在【资料】里",IF(N($M10)&gt;N($L10),"※已还本金大于典当金额",IF(AND($I10&lt;&gt;"",$J10&lt;&gt;"",$J10&lt;$I10),"※到期日早于当票日期",IF(AND($H10&lt;&gt;"",COUNTIF($H$4:$H$403,$H10)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L10&lt;&gt;"",$E10=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -12258,7 +12321,7 @@
       <c r="V11" s="12" t="n"/>
       <c r="W11" s="12" t="n"/>
       <c r="X11" s="18">
-        <f>IF($E11="","",IF(AND($B11&lt;&gt;"",ISNA(MATCH($B11,机构表,0))),"※机构不在【资料】里",IF(AND($D11&lt;&gt;"",ISNA(MATCH($D11,状态表,0))),"※状态不在【资料】里",IF(N($M11)&gt;N($L11),"※已还本金大于典当金额",IF(AND($I11&lt;&gt;"",$J11&lt;&gt;"",$J11&lt;$I11),"※到期日早于当票日期",IF(AND($H11&lt;&gt;"",COUNTIF($H$4:$H$403,$H11)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L11&lt;&gt;"",$E11=""),"※有金额没写客户","")))))</f>
+        <f>IF($E11="","",IF(AND($B11&lt;&gt;"",ISNA(MATCH($B11,机构表,0))),"※机构不在【资料】里",IF(AND($D11&lt;&gt;"",ISNA(MATCH($D11,状态表,0))),"※状态不在【资料】里",IF(N($M11)&gt;N($L11),"※已还本金大于典当金额",IF(AND($I11&lt;&gt;"",$J11&lt;&gt;"",$J11&lt;$I11),"※到期日早于当票日期",IF(AND($H11&lt;&gt;"",COUNTIF($H$4:$H$403,$H11)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L11&lt;&gt;"",$E11=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -12321,7 +12384,7 @@
       <c r="V12" s="12" t="n"/>
       <c r="W12" s="12" t="n"/>
       <c r="X12" s="18">
-        <f>IF($E12="","",IF(AND($B12&lt;&gt;"",ISNA(MATCH($B12,机构表,0))),"※机构不在【资料】里",IF(AND($D12&lt;&gt;"",ISNA(MATCH($D12,状态表,0))),"※状态不在【资料】里",IF(N($M12)&gt;N($L12),"※已还本金大于典当金额",IF(AND($I12&lt;&gt;"",$J12&lt;&gt;"",$J12&lt;$I12),"※到期日早于当票日期",IF(AND($H12&lt;&gt;"",COUNTIF($H$4:$H$403,$H12)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L12&lt;&gt;"",$E12=""),"※有金额没写客户","")))))</f>
+        <f>IF($E12="","",IF(AND($B12&lt;&gt;"",ISNA(MATCH($B12,机构表,0))),"※机构不在【资料】里",IF(AND($D12&lt;&gt;"",ISNA(MATCH($D12,状态表,0))),"※状态不在【资料】里",IF(N($M12)&gt;N($L12),"※已还本金大于典当金额",IF(AND($I12&lt;&gt;"",$J12&lt;&gt;"",$J12&lt;$I12),"※到期日早于当票日期",IF(AND($H12&lt;&gt;"",COUNTIF($H$4:$H$403,$H12)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L12&lt;&gt;"",$E12=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -12384,7 +12447,7 @@
       <c r="V13" s="12" t="n"/>
       <c r="W13" s="12" t="n"/>
       <c r="X13" s="18">
-        <f>IF($E13="","",IF(AND($B13&lt;&gt;"",ISNA(MATCH($B13,机构表,0))),"※机构不在【资料】里",IF(AND($D13&lt;&gt;"",ISNA(MATCH($D13,状态表,0))),"※状态不在【资料】里",IF(N($M13)&gt;N($L13),"※已还本金大于典当金额",IF(AND($I13&lt;&gt;"",$J13&lt;&gt;"",$J13&lt;$I13),"※到期日早于当票日期",IF(AND($H13&lt;&gt;"",COUNTIF($H$4:$H$403,$H13)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L13&lt;&gt;"",$E13=""),"※有金额没写客户","")))))</f>
+        <f>IF($E13="","",IF(AND($B13&lt;&gt;"",ISNA(MATCH($B13,机构表,0))),"※机构不在【资料】里",IF(AND($D13&lt;&gt;"",ISNA(MATCH($D13,状态表,0))),"※状态不在【资料】里",IF(N($M13)&gt;N($L13),"※已还本金大于典当金额",IF(AND($I13&lt;&gt;"",$J13&lt;&gt;"",$J13&lt;$I13),"※到期日早于当票日期",IF(AND($H13&lt;&gt;"",COUNTIF($H$4:$H$403,$H13)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L13&lt;&gt;"",$E13=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -12449,7 +12512,7 @@
       <c r="V14" s="12" t="n"/>
       <c r="W14" s="12" t="n"/>
       <c r="X14" s="18">
-        <f>IF($E14="","",IF(AND($B14&lt;&gt;"",ISNA(MATCH($B14,机构表,0))),"※机构不在【资料】里",IF(AND($D14&lt;&gt;"",ISNA(MATCH($D14,状态表,0))),"※状态不在【资料】里",IF(N($M14)&gt;N($L14),"※已还本金大于典当金额",IF(AND($I14&lt;&gt;"",$J14&lt;&gt;"",$J14&lt;$I14),"※到期日早于当票日期",IF(AND($H14&lt;&gt;"",COUNTIF($H$4:$H$403,$H14)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L14&lt;&gt;"",$E14=""),"※有金额没写客户","")))))</f>
+        <f>IF($E14="","",IF(AND($B14&lt;&gt;"",ISNA(MATCH($B14,机构表,0))),"※机构不在【资料】里",IF(AND($D14&lt;&gt;"",ISNA(MATCH($D14,状态表,0))),"※状态不在【资料】里",IF(N($M14)&gt;N($L14),"※已还本金大于典当金额",IF(AND($I14&lt;&gt;"",$J14&lt;&gt;"",$J14&lt;$I14),"※到期日早于当票日期",IF(AND($H14&lt;&gt;"",COUNTIF($H$4:$H$403,$H14)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L14&lt;&gt;"",$E14=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -12512,7 +12575,7 @@
       <c r="V15" s="12" t="n"/>
       <c r="W15" s="12" t="n"/>
       <c r="X15" s="18">
-        <f>IF($E15="","",IF(AND($B15&lt;&gt;"",ISNA(MATCH($B15,机构表,0))),"※机构不在【资料】里",IF(AND($D15&lt;&gt;"",ISNA(MATCH($D15,状态表,0))),"※状态不在【资料】里",IF(N($M15)&gt;N($L15),"※已还本金大于典当金额",IF(AND($I15&lt;&gt;"",$J15&lt;&gt;"",$J15&lt;$I15),"※到期日早于当票日期",IF(AND($H15&lt;&gt;"",COUNTIF($H$4:$H$403,$H15)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L15&lt;&gt;"",$E15=""),"※有金额没写客户","")))))</f>
+        <f>IF($E15="","",IF(AND($B15&lt;&gt;"",ISNA(MATCH($B15,机构表,0))),"※机构不在【资料】里",IF(AND($D15&lt;&gt;"",ISNA(MATCH($D15,状态表,0))),"※状态不在【资料】里",IF(N($M15)&gt;N($L15),"※已还本金大于典当金额",IF(AND($I15&lt;&gt;"",$J15&lt;&gt;"",$J15&lt;$I15),"※到期日早于当票日期",IF(AND($H15&lt;&gt;"",COUNTIF($H$4:$H$403,$H15)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L15&lt;&gt;"",$E15=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -12575,7 +12638,7 @@
       <c r="V16" s="12" t="n"/>
       <c r="W16" s="12" t="n"/>
       <c r="X16" s="18">
-        <f>IF($E16="","",IF(AND($B16&lt;&gt;"",ISNA(MATCH($B16,机构表,0))),"※机构不在【资料】里",IF(AND($D16&lt;&gt;"",ISNA(MATCH($D16,状态表,0))),"※状态不在【资料】里",IF(N($M16)&gt;N($L16),"※已还本金大于典当金额",IF(AND($I16&lt;&gt;"",$J16&lt;&gt;"",$J16&lt;$I16),"※到期日早于当票日期",IF(AND($H16&lt;&gt;"",COUNTIF($H$4:$H$403,$H16)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L16&lt;&gt;"",$E16=""),"※有金额没写客户","")))))</f>
+        <f>IF($E16="","",IF(AND($B16&lt;&gt;"",ISNA(MATCH($B16,机构表,0))),"※机构不在【资料】里",IF(AND($D16&lt;&gt;"",ISNA(MATCH($D16,状态表,0))),"※状态不在【资料】里",IF(N($M16)&gt;N($L16),"※已还本金大于典当金额",IF(AND($I16&lt;&gt;"",$J16&lt;&gt;"",$J16&lt;$I16),"※到期日早于当票日期",IF(AND($H16&lt;&gt;"",COUNTIF($H$4:$H$403,$H16)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L16&lt;&gt;"",$E16=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -12646,7 +12709,7 @@
       <c r="V17" s="12" t="n"/>
       <c r="W17" s="12" t="n"/>
       <c r="X17" s="18">
-        <f>IF($E17="","",IF(AND($B17&lt;&gt;"",ISNA(MATCH($B17,机构表,0))),"※机构不在【资料】里",IF(AND($D17&lt;&gt;"",ISNA(MATCH($D17,状态表,0))),"※状态不在【资料】里",IF(N($M17)&gt;N($L17),"※已还本金大于典当金额",IF(AND($I17&lt;&gt;"",$J17&lt;&gt;"",$J17&lt;$I17),"※到期日早于当票日期",IF(AND($H17&lt;&gt;"",COUNTIF($H$4:$H$403,$H17)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L17&lt;&gt;"",$E17=""),"※有金额没写客户","")))))</f>
+        <f>IF($E17="","",IF(AND($B17&lt;&gt;"",ISNA(MATCH($B17,机构表,0))),"※机构不在【资料】里",IF(AND($D17&lt;&gt;"",ISNA(MATCH($D17,状态表,0))),"※状态不在【资料】里",IF(N($M17)&gt;N($L17),"※已还本金大于典当金额",IF(AND($I17&lt;&gt;"",$J17&lt;&gt;"",$J17&lt;$I17),"※到期日早于当票日期",IF(AND($H17&lt;&gt;"",COUNTIF($H$4:$H$403,$H17)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L17&lt;&gt;"",$E17=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -12723,7 +12786,7 @@
       </c>
       <c r="W18" s="12" t="n"/>
       <c r="X18" s="18">
-        <f>IF($E18="","",IF(AND($B18&lt;&gt;"",ISNA(MATCH($B18,机构表,0))),"※机构不在【资料】里",IF(AND($D18&lt;&gt;"",ISNA(MATCH($D18,状态表,0))),"※状态不在【资料】里",IF(N($M18)&gt;N($L18),"※已还本金大于典当金额",IF(AND($I18&lt;&gt;"",$J18&lt;&gt;"",$J18&lt;$I18),"※到期日早于当票日期",IF(AND($H18&lt;&gt;"",COUNTIF($H$4:$H$403,$H18)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L18&lt;&gt;"",$E18=""),"※有金额没写客户","")))))</f>
+        <f>IF($E18="","",IF(AND($B18&lt;&gt;"",ISNA(MATCH($B18,机构表,0))),"※机构不在【资料】里",IF(AND($D18&lt;&gt;"",ISNA(MATCH($D18,状态表,0))),"※状态不在【资料】里",IF(N($M18)&gt;N($L18),"※已还本金大于典当金额",IF(AND($I18&lt;&gt;"",$J18&lt;&gt;"",$J18&lt;$I18),"※到期日早于当票日期",IF(AND($H18&lt;&gt;"",COUNTIF($H$4:$H$403,$H18)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L18&lt;&gt;"",$E18=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -12786,7 +12849,7 @@
       <c r="V19" s="12" t="n"/>
       <c r="W19" s="12" t="n"/>
       <c r="X19" s="18">
-        <f>IF($E19="","",IF(AND($B19&lt;&gt;"",ISNA(MATCH($B19,机构表,0))),"※机构不在【资料】里",IF(AND($D19&lt;&gt;"",ISNA(MATCH($D19,状态表,0))),"※状态不在【资料】里",IF(N($M19)&gt;N($L19),"※已还本金大于典当金额",IF(AND($I19&lt;&gt;"",$J19&lt;&gt;"",$J19&lt;$I19),"※到期日早于当票日期",IF(AND($H19&lt;&gt;"",COUNTIF($H$4:$H$403,$H19)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L19&lt;&gt;"",$E19=""),"※有金额没写客户","")))))</f>
+        <f>IF($E19="","",IF(AND($B19&lt;&gt;"",ISNA(MATCH($B19,机构表,0))),"※机构不在【资料】里",IF(AND($D19&lt;&gt;"",ISNA(MATCH($D19,状态表,0))),"※状态不在【资料】里",IF(N($M19)&gt;N($L19),"※已还本金大于典当金额",IF(AND($I19&lt;&gt;"",$J19&lt;&gt;"",$J19&lt;$I19),"※到期日早于当票日期",IF(AND($H19&lt;&gt;"",COUNTIF($H$4:$H$403,$H19)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L19&lt;&gt;"",$E19=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -12857,7 +12920,7 @@
       </c>
       <c r="W20" s="12" t="n"/>
       <c r="X20" s="18">
-        <f>IF($E20="","",IF(AND($B20&lt;&gt;"",ISNA(MATCH($B20,机构表,0))),"※机构不在【资料】里",IF(AND($D20&lt;&gt;"",ISNA(MATCH($D20,状态表,0))),"※状态不在【资料】里",IF(N($M20)&gt;N($L20),"※已还本金大于典当金额",IF(AND($I20&lt;&gt;"",$J20&lt;&gt;"",$J20&lt;$I20),"※到期日早于当票日期",IF(AND($H20&lt;&gt;"",COUNTIF($H$4:$H$403,$H20)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L20&lt;&gt;"",$E20=""),"※有金额没写客户","")))))</f>
+        <f>IF($E20="","",IF(AND($B20&lt;&gt;"",ISNA(MATCH($B20,机构表,0))),"※机构不在【资料】里",IF(AND($D20&lt;&gt;"",ISNA(MATCH($D20,状态表,0))),"※状态不在【资料】里",IF(N($M20)&gt;N($L20),"※已还本金大于典当金额",IF(AND($I20&lt;&gt;"",$J20&lt;&gt;"",$J20&lt;$I20),"※到期日早于当票日期",IF(AND($H20&lt;&gt;"",COUNTIF($H$4:$H$403,$H20)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L20&lt;&gt;"",$E20=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -12926,7 +12989,7 @@
       </c>
       <c r="W21" s="12" t="n"/>
       <c r="X21" s="18">
-        <f>IF($E21="","",IF(AND($B21&lt;&gt;"",ISNA(MATCH($B21,机构表,0))),"※机构不在【资料】里",IF(AND($D21&lt;&gt;"",ISNA(MATCH($D21,状态表,0))),"※状态不在【资料】里",IF(N($M21)&gt;N($L21),"※已还本金大于典当金额",IF(AND($I21&lt;&gt;"",$J21&lt;&gt;"",$J21&lt;$I21),"※到期日早于当票日期",IF(AND($H21&lt;&gt;"",COUNTIF($H$4:$H$403,$H21)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L21&lt;&gt;"",$E21=""),"※有金额没写客户","")))))</f>
+        <f>IF($E21="","",IF(AND($B21&lt;&gt;"",ISNA(MATCH($B21,机构表,0))),"※机构不在【资料】里",IF(AND($D21&lt;&gt;"",ISNA(MATCH($D21,状态表,0))),"※状态不在【资料】里",IF(N($M21)&gt;N($L21),"※已还本金大于典当金额",IF(AND($I21&lt;&gt;"",$J21&lt;&gt;"",$J21&lt;$I21),"※到期日早于当票日期",IF(AND($H21&lt;&gt;"",COUNTIF($H$4:$H$403,$H21)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L21&lt;&gt;"",$E21=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -12985,7 +13048,7 @@
       <c r="V22" s="12" t="n"/>
       <c r="W22" s="12" t="n"/>
       <c r="X22" s="18">
-        <f>IF($E22="","",IF(AND($B22&lt;&gt;"",ISNA(MATCH($B22,机构表,0))),"※机构不在【资料】里",IF(AND($D22&lt;&gt;"",ISNA(MATCH($D22,状态表,0))),"※状态不在【资料】里",IF(N($M22)&gt;N($L22),"※已还本金大于典当金额",IF(AND($I22&lt;&gt;"",$J22&lt;&gt;"",$J22&lt;$I22),"※到期日早于当票日期",IF(AND($H22&lt;&gt;"",COUNTIF($H$4:$H$403,$H22)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L22&lt;&gt;"",$E22=""),"※有金额没写客户","")))))</f>
+        <f>IF($E22="","",IF(AND($B22&lt;&gt;"",ISNA(MATCH($B22,机构表,0))),"※机构不在【资料】里",IF(AND($D22&lt;&gt;"",ISNA(MATCH($D22,状态表,0))),"※状态不在【资料】里",IF(N($M22)&gt;N($L22),"※已还本金大于典当金额",IF(AND($I22&lt;&gt;"",$J22&lt;&gt;"",$J22&lt;$I22),"※到期日早于当票日期",IF(AND($H22&lt;&gt;"",COUNTIF($H$4:$H$403,$H22)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L22&lt;&gt;"",$E22=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -13050,7 +13113,7 @@
       <c r="V23" s="12" t="n"/>
       <c r="W23" s="12" t="n"/>
       <c r="X23" s="18">
-        <f>IF($E23="","",IF(AND($B23&lt;&gt;"",ISNA(MATCH($B23,机构表,0))),"※机构不在【资料】里",IF(AND($D23&lt;&gt;"",ISNA(MATCH($D23,状态表,0))),"※状态不在【资料】里",IF(N($M23)&gt;N($L23),"※已还本金大于典当金额",IF(AND($I23&lt;&gt;"",$J23&lt;&gt;"",$J23&lt;$I23),"※到期日早于当票日期",IF(AND($H23&lt;&gt;"",COUNTIF($H$4:$H$403,$H23)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L23&lt;&gt;"",$E23=""),"※有金额没写客户","")))))</f>
+        <f>IF($E23="","",IF(AND($B23&lt;&gt;"",ISNA(MATCH($B23,机构表,0))),"※机构不在【资料】里",IF(AND($D23&lt;&gt;"",ISNA(MATCH($D23,状态表,0))),"※状态不在【资料】里",IF(N($M23)&gt;N($L23),"※已还本金大于典当金额",IF(AND($I23&lt;&gt;"",$J23&lt;&gt;"",$J23&lt;$I23),"※到期日早于当票日期",IF(AND($H23&lt;&gt;"",COUNTIF($H$4:$H$403,$H23)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L23&lt;&gt;"",$E23=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -13115,7 +13178,7 @@
       <c r="V24" s="12" t="n"/>
       <c r="W24" s="12" t="n"/>
       <c r="X24" s="18">
-        <f>IF($E24="","",IF(AND($B24&lt;&gt;"",ISNA(MATCH($B24,机构表,0))),"※机构不在【资料】里",IF(AND($D24&lt;&gt;"",ISNA(MATCH($D24,状态表,0))),"※状态不在【资料】里",IF(N($M24)&gt;N($L24),"※已还本金大于典当金额",IF(AND($I24&lt;&gt;"",$J24&lt;&gt;"",$J24&lt;$I24),"※到期日早于当票日期",IF(AND($H24&lt;&gt;"",COUNTIF($H$4:$H$403,$H24)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L24&lt;&gt;"",$E24=""),"※有金额没写客户","")))))</f>
+        <f>IF($E24="","",IF(AND($B24&lt;&gt;"",ISNA(MATCH($B24,机构表,0))),"※机构不在【资料】里",IF(AND($D24&lt;&gt;"",ISNA(MATCH($D24,状态表,0))),"※状态不在【资料】里",IF(N($M24)&gt;N($L24),"※已还本金大于典当金额",IF(AND($I24&lt;&gt;"",$J24&lt;&gt;"",$J24&lt;$I24),"※到期日早于当票日期",IF(AND($H24&lt;&gt;"",COUNTIF($H$4:$H$403,$H24)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L24&lt;&gt;"",$E24=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -13180,7 +13243,7 @@
       <c r="V25" s="12" t="n"/>
       <c r="W25" s="12" t="n"/>
       <c r="X25" s="18">
-        <f>IF($E25="","",IF(AND($B25&lt;&gt;"",ISNA(MATCH($B25,机构表,0))),"※机构不在【资料】里",IF(AND($D25&lt;&gt;"",ISNA(MATCH($D25,状态表,0))),"※状态不在【资料】里",IF(N($M25)&gt;N($L25),"※已还本金大于典当金额",IF(AND($I25&lt;&gt;"",$J25&lt;&gt;"",$J25&lt;$I25),"※到期日早于当票日期",IF(AND($H25&lt;&gt;"",COUNTIF($H$4:$H$403,$H25)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L25&lt;&gt;"",$E25=""),"※有金额没写客户","")))))</f>
+        <f>IF($E25="","",IF(AND($B25&lt;&gt;"",ISNA(MATCH($B25,机构表,0))),"※机构不在【资料】里",IF(AND($D25&lt;&gt;"",ISNA(MATCH($D25,状态表,0))),"※状态不在【资料】里",IF(N($M25)&gt;N($L25),"※已还本金大于典当金额",IF(AND($I25&lt;&gt;"",$J25&lt;&gt;"",$J25&lt;$I25),"※到期日早于当票日期",IF(AND($H25&lt;&gt;"",COUNTIF($H$4:$H$403,$H25)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L25&lt;&gt;"",$E25=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -13243,7 +13306,7 @@
       <c r="V26" s="12" t="n"/>
       <c r="W26" s="12" t="n"/>
       <c r="X26" s="18">
-        <f>IF($E26="","",IF(AND($B26&lt;&gt;"",ISNA(MATCH($B26,机构表,0))),"※机构不在【资料】里",IF(AND($D26&lt;&gt;"",ISNA(MATCH($D26,状态表,0))),"※状态不在【资料】里",IF(N($M26)&gt;N($L26),"※已还本金大于典当金额",IF(AND($I26&lt;&gt;"",$J26&lt;&gt;"",$J26&lt;$I26),"※到期日早于当票日期",IF(AND($H26&lt;&gt;"",COUNTIF($H$4:$H$403,$H26)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L26&lt;&gt;"",$E26=""),"※有金额没写客户","")))))</f>
+        <f>IF($E26="","",IF(AND($B26&lt;&gt;"",ISNA(MATCH($B26,机构表,0))),"※机构不在【资料】里",IF(AND($D26&lt;&gt;"",ISNA(MATCH($D26,状态表,0))),"※状态不在【资料】里",IF(N($M26)&gt;N($L26),"※已还本金大于典当金额",IF(AND($I26&lt;&gt;"",$J26&lt;&gt;"",$J26&lt;$I26),"※到期日早于当票日期",IF(AND($H26&lt;&gt;"",COUNTIF($H$4:$H$403,$H26)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L26&lt;&gt;"",$E26=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -13306,7 +13369,7 @@
       <c r="V27" s="12" t="n"/>
       <c r="W27" s="12" t="n"/>
       <c r="X27" s="18">
-        <f>IF($E27="","",IF(AND($B27&lt;&gt;"",ISNA(MATCH($B27,机构表,0))),"※机构不在【资料】里",IF(AND($D27&lt;&gt;"",ISNA(MATCH($D27,状态表,0))),"※状态不在【资料】里",IF(N($M27)&gt;N($L27),"※已还本金大于典当金额",IF(AND($I27&lt;&gt;"",$J27&lt;&gt;"",$J27&lt;$I27),"※到期日早于当票日期",IF(AND($H27&lt;&gt;"",COUNTIF($H$4:$H$403,$H27)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L27&lt;&gt;"",$E27=""),"※有金额没写客户","")))))</f>
+        <f>IF($E27="","",IF(AND($B27&lt;&gt;"",ISNA(MATCH($B27,机构表,0))),"※机构不在【资料】里",IF(AND($D27&lt;&gt;"",ISNA(MATCH($D27,状态表,0))),"※状态不在【资料】里",IF(N($M27)&gt;N($L27),"※已还本金大于典当金额",IF(AND($I27&lt;&gt;"",$J27&lt;&gt;"",$J27&lt;$I27),"※到期日早于当票日期",IF(AND($H27&lt;&gt;"",COUNTIF($H$4:$H$403,$H27)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L27&lt;&gt;"",$E27=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -13369,7 +13432,7 @@
       <c r="V28" s="12" t="n"/>
       <c r="W28" s="12" t="n"/>
       <c r="X28" s="18">
-        <f>IF($E28="","",IF(AND($B28&lt;&gt;"",ISNA(MATCH($B28,机构表,0))),"※机构不在【资料】里",IF(AND($D28&lt;&gt;"",ISNA(MATCH($D28,状态表,0))),"※状态不在【资料】里",IF(N($M28)&gt;N($L28),"※已还本金大于典当金额",IF(AND($I28&lt;&gt;"",$J28&lt;&gt;"",$J28&lt;$I28),"※到期日早于当票日期",IF(AND($H28&lt;&gt;"",COUNTIF($H$4:$H$403,$H28)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L28&lt;&gt;"",$E28=""),"※有金额没写客户","")))))</f>
+        <f>IF($E28="","",IF(AND($B28&lt;&gt;"",ISNA(MATCH($B28,机构表,0))),"※机构不在【资料】里",IF(AND($D28&lt;&gt;"",ISNA(MATCH($D28,状态表,0))),"※状态不在【资料】里",IF(N($M28)&gt;N($L28),"※已还本金大于典当金额",IF(AND($I28&lt;&gt;"",$J28&lt;&gt;"",$J28&lt;$I28),"※到期日早于当票日期",IF(AND($H28&lt;&gt;"",COUNTIF($H$4:$H$403,$H28)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L28&lt;&gt;"",$E28=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -13442,7 +13505,7 @@
       </c>
       <c r="W29" s="12" t="n"/>
       <c r="X29" s="18">
-        <f>IF($E29="","",IF(AND($B29&lt;&gt;"",ISNA(MATCH($B29,机构表,0))),"※机构不在【资料】里",IF(AND($D29&lt;&gt;"",ISNA(MATCH($D29,状态表,0))),"※状态不在【资料】里",IF(N($M29)&gt;N($L29),"※已还本金大于典当金额",IF(AND($I29&lt;&gt;"",$J29&lt;&gt;"",$J29&lt;$I29),"※到期日早于当票日期",IF(AND($H29&lt;&gt;"",COUNTIF($H$4:$H$403,$H29)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L29&lt;&gt;"",$E29=""),"※有金额没写客户","")))))</f>
+        <f>IF($E29="","",IF(AND($B29&lt;&gt;"",ISNA(MATCH($B29,机构表,0))),"※机构不在【资料】里",IF(AND($D29&lt;&gt;"",ISNA(MATCH($D29,状态表,0))),"※状态不在【资料】里",IF(N($M29)&gt;N($L29),"※已还本金大于典当金额",IF(AND($I29&lt;&gt;"",$J29&lt;&gt;"",$J29&lt;$I29),"※到期日早于当票日期",IF(AND($H29&lt;&gt;"",COUNTIF($H$4:$H$403,$H29)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L29&lt;&gt;"",$E29=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -13517,7 +13580,7 @@
       </c>
       <c r="W30" s="12" t="n"/>
       <c r="X30" s="18">
-        <f>IF($E30="","",IF(AND($B30&lt;&gt;"",ISNA(MATCH($B30,机构表,0))),"※机构不在【资料】里",IF(AND($D30&lt;&gt;"",ISNA(MATCH($D30,状态表,0))),"※状态不在【资料】里",IF(N($M30)&gt;N($L30),"※已还本金大于典当金额",IF(AND($I30&lt;&gt;"",$J30&lt;&gt;"",$J30&lt;$I30),"※到期日早于当票日期",IF(AND($H30&lt;&gt;"",COUNTIF($H$4:$H$403,$H30)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L30&lt;&gt;"",$E30=""),"※有金额没写客户","")))))</f>
+        <f>IF($E30="","",IF(AND($B30&lt;&gt;"",ISNA(MATCH($B30,机构表,0))),"※机构不在【资料】里",IF(AND($D30&lt;&gt;"",ISNA(MATCH($D30,状态表,0))),"※状态不在【资料】里",IF(N($M30)&gt;N($L30),"※已还本金大于典当金额",IF(AND($I30&lt;&gt;"",$J30&lt;&gt;"",$J30&lt;$I30),"※到期日早于当票日期",IF(AND($H30&lt;&gt;"",COUNTIF($H$4:$H$403,$H30)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L30&lt;&gt;"",$E30=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -13588,7 +13651,7 @@
       </c>
       <c r="W31" s="12" t="n"/>
       <c r="X31" s="18">
-        <f>IF($E31="","",IF(AND($B31&lt;&gt;"",ISNA(MATCH($B31,机构表,0))),"※机构不在【资料】里",IF(AND($D31&lt;&gt;"",ISNA(MATCH($D31,状态表,0))),"※状态不在【资料】里",IF(N($M31)&gt;N($L31),"※已还本金大于典当金额",IF(AND($I31&lt;&gt;"",$J31&lt;&gt;"",$J31&lt;$I31),"※到期日早于当票日期",IF(AND($H31&lt;&gt;"",COUNTIF($H$4:$H$403,$H31)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L31&lt;&gt;"",$E31=""),"※有金额没写客户","")))))</f>
+        <f>IF($E31="","",IF(AND($B31&lt;&gt;"",ISNA(MATCH($B31,机构表,0))),"※机构不在【资料】里",IF(AND($D31&lt;&gt;"",ISNA(MATCH($D31,状态表,0))),"※状态不在【资料】里",IF(N($M31)&gt;N($L31),"※已还本金大于典当金额",IF(AND($I31&lt;&gt;"",$J31&lt;&gt;"",$J31&lt;$I31),"※到期日早于当票日期",IF(AND($H31&lt;&gt;"",COUNTIF($H$4:$H$403,$H31)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L31&lt;&gt;"",$E31=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -13651,7 +13714,7 @@
       <c r="V32" s="12" t="n"/>
       <c r="W32" s="12" t="n"/>
       <c r="X32" s="18">
-        <f>IF($E32="","",IF(AND($B32&lt;&gt;"",ISNA(MATCH($B32,机构表,0))),"※机构不在【资料】里",IF(AND($D32&lt;&gt;"",ISNA(MATCH($D32,状态表,0))),"※状态不在【资料】里",IF(N($M32)&gt;N($L32),"※已还本金大于典当金额",IF(AND($I32&lt;&gt;"",$J32&lt;&gt;"",$J32&lt;$I32),"※到期日早于当票日期",IF(AND($H32&lt;&gt;"",COUNTIF($H$4:$H$403,$H32)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L32&lt;&gt;"",$E32=""),"※有金额没写客户","")))))</f>
+        <f>IF($E32="","",IF(AND($B32&lt;&gt;"",ISNA(MATCH($B32,机构表,0))),"※机构不在【资料】里",IF(AND($D32&lt;&gt;"",ISNA(MATCH($D32,状态表,0))),"※状态不在【资料】里",IF(N($M32)&gt;N($L32),"※已还本金大于典当金额",IF(AND($I32&lt;&gt;"",$J32&lt;&gt;"",$J32&lt;$I32),"※到期日早于当票日期",IF(AND($H32&lt;&gt;"",COUNTIF($H$4:$H$403,$H32)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L32&lt;&gt;"",$E32=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -13724,7 +13787,7 @@
       <c r="V33" s="12" t="n"/>
       <c r="W33" s="12" t="n"/>
       <c r="X33" s="18">
-        <f>IF($E33="","",IF(AND($B33&lt;&gt;"",ISNA(MATCH($B33,机构表,0))),"※机构不在【资料】里",IF(AND($D33&lt;&gt;"",ISNA(MATCH($D33,状态表,0))),"※状态不在【资料】里",IF(N($M33)&gt;N($L33),"※已还本金大于典当金额",IF(AND($I33&lt;&gt;"",$J33&lt;&gt;"",$J33&lt;$I33),"※到期日早于当票日期",IF(AND($H33&lt;&gt;"",COUNTIF($H$4:$H$403,$H33)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L33&lt;&gt;"",$E33=""),"※有金额没写客户","")))))</f>
+        <f>IF($E33="","",IF(AND($B33&lt;&gt;"",ISNA(MATCH($B33,机构表,0))),"※机构不在【资料】里",IF(AND($D33&lt;&gt;"",ISNA(MATCH($D33,状态表,0))),"※状态不在【资料】里",IF(N($M33)&gt;N($L33),"※已还本金大于典当金额",IF(AND($I33&lt;&gt;"",$J33&lt;&gt;"",$J33&lt;$I33),"※到期日早于当票日期",IF(AND($H33&lt;&gt;"",COUNTIF($H$4:$H$403,$H33)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L33&lt;&gt;"",$E33=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -13787,7 +13850,7 @@
       <c r="V34" s="12" t="n"/>
       <c r="W34" s="12" t="n"/>
       <c r="X34" s="18">
-        <f>IF($E34="","",IF(AND($B34&lt;&gt;"",ISNA(MATCH($B34,机构表,0))),"※机构不在【资料】里",IF(AND($D34&lt;&gt;"",ISNA(MATCH($D34,状态表,0))),"※状态不在【资料】里",IF(N($M34)&gt;N($L34),"※已还本金大于典当金额",IF(AND($I34&lt;&gt;"",$J34&lt;&gt;"",$J34&lt;$I34),"※到期日早于当票日期",IF(AND($H34&lt;&gt;"",COUNTIF($H$4:$H$403,$H34)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L34&lt;&gt;"",$E34=""),"※有金额没写客户","")))))</f>
+        <f>IF($E34="","",IF(AND($B34&lt;&gt;"",ISNA(MATCH($B34,机构表,0))),"※机构不在【资料】里",IF(AND($D34&lt;&gt;"",ISNA(MATCH($D34,状态表,0))),"※状态不在【资料】里",IF(N($M34)&gt;N($L34),"※已还本金大于典当金额",IF(AND($I34&lt;&gt;"",$J34&lt;&gt;"",$J34&lt;$I34),"※到期日早于当票日期",IF(AND($H34&lt;&gt;"",COUNTIF($H$4:$H$403,$H34)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L34&lt;&gt;"",$E34=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -13850,7 +13913,7 @@
       <c r="V35" s="12" t="n"/>
       <c r="W35" s="12" t="n"/>
       <c r="X35" s="18">
-        <f>IF($E35="","",IF(AND($B35&lt;&gt;"",ISNA(MATCH($B35,机构表,0))),"※机构不在【资料】里",IF(AND($D35&lt;&gt;"",ISNA(MATCH($D35,状态表,0))),"※状态不在【资料】里",IF(N($M35)&gt;N($L35),"※已还本金大于典当金额",IF(AND($I35&lt;&gt;"",$J35&lt;&gt;"",$J35&lt;$I35),"※到期日早于当票日期",IF(AND($H35&lt;&gt;"",COUNTIF($H$4:$H$403,$H35)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L35&lt;&gt;"",$E35=""),"※有金额没写客户","")))))</f>
+        <f>IF($E35="","",IF(AND($B35&lt;&gt;"",ISNA(MATCH($B35,机构表,0))),"※机构不在【资料】里",IF(AND($D35&lt;&gt;"",ISNA(MATCH($D35,状态表,0))),"※状态不在【资料】里",IF(N($M35)&gt;N($L35),"※已还本金大于典当金额",IF(AND($I35&lt;&gt;"",$J35&lt;&gt;"",$J35&lt;$I35),"※到期日早于当票日期",IF(AND($H35&lt;&gt;"",COUNTIF($H$4:$H$403,$H35)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L35&lt;&gt;"",$E35=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -13915,7 +13978,7 @@
       <c r="V36" s="12" t="n"/>
       <c r="W36" s="12" t="n"/>
       <c r="X36" s="18">
-        <f>IF($E36="","",IF(AND($B36&lt;&gt;"",ISNA(MATCH($B36,机构表,0))),"※机构不在【资料】里",IF(AND($D36&lt;&gt;"",ISNA(MATCH($D36,状态表,0))),"※状态不在【资料】里",IF(N($M36)&gt;N($L36),"※已还本金大于典当金额",IF(AND($I36&lt;&gt;"",$J36&lt;&gt;"",$J36&lt;$I36),"※到期日早于当票日期",IF(AND($H36&lt;&gt;"",COUNTIF($H$4:$H$403,$H36)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L36&lt;&gt;"",$E36=""),"※有金额没写客户","")))))</f>
+        <f>IF($E36="","",IF(AND($B36&lt;&gt;"",ISNA(MATCH($B36,机构表,0))),"※机构不在【资料】里",IF(AND($D36&lt;&gt;"",ISNA(MATCH($D36,状态表,0))),"※状态不在【资料】里",IF(N($M36)&gt;N($L36),"※已还本金大于典当金额",IF(AND($I36&lt;&gt;"",$J36&lt;&gt;"",$J36&lt;$I36),"※到期日早于当票日期",IF(AND($H36&lt;&gt;"",COUNTIF($H$4:$H$403,$H36)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L36&lt;&gt;"",$E36=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -13996,7 +14059,7 @@
         </is>
       </c>
       <c r="X37" s="18">
-        <f>IF($E37="","",IF(AND($B37&lt;&gt;"",ISNA(MATCH($B37,机构表,0))),"※机构不在【资料】里",IF(AND($D37&lt;&gt;"",ISNA(MATCH($D37,状态表,0))),"※状态不在【资料】里",IF(N($M37)&gt;N($L37),"※已还本金大于典当金额",IF(AND($I37&lt;&gt;"",$J37&lt;&gt;"",$J37&lt;$I37),"※到期日早于当票日期",IF(AND($H37&lt;&gt;"",COUNTIF($H$4:$H$403,$H37)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L37&lt;&gt;"",$E37=""),"※有金额没写客户","")))))</f>
+        <f>IF($E37="","",IF(AND($B37&lt;&gt;"",ISNA(MATCH($B37,机构表,0))),"※机构不在【资料】里",IF(AND($D37&lt;&gt;"",ISNA(MATCH($D37,状态表,0))),"※状态不在【资料】里",IF(N($M37)&gt;N($L37),"※已还本金大于典当金额",IF(AND($I37&lt;&gt;"",$J37&lt;&gt;"",$J37&lt;$I37),"※到期日早于当票日期",IF(AND($H37&lt;&gt;"",COUNTIF($H$4:$H$403,$H37)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L37&lt;&gt;"",$E37=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -14063,7 +14126,7 @@
         </is>
       </c>
       <c r="X38" s="18">
-        <f>IF($E38="","",IF(AND($B38&lt;&gt;"",ISNA(MATCH($B38,机构表,0))),"※机构不在【资料】里",IF(AND($D38&lt;&gt;"",ISNA(MATCH($D38,状态表,0))),"※状态不在【资料】里",IF(N($M38)&gt;N($L38),"※已还本金大于典当金额",IF(AND($I38&lt;&gt;"",$J38&lt;&gt;"",$J38&lt;$I38),"※到期日早于当票日期",IF(AND($H38&lt;&gt;"",COUNTIF($H$4:$H$403,$H38)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L38&lt;&gt;"",$E38=""),"※有金额没写客户","")))))</f>
+        <f>IF($E38="","",IF(AND($B38&lt;&gt;"",ISNA(MATCH($B38,机构表,0))),"※机构不在【资料】里",IF(AND($D38&lt;&gt;"",ISNA(MATCH($D38,状态表,0))),"※状态不在【资料】里",IF(N($M38)&gt;N($L38),"※已还本金大于典当金额",IF(AND($I38&lt;&gt;"",$J38&lt;&gt;"",$J38&lt;$I38),"※到期日早于当票日期",IF(AND($H38&lt;&gt;"",COUNTIF($H$4:$H$403,$H38)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L38&lt;&gt;"",$E38=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -14138,7 +14201,7 @@
       </c>
       <c r="W39" s="12" t="n"/>
       <c r="X39" s="18">
-        <f>IF($E39="","",IF(AND($B39&lt;&gt;"",ISNA(MATCH($B39,机构表,0))),"※机构不在【资料】里",IF(AND($D39&lt;&gt;"",ISNA(MATCH($D39,状态表,0))),"※状态不在【资料】里",IF(N($M39)&gt;N($L39),"※已还本金大于典当金额",IF(AND($I39&lt;&gt;"",$J39&lt;&gt;"",$J39&lt;$I39),"※到期日早于当票日期",IF(AND($H39&lt;&gt;"",COUNTIF($H$4:$H$403,$H39)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L39&lt;&gt;"",$E39=""),"※有金额没写客户","")))))</f>
+        <f>IF($E39="","",IF(AND($B39&lt;&gt;"",ISNA(MATCH($B39,机构表,0))),"※机构不在【资料】里",IF(AND($D39&lt;&gt;"",ISNA(MATCH($D39,状态表,0))),"※状态不在【资料】里",IF(N($M39)&gt;N($L39),"※已还本金大于典当金额",IF(AND($I39&lt;&gt;"",$J39&lt;&gt;"",$J39&lt;$I39),"※到期日早于当票日期",IF(AND($H39&lt;&gt;"",COUNTIF($H$4:$H$403,$H39)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L39&lt;&gt;"",$E39=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -14203,7 +14266,7 @@
       <c r="V40" s="12" t="n"/>
       <c r="W40" s="12" t="n"/>
       <c r="X40" s="18">
-        <f>IF($E40="","",IF(AND($B40&lt;&gt;"",ISNA(MATCH($B40,机构表,0))),"※机构不在【资料】里",IF(AND($D40&lt;&gt;"",ISNA(MATCH($D40,状态表,0))),"※状态不在【资料】里",IF(N($M40)&gt;N($L40),"※已还本金大于典当金额",IF(AND($I40&lt;&gt;"",$J40&lt;&gt;"",$J40&lt;$I40),"※到期日早于当票日期",IF(AND($H40&lt;&gt;"",COUNTIF($H$4:$H$403,$H40)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L40&lt;&gt;"",$E40=""),"※有金额没写客户","")))))</f>
+        <f>IF($E40="","",IF(AND($B40&lt;&gt;"",ISNA(MATCH($B40,机构表,0))),"※机构不在【资料】里",IF(AND($D40&lt;&gt;"",ISNA(MATCH($D40,状态表,0))),"※状态不在【资料】里",IF(N($M40)&gt;N($L40),"※已还本金大于典当金额",IF(AND($I40&lt;&gt;"",$J40&lt;&gt;"",$J40&lt;$I40),"※到期日早于当票日期",IF(AND($H40&lt;&gt;"",COUNTIF($H$4:$H$403,$H40)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L40&lt;&gt;"",$E40=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -14280,7 +14343,7 @@
       </c>
       <c r="W41" s="12" t="n"/>
       <c r="X41" s="18">
-        <f>IF($E41="","",IF(AND($B41&lt;&gt;"",ISNA(MATCH($B41,机构表,0))),"※机构不在【资料】里",IF(AND($D41&lt;&gt;"",ISNA(MATCH($D41,状态表,0))),"※状态不在【资料】里",IF(N($M41)&gt;N($L41),"※已还本金大于典当金额",IF(AND($I41&lt;&gt;"",$J41&lt;&gt;"",$J41&lt;$I41),"※到期日早于当票日期",IF(AND($H41&lt;&gt;"",COUNTIF($H$4:$H$403,$H41)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L41&lt;&gt;"",$E41=""),"※有金额没写客户","")))))</f>
+        <f>IF($E41="","",IF(AND($B41&lt;&gt;"",ISNA(MATCH($B41,机构表,0))),"※机构不在【资料】里",IF(AND($D41&lt;&gt;"",ISNA(MATCH($D41,状态表,0))),"※状态不在【资料】里",IF(N($M41)&gt;N($L41),"※已还本金大于典当金额",IF(AND($I41&lt;&gt;"",$J41&lt;&gt;"",$J41&lt;$I41),"※到期日早于当票日期",IF(AND($H41&lt;&gt;"",COUNTIF($H$4:$H$403,$H41)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L41&lt;&gt;"",$E41=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -14353,7 +14416,7 @@
       <c r="V42" s="12" t="n"/>
       <c r="W42" s="12" t="n"/>
       <c r="X42" s="18">
-        <f>IF($E42="","",IF(AND($B42&lt;&gt;"",ISNA(MATCH($B42,机构表,0))),"※机构不在【资料】里",IF(AND($D42&lt;&gt;"",ISNA(MATCH($D42,状态表,0))),"※状态不在【资料】里",IF(N($M42)&gt;N($L42),"※已还本金大于典当金额",IF(AND($I42&lt;&gt;"",$J42&lt;&gt;"",$J42&lt;$I42),"※到期日早于当票日期",IF(AND($H42&lt;&gt;"",COUNTIF($H$4:$H$403,$H42)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L42&lt;&gt;"",$E42=""),"※有金额没写客户","")))))</f>
+        <f>IF($E42="","",IF(AND($B42&lt;&gt;"",ISNA(MATCH($B42,机构表,0))),"※机构不在【资料】里",IF(AND($D42&lt;&gt;"",ISNA(MATCH($D42,状态表,0))),"※状态不在【资料】里",IF(N($M42)&gt;N($L42),"※已还本金大于典当金额",IF(AND($I42&lt;&gt;"",$J42&lt;&gt;"",$J42&lt;$I42),"※到期日早于当票日期",IF(AND($H42&lt;&gt;"",COUNTIF($H$4:$H$403,$H42)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L42&lt;&gt;"",$E42=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -14416,7 +14479,7 @@
       <c r="V43" s="12" t="n"/>
       <c r="W43" s="12" t="n"/>
       <c r="X43" s="18">
-        <f>IF($E43="","",IF(AND($B43&lt;&gt;"",ISNA(MATCH($B43,机构表,0))),"※机构不在【资料】里",IF(AND($D43&lt;&gt;"",ISNA(MATCH($D43,状态表,0))),"※状态不在【资料】里",IF(N($M43)&gt;N($L43),"※已还本金大于典当金额",IF(AND($I43&lt;&gt;"",$J43&lt;&gt;"",$J43&lt;$I43),"※到期日早于当票日期",IF(AND($H43&lt;&gt;"",COUNTIF($H$4:$H$403,$H43)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L43&lt;&gt;"",$E43=""),"※有金额没写客户","")))))</f>
+        <f>IF($E43="","",IF(AND($B43&lt;&gt;"",ISNA(MATCH($B43,机构表,0))),"※机构不在【资料】里",IF(AND($D43&lt;&gt;"",ISNA(MATCH($D43,状态表,0))),"※状态不在【资料】里",IF(N($M43)&gt;N($L43),"※已还本金大于典当金额",IF(AND($I43&lt;&gt;"",$J43&lt;&gt;"",$J43&lt;$I43),"※到期日早于当票日期",IF(AND($H43&lt;&gt;"",COUNTIF($H$4:$H$403,$H43)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L43&lt;&gt;"",$E43=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -14479,7 +14542,7 @@
       <c r="V44" s="12" t="n"/>
       <c r="W44" s="12" t="n"/>
       <c r="X44" s="18">
-        <f>IF($E44="","",IF(AND($B44&lt;&gt;"",ISNA(MATCH($B44,机构表,0))),"※机构不在【资料】里",IF(AND($D44&lt;&gt;"",ISNA(MATCH($D44,状态表,0))),"※状态不在【资料】里",IF(N($M44)&gt;N($L44),"※已还本金大于典当金额",IF(AND($I44&lt;&gt;"",$J44&lt;&gt;"",$J44&lt;$I44),"※到期日早于当票日期",IF(AND($H44&lt;&gt;"",COUNTIF($H$4:$H$403,$H44)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L44&lt;&gt;"",$E44=""),"※有金额没写客户","")))))</f>
+        <f>IF($E44="","",IF(AND($B44&lt;&gt;"",ISNA(MATCH($B44,机构表,0))),"※机构不在【资料】里",IF(AND($D44&lt;&gt;"",ISNA(MATCH($D44,状态表,0))),"※状态不在【资料】里",IF(N($M44)&gt;N($L44),"※已还本金大于典当金额",IF(AND($I44&lt;&gt;"",$J44&lt;&gt;"",$J44&lt;$I44),"※到期日早于当票日期",IF(AND($H44&lt;&gt;"",COUNTIF($H$4:$H$403,$H44)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L44&lt;&gt;"",$E44=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -14556,7 +14619,7 @@
       </c>
       <c r="W45" s="12" t="n"/>
       <c r="X45" s="18">
-        <f>IF($E45="","",IF(AND($B45&lt;&gt;"",ISNA(MATCH($B45,机构表,0))),"※机构不在【资料】里",IF(AND($D45&lt;&gt;"",ISNA(MATCH($D45,状态表,0))),"※状态不在【资料】里",IF(N($M45)&gt;N($L45),"※已还本金大于典当金额",IF(AND($I45&lt;&gt;"",$J45&lt;&gt;"",$J45&lt;$I45),"※到期日早于当票日期",IF(AND($H45&lt;&gt;"",COUNTIF($H$4:$H$403,$H45)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L45&lt;&gt;"",$E45=""),"※有金额没写客户","")))))</f>
+        <f>IF($E45="","",IF(AND($B45&lt;&gt;"",ISNA(MATCH($B45,机构表,0))),"※机构不在【资料】里",IF(AND($D45&lt;&gt;"",ISNA(MATCH($D45,状态表,0))),"※状态不在【资料】里",IF(N($M45)&gt;N($L45),"※已还本金大于典当金额",IF(AND($I45&lt;&gt;"",$J45&lt;&gt;"",$J45&lt;$I45),"※到期日早于当票日期",IF(AND($H45&lt;&gt;"",COUNTIF($H$4:$H$403,$H45)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L45&lt;&gt;"",$E45=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -14619,7 +14682,7 @@
       <c r="V46" s="12" t="n"/>
       <c r="W46" s="12" t="n"/>
       <c r="X46" s="18">
-        <f>IF($E46="","",IF(AND($B46&lt;&gt;"",ISNA(MATCH($B46,机构表,0))),"※机构不在【资料】里",IF(AND($D46&lt;&gt;"",ISNA(MATCH($D46,状态表,0))),"※状态不在【资料】里",IF(N($M46)&gt;N($L46),"※已还本金大于典当金额",IF(AND($I46&lt;&gt;"",$J46&lt;&gt;"",$J46&lt;$I46),"※到期日早于当票日期",IF(AND($H46&lt;&gt;"",COUNTIF($H$4:$H$403,$H46)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L46&lt;&gt;"",$E46=""),"※有金额没写客户","")))))</f>
+        <f>IF($E46="","",IF(AND($B46&lt;&gt;"",ISNA(MATCH($B46,机构表,0))),"※机构不在【资料】里",IF(AND($D46&lt;&gt;"",ISNA(MATCH($D46,状态表,0))),"※状态不在【资料】里",IF(N($M46)&gt;N($L46),"※已还本金大于典当金额",IF(AND($I46&lt;&gt;"",$J46&lt;&gt;"",$J46&lt;$I46),"※到期日早于当票日期",IF(AND($H46&lt;&gt;"",COUNTIF($H$4:$H$403,$H46)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L46&lt;&gt;"",$E46=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -14684,7 +14747,7 @@
       <c r="V47" s="12" t="n"/>
       <c r="W47" s="12" t="n"/>
       <c r="X47" s="18">
-        <f>IF($E47="","",IF(AND($B47&lt;&gt;"",ISNA(MATCH($B47,机构表,0))),"※机构不在【资料】里",IF(AND($D47&lt;&gt;"",ISNA(MATCH($D47,状态表,0))),"※状态不在【资料】里",IF(N($M47)&gt;N($L47),"※已还本金大于典当金额",IF(AND($I47&lt;&gt;"",$J47&lt;&gt;"",$J47&lt;$I47),"※到期日早于当票日期",IF(AND($H47&lt;&gt;"",COUNTIF($H$4:$H$403,$H47)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L47&lt;&gt;"",$E47=""),"※有金额没写客户","")))))</f>
+        <f>IF($E47="","",IF(AND($B47&lt;&gt;"",ISNA(MATCH($B47,机构表,0))),"※机构不在【资料】里",IF(AND($D47&lt;&gt;"",ISNA(MATCH($D47,状态表,0))),"※状态不在【资料】里",IF(N($M47)&gt;N($L47),"※已还本金大于典当金额",IF(AND($I47&lt;&gt;"",$J47&lt;&gt;"",$J47&lt;$I47),"※到期日早于当票日期",IF(AND($H47&lt;&gt;"",COUNTIF($H$4:$H$403,$H47)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L47&lt;&gt;"",$E47=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -14749,7 +14812,7 @@
       <c r="V48" s="12" t="n"/>
       <c r="W48" s="12" t="n"/>
       <c r="X48" s="18">
-        <f>IF($E48="","",IF(AND($B48&lt;&gt;"",ISNA(MATCH($B48,机构表,0))),"※机构不在【资料】里",IF(AND($D48&lt;&gt;"",ISNA(MATCH($D48,状态表,0))),"※状态不在【资料】里",IF(N($M48)&gt;N($L48),"※已还本金大于典当金额",IF(AND($I48&lt;&gt;"",$J48&lt;&gt;"",$J48&lt;$I48),"※到期日早于当票日期",IF(AND($H48&lt;&gt;"",COUNTIF($H$4:$H$403,$H48)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L48&lt;&gt;"",$E48=""),"※有金额没写客户","")))))</f>
+        <f>IF($E48="","",IF(AND($B48&lt;&gt;"",ISNA(MATCH($B48,机构表,0))),"※机构不在【资料】里",IF(AND($D48&lt;&gt;"",ISNA(MATCH($D48,状态表,0))),"※状态不在【资料】里",IF(N($M48)&gt;N($L48),"※已还本金大于典当金额",IF(AND($I48&lt;&gt;"",$J48&lt;&gt;"",$J48&lt;$I48),"※到期日早于当票日期",IF(AND($H48&lt;&gt;"",COUNTIF($H$4:$H$403,$H48)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L48&lt;&gt;"",$E48=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -14820,7 +14883,7 @@
       <c r="V49" s="12" t="n"/>
       <c r="W49" s="12" t="n"/>
       <c r="X49" s="18">
-        <f>IF($E49="","",IF(AND($B49&lt;&gt;"",ISNA(MATCH($B49,机构表,0))),"※机构不在【资料】里",IF(AND($D49&lt;&gt;"",ISNA(MATCH($D49,状态表,0))),"※状态不在【资料】里",IF(N($M49)&gt;N($L49),"※已还本金大于典当金额",IF(AND($I49&lt;&gt;"",$J49&lt;&gt;"",$J49&lt;$I49),"※到期日早于当票日期",IF(AND($H49&lt;&gt;"",COUNTIF($H$4:$H$403,$H49)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L49&lt;&gt;"",$E49=""),"※有金额没写客户","")))))</f>
+        <f>IF($E49="","",IF(AND($B49&lt;&gt;"",ISNA(MATCH($B49,机构表,0))),"※机构不在【资料】里",IF(AND($D49&lt;&gt;"",ISNA(MATCH($D49,状态表,0))),"※状态不在【资料】里",IF(N($M49)&gt;N($L49),"※已还本金大于典当金额",IF(AND($I49&lt;&gt;"",$J49&lt;&gt;"",$J49&lt;$I49),"※到期日早于当票日期",IF(AND($H49&lt;&gt;"",COUNTIF($H$4:$H$403,$H49)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L49&lt;&gt;"",$E49=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -14883,7 +14946,7 @@
       <c r="V50" s="12" t="n"/>
       <c r="W50" s="12" t="n"/>
       <c r="X50" s="18">
-        <f>IF($E50="","",IF(AND($B50&lt;&gt;"",ISNA(MATCH($B50,机构表,0))),"※机构不在【资料】里",IF(AND($D50&lt;&gt;"",ISNA(MATCH($D50,状态表,0))),"※状态不在【资料】里",IF(N($M50)&gt;N($L50),"※已还本金大于典当金额",IF(AND($I50&lt;&gt;"",$J50&lt;&gt;"",$J50&lt;$I50),"※到期日早于当票日期",IF(AND($H50&lt;&gt;"",COUNTIF($H$4:$H$403,$H50)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L50&lt;&gt;"",$E50=""),"※有金额没写客户","")))))</f>
+        <f>IF($E50="","",IF(AND($B50&lt;&gt;"",ISNA(MATCH($B50,机构表,0))),"※机构不在【资料】里",IF(AND($D50&lt;&gt;"",ISNA(MATCH($D50,状态表,0))),"※状态不在【资料】里",IF(N($M50)&gt;N($L50),"※已还本金大于典当金额",IF(AND($I50&lt;&gt;"",$J50&lt;&gt;"",$J50&lt;$I50),"※到期日早于当票日期",IF(AND($H50&lt;&gt;"",COUNTIF($H$4:$H$403,$H50)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L50&lt;&gt;"",$E50=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -14960,7 +15023,7 @@
       </c>
       <c r="W51" s="12" t="n"/>
       <c r="X51" s="18">
-        <f>IF($E51="","",IF(AND($B51&lt;&gt;"",ISNA(MATCH($B51,机构表,0))),"※机构不在【资料】里",IF(AND($D51&lt;&gt;"",ISNA(MATCH($D51,状态表,0))),"※状态不在【资料】里",IF(N($M51)&gt;N($L51),"※已还本金大于典当金额",IF(AND($I51&lt;&gt;"",$J51&lt;&gt;"",$J51&lt;$I51),"※到期日早于当票日期",IF(AND($H51&lt;&gt;"",COUNTIF($H$4:$H$403,$H51)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L51&lt;&gt;"",$E51=""),"※有金额没写客户","")))))</f>
+        <f>IF($E51="","",IF(AND($B51&lt;&gt;"",ISNA(MATCH($B51,机构表,0))),"※机构不在【资料】里",IF(AND($D51&lt;&gt;"",ISNA(MATCH($D51,状态表,0))),"※状态不在【资料】里",IF(N($M51)&gt;N($L51),"※已还本金大于典当金额",IF(AND($I51&lt;&gt;"",$J51&lt;&gt;"",$J51&lt;$I51),"※到期日早于当票日期",IF(AND($H51&lt;&gt;"",COUNTIF($H$4:$H$403,$H51)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L51&lt;&gt;"",$E51=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -15033,7 +15096,7 @@
       <c r="V52" s="12" t="n"/>
       <c r="W52" s="12" t="n"/>
       <c r="X52" s="18">
-        <f>IF($E52="","",IF(AND($B52&lt;&gt;"",ISNA(MATCH($B52,机构表,0))),"※机构不在【资料】里",IF(AND($D52&lt;&gt;"",ISNA(MATCH($D52,状态表,0))),"※状态不在【资料】里",IF(N($M52)&gt;N($L52),"※已还本金大于典当金额",IF(AND($I52&lt;&gt;"",$J52&lt;&gt;"",$J52&lt;$I52),"※到期日早于当票日期",IF(AND($H52&lt;&gt;"",COUNTIF($H$4:$H$403,$H52)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L52&lt;&gt;"",$E52=""),"※有金额没写客户","")))))</f>
+        <f>IF($E52="","",IF(AND($B52&lt;&gt;"",ISNA(MATCH($B52,机构表,0))),"※机构不在【资料】里",IF(AND($D52&lt;&gt;"",ISNA(MATCH($D52,状态表,0))),"※状态不在【资料】里",IF(N($M52)&gt;N($L52),"※已还本金大于典当金额",IF(AND($I52&lt;&gt;"",$J52&lt;&gt;"",$J52&lt;$I52),"※到期日早于当票日期",IF(AND($H52&lt;&gt;"",COUNTIF($H$4:$H$403,$H52)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L52&lt;&gt;"",$E52=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -15098,7 +15161,7 @@
       <c r="V53" s="12" t="n"/>
       <c r="W53" s="12" t="n"/>
       <c r="X53" s="18">
-        <f>IF($E53="","",IF(AND($B53&lt;&gt;"",ISNA(MATCH($B53,机构表,0))),"※机构不在【资料】里",IF(AND($D53&lt;&gt;"",ISNA(MATCH($D53,状态表,0))),"※状态不在【资料】里",IF(N($M53)&gt;N($L53),"※已还本金大于典当金额",IF(AND($I53&lt;&gt;"",$J53&lt;&gt;"",$J53&lt;$I53),"※到期日早于当票日期",IF(AND($H53&lt;&gt;"",COUNTIF($H$4:$H$403,$H53)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L53&lt;&gt;"",$E53=""),"※有金额没写客户","")))))</f>
+        <f>IF($E53="","",IF(AND($B53&lt;&gt;"",ISNA(MATCH($B53,机构表,0))),"※机构不在【资料】里",IF(AND($D53&lt;&gt;"",ISNA(MATCH($D53,状态表,0))),"※状态不在【资料】里",IF(N($M53)&gt;N($L53),"※已还本金大于典当金额",IF(AND($I53&lt;&gt;"",$J53&lt;&gt;"",$J53&lt;$I53),"※到期日早于当票日期",IF(AND($H53&lt;&gt;"",COUNTIF($H$4:$H$403,$H53)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L53&lt;&gt;"",$E53=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -15163,7 +15226,7 @@
       <c r="V54" s="12" t="n"/>
       <c r="W54" s="12" t="n"/>
       <c r="X54" s="18">
-        <f>IF($E54="","",IF(AND($B54&lt;&gt;"",ISNA(MATCH($B54,机构表,0))),"※机构不在【资料】里",IF(AND($D54&lt;&gt;"",ISNA(MATCH($D54,状态表,0))),"※状态不在【资料】里",IF(N($M54)&gt;N($L54),"※已还本金大于典当金额",IF(AND($I54&lt;&gt;"",$J54&lt;&gt;"",$J54&lt;$I54),"※到期日早于当票日期",IF(AND($H54&lt;&gt;"",COUNTIF($H$4:$H$403,$H54)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L54&lt;&gt;"",$E54=""),"※有金额没写客户","")))))</f>
+        <f>IF($E54="","",IF(AND($B54&lt;&gt;"",ISNA(MATCH($B54,机构表,0))),"※机构不在【资料】里",IF(AND($D54&lt;&gt;"",ISNA(MATCH($D54,状态表,0))),"※状态不在【资料】里",IF(N($M54)&gt;N($L54),"※已还本金大于典当金额",IF(AND($I54&lt;&gt;"",$J54&lt;&gt;"",$J54&lt;$I54),"※到期日早于当票日期",IF(AND($H54&lt;&gt;"",COUNTIF($H$4:$H$403,$H54)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L54&lt;&gt;"",$E54=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -15226,7 +15289,7 @@
       <c r="V55" s="12" t="n"/>
       <c r="W55" s="12" t="n"/>
       <c r="X55" s="18">
-        <f>IF($E55="","",IF(AND($B55&lt;&gt;"",ISNA(MATCH($B55,机构表,0))),"※机构不在【资料】里",IF(AND($D55&lt;&gt;"",ISNA(MATCH($D55,状态表,0))),"※状态不在【资料】里",IF(N($M55)&gt;N($L55),"※已还本金大于典当金额",IF(AND($I55&lt;&gt;"",$J55&lt;&gt;"",$J55&lt;$I55),"※到期日早于当票日期",IF(AND($H55&lt;&gt;"",COUNTIF($H$4:$H$403,$H55)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L55&lt;&gt;"",$E55=""),"※有金额没写客户","")))))</f>
+        <f>IF($E55="","",IF(AND($B55&lt;&gt;"",ISNA(MATCH($B55,机构表,0))),"※机构不在【资料】里",IF(AND($D55&lt;&gt;"",ISNA(MATCH($D55,状态表,0))),"※状态不在【资料】里",IF(N($M55)&gt;N($L55),"※已还本金大于典当金额",IF(AND($I55&lt;&gt;"",$J55&lt;&gt;"",$J55&lt;$I55),"※到期日早于当票日期",IF(AND($H55&lt;&gt;"",COUNTIF($H$4:$H$403,$H55)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L55&lt;&gt;"",$E55=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -15281,7 +15344,7 @@
       <c r="V56" s="12" t="n"/>
       <c r="W56" s="12" t="n"/>
       <c r="X56" s="18">
-        <f>IF($E56="","",IF(AND($B56&lt;&gt;"",ISNA(MATCH($B56,机构表,0))),"※机构不在【资料】里",IF(AND($D56&lt;&gt;"",ISNA(MATCH($D56,状态表,0))),"※状态不在【资料】里",IF(N($M56)&gt;N($L56),"※已还本金大于典当金额",IF(AND($I56&lt;&gt;"",$J56&lt;&gt;"",$J56&lt;$I56),"※到期日早于当票日期",IF(AND($H56&lt;&gt;"",COUNTIF($H$4:$H$403,$H56)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L56&lt;&gt;"",$E56=""),"※有金额没写客户","")))))</f>
+        <f>IF($E56="","",IF(AND($B56&lt;&gt;"",ISNA(MATCH($B56,机构表,0))),"※机构不在【资料】里",IF(AND($D56&lt;&gt;"",ISNA(MATCH($D56,状态表,0))),"※状态不在【资料】里",IF(N($M56)&gt;N($L56),"※已还本金大于典当金额",IF(AND($I56&lt;&gt;"",$J56&lt;&gt;"",$J56&lt;$I56),"※到期日早于当票日期",IF(AND($H56&lt;&gt;"",COUNTIF($H$4:$H$403,$H56)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L56&lt;&gt;"",$E56=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -15344,7 +15407,7 @@
       <c r="V57" s="12" t="n"/>
       <c r="W57" s="12" t="n"/>
       <c r="X57" s="18">
-        <f>IF($E57="","",IF(AND($B57&lt;&gt;"",ISNA(MATCH($B57,机构表,0))),"※机构不在【资料】里",IF(AND($D57&lt;&gt;"",ISNA(MATCH($D57,状态表,0))),"※状态不在【资料】里",IF(N($M57)&gt;N($L57),"※已还本金大于典当金额",IF(AND($I57&lt;&gt;"",$J57&lt;&gt;"",$J57&lt;$I57),"※到期日早于当票日期",IF(AND($H57&lt;&gt;"",COUNTIF($H$4:$H$403,$H57)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L57&lt;&gt;"",$E57=""),"※有金额没写客户","")))))</f>
+        <f>IF($E57="","",IF(AND($B57&lt;&gt;"",ISNA(MATCH($B57,机构表,0))),"※机构不在【资料】里",IF(AND($D57&lt;&gt;"",ISNA(MATCH($D57,状态表,0))),"※状态不在【资料】里",IF(N($M57)&gt;N($L57),"※已还本金大于典当金额",IF(AND($I57&lt;&gt;"",$J57&lt;&gt;"",$J57&lt;$I57),"※到期日早于当票日期",IF(AND($H57&lt;&gt;"",COUNTIF($H$4:$H$403,$H57)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L57&lt;&gt;"",$E57=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -15399,7 +15462,7 @@
       <c r="V58" s="12" t="n"/>
       <c r="W58" s="12" t="n"/>
       <c r="X58" s="18">
-        <f>IF($E58="","",IF(AND($B58&lt;&gt;"",ISNA(MATCH($B58,机构表,0))),"※机构不在【资料】里",IF(AND($D58&lt;&gt;"",ISNA(MATCH($D58,状态表,0))),"※状态不在【资料】里",IF(N($M58)&gt;N($L58),"※已还本金大于典当金额",IF(AND($I58&lt;&gt;"",$J58&lt;&gt;"",$J58&lt;$I58),"※到期日早于当票日期",IF(AND($H58&lt;&gt;"",COUNTIF($H$4:$H$403,$H58)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L58&lt;&gt;"",$E58=""),"※有金额没写客户","")))))</f>
+        <f>IF($E58="","",IF(AND($B58&lt;&gt;"",ISNA(MATCH($B58,机构表,0))),"※机构不在【资料】里",IF(AND($D58&lt;&gt;"",ISNA(MATCH($D58,状态表,0))),"※状态不在【资料】里",IF(N($M58)&gt;N($L58),"※已还本金大于典当金额",IF(AND($I58&lt;&gt;"",$J58&lt;&gt;"",$J58&lt;$I58),"※到期日早于当票日期",IF(AND($H58&lt;&gt;"",COUNTIF($H$4:$H$403,$H58)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L58&lt;&gt;"",$E58=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -15466,7 +15529,7 @@
       <c r="V59" s="12" t="n"/>
       <c r="W59" s="12" t="n"/>
       <c r="X59" s="18">
-        <f>IF($E59="","",IF(AND($B59&lt;&gt;"",ISNA(MATCH($B59,机构表,0))),"※机构不在【资料】里",IF(AND($D59&lt;&gt;"",ISNA(MATCH($D59,状态表,0))),"※状态不在【资料】里",IF(N($M59)&gt;N($L59),"※已还本金大于典当金额",IF(AND($I59&lt;&gt;"",$J59&lt;&gt;"",$J59&lt;$I59),"※到期日早于当票日期",IF(AND($H59&lt;&gt;"",COUNTIF($H$4:$H$403,$H59)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L59&lt;&gt;"",$E59=""),"※有金额没写客户","")))))</f>
+        <f>IF($E59="","",IF(AND($B59&lt;&gt;"",ISNA(MATCH($B59,机构表,0))),"※机构不在【资料】里",IF(AND($D59&lt;&gt;"",ISNA(MATCH($D59,状态表,0))),"※状态不在【资料】里",IF(N($M59)&gt;N($L59),"※已还本金大于典当金额",IF(AND($I59&lt;&gt;"",$J59&lt;&gt;"",$J59&lt;$I59),"※到期日早于当票日期",IF(AND($H59&lt;&gt;"",COUNTIF($H$4:$H$403,$H59)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L59&lt;&gt;"",$E59=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -15529,7 +15592,7 @@
       <c r="V60" s="12" t="n"/>
       <c r="W60" s="12" t="n"/>
       <c r="X60" s="18">
-        <f>IF($E60="","",IF(AND($B60&lt;&gt;"",ISNA(MATCH($B60,机构表,0))),"※机构不在【资料】里",IF(AND($D60&lt;&gt;"",ISNA(MATCH($D60,状态表,0))),"※状态不在【资料】里",IF(N($M60)&gt;N($L60),"※已还本金大于典当金额",IF(AND($I60&lt;&gt;"",$J60&lt;&gt;"",$J60&lt;$I60),"※到期日早于当票日期",IF(AND($H60&lt;&gt;"",COUNTIF($H$4:$H$403,$H60)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L60&lt;&gt;"",$E60=""),"※有金额没写客户","")))))</f>
+        <f>IF($E60="","",IF(AND($B60&lt;&gt;"",ISNA(MATCH($B60,机构表,0))),"※机构不在【资料】里",IF(AND($D60&lt;&gt;"",ISNA(MATCH($D60,状态表,0))),"※状态不在【资料】里",IF(N($M60)&gt;N($L60),"※已还本金大于典当金额",IF(AND($I60&lt;&gt;"",$J60&lt;&gt;"",$J60&lt;$I60),"※到期日早于当票日期",IF(AND($H60&lt;&gt;"",COUNTIF($H$4:$H$403,$H60)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L60&lt;&gt;"",$E60=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -15592,7 +15655,7 @@
       <c r="V61" s="12" t="n"/>
       <c r="W61" s="12" t="n"/>
       <c r="X61" s="18">
-        <f>IF($E61="","",IF(AND($B61&lt;&gt;"",ISNA(MATCH($B61,机构表,0))),"※机构不在【资料】里",IF(AND($D61&lt;&gt;"",ISNA(MATCH($D61,状态表,0))),"※状态不在【资料】里",IF(N($M61)&gt;N($L61),"※已还本金大于典当金额",IF(AND($I61&lt;&gt;"",$J61&lt;&gt;"",$J61&lt;$I61),"※到期日早于当票日期",IF(AND($H61&lt;&gt;"",COUNTIF($H$4:$H$403,$H61)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L61&lt;&gt;"",$E61=""),"※有金额没写客户","")))))</f>
+        <f>IF($E61="","",IF(AND($B61&lt;&gt;"",ISNA(MATCH($B61,机构表,0))),"※机构不在【资料】里",IF(AND($D61&lt;&gt;"",ISNA(MATCH($D61,状态表,0))),"※状态不在【资料】里",IF(N($M61)&gt;N($L61),"※已还本金大于典当金额",IF(AND($I61&lt;&gt;"",$J61&lt;&gt;"",$J61&lt;$I61),"※到期日早于当票日期",IF(AND($H61&lt;&gt;"",COUNTIF($H$4:$H$403,$H61)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L61&lt;&gt;"",$E61=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -15655,7 +15718,7 @@
       <c r="V62" s="12" t="n"/>
       <c r="W62" s="12" t="n"/>
       <c r="X62" s="18">
-        <f>IF($E62="","",IF(AND($B62&lt;&gt;"",ISNA(MATCH($B62,机构表,0))),"※机构不在【资料】里",IF(AND($D62&lt;&gt;"",ISNA(MATCH($D62,状态表,0))),"※状态不在【资料】里",IF(N($M62)&gt;N($L62),"※已还本金大于典当金额",IF(AND($I62&lt;&gt;"",$J62&lt;&gt;"",$J62&lt;$I62),"※到期日早于当票日期",IF(AND($H62&lt;&gt;"",COUNTIF($H$4:$H$403,$H62)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L62&lt;&gt;"",$E62=""),"※有金额没写客户","")))))</f>
+        <f>IF($E62="","",IF(AND($B62&lt;&gt;"",ISNA(MATCH($B62,机构表,0))),"※机构不在【资料】里",IF(AND($D62&lt;&gt;"",ISNA(MATCH($D62,状态表,0))),"※状态不在【资料】里",IF(N($M62)&gt;N($L62),"※已还本金大于典当金额",IF(AND($I62&lt;&gt;"",$J62&lt;&gt;"",$J62&lt;$I62),"※到期日早于当票日期",IF(AND($H62&lt;&gt;"",COUNTIF($H$4:$H$403,$H62)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L62&lt;&gt;"",$E62=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -15716,7 +15779,7 @@
       <c r="V63" s="12" t="n"/>
       <c r="W63" s="12" t="n"/>
       <c r="X63" s="18">
-        <f>IF($E63="","",IF(AND($B63&lt;&gt;"",ISNA(MATCH($B63,机构表,0))),"※机构不在【资料】里",IF(AND($D63&lt;&gt;"",ISNA(MATCH($D63,状态表,0))),"※状态不在【资料】里",IF(N($M63)&gt;N($L63),"※已还本金大于典当金额",IF(AND($I63&lt;&gt;"",$J63&lt;&gt;"",$J63&lt;$I63),"※到期日早于当票日期",IF(AND($H63&lt;&gt;"",COUNTIF($H$4:$H$403,$H63)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L63&lt;&gt;"",$E63=""),"※有金额没写客户","")))))</f>
+        <f>IF($E63="","",IF(AND($B63&lt;&gt;"",ISNA(MATCH($B63,机构表,0))),"※机构不在【资料】里",IF(AND($D63&lt;&gt;"",ISNA(MATCH($D63,状态表,0))),"※状态不在【资料】里",IF(N($M63)&gt;N($L63),"※已还本金大于典当金额",IF(AND($I63&lt;&gt;"",$J63&lt;&gt;"",$J63&lt;$I63),"※到期日早于当票日期",IF(AND($H63&lt;&gt;"",COUNTIF($H$4:$H$403,$H63)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L63&lt;&gt;"",$E63=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -15779,7 +15842,7 @@
       <c r="V64" s="12" t="n"/>
       <c r="W64" s="12" t="n"/>
       <c r="X64" s="18">
-        <f>IF($E64="","",IF(AND($B64&lt;&gt;"",ISNA(MATCH($B64,机构表,0))),"※机构不在【资料】里",IF(AND($D64&lt;&gt;"",ISNA(MATCH($D64,状态表,0))),"※状态不在【资料】里",IF(N($M64)&gt;N($L64),"※已还本金大于典当金额",IF(AND($I64&lt;&gt;"",$J64&lt;&gt;"",$J64&lt;$I64),"※到期日早于当票日期",IF(AND($H64&lt;&gt;"",COUNTIF($H$4:$H$403,$H64)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L64&lt;&gt;"",$E64=""),"※有金额没写客户","")))))</f>
+        <f>IF($E64="","",IF(AND($B64&lt;&gt;"",ISNA(MATCH($B64,机构表,0))),"※机构不在【资料】里",IF(AND($D64&lt;&gt;"",ISNA(MATCH($D64,状态表,0))),"※状态不在【资料】里",IF(N($M64)&gt;N($L64),"※已还本金大于典当金额",IF(AND($I64&lt;&gt;"",$J64&lt;&gt;"",$J64&lt;$I64),"※到期日早于当票日期",IF(AND($H64&lt;&gt;"",COUNTIF($H$4:$H$403,$H64)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L64&lt;&gt;"",$E64=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -15844,7 +15907,7 @@
       <c r="V65" s="12" t="n"/>
       <c r="W65" s="12" t="n"/>
       <c r="X65" s="18">
-        <f>IF($E65="","",IF(AND($B65&lt;&gt;"",ISNA(MATCH($B65,机构表,0))),"※机构不在【资料】里",IF(AND($D65&lt;&gt;"",ISNA(MATCH($D65,状态表,0))),"※状态不在【资料】里",IF(N($M65)&gt;N($L65),"※已还本金大于典当金额",IF(AND($I65&lt;&gt;"",$J65&lt;&gt;"",$J65&lt;$I65),"※到期日早于当票日期",IF(AND($H65&lt;&gt;"",COUNTIF($H$4:$H$403,$H65)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L65&lt;&gt;"",$E65=""),"※有金额没写客户","")))))</f>
+        <f>IF($E65="","",IF(AND($B65&lt;&gt;"",ISNA(MATCH($B65,机构表,0))),"※机构不在【资料】里",IF(AND($D65&lt;&gt;"",ISNA(MATCH($D65,状态表,0))),"※状态不在【资料】里",IF(N($M65)&gt;N($L65),"※已还本金大于典当金额",IF(AND($I65&lt;&gt;"",$J65&lt;&gt;"",$J65&lt;$I65),"※到期日早于当票日期",IF(AND($H65&lt;&gt;"",COUNTIF($H$4:$H$403,$H65)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L65&lt;&gt;"",$E65=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -15903,7 +15966,7 @@
       <c r="V66" s="12" t="n"/>
       <c r="W66" s="12" t="n"/>
       <c r="X66" s="18">
-        <f>IF($E66="","",IF(AND($B66&lt;&gt;"",ISNA(MATCH($B66,机构表,0))),"※机构不在【资料】里",IF(AND($D66&lt;&gt;"",ISNA(MATCH($D66,状态表,0))),"※状态不在【资料】里",IF(N($M66)&gt;N($L66),"※已还本金大于典当金额",IF(AND($I66&lt;&gt;"",$J66&lt;&gt;"",$J66&lt;$I66),"※到期日早于当票日期",IF(AND($H66&lt;&gt;"",COUNTIF($H$4:$H$403,$H66)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L66&lt;&gt;"",$E66=""),"※有金额没写客户","")))))</f>
+        <f>IF($E66="","",IF(AND($B66&lt;&gt;"",ISNA(MATCH($B66,机构表,0))),"※机构不在【资料】里",IF(AND($D66&lt;&gt;"",ISNA(MATCH($D66,状态表,0))),"※状态不在【资料】里",IF(N($M66)&gt;N($L66),"※已还本金大于典当金额",IF(AND($I66&lt;&gt;"",$J66&lt;&gt;"",$J66&lt;$I66),"※到期日早于当票日期",IF(AND($H66&lt;&gt;"",COUNTIF($H$4:$H$403,$H66)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L66&lt;&gt;"",$E66=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -15980,7 +16043,7 @@
       </c>
       <c r="W67" s="12" t="n"/>
       <c r="X67" s="18">
-        <f>IF($E67="","",IF(AND($B67&lt;&gt;"",ISNA(MATCH($B67,机构表,0))),"※机构不在【资料】里",IF(AND($D67&lt;&gt;"",ISNA(MATCH($D67,状态表,0))),"※状态不在【资料】里",IF(N($M67)&gt;N($L67),"※已还本金大于典当金额",IF(AND($I67&lt;&gt;"",$J67&lt;&gt;"",$J67&lt;$I67),"※到期日早于当票日期",IF(AND($H67&lt;&gt;"",COUNTIF($H$4:$H$403,$H67)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L67&lt;&gt;"",$E67=""),"※有金额没写客户","")))))</f>
+        <f>IF($E67="","",IF(AND($B67&lt;&gt;"",ISNA(MATCH($B67,机构表,0))),"※机构不在【资料】里",IF(AND($D67&lt;&gt;"",ISNA(MATCH($D67,状态表,0))),"※状态不在【资料】里",IF(N($M67)&gt;N($L67),"※已还本金大于典当金额",IF(AND($I67&lt;&gt;"",$J67&lt;&gt;"",$J67&lt;$I67),"※到期日早于当票日期",IF(AND($H67&lt;&gt;"",COUNTIF($H$4:$H$403,$H67)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L67&lt;&gt;"",$E67=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -16045,7 +16108,7 @@
       <c r="V68" s="12" t="n"/>
       <c r="W68" s="12" t="n"/>
       <c r="X68" s="18">
-        <f>IF($E68="","",IF(AND($B68&lt;&gt;"",ISNA(MATCH($B68,机构表,0))),"※机构不在【资料】里",IF(AND($D68&lt;&gt;"",ISNA(MATCH($D68,状态表,0))),"※状态不在【资料】里",IF(N($M68)&gt;N($L68),"※已还本金大于典当金额",IF(AND($I68&lt;&gt;"",$J68&lt;&gt;"",$J68&lt;$I68),"※到期日早于当票日期",IF(AND($H68&lt;&gt;"",COUNTIF($H$4:$H$403,$H68)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L68&lt;&gt;"",$E68=""),"※有金额没写客户","")))))</f>
+        <f>IF($E68="","",IF(AND($B68&lt;&gt;"",ISNA(MATCH($B68,机构表,0))),"※机构不在【资料】里",IF(AND($D68&lt;&gt;"",ISNA(MATCH($D68,状态表,0))),"※状态不在【资料】里",IF(N($M68)&gt;N($L68),"※已还本金大于典当金额",IF(AND($I68&lt;&gt;"",$J68&lt;&gt;"",$J68&lt;$I68),"※到期日早于当票日期",IF(AND($H68&lt;&gt;"",COUNTIF($H$4:$H$403,$H68)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L68&lt;&gt;"",$E68=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -16108,7 +16171,7 @@
         </is>
       </c>
       <c r="X69" s="18">
-        <f>IF($E69="","",IF(AND($B69&lt;&gt;"",ISNA(MATCH($B69,机构表,0))),"※机构不在【资料】里",IF(AND($D69&lt;&gt;"",ISNA(MATCH($D69,状态表,0))),"※状态不在【资料】里",IF(N($M69)&gt;N($L69),"※已还本金大于典当金额",IF(AND($I69&lt;&gt;"",$J69&lt;&gt;"",$J69&lt;$I69),"※到期日早于当票日期",IF(AND($H69&lt;&gt;"",COUNTIF($H$4:$H$403,$H69)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L69&lt;&gt;"",$E69=""),"※有金额没写客户","")))))</f>
+        <f>IF($E69="","",IF(AND($B69&lt;&gt;"",ISNA(MATCH($B69,机构表,0))),"※机构不在【资料】里",IF(AND($D69&lt;&gt;"",ISNA(MATCH($D69,状态表,0))),"※状态不在【资料】里",IF(N($M69)&gt;N($L69),"※已还本金大于典当金额",IF(AND($I69&lt;&gt;"",$J69&lt;&gt;"",$J69&lt;$I69),"※到期日早于当票日期",IF(AND($H69&lt;&gt;"",COUNTIF($H$4:$H$403,$H69)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L69&lt;&gt;"",$E69=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -16181,7 +16244,7 @@
       <c r="V70" s="12" t="n"/>
       <c r="W70" s="12" t="n"/>
       <c r="X70" s="18">
-        <f>IF($E70="","",IF(AND($B70&lt;&gt;"",ISNA(MATCH($B70,机构表,0))),"※机构不在【资料】里",IF(AND($D70&lt;&gt;"",ISNA(MATCH($D70,状态表,0))),"※状态不在【资料】里",IF(N($M70)&gt;N($L70),"※已还本金大于典当金额",IF(AND($I70&lt;&gt;"",$J70&lt;&gt;"",$J70&lt;$I70),"※到期日早于当票日期",IF(AND($H70&lt;&gt;"",COUNTIF($H$4:$H$403,$H70)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L70&lt;&gt;"",$E70=""),"※有金额没写客户","")))))</f>
+        <f>IF($E70="","",IF(AND($B70&lt;&gt;"",ISNA(MATCH($B70,机构表,0))),"※机构不在【资料】里",IF(AND($D70&lt;&gt;"",ISNA(MATCH($D70,状态表,0))),"※状态不在【资料】里",IF(N($M70)&gt;N($L70),"※已还本金大于典当金额",IF(AND($I70&lt;&gt;"",$J70&lt;&gt;"",$J70&lt;$I70),"※到期日早于当票日期",IF(AND($H70&lt;&gt;"",COUNTIF($H$4:$H$403,$H70)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L70&lt;&gt;"",$E70=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -16246,7 +16309,7 @@
       <c r="V71" s="12" t="n"/>
       <c r="W71" s="12" t="n"/>
       <c r="X71" s="18">
-        <f>IF($E71="","",IF(AND($B71&lt;&gt;"",ISNA(MATCH($B71,机构表,0))),"※机构不在【资料】里",IF(AND($D71&lt;&gt;"",ISNA(MATCH($D71,状态表,0))),"※状态不在【资料】里",IF(N($M71)&gt;N($L71),"※已还本金大于典当金额",IF(AND($I71&lt;&gt;"",$J71&lt;&gt;"",$J71&lt;$I71),"※到期日早于当票日期",IF(AND($H71&lt;&gt;"",COUNTIF($H$4:$H$403,$H71)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L71&lt;&gt;"",$E71=""),"※有金额没写客户","")))))</f>
+        <f>IF($E71="","",IF(AND($B71&lt;&gt;"",ISNA(MATCH($B71,机构表,0))),"※机构不在【资料】里",IF(AND($D71&lt;&gt;"",ISNA(MATCH($D71,状态表,0))),"※状态不在【资料】里",IF(N($M71)&gt;N($L71),"※已还本金大于典当金额",IF(AND($I71&lt;&gt;"",$J71&lt;&gt;"",$J71&lt;$I71),"※到期日早于当票日期",IF(AND($H71&lt;&gt;"",COUNTIF($H$4:$H$403,$H71)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L71&lt;&gt;"",$E71=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -16321,7 +16384,7 @@
       </c>
       <c r="W72" s="12" t="n"/>
       <c r="X72" s="18">
-        <f>IF($E72="","",IF(AND($B72&lt;&gt;"",ISNA(MATCH($B72,机构表,0))),"※机构不在【资料】里",IF(AND($D72&lt;&gt;"",ISNA(MATCH($D72,状态表,0))),"※状态不在【资料】里",IF(N($M72)&gt;N($L72),"※已还本金大于典当金额",IF(AND($I72&lt;&gt;"",$J72&lt;&gt;"",$J72&lt;$I72),"※到期日早于当票日期",IF(AND($H72&lt;&gt;"",COUNTIF($H$4:$H$403,$H72)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L72&lt;&gt;"",$E72=""),"※有金额没写客户","")))))</f>
+        <f>IF($E72="","",IF(AND($B72&lt;&gt;"",ISNA(MATCH($B72,机构表,0))),"※机构不在【资料】里",IF(AND($D72&lt;&gt;"",ISNA(MATCH($D72,状态表,0))),"※状态不在【资料】里",IF(N($M72)&gt;N($L72),"※已还本金大于典当金额",IF(AND($I72&lt;&gt;"",$J72&lt;&gt;"",$J72&lt;$I72),"※到期日早于当票日期",IF(AND($H72&lt;&gt;"",COUNTIF($H$4:$H$403,$H72)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L72&lt;&gt;"",$E72=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -16392,7 +16455,7 @@
       <c r="V73" s="12" t="n"/>
       <c r="W73" s="12" t="n"/>
       <c r="X73" s="18">
-        <f>IF($E73="","",IF(AND($B73&lt;&gt;"",ISNA(MATCH($B73,机构表,0))),"※机构不在【资料】里",IF(AND($D73&lt;&gt;"",ISNA(MATCH($D73,状态表,0))),"※状态不在【资料】里",IF(N($M73)&gt;N($L73),"※已还本金大于典当金额",IF(AND($I73&lt;&gt;"",$J73&lt;&gt;"",$J73&lt;$I73),"※到期日早于当票日期",IF(AND($H73&lt;&gt;"",COUNTIF($H$4:$H$403,$H73)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L73&lt;&gt;"",$E73=""),"※有金额没写客户","")))))</f>
+        <f>IF($E73="","",IF(AND($B73&lt;&gt;"",ISNA(MATCH($B73,机构表,0))),"※机构不在【资料】里",IF(AND($D73&lt;&gt;"",ISNA(MATCH($D73,状态表,0))),"※状态不在【资料】里",IF(N($M73)&gt;N($L73),"※已还本金大于典当金额",IF(AND($I73&lt;&gt;"",$J73&lt;&gt;"",$J73&lt;$I73),"※到期日早于当票日期",IF(AND($H73&lt;&gt;"",COUNTIF($H$4:$H$403,$H73)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L73&lt;&gt;"",$E73=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -16457,7 +16520,7 @@
       <c r="V74" s="12" t="n"/>
       <c r="W74" s="12" t="n"/>
       <c r="X74" s="18">
-        <f>IF($E74="","",IF(AND($B74&lt;&gt;"",ISNA(MATCH($B74,机构表,0))),"※机构不在【资料】里",IF(AND($D74&lt;&gt;"",ISNA(MATCH($D74,状态表,0))),"※状态不在【资料】里",IF(N($M74)&gt;N($L74),"※已还本金大于典当金额",IF(AND($I74&lt;&gt;"",$J74&lt;&gt;"",$J74&lt;$I74),"※到期日早于当票日期",IF(AND($H74&lt;&gt;"",COUNTIF($H$4:$H$403,$H74)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L74&lt;&gt;"",$E74=""),"※有金额没写客户","")))))</f>
+        <f>IF($E74="","",IF(AND($B74&lt;&gt;"",ISNA(MATCH($B74,机构表,0))),"※机构不在【资料】里",IF(AND($D74&lt;&gt;"",ISNA(MATCH($D74,状态表,0))),"※状态不在【资料】里",IF(N($M74)&gt;N($L74),"※已还本金大于典当金额",IF(AND($I74&lt;&gt;"",$J74&lt;&gt;"",$J74&lt;$I74),"※到期日早于当票日期",IF(AND($H74&lt;&gt;"",COUNTIF($H$4:$H$403,$H74)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L74&lt;&gt;"",$E74=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -16520,7 +16583,7 @@
       <c r="V75" s="12" t="n"/>
       <c r="W75" s="12" t="n"/>
       <c r="X75" s="18">
-        <f>IF($E75="","",IF(AND($B75&lt;&gt;"",ISNA(MATCH($B75,机构表,0))),"※机构不在【资料】里",IF(AND($D75&lt;&gt;"",ISNA(MATCH($D75,状态表,0))),"※状态不在【资料】里",IF(N($M75)&gt;N($L75),"※已还本金大于典当金额",IF(AND($I75&lt;&gt;"",$J75&lt;&gt;"",$J75&lt;$I75),"※到期日早于当票日期",IF(AND($H75&lt;&gt;"",COUNTIF($H$4:$H$403,$H75)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L75&lt;&gt;"",$E75=""),"※有金额没写客户","")))))</f>
+        <f>IF($E75="","",IF(AND($B75&lt;&gt;"",ISNA(MATCH($B75,机构表,0))),"※机构不在【资料】里",IF(AND($D75&lt;&gt;"",ISNA(MATCH($D75,状态表,0))),"※状态不在【资料】里",IF(N($M75)&gt;N($L75),"※已还本金大于典当金额",IF(AND($I75&lt;&gt;"",$J75&lt;&gt;"",$J75&lt;$I75),"※到期日早于当票日期",IF(AND($H75&lt;&gt;"",COUNTIF($H$4:$H$403,$H75)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L75&lt;&gt;"",$E75=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -16583,7 +16646,7 @@
       <c r="V76" s="12" t="n"/>
       <c r="W76" s="12" t="n"/>
       <c r="X76" s="18">
-        <f>IF($E76="","",IF(AND($B76&lt;&gt;"",ISNA(MATCH($B76,机构表,0))),"※机构不在【资料】里",IF(AND($D76&lt;&gt;"",ISNA(MATCH($D76,状态表,0))),"※状态不在【资料】里",IF(N($M76)&gt;N($L76),"※已还本金大于典当金额",IF(AND($I76&lt;&gt;"",$J76&lt;&gt;"",$J76&lt;$I76),"※到期日早于当票日期",IF(AND($H76&lt;&gt;"",COUNTIF($H$4:$H$403,$H76)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L76&lt;&gt;"",$E76=""),"※有金额没写客户","")))))</f>
+        <f>IF($E76="","",IF(AND($B76&lt;&gt;"",ISNA(MATCH($B76,机构表,0))),"※机构不在【资料】里",IF(AND($D76&lt;&gt;"",ISNA(MATCH($D76,状态表,0))),"※状态不在【资料】里",IF(N($M76)&gt;N($L76),"※已还本金大于典当金额",IF(AND($I76&lt;&gt;"",$J76&lt;&gt;"",$J76&lt;$I76),"※到期日早于当票日期",IF(AND($H76&lt;&gt;"",COUNTIF($H$4:$H$403,$H76)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L76&lt;&gt;"",$E76=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -16646,7 +16709,7 @@
       <c r="V77" s="12" t="n"/>
       <c r="W77" s="12" t="n"/>
       <c r="X77" s="18">
-        <f>IF($E77="","",IF(AND($B77&lt;&gt;"",ISNA(MATCH($B77,机构表,0))),"※机构不在【资料】里",IF(AND($D77&lt;&gt;"",ISNA(MATCH($D77,状态表,0))),"※状态不在【资料】里",IF(N($M77)&gt;N($L77),"※已还本金大于典当金额",IF(AND($I77&lt;&gt;"",$J77&lt;&gt;"",$J77&lt;$I77),"※到期日早于当票日期",IF(AND($H77&lt;&gt;"",COUNTIF($H$4:$H$403,$H77)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L77&lt;&gt;"",$E77=""),"※有金额没写客户","")))))</f>
+        <f>IF($E77="","",IF(AND($B77&lt;&gt;"",ISNA(MATCH($B77,机构表,0))),"※机构不在【资料】里",IF(AND($D77&lt;&gt;"",ISNA(MATCH($D77,状态表,0))),"※状态不在【资料】里",IF(N($M77)&gt;N($L77),"※已还本金大于典当金额",IF(AND($I77&lt;&gt;"",$J77&lt;&gt;"",$J77&lt;$I77),"※到期日早于当票日期",IF(AND($H77&lt;&gt;"",COUNTIF($H$4:$H$403,$H77)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L77&lt;&gt;"",$E77=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -16709,7 +16772,7 @@
       <c r="V78" s="12" t="n"/>
       <c r="W78" s="12" t="n"/>
       <c r="X78" s="18">
-        <f>IF($E78="","",IF(AND($B78&lt;&gt;"",ISNA(MATCH($B78,机构表,0))),"※机构不在【资料】里",IF(AND($D78&lt;&gt;"",ISNA(MATCH($D78,状态表,0))),"※状态不在【资料】里",IF(N($M78)&gt;N($L78),"※已还本金大于典当金额",IF(AND($I78&lt;&gt;"",$J78&lt;&gt;"",$J78&lt;$I78),"※到期日早于当票日期",IF(AND($H78&lt;&gt;"",COUNTIF($H$4:$H$403,$H78)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L78&lt;&gt;"",$E78=""),"※有金额没写客户","")))))</f>
+        <f>IF($E78="","",IF(AND($B78&lt;&gt;"",ISNA(MATCH($B78,机构表,0))),"※机构不在【资料】里",IF(AND($D78&lt;&gt;"",ISNA(MATCH($D78,状态表,0))),"※状态不在【资料】里",IF(N($M78)&gt;N($L78),"※已还本金大于典当金额",IF(AND($I78&lt;&gt;"",$J78&lt;&gt;"",$J78&lt;$I78),"※到期日早于当票日期",IF(AND($H78&lt;&gt;"",COUNTIF($H$4:$H$403,$H78)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L78&lt;&gt;"",$E78=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -16772,7 +16835,7 @@
       <c r="V79" s="12" t="n"/>
       <c r="W79" s="12" t="n"/>
       <c r="X79" s="18">
-        <f>IF($E79="","",IF(AND($B79&lt;&gt;"",ISNA(MATCH($B79,机构表,0))),"※机构不在【资料】里",IF(AND($D79&lt;&gt;"",ISNA(MATCH($D79,状态表,0))),"※状态不在【资料】里",IF(N($M79)&gt;N($L79),"※已还本金大于典当金额",IF(AND($I79&lt;&gt;"",$J79&lt;&gt;"",$J79&lt;$I79),"※到期日早于当票日期",IF(AND($H79&lt;&gt;"",COUNTIF($H$4:$H$403,$H79)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L79&lt;&gt;"",$E79=""),"※有金额没写客户","")))))</f>
+        <f>IF($E79="","",IF(AND($B79&lt;&gt;"",ISNA(MATCH($B79,机构表,0))),"※机构不在【资料】里",IF(AND($D79&lt;&gt;"",ISNA(MATCH($D79,状态表,0))),"※状态不在【资料】里",IF(N($M79)&gt;N($L79),"※已还本金大于典当金额",IF(AND($I79&lt;&gt;"",$J79&lt;&gt;"",$J79&lt;$I79),"※到期日早于当票日期",IF(AND($H79&lt;&gt;"",COUNTIF($H$4:$H$403,$H79)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L79&lt;&gt;"",$E79=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -16835,7 +16898,7 @@
       <c r="V80" s="12" t="n"/>
       <c r="W80" s="12" t="n"/>
       <c r="X80" s="18">
-        <f>IF($E80="","",IF(AND($B80&lt;&gt;"",ISNA(MATCH($B80,机构表,0))),"※机构不在【资料】里",IF(AND($D80&lt;&gt;"",ISNA(MATCH($D80,状态表,0))),"※状态不在【资料】里",IF(N($M80)&gt;N($L80),"※已还本金大于典当金额",IF(AND($I80&lt;&gt;"",$J80&lt;&gt;"",$J80&lt;$I80),"※到期日早于当票日期",IF(AND($H80&lt;&gt;"",COUNTIF($H$4:$H$403,$H80)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L80&lt;&gt;"",$E80=""),"※有金额没写客户","")))))</f>
+        <f>IF($E80="","",IF(AND($B80&lt;&gt;"",ISNA(MATCH($B80,机构表,0))),"※机构不在【资料】里",IF(AND($D80&lt;&gt;"",ISNA(MATCH($D80,状态表,0))),"※状态不在【资料】里",IF(N($M80)&gt;N($L80),"※已还本金大于典当金额",IF(AND($I80&lt;&gt;"",$J80&lt;&gt;"",$J80&lt;$I80),"※到期日早于当票日期",IF(AND($H80&lt;&gt;"",COUNTIF($H$4:$H$403,$H80)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L80&lt;&gt;"",$E80=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -16898,7 +16961,7 @@
       <c r="V81" s="12" t="n"/>
       <c r="W81" s="12" t="n"/>
       <c r="X81" s="18">
-        <f>IF($E81="","",IF(AND($B81&lt;&gt;"",ISNA(MATCH($B81,机构表,0))),"※机构不在【资料】里",IF(AND($D81&lt;&gt;"",ISNA(MATCH($D81,状态表,0))),"※状态不在【资料】里",IF(N($M81)&gt;N($L81),"※已还本金大于典当金额",IF(AND($I81&lt;&gt;"",$J81&lt;&gt;"",$J81&lt;$I81),"※到期日早于当票日期",IF(AND($H81&lt;&gt;"",COUNTIF($H$4:$H$403,$H81)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L81&lt;&gt;"",$E81=""),"※有金额没写客户","")))))</f>
+        <f>IF($E81="","",IF(AND($B81&lt;&gt;"",ISNA(MATCH($B81,机构表,0))),"※机构不在【资料】里",IF(AND($D81&lt;&gt;"",ISNA(MATCH($D81,状态表,0))),"※状态不在【资料】里",IF(N($M81)&gt;N($L81),"※已还本金大于典当金额",IF(AND($I81&lt;&gt;"",$J81&lt;&gt;"",$J81&lt;$I81),"※到期日早于当票日期",IF(AND($H81&lt;&gt;"",COUNTIF($H$4:$H$403,$H81)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L81&lt;&gt;"",$E81=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -16961,7 +17024,7 @@
       <c r="V82" s="12" t="n"/>
       <c r="W82" s="12" t="n"/>
       <c r="X82" s="18">
-        <f>IF($E82="","",IF(AND($B82&lt;&gt;"",ISNA(MATCH($B82,机构表,0))),"※机构不在【资料】里",IF(AND($D82&lt;&gt;"",ISNA(MATCH($D82,状态表,0))),"※状态不在【资料】里",IF(N($M82)&gt;N($L82),"※已还本金大于典当金额",IF(AND($I82&lt;&gt;"",$J82&lt;&gt;"",$J82&lt;$I82),"※到期日早于当票日期",IF(AND($H82&lt;&gt;"",COUNTIF($H$4:$H$403,$H82)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L82&lt;&gt;"",$E82=""),"※有金额没写客户","")))))</f>
+        <f>IF($E82="","",IF(AND($B82&lt;&gt;"",ISNA(MATCH($B82,机构表,0))),"※机构不在【资料】里",IF(AND($D82&lt;&gt;"",ISNA(MATCH($D82,状态表,0))),"※状态不在【资料】里",IF(N($M82)&gt;N($L82),"※已还本金大于典当金额",IF(AND($I82&lt;&gt;"",$J82&lt;&gt;"",$J82&lt;$I82),"※到期日早于当票日期",IF(AND($H82&lt;&gt;"",COUNTIF($H$4:$H$403,$H82)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L82&lt;&gt;"",$E82=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -17024,7 +17087,7 @@
       <c r="V83" s="12" t="n"/>
       <c r="W83" s="12" t="n"/>
       <c r="X83" s="18">
-        <f>IF($E83="","",IF(AND($B83&lt;&gt;"",ISNA(MATCH($B83,机构表,0))),"※机构不在【资料】里",IF(AND($D83&lt;&gt;"",ISNA(MATCH($D83,状态表,0))),"※状态不在【资料】里",IF(N($M83)&gt;N($L83),"※已还本金大于典当金额",IF(AND($I83&lt;&gt;"",$J83&lt;&gt;"",$J83&lt;$I83),"※到期日早于当票日期",IF(AND($H83&lt;&gt;"",COUNTIF($H$4:$H$403,$H83)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L83&lt;&gt;"",$E83=""),"※有金额没写客户","")))))</f>
+        <f>IF($E83="","",IF(AND($B83&lt;&gt;"",ISNA(MATCH($B83,机构表,0))),"※机构不在【资料】里",IF(AND($D83&lt;&gt;"",ISNA(MATCH($D83,状态表,0))),"※状态不在【资料】里",IF(N($M83)&gt;N($L83),"※已还本金大于典当金额",IF(AND($I83&lt;&gt;"",$J83&lt;&gt;"",$J83&lt;$I83),"※到期日早于当票日期",IF(AND($H83&lt;&gt;"",COUNTIF($H$4:$H$403,$H83)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L83&lt;&gt;"",$E83=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -17087,7 +17150,7 @@
       <c r="V84" s="12" t="n"/>
       <c r="W84" s="12" t="n"/>
       <c r="X84" s="18">
-        <f>IF($E84="","",IF(AND($B84&lt;&gt;"",ISNA(MATCH($B84,机构表,0))),"※机构不在【资料】里",IF(AND($D84&lt;&gt;"",ISNA(MATCH($D84,状态表,0))),"※状态不在【资料】里",IF(N($M84)&gt;N($L84),"※已还本金大于典当金额",IF(AND($I84&lt;&gt;"",$J84&lt;&gt;"",$J84&lt;$I84),"※到期日早于当票日期",IF(AND($H84&lt;&gt;"",COUNTIF($H$4:$H$403,$H84)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L84&lt;&gt;"",$E84=""),"※有金额没写客户","")))))</f>
+        <f>IF($E84="","",IF(AND($B84&lt;&gt;"",ISNA(MATCH($B84,机构表,0))),"※机构不在【资料】里",IF(AND($D84&lt;&gt;"",ISNA(MATCH($D84,状态表,0))),"※状态不在【资料】里",IF(N($M84)&gt;N($L84),"※已还本金大于典当金额",IF(AND($I84&lt;&gt;"",$J84&lt;&gt;"",$J84&lt;$I84),"※到期日早于当票日期",IF(AND($H84&lt;&gt;"",COUNTIF($H$4:$H$403,$H84)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L84&lt;&gt;"",$E84=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -17152,7 +17215,7 @@
       <c r="V85" s="12" t="n"/>
       <c r="W85" s="12" t="n"/>
       <c r="X85" s="18">
-        <f>IF($E85="","",IF(AND($B85&lt;&gt;"",ISNA(MATCH($B85,机构表,0))),"※机构不在【资料】里",IF(AND($D85&lt;&gt;"",ISNA(MATCH($D85,状态表,0))),"※状态不在【资料】里",IF(N($M85)&gt;N($L85),"※已还本金大于典当金额",IF(AND($I85&lt;&gt;"",$J85&lt;&gt;"",$J85&lt;$I85),"※到期日早于当票日期",IF(AND($H85&lt;&gt;"",COUNTIF($H$4:$H$403,$H85)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L85&lt;&gt;"",$E85=""),"※有金额没写客户","")))))</f>
+        <f>IF($E85="","",IF(AND($B85&lt;&gt;"",ISNA(MATCH($B85,机构表,0))),"※机构不在【资料】里",IF(AND($D85&lt;&gt;"",ISNA(MATCH($D85,状态表,0))),"※状态不在【资料】里",IF(N($M85)&gt;N($L85),"※已还本金大于典当金额",IF(AND($I85&lt;&gt;"",$J85&lt;&gt;"",$J85&lt;$I85),"※到期日早于当票日期",IF(AND($H85&lt;&gt;"",COUNTIF($H$4:$H$403,$H85)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L85&lt;&gt;"",$E85=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -17223,7 +17286,7 @@
       <c r="V86" s="12" t="n"/>
       <c r="W86" s="12" t="n"/>
       <c r="X86" s="18">
-        <f>IF($E86="","",IF(AND($B86&lt;&gt;"",ISNA(MATCH($B86,机构表,0))),"※机构不在【资料】里",IF(AND($D86&lt;&gt;"",ISNA(MATCH($D86,状态表,0))),"※状态不在【资料】里",IF(N($M86)&gt;N($L86),"※已还本金大于典当金额",IF(AND($I86&lt;&gt;"",$J86&lt;&gt;"",$J86&lt;$I86),"※到期日早于当票日期",IF(AND($H86&lt;&gt;"",COUNTIF($H$4:$H$403,$H86)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L86&lt;&gt;"",$E86=""),"※有金额没写客户","")))))</f>
+        <f>IF($E86="","",IF(AND($B86&lt;&gt;"",ISNA(MATCH($B86,机构表,0))),"※机构不在【资料】里",IF(AND($D86&lt;&gt;"",ISNA(MATCH($D86,状态表,0))),"※状态不在【资料】里",IF(N($M86)&gt;N($L86),"※已还本金大于典当金额",IF(AND($I86&lt;&gt;"",$J86&lt;&gt;"",$J86&lt;$I86),"※到期日早于当票日期",IF(AND($H86&lt;&gt;"",COUNTIF($H$4:$H$403,$H86)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L86&lt;&gt;"",$E86=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -17296,7 +17359,7 @@
       </c>
       <c r="W87" s="12" t="n"/>
       <c r="X87" s="18">
-        <f>IF($E87="","",IF(AND($B87&lt;&gt;"",ISNA(MATCH($B87,机构表,0))),"※机构不在【资料】里",IF(AND($D87&lt;&gt;"",ISNA(MATCH($D87,状态表,0))),"※状态不在【资料】里",IF(N($M87)&gt;N($L87),"※已还本金大于典当金额",IF(AND($I87&lt;&gt;"",$J87&lt;&gt;"",$J87&lt;$I87),"※到期日早于当票日期",IF(AND($H87&lt;&gt;"",COUNTIF($H$4:$H$403,$H87)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L87&lt;&gt;"",$E87=""),"※有金额没写客户","")))))</f>
+        <f>IF($E87="","",IF(AND($B87&lt;&gt;"",ISNA(MATCH($B87,机构表,0))),"※机构不在【资料】里",IF(AND($D87&lt;&gt;"",ISNA(MATCH($D87,状态表,0))),"※状态不在【资料】里",IF(N($M87)&gt;N($L87),"※已还本金大于典当金额",IF(AND($I87&lt;&gt;"",$J87&lt;&gt;"",$J87&lt;$I87),"※到期日早于当票日期",IF(AND($H87&lt;&gt;"",COUNTIF($H$4:$H$403,$H87)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L87&lt;&gt;"",$E87=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -17361,7 +17424,7 @@
       <c r="V88" s="12" t="n"/>
       <c r="W88" s="12" t="n"/>
       <c r="X88" s="18">
-        <f>IF($E88="","",IF(AND($B88&lt;&gt;"",ISNA(MATCH($B88,机构表,0))),"※机构不在【资料】里",IF(AND($D88&lt;&gt;"",ISNA(MATCH($D88,状态表,0))),"※状态不在【资料】里",IF(N($M88)&gt;N($L88),"※已还本金大于典当金额",IF(AND($I88&lt;&gt;"",$J88&lt;&gt;"",$J88&lt;$I88),"※到期日早于当票日期",IF(AND($H88&lt;&gt;"",COUNTIF($H$4:$H$403,$H88)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L88&lt;&gt;"",$E88=""),"※有金额没写客户","")))))</f>
+        <f>IF($E88="","",IF(AND($B88&lt;&gt;"",ISNA(MATCH($B88,机构表,0))),"※机构不在【资料】里",IF(AND($D88&lt;&gt;"",ISNA(MATCH($D88,状态表,0))),"※状态不在【资料】里",IF(N($M88)&gt;N($L88),"※已还本金大于典当金额",IF(AND($I88&lt;&gt;"",$J88&lt;&gt;"",$J88&lt;$I88),"※到期日早于当票日期",IF(AND($H88&lt;&gt;"",COUNTIF($H$4:$H$403,$H88)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L88&lt;&gt;"",$E88=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -17418,7 +17481,7 @@
       <c r="V89" s="12" t="n"/>
       <c r="W89" s="12" t="n"/>
       <c r="X89" s="18">
-        <f>IF($E89="","",IF(AND($B89&lt;&gt;"",ISNA(MATCH($B89,机构表,0))),"※机构不在【资料】里",IF(AND($D89&lt;&gt;"",ISNA(MATCH($D89,状态表,0))),"※状态不在【资料】里",IF(N($M89)&gt;N($L89),"※已还本金大于典当金额",IF(AND($I89&lt;&gt;"",$J89&lt;&gt;"",$J89&lt;$I89),"※到期日早于当票日期",IF(AND($H89&lt;&gt;"",COUNTIF($H$4:$H$403,$H89)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L89&lt;&gt;"",$E89=""),"※有金额没写客户","")))))</f>
+        <f>IF($E89="","",IF(AND($B89&lt;&gt;"",ISNA(MATCH($B89,机构表,0))),"※机构不在【资料】里",IF(AND($D89&lt;&gt;"",ISNA(MATCH($D89,状态表,0))),"※状态不在【资料】里",IF(N($M89)&gt;N($L89),"※已还本金大于典当金额",IF(AND($I89&lt;&gt;"",$J89&lt;&gt;"",$J89&lt;$I89),"※到期日早于当票日期",IF(AND($H89&lt;&gt;"",COUNTIF($H$4:$H$403,$H89)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L89&lt;&gt;"",$E89=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -17473,7 +17536,7 @@
       <c r="V90" s="12" t="n"/>
       <c r="W90" s="12" t="n"/>
       <c r="X90" s="18">
-        <f>IF($E90="","",IF(AND($B90&lt;&gt;"",ISNA(MATCH($B90,机构表,0))),"※机构不在【资料】里",IF(AND($D90&lt;&gt;"",ISNA(MATCH($D90,状态表,0))),"※状态不在【资料】里",IF(N($M90)&gt;N($L90),"※已还本金大于典当金额",IF(AND($I90&lt;&gt;"",$J90&lt;&gt;"",$J90&lt;$I90),"※到期日早于当票日期",IF(AND($H90&lt;&gt;"",COUNTIF($H$4:$H$403,$H90)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L90&lt;&gt;"",$E90=""),"※有金额没写客户","")))))</f>
+        <f>IF($E90="","",IF(AND($B90&lt;&gt;"",ISNA(MATCH($B90,机构表,0))),"※机构不在【资料】里",IF(AND($D90&lt;&gt;"",ISNA(MATCH($D90,状态表,0))),"※状态不在【资料】里",IF(N($M90)&gt;N($L90),"※已还本金大于典当金额",IF(AND($I90&lt;&gt;"",$J90&lt;&gt;"",$J90&lt;$I90),"※到期日早于当票日期",IF(AND($H90&lt;&gt;"",COUNTIF($H$4:$H$403,$H90)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L90&lt;&gt;"",$E90=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -17546,7 +17609,7 @@
       <c r="V91" s="12" t="n"/>
       <c r="W91" s="12" t="n"/>
       <c r="X91" s="18">
-        <f>IF($E91="","",IF(AND($B91&lt;&gt;"",ISNA(MATCH($B91,机构表,0))),"※机构不在【资料】里",IF(AND($D91&lt;&gt;"",ISNA(MATCH($D91,状态表,0))),"※状态不在【资料】里",IF(N($M91)&gt;N($L91),"※已还本金大于典当金额",IF(AND($I91&lt;&gt;"",$J91&lt;&gt;"",$J91&lt;$I91),"※到期日早于当票日期",IF(AND($H91&lt;&gt;"",COUNTIF($H$4:$H$403,$H91)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L91&lt;&gt;"",$E91=""),"※有金额没写客户","")))))</f>
+        <f>IF($E91="","",IF(AND($B91&lt;&gt;"",ISNA(MATCH($B91,机构表,0))),"※机构不在【资料】里",IF(AND($D91&lt;&gt;"",ISNA(MATCH($D91,状态表,0))),"※状态不在【资料】里",IF(N($M91)&gt;N($L91),"※已还本金大于典当金额",IF(AND($I91&lt;&gt;"",$J91&lt;&gt;"",$J91&lt;$I91),"※到期日早于当票日期",IF(AND($H91&lt;&gt;"",COUNTIF($H$4:$H$403,$H91)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L91&lt;&gt;"",$E91=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -17621,7 +17684,7 @@
         </is>
       </c>
       <c r="X92" s="18">
-        <f>IF($E92="","",IF(AND($B92&lt;&gt;"",ISNA(MATCH($B92,机构表,0))),"※机构不在【资料】里",IF(AND($D92&lt;&gt;"",ISNA(MATCH($D92,状态表,0))),"※状态不在【资料】里",IF(N($M92)&gt;N($L92),"※已还本金大于典当金额",IF(AND($I92&lt;&gt;"",$J92&lt;&gt;"",$J92&lt;$I92),"※到期日早于当票日期",IF(AND($H92&lt;&gt;"",COUNTIF($H$4:$H$403,$H92)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L92&lt;&gt;"",$E92=""),"※有金额没写客户","")))))</f>
+        <f>IF($E92="","",IF(AND($B92&lt;&gt;"",ISNA(MATCH($B92,机构表,0))),"※机构不在【资料】里",IF(AND($D92&lt;&gt;"",ISNA(MATCH($D92,状态表,0))),"※状态不在【资料】里",IF(N($M92)&gt;N($L92),"※已还本金大于典当金额",IF(AND($I92&lt;&gt;"",$J92&lt;&gt;"",$J92&lt;$I92),"※到期日早于当票日期",IF(AND($H92&lt;&gt;"",COUNTIF($H$4:$H$403,$H92)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L92&lt;&gt;"",$E92=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -17696,7 +17759,7 @@
         </is>
       </c>
       <c r="X93" s="18">
-        <f>IF($E93="","",IF(AND($B93&lt;&gt;"",ISNA(MATCH($B93,机构表,0))),"※机构不在【资料】里",IF(AND($D93&lt;&gt;"",ISNA(MATCH($D93,状态表,0))),"※状态不在【资料】里",IF(N($M93)&gt;N($L93),"※已还本金大于典当金额",IF(AND($I93&lt;&gt;"",$J93&lt;&gt;"",$J93&lt;$I93),"※到期日早于当票日期",IF(AND($H93&lt;&gt;"",COUNTIF($H$4:$H$403,$H93)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L93&lt;&gt;"",$E93=""),"※有金额没写客户","")))))</f>
+        <f>IF($E93="","",IF(AND($B93&lt;&gt;"",ISNA(MATCH($B93,机构表,0))),"※机构不在【资料】里",IF(AND($D93&lt;&gt;"",ISNA(MATCH($D93,状态表,0))),"※状态不在【资料】里",IF(N($M93)&gt;N($L93),"※已还本金大于典当金额",IF(AND($I93&lt;&gt;"",$J93&lt;&gt;"",$J93&lt;$I93),"※到期日早于当票日期",IF(AND($H93&lt;&gt;"",COUNTIF($H$4:$H$403,$H93)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L93&lt;&gt;"",$E93=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -17753,7 +17816,7 @@
       <c r="V94" s="12" t="n"/>
       <c r="W94" s="12" t="n"/>
       <c r="X94" s="18">
-        <f>IF($E94="","",IF(AND($B94&lt;&gt;"",ISNA(MATCH($B94,机构表,0))),"※机构不在【资料】里",IF(AND($D94&lt;&gt;"",ISNA(MATCH($D94,状态表,0))),"※状态不在【资料】里",IF(N($M94)&gt;N($L94),"※已还本金大于典当金额",IF(AND($I94&lt;&gt;"",$J94&lt;&gt;"",$J94&lt;$I94),"※到期日早于当票日期",IF(AND($H94&lt;&gt;"",COUNTIF($H$4:$H$403,$H94)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L94&lt;&gt;"",$E94=""),"※有金额没写客户","")))))</f>
+        <f>IF($E94="","",IF(AND($B94&lt;&gt;"",ISNA(MATCH($B94,机构表,0))),"※机构不在【资料】里",IF(AND($D94&lt;&gt;"",ISNA(MATCH($D94,状态表,0))),"※状态不在【资料】里",IF(N($M94)&gt;N($L94),"※已还本金大于典当金额",IF(AND($I94&lt;&gt;"",$J94&lt;&gt;"",$J94&lt;$I94),"※到期日早于当票日期",IF(AND($H94&lt;&gt;"",COUNTIF($H$4:$H$403,$H94)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L94&lt;&gt;"",$E94=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -17816,7 +17879,7 @@
       <c r="V95" s="12" t="n"/>
       <c r="W95" s="12" t="n"/>
       <c r="X95" s="18">
-        <f>IF($E95="","",IF(AND($B95&lt;&gt;"",ISNA(MATCH($B95,机构表,0))),"※机构不在【资料】里",IF(AND($D95&lt;&gt;"",ISNA(MATCH($D95,状态表,0))),"※状态不在【资料】里",IF(N($M95)&gt;N($L95),"※已还本金大于典当金额",IF(AND($I95&lt;&gt;"",$J95&lt;&gt;"",$J95&lt;$I95),"※到期日早于当票日期",IF(AND($H95&lt;&gt;"",COUNTIF($H$4:$H$403,$H95)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L95&lt;&gt;"",$E95=""),"※有金额没写客户","")))))</f>
+        <f>IF($E95="","",IF(AND($B95&lt;&gt;"",ISNA(MATCH($B95,机构表,0))),"※机构不在【资料】里",IF(AND($D95&lt;&gt;"",ISNA(MATCH($D95,状态表,0))),"※状态不在【资料】里",IF(N($M95)&gt;N($L95),"※已还本金大于典当金额",IF(AND($I95&lt;&gt;"",$J95&lt;&gt;"",$J95&lt;$I95),"※到期日早于当票日期",IF(AND($H95&lt;&gt;"",COUNTIF($H$4:$H$403,$H95)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L95&lt;&gt;"",$E95=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -17879,7 +17942,7 @@
       <c r="V96" s="12" t="n"/>
       <c r="W96" s="12" t="n"/>
       <c r="X96" s="18">
-        <f>IF($E96="","",IF(AND($B96&lt;&gt;"",ISNA(MATCH($B96,机构表,0))),"※机构不在【资料】里",IF(AND($D96&lt;&gt;"",ISNA(MATCH($D96,状态表,0))),"※状态不在【资料】里",IF(N($M96)&gt;N($L96),"※已还本金大于典当金额",IF(AND($I96&lt;&gt;"",$J96&lt;&gt;"",$J96&lt;$I96),"※到期日早于当票日期",IF(AND($H96&lt;&gt;"",COUNTIF($H$4:$H$403,$H96)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L96&lt;&gt;"",$E96=""),"※有金额没写客户","")))))</f>
+        <f>IF($E96="","",IF(AND($B96&lt;&gt;"",ISNA(MATCH($B96,机构表,0))),"※机构不在【资料】里",IF(AND($D96&lt;&gt;"",ISNA(MATCH($D96,状态表,0))),"※状态不在【资料】里",IF(N($M96)&gt;N($L96),"※已还本金大于典当金额",IF(AND($I96&lt;&gt;"",$J96&lt;&gt;"",$J96&lt;$I96),"※到期日早于当票日期",IF(AND($H96&lt;&gt;"",COUNTIF($H$4:$H$403,$H96)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L96&lt;&gt;"",$E96=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -17942,7 +18005,7 @@
       <c r="V97" s="12" t="n"/>
       <c r="W97" s="12" t="n"/>
       <c r="X97" s="18">
-        <f>IF($E97="","",IF(AND($B97&lt;&gt;"",ISNA(MATCH($B97,机构表,0))),"※机构不在【资料】里",IF(AND($D97&lt;&gt;"",ISNA(MATCH($D97,状态表,0))),"※状态不在【资料】里",IF(N($M97)&gt;N($L97),"※已还本金大于典当金额",IF(AND($I97&lt;&gt;"",$J97&lt;&gt;"",$J97&lt;$I97),"※到期日早于当票日期",IF(AND($H97&lt;&gt;"",COUNTIF($H$4:$H$403,$H97)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L97&lt;&gt;"",$E97=""),"※有金额没写客户","")))))</f>
+        <f>IF($E97="","",IF(AND($B97&lt;&gt;"",ISNA(MATCH($B97,机构表,0))),"※机构不在【资料】里",IF(AND($D97&lt;&gt;"",ISNA(MATCH($D97,状态表,0))),"※状态不在【资料】里",IF(N($M97)&gt;N($L97),"※已还本金大于典当金额",IF(AND($I97&lt;&gt;"",$J97&lt;&gt;"",$J97&lt;$I97),"※到期日早于当票日期",IF(AND($H97&lt;&gt;"",COUNTIF($H$4:$H$403,$H97)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L97&lt;&gt;"",$E97=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -18007,7 +18070,7 @@
       <c r="V98" s="12" t="n"/>
       <c r="W98" s="12" t="n"/>
       <c r="X98" s="18">
-        <f>IF($E98="","",IF(AND($B98&lt;&gt;"",ISNA(MATCH($B98,机构表,0))),"※机构不在【资料】里",IF(AND($D98&lt;&gt;"",ISNA(MATCH($D98,状态表,0))),"※状态不在【资料】里",IF(N($M98)&gt;N($L98),"※已还本金大于典当金额",IF(AND($I98&lt;&gt;"",$J98&lt;&gt;"",$J98&lt;$I98),"※到期日早于当票日期",IF(AND($H98&lt;&gt;"",COUNTIF($H$4:$H$403,$H98)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L98&lt;&gt;"",$E98=""),"※有金额没写客户","")))))</f>
+        <f>IF($E98="","",IF(AND($B98&lt;&gt;"",ISNA(MATCH($B98,机构表,0))),"※机构不在【资料】里",IF(AND($D98&lt;&gt;"",ISNA(MATCH($D98,状态表,0))),"※状态不在【资料】里",IF(N($M98)&gt;N($L98),"※已还本金大于典当金额",IF(AND($I98&lt;&gt;"",$J98&lt;&gt;"",$J98&lt;$I98),"※到期日早于当票日期",IF(AND($H98&lt;&gt;"",COUNTIF($H$4:$H$403,$H98)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L98&lt;&gt;"",$E98=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -18080,7 +18143,7 @@
       </c>
       <c r="W99" s="12" t="n"/>
       <c r="X99" s="18">
-        <f>IF($E99="","",IF(AND($B99&lt;&gt;"",ISNA(MATCH($B99,机构表,0))),"※机构不在【资料】里",IF(AND($D99&lt;&gt;"",ISNA(MATCH($D99,状态表,0))),"※状态不在【资料】里",IF(N($M99)&gt;N($L99),"※已还本金大于典当金额",IF(AND($I99&lt;&gt;"",$J99&lt;&gt;"",$J99&lt;$I99),"※到期日早于当票日期",IF(AND($H99&lt;&gt;"",COUNTIF($H$4:$H$403,$H99)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L99&lt;&gt;"",$E99=""),"※有金额没写客户","")))))</f>
+        <f>IF($E99="","",IF(AND($B99&lt;&gt;"",ISNA(MATCH($B99,机构表,0))),"※机构不在【资料】里",IF(AND($D99&lt;&gt;"",ISNA(MATCH($D99,状态表,0))),"※状态不在【资料】里",IF(N($M99)&gt;N($L99),"※已还本金大于典当金额",IF(AND($I99&lt;&gt;"",$J99&lt;&gt;"",$J99&lt;$I99),"※到期日早于当票日期",IF(AND($H99&lt;&gt;"",COUNTIF($H$4:$H$403,$H99)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L99&lt;&gt;"",$E99=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -18145,7 +18208,7 @@
       <c r="V100" s="12" t="n"/>
       <c r="W100" s="12" t="n"/>
       <c r="X100" s="18">
-        <f>IF($E100="","",IF(AND($B100&lt;&gt;"",ISNA(MATCH($B100,机构表,0))),"※机构不在【资料】里",IF(AND($D100&lt;&gt;"",ISNA(MATCH($D100,状态表,0))),"※状态不在【资料】里",IF(N($M100)&gt;N($L100),"※已还本金大于典当金额",IF(AND($I100&lt;&gt;"",$J100&lt;&gt;"",$J100&lt;$I100),"※到期日早于当票日期",IF(AND($H100&lt;&gt;"",COUNTIF($H$4:$H$403,$H100)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L100&lt;&gt;"",$E100=""),"※有金额没写客户","")))))</f>
+        <f>IF($E100="","",IF(AND($B100&lt;&gt;"",ISNA(MATCH($B100,机构表,0))),"※机构不在【资料】里",IF(AND($D100&lt;&gt;"",ISNA(MATCH($D100,状态表,0))),"※状态不在【资料】里",IF(N($M100)&gt;N($L100),"※已还本金大于典当金额",IF(AND($I100&lt;&gt;"",$J100&lt;&gt;"",$J100&lt;$I100),"※到期日早于当票日期",IF(AND($H100&lt;&gt;"",COUNTIF($H$4:$H$403,$H100)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L100&lt;&gt;"",$E100=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -18206,7 +18269,7 @@
       <c r="V101" s="12" t="n"/>
       <c r="W101" s="12" t="n"/>
       <c r="X101" s="18">
-        <f>IF($E101="","",IF(AND($B101&lt;&gt;"",ISNA(MATCH($B101,机构表,0))),"※机构不在【资料】里",IF(AND($D101&lt;&gt;"",ISNA(MATCH($D101,状态表,0))),"※状态不在【资料】里",IF(N($M101)&gt;N($L101),"※已还本金大于典当金额",IF(AND($I101&lt;&gt;"",$J101&lt;&gt;"",$J101&lt;$I101),"※到期日早于当票日期",IF(AND($H101&lt;&gt;"",COUNTIF($H$4:$H$403,$H101)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L101&lt;&gt;"",$E101=""),"※有金额没写客户","")))))</f>
+        <f>IF($E101="","",IF(AND($B101&lt;&gt;"",ISNA(MATCH($B101,机构表,0))),"※机构不在【资料】里",IF(AND($D101&lt;&gt;"",ISNA(MATCH($D101,状态表,0))),"※状态不在【资料】里",IF(N($M101)&gt;N($L101),"※已还本金大于典当金额",IF(AND($I101&lt;&gt;"",$J101&lt;&gt;"",$J101&lt;$I101),"※到期日早于当票日期",IF(AND($H101&lt;&gt;"",COUNTIF($H$4:$H$403,$H101)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L101&lt;&gt;"",$E101=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -18265,7 +18328,7 @@
         </is>
       </c>
       <c r="X102" s="18">
-        <f>IF($E102="","",IF(AND($B102&lt;&gt;"",ISNA(MATCH($B102,机构表,0))),"※机构不在【资料】里",IF(AND($D102&lt;&gt;"",ISNA(MATCH($D102,状态表,0))),"※状态不在【资料】里",IF(N($M102)&gt;N($L102),"※已还本金大于典当金额",IF(AND($I102&lt;&gt;"",$J102&lt;&gt;"",$J102&lt;$I102),"※到期日早于当票日期",IF(AND($H102&lt;&gt;"",COUNTIF($H$4:$H$403,$H102)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L102&lt;&gt;"",$E102=""),"※有金额没写客户","")))))</f>
+        <f>IF($E102="","",IF(AND($B102&lt;&gt;"",ISNA(MATCH($B102,机构表,0))),"※机构不在【资料】里",IF(AND($D102&lt;&gt;"",ISNA(MATCH($D102,状态表,0))),"※状态不在【资料】里",IF(N($M102)&gt;N($L102),"※已还本金大于典当金额",IF(AND($I102&lt;&gt;"",$J102&lt;&gt;"",$J102&lt;$I102),"※到期日早于当票日期",IF(AND($H102&lt;&gt;"",COUNTIF($H$4:$H$403,$H102)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L102&lt;&gt;"",$E102=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -18324,7 +18387,7 @@
         </is>
       </c>
       <c r="X103" s="18">
-        <f>IF($E103="","",IF(AND($B103&lt;&gt;"",ISNA(MATCH($B103,机构表,0))),"※机构不在【资料】里",IF(AND($D103&lt;&gt;"",ISNA(MATCH($D103,状态表,0))),"※状态不在【资料】里",IF(N($M103)&gt;N($L103),"※已还本金大于典当金额",IF(AND($I103&lt;&gt;"",$J103&lt;&gt;"",$J103&lt;$I103),"※到期日早于当票日期",IF(AND($H103&lt;&gt;"",COUNTIF($H$4:$H$403,$H103)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L103&lt;&gt;"",$E103=""),"※有金额没写客户","")))))</f>
+        <f>IF($E103="","",IF(AND($B103&lt;&gt;"",ISNA(MATCH($B103,机构表,0))),"※机构不在【资料】里",IF(AND($D103&lt;&gt;"",ISNA(MATCH($D103,状态表,0))),"※状态不在【资料】里",IF(N($M103)&gt;N($L103),"※已还本金大于典当金额",IF(AND($I103&lt;&gt;"",$J103&lt;&gt;"",$J103&lt;$I103),"※到期日早于当票日期",IF(AND($H103&lt;&gt;"",COUNTIF($H$4:$H$403,$H103)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L103&lt;&gt;"",$E103=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -18383,7 +18446,7 @@
         </is>
       </c>
       <c r="X104" s="18">
-        <f>IF($E104="","",IF(AND($B104&lt;&gt;"",ISNA(MATCH($B104,机构表,0))),"※机构不在【资料】里",IF(AND($D104&lt;&gt;"",ISNA(MATCH($D104,状态表,0))),"※状态不在【资料】里",IF(N($M104)&gt;N($L104),"※已还本金大于典当金额",IF(AND($I104&lt;&gt;"",$J104&lt;&gt;"",$J104&lt;$I104),"※到期日早于当票日期",IF(AND($H104&lt;&gt;"",COUNTIF($H$4:$H$403,$H104)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L104&lt;&gt;"",$E104=""),"※有金额没写客户","")))))</f>
+        <f>IF($E104="","",IF(AND($B104&lt;&gt;"",ISNA(MATCH($B104,机构表,0))),"※机构不在【资料】里",IF(AND($D104&lt;&gt;"",ISNA(MATCH($D104,状态表,0))),"※状态不在【资料】里",IF(N($M104)&gt;N($L104),"※已还本金大于典当金额",IF(AND($I104&lt;&gt;"",$J104&lt;&gt;"",$J104&lt;$I104),"※到期日早于当票日期",IF(AND($H104&lt;&gt;"",COUNTIF($H$4:$H$403,$H104)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L104&lt;&gt;"",$E104=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -18448,7 +18511,7 @@
       <c r="V105" s="12" t="n"/>
       <c r="W105" s="12" t="n"/>
       <c r="X105" s="18">
-        <f>IF($E105="","",IF(AND($B105&lt;&gt;"",ISNA(MATCH($B105,机构表,0))),"※机构不在【资料】里",IF(AND($D105&lt;&gt;"",ISNA(MATCH($D105,状态表,0))),"※状态不在【资料】里",IF(N($M105)&gt;N($L105),"※已还本金大于典当金额",IF(AND($I105&lt;&gt;"",$J105&lt;&gt;"",$J105&lt;$I105),"※到期日早于当票日期",IF(AND($H105&lt;&gt;"",COUNTIF($H$4:$H$403,$H105)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L105&lt;&gt;"",$E105=""),"※有金额没写客户","")))))</f>
+        <f>IF($E105="","",IF(AND($B105&lt;&gt;"",ISNA(MATCH($B105,机构表,0))),"※机构不在【资料】里",IF(AND($D105&lt;&gt;"",ISNA(MATCH($D105,状态表,0))),"※状态不在【资料】里",IF(N($M105)&gt;N($L105),"※已还本金大于典当金额",IF(AND($I105&lt;&gt;"",$J105&lt;&gt;"",$J105&lt;$I105),"※到期日早于当票日期",IF(AND($H105&lt;&gt;"",COUNTIF($H$4:$H$403,$H105)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L105&lt;&gt;"",$E105=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -18513,7 +18576,7 @@
       <c r="V106" s="12" t="n"/>
       <c r="W106" s="12" t="n"/>
       <c r="X106" s="18">
-        <f>IF($E106="","",IF(AND($B106&lt;&gt;"",ISNA(MATCH($B106,机构表,0))),"※机构不在【资料】里",IF(AND($D106&lt;&gt;"",ISNA(MATCH($D106,状态表,0))),"※状态不在【资料】里",IF(N($M106)&gt;N($L106),"※已还本金大于典当金额",IF(AND($I106&lt;&gt;"",$J106&lt;&gt;"",$J106&lt;$I106),"※到期日早于当票日期",IF(AND($H106&lt;&gt;"",COUNTIF($H$4:$H$403,$H106)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L106&lt;&gt;"",$E106=""),"※有金额没写客户","")))))</f>
+        <f>IF($E106="","",IF(AND($B106&lt;&gt;"",ISNA(MATCH($B106,机构表,0))),"※机构不在【资料】里",IF(AND($D106&lt;&gt;"",ISNA(MATCH($D106,状态表,0))),"※状态不在【资料】里",IF(N($M106)&gt;N($L106),"※已还本金大于典当金额",IF(AND($I106&lt;&gt;"",$J106&lt;&gt;"",$J106&lt;$I106),"※到期日早于当票日期",IF(AND($H106&lt;&gt;"",COUNTIF($H$4:$H$403,$H106)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L106&lt;&gt;"",$E106=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -18572,7 +18635,7 @@
         </is>
       </c>
       <c r="X107" s="18">
-        <f>IF($E107="","",IF(AND($B107&lt;&gt;"",ISNA(MATCH($B107,机构表,0))),"※机构不在【资料】里",IF(AND($D107&lt;&gt;"",ISNA(MATCH($D107,状态表,0))),"※状态不在【资料】里",IF(N($M107)&gt;N($L107),"※已还本金大于典当金额",IF(AND($I107&lt;&gt;"",$J107&lt;&gt;"",$J107&lt;$I107),"※到期日早于当票日期",IF(AND($H107&lt;&gt;"",COUNTIF($H$4:$H$403,$H107)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L107&lt;&gt;"",$E107=""),"※有金额没写客户","")))))</f>
+        <f>IF($E107="","",IF(AND($B107&lt;&gt;"",ISNA(MATCH($B107,机构表,0))),"※机构不在【资料】里",IF(AND($D107&lt;&gt;"",ISNA(MATCH($D107,状态表,0))),"※状态不在【资料】里",IF(N($M107)&gt;N($L107),"※已还本金大于典当金额",IF(AND($I107&lt;&gt;"",$J107&lt;&gt;"",$J107&lt;$I107),"※到期日早于当票日期",IF(AND($H107&lt;&gt;"",COUNTIF($H$4:$H$403,$H107)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L107&lt;&gt;"",$E107=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -18649,7 +18712,7 @@
       </c>
       <c r="W108" s="12" t="n"/>
       <c r="X108" s="18">
-        <f>IF($E108="","",IF(AND($B108&lt;&gt;"",ISNA(MATCH($B108,机构表,0))),"※机构不在【资料】里",IF(AND($D108&lt;&gt;"",ISNA(MATCH($D108,状态表,0))),"※状态不在【资料】里",IF(N($M108)&gt;N($L108),"※已还本金大于典当金额",IF(AND($I108&lt;&gt;"",$J108&lt;&gt;"",$J108&lt;$I108),"※到期日早于当票日期",IF(AND($H108&lt;&gt;"",COUNTIF($H$4:$H$403,$H108)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L108&lt;&gt;"",$E108=""),"※有金额没写客户","")))))</f>
+        <f>IF($E108="","",IF(AND($B108&lt;&gt;"",ISNA(MATCH($B108,机构表,0))),"※机构不在【资料】里",IF(AND($D108&lt;&gt;"",ISNA(MATCH($D108,状态表,0))),"※状态不在【资料】里",IF(N($M108)&gt;N($L108),"※已还本金大于典当金额",IF(AND($I108&lt;&gt;"",$J108&lt;&gt;"",$J108&lt;$I108),"※到期日早于当票日期",IF(AND($H108&lt;&gt;"",COUNTIF($H$4:$H$403,$H108)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L108&lt;&gt;"",$E108=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -18712,7 +18775,7 @@
       <c r="V109" s="12" t="n"/>
       <c r="W109" s="12" t="n"/>
       <c r="X109" s="18">
-        <f>IF($E109="","",IF(AND($B109&lt;&gt;"",ISNA(MATCH($B109,机构表,0))),"※机构不在【资料】里",IF(AND($D109&lt;&gt;"",ISNA(MATCH($D109,状态表,0))),"※状态不在【资料】里",IF(N($M109)&gt;N($L109),"※已还本金大于典当金额",IF(AND($I109&lt;&gt;"",$J109&lt;&gt;"",$J109&lt;$I109),"※到期日早于当票日期",IF(AND($H109&lt;&gt;"",COUNTIF($H$4:$H$403,$H109)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L109&lt;&gt;"",$E109=""),"※有金额没写客户","")))))</f>
+        <f>IF($E109="","",IF(AND($B109&lt;&gt;"",ISNA(MATCH($B109,机构表,0))),"※机构不在【资料】里",IF(AND($D109&lt;&gt;"",ISNA(MATCH($D109,状态表,0))),"※状态不在【资料】里",IF(N($M109)&gt;N($L109),"※已还本金大于典当金额",IF(AND($I109&lt;&gt;"",$J109&lt;&gt;"",$J109&lt;$I109),"※到期日早于当票日期",IF(AND($H109&lt;&gt;"",COUNTIF($H$4:$H$403,$H109)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L109&lt;&gt;"",$E109=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -18787,7 +18850,7 @@
         </is>
       </c>
       <c r="X110" s="18">
-        <f>IF($E110="","",IF(AND($B110&lt;&gt;"",ISNA(MATCH($B110,机构表,0))),"※机构不在【资料】里",IF(AND($D110&lt;&gt;"",ISNA(MATCH($D110,状态表,0))),"※状态不在【资料】里",IF(N($M110)&gt;N($L110),"※已还本金大于典当金额",IF(AND($I110&lt;&gt;"",$J110&lt;&gt;"",$J110&lt;$I110),"※到期日早于当票日期",IF(AND($H110&lt;&gt;"",COUNTIF($H$4:$H$403,$H110)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L110&lt;&gt;"",$E110=""),"※有金额没写客户","")))))</f>
+        <f>IF($E110="","",IF(AND($B110&lt;&gt;"",ISNA(MATCH($B110,机构表,0))),"※机构不在【资料】里",IF(AND($D110&lt;&gt;"",ISNA(MATCH($D110,状态表,0))),"※状态不在【资料】里",IF(N($M110)&gt;N($L110),"※已还本金大于典当金额",IF(AND($I110&lt;&gt;"",$J110&lt;&gt;"",$J110&lt;$I110),"※到期日早于当票日期",IF(AND($H110&lt;&gt;"",COUNTIF($H$4:$H$403,$H110)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L110&lt;&gt;"",$E110=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -18858,7 +18921,7 @@
       <c r="V111" s="12" t="n"/>
       <c r="W111" s="12" t="n"/>
       <c r="X111" s="18">
-        <f>IF($E111="","",IF(AND($B111&lt;&gt;"",ISNA(MATCH($B111,机构表,0))),"※机构不在【资料】里",IF(AND($D111&lt;&gt;"",ISNA(MATCH($D111,状态表,0))),"※状态不在【资料】里",IF(N($M111)&gt;N($L111),"※已还本金大于典当金额",IF(AND($I111&lt;&gt;"",$J111&lt;&gt;"",$J111&lt;$I111),"※到期日早于当票日期",IF(AND($H111&lt;&gt;"",COUNTIF($H$4:$H$403,$H111)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L111&lt;&gt;"",$E111=""),"※有金额没写客户","")))))</f>
+        <f>IF($E111="","",IF(AND($B111&lt;&gt;"",ISNA(MATCH($B111,机构表,0))),"※机构不在【资料】里",IF(AND($D111&lt;&gt;"",ISNA(MATCH($D111,状态表,0))),"※状态不在【资料】里",IF(N($M111)&gt;N($L111),"※已还本金大于典当金额",IF(AND($I111&lt;&gt;"",$J111&lt;&gt;"",$J111&lt;$I111),"※到期日早于当票日期",IF(AND($H111&lt;&gt;"",COUNTIF($H$4:$H$403,$H111)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L111&lt;&gt;"",$E111=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -18935,7 +18998,7 @@
       </c>
       <c r="W112" s="12" t="n"/>
       <c r="X112" s="18">
-        <f>IF($E112="","",IF(AND($B112&lt;&gt;"",ISNA(MATCH($B112,机构表,0))),"※机构不在【资料】里",IF(AND($D112&lt;&gt;"",ISNA(MATCH($D112,状态表,0))),"※状态不在【资料】里",IF(N($M112)&gt;N($L112),"※已还本金大于典当金额",IF(AND($I112&lt;&gt;"",$J112&lt;&gt;"",$J112&lt;$I112),"※到期日早于当票日期",IF(AND($H112&lt;&gt;"",COUNTIF($H$4:$H$403,$H112)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L112&lt;&gt;"",$E112=""),"※有金额没写客户","")))))</f>
+        <f>IF($E112="","",IF(AND($B112&lt;&gt;"",ISNA(MATCH($B112,机构表,0))),"※机构不在【资料】里",IF(AND($D112&lt;&gt;"",ISNA(MATCH($D112,状态表,0))),"※状态不在【资料】里",IF(N($M112)&gt;N($L112),"※已还本金大于典当金额",IF(AND($I112&lt;&gt;"",$J112&lt;&gt;"",$J112&lt;$I112),"※到期日早于当票日期",IF(AND($H112&lt;&gt;"",COUNTIF($H$4:$H$403,$H112)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L112&lt;&gt;"",$E112=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -19008,7 +19071,7 @@
       </c>
       <c r="W113" s="12" t="n"/>
       <c r="X113" s="18">
-        <f>IF($E113="","",IF(AND($B113&lt;&gt;"",ISNA(MATCH($B113,机构表,0))),"※机构不在【资料】里",IF(AND($D113&lt;&gt;"",ISNA(MATCH($D113,状态表,0))),"※状态不在【资料】里",IF(N($M113)&gt;N($L113),"※已还本金大于典当金额",IF(AND($I113&lt;&gt;"",$J113&lt;&gt;"",$J113&lt;$I113),"※到期日早于当票日期",IF(AND($H113&lt;&gt;"",COUNTIF($H$4:$H$403,$H113)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L113&lt;&gt;"",$E113=""),"※有金额没写客户","")))))</f>
+        <f>IF($E113="","",IF(AND($B113&lt;&gt;"",ISNA(MATCH($B113,机构表,0))),"※机构不在【资料】里",IF(AND($D113&lt;&gt;"",ISNA(MATCH($D113,状态表,0))),"※状态不在【资料】里",IF(N($M113)&gt;N($L113),"※已还本金大于典当金额",IF(AND($I113&lt;&gt;"",$J113&lt;&gt;"",$J113&lt;$I113),"※到期日早于当票日期",IF(AND($H113&lt;&gt;"",COUNTIF($H$4:$H$403,$H113)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L113&lt;&gt;"",$E113=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -19085,7 +19148,7 @@
       </c>
       <c r="W114" s="12" t="n"/>
       <c r="X114" s="18">
-        <f>IF($E114="","",IF(AND($B114&lt;&gt;"",ISNA(MATCH($B114,机构表,0))),"※机构不在【资料】里",IF(AND($D114&lt;&gt;"",ISNA(MATCH($D114,状态表,0))),"※状态不在【资料】里",IF(N($M114)&gt;N($L114),"※已还本金大于典当金额",IF(AND($I114&lt;&gt;"",$J114&lt;&gt;"",$J114&lt;$I114),"※到期日早于当票日期",IF(AND($H114&lt;&gt;"",COUNTIF($H$4:$H$403,$H114)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L114&lt;&gt;"",$E114=""),"※有金额没写客户","")))))</f>
+        <f>IF($E114="","",IF(AND($B114&lt;&gt;"",ISNA(MATCH($B114,机构表,0))),"※机构不在【资料】里",IF(AND($D114&lt;&gt;"",ISNA(MATCH($D114,状态表,0))),"※状态不在【资料】里",IF(N($M114)&gt;N($L114),"※已还本金大于典当金额",IF(AND($I114&lt;&gt;"",$J114&lt;&gt;"",$J114&lt;$I114),"※到期日早于当票日期",IF(AND($H114&lt;&gt;"",COUNTIF($H$4:$H$403,$H114)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L114&lt;&gt;"",$E114=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -19160,7 +19223,7 @@
       </c>
       <c r="W115" s="12" t="n"/>
       <c r="X115" s="18">
-        <f>IF($E115="","",IF(AND($B115&lt;&gt;"",ISNA(MATCH($B115,机构表,0))),"※机构不在【资料】里",IF(AND($D115&lt;&gt;"",ISNA(MATCH($D115,状态表,0))),"※状态不在【资料】里",IF(N($M115)&gt;N($L115),"※已还本金大于典当金额",IF(AND($I115&lt;&gt;"",$J115&lt;&gt;"",$J115&lt;$I115),"※到期日早于当票日期",IF(AND($H115&lt;&gt;"",COUNTIF($H$4:$H$403,$H115)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L115&lt;&gt;"",$E115=""),"※有金额没写客户","")))))</f>
+        <f>IF($E115="","",IF(AND($B115&lt;&gt;"",ISNA(MATCH($B115,机构表,0))),"※机构不在【资料】里",IF(AND($D115&lt;&gt;"",ISNA(MATCH($D115,状态表,0))),"※状态不在【资料】里",IF(N($M115)&gt;N($L115),"※已还本金大于典当金额",IF(AND($I115&lt;&gt;"",$J115&lt;&gt;"",$J115&lt;$I115),"※到期日早于当票日期",IF(AND($H115&lt;&gt;"",COUNTIF($H$4:$H$403,$H115)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L115&lt;&gt;"",$E115=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -19227,7 +19290,7 @@
         </is>
       </c>
       <c r="X116" s="18">
-        <f>IF($E116="","",IF(AND($B116&lt;&gt;"",ISNA(MATCH($B116,机构表,0))),"※机构不在【资料】里",IF(AND($D116&lt;&gt;"",ISNA(MATCH($D116,状态表,0))),"※状态不在【资料】里",IF(N($M116)&gt;N($L116),"※已还本金大于典当金额",IF(AND($I116&lt;&gt;"",$J116&lt;&gt;"",$J116&lt;$I116),"※到期日早于当票日期",IF(AND($H116&lt;&gt;"",COUNTIF($H$4:$H$403,$H116)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L116&lt;&gt;"",$E116=""),"※有金额没写客户","")))))</f>
+        <f>IF($E116="","",IF(AND($B116&lt;&gt;"",ISNA(MATCH($B116,机构表,0))),"※机构不在【资料】里",IF(AND($D116&lt;&gt;"",ISNA(MATCH($D116,状态表,0))),"※状态不在【资料】里",IF(N($M116)&gt;N($L116),"※已还本金大于典当金额",IF(AND($I116&lt;&gt;"",$J116&lt;&gt;"",$J116&lt;$I116),"※到期日早于当票日期",IF(AND($H116&lt;&gt;"",COUNTIF($H$4:$H$403,$H116)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L116&lt;&gt;"",$E116=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -19292,7 +19355,7 @@
         </is>
       </c>
       <c r="X117" s="18">
-        <f>IF($E117="","",IF(AND($B117&lt;&gt;"",ISNA(MATCH($B117,机构表,0))),"※机构不在【资料】里",IF(AND($D117&lt;&gt;"",ISNA(MATCH($D117,状态表,0))),"※状态不在【资料】里",IF(N($M117)&gt;N($L117),"※已还本金大于典当金额",IF(AND($I117&lt;&gt;"",$J117&lt;&gt;"",$J117&lt;$I117),"※到期日早于当票日期",IF(AND($H117&lt;&gt;"",COUNTIF($H$4:$H$403,$H117)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L117&lt;&gt;"",$E117=""),"※有金额没写客户","")))))</f>
+        <f>IF($E117="","",IF(AND($B117&lt;&gt;"",ISNA(MATCH($B117,机构表,0))),"※机构不在【资料】里",IF(AND($D117&lt;&gt;"",ISNA(MATCH($D117,状态表,0))),"※状态不在【资料】里",IF(N($M117)&gt;N($L117),"※已还本金大于典当金额",IF(AND($I117&lt;&gt;"",$J117&lt;&gt;"",$J117&lt;$I117),"※到期日早于当票日期",IF(AND($H117&lt;&gt;"",COUNTIF($H$4:$H$403,$H117)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L117&lt;&gt;"",$E117=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -19365,7 +19428,7 @@
       <c r="V118" s="12" t="n"/>
       <c r="W118" s="12" t="n"/>
       <c r="X118" s="18">
-        <f>IF($E118="","",IF(AND($B118&lt;&gt;"",ISNA(MATCH($B118,机构表,0))),"※机构不在【资料】里",IF(AND($D118&lt;&gt;"",ISNA(MATCH($D118,状态表,0))),"※状态不在【资料】里",IF(N($M118)&gt;N($L118),"※已还本金大于典当金额",IF(AND($I118&lt;&gt;"",$J118&lt;&gt;"",$J118&lt;$I118),"※到期日早于当票日期",IF(AND($H118&lt;&gt;"",COUNTIF($H$4:$H$403,$H118)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L118&lt;&gt;"",$E118=""),"※有金额没写客户","")))))</f>
+        <f>IF($E118="","",IF(AND($B118&lt;&gt;"",ISNA(MATCH($B118,机构表,0))),"※机构不在【资料】里",IF(AND($D118&lt;&gt;"",ISNA(MATCH($D118,状态表,0))),"※状态不在【资料】里",IF(N($M118)&gt;N($L118),"※已还本金大于典当金额",IF(AND($I118&lt;&gt;"",$J118&lt;&gt;"",$J118&lt;$I118),"※到期日早于当票日期",IF(AND($H118&lt;&gt;"",COUNTIF($H$4:$H$403,$H118)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L118&lt;&gt;"",$E118=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -19430,7 +19493,7 @@
       <c r="V119" s="12" t="n"/>
       <c r="W119" s="12" t="n"/>
       <c r="X119" s="18">
-        <f>IF($E119="","",IF(AND($B119&lt;&gt;"",ISNA(MATCH($B119,机构表,0))),"※机构不在【资料】里",IF(AND($D119&lt;&gt;"",ISNA(MATCH($D119,状态表,0))),"※状态不在【资料】里",IF(N($M119)&gt;N($L119),"※已还本金大于典当金额",IF(AND($I119&lt;&gt;"",$J119&lt;&gt;"",$J119&lt;$I119),"※到期日早于当票日期",IF(AND($H119&lt;&gt;"",COUNTIF($H$4:$H$403,$H119)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L119&lt;&gt;"",$E119=""),"※有金额没写客户","")))))</f>
+        <f>IF($E119="","",IF(AND($B119&lt;&gt;"",ISNA(MATCH($B119,机构表,0))),"※机构不在【资料】里",IF(AND($D119&lt;&gt;"",ISNA(MATCH($D119,状态表,0))),"※状态不在【资料】里",IF(N($M119)&gt;N($L119),"※已还本金大于典当金额",IF(AND($I119&lt;&gt;"",$J119&lt;&gt;"",$J119&lt;$I119),"※到期日早于当票日期",IF(AND($H119&lt;&gt;"",COUNTIF($H$4:$H$403,$H119)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L119&lt;&gt;"",$E119=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -19493,7 +19556,7 @@
       <c r="V120" s="12" t="n"/>
       <c r="W120" s="12" t="n"/>
       <c r="X120" s="18">
-        <f>IF($E120="","",IF(AND($B120&lt;&gt;"",ISNA(MATCH($B120,机构表,0))),"※机构不在【资料】里",IF(AND($D120&lt;&gt;"",ISNA(MATCH($D120,状态表,0))),"※状态不在【资料】里",IF(N($M120)&gt;N($L120),"※已还本金大于典当金额",IF(AND($I120&lt;&gt;"",$J120&lt;&gt;"",$J120&lt;$I120),"※到期日早于当票日期",IF(AND($H120&lt;&gt;"",COUNTIF($H$4:$H$403,$H120)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L120&lt;&gt;"",$E120=""),"※有金额没写客户","")))))</f>
+        <f>IF($E120="","",IF(AND($B120&lt;&gt;"",ISNA(MATCH($B120,机构表,0))),"※机构不在【资料】里",IF(AND($D120&lt;&gt;"",ISNA(MATCH($D120,状态表,0))),"※状态不在【资料】里",IF(N($M120)&gt;N($L120),"※已还本金大于典当金额",IF(AND($I120&lt;&gt;"",$J120&lt;&gt;"",$J120&lt;$I120),"※到期日早于当票日期",IF(AND($H120&lt;&gt;"",COUNTIF($H$4:$H$403,$H120)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L120&lt;&gt;"",$E120=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -19564,7 +19627,7 @@
       <c r="V121" s="12" t="n"/>
       <c r="W121" s="12" t="n"/>
       <c r="X121" s="18">
-        <f>IF($E121="","",IF(AND($B121&lt;&gt;"",ISNA(MATCH($B121,机构表,0))),"※机构不在【资料】里",IF(AND($D121&lt;&gt;"",ISNA(MATCH($D121,状态表,0))),"※状态不在【资料】里",IF(N($M121)&gt;N($L121),"※已还本金大于典当金额",IF(AND($I121&lt;&gt;"",$J121&lt;&gt;"",$J121&lt;$I121),"※到期日早于当票日期",IF(AND($H121&lt;&gt;"",COUNTIF($H$4:$H$403,$H121)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L121&lt;&gt;"",$E121=""),"※有金额没写客户","")))))</f>
+        <f>IF($E121="","",IF(AND($B121&lt;&gt;"",ISNA(MATCH($B121,机构表,0))),"※机构不在【资料】里",IF(AND($D121&lt;&gt;"",ISNA(MATCH($D121,状态表,0))),"※状态不在【资料】里",IF(N($M121)&gt;N($L121),"※已还本金大于典当金额",IF(AND($I121&lt;&gt;"",$J121&lt;&gt;"",$J121&lt;$I121),"※到期日早于当票日期",IF(AND($H121&lt;&gt;"",COUNTIF($H$4:$H$403,$H121)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L121&lt;&gt;"",$E121=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -19627,7 +19690,7 @@
       <c r="V122" s="12" t="n"/>
       <c r="W122" s="12" t="n"/>
       <c r="X122" s="18">
-        <f>IF($E122="","",IF(AND($B122&lt;&gt;"",ISNA(MATCH($B122,机构表,0))),"※机构不在【资料】里",IF(AND($D122&lt;&gt;"",ISNA(MATCH($D122,状态表,0))),"※状态不在【资料】里",IF(N($M122)&gt;N($L122),"※已还本金大于典当金额",IF(AND($I122&lt;&gt;"",$J122&lt;&gt;"",$J122&lt;$I122),"※到期日早于当票日期",IF(AND($H122&lt;&gt;"",COUNTIF($H$4:$H$403,$H122)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L122&lt;&gt;"",$E122=""),"※有金额没写客户","")))))</f>
+        <f>IF($E122="","",IF(AND($B122&lt;&gt;"",ISNA(MATCH($B122,机构表,0))),"※机构不在【资料】里",IF(AND($D122&lt;&gt;"",ISNA(MATCH($D122,状态表,0))),"※状态不在【资料】里",IF(N($M122)&gt;N($L122),"※已还本金大于典当金额",IF(AND($I122&lt;&gt;"",$J122&lt;&gt;"",$J122&lt;$I122),"※到期日早于当票日期",IF(AND($H122&lt;&gt;"",COUNTIF($H$4:$H$403,$H122)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L122&lt;&gt;"",$E122=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -19690,7 +19753,7 @@
       <c r="V123" s="12" t="n"/>
       <c r="W123" s="12" t="n"/>
       <c r="X123" s="18">
-        <f>IF($E123="","",IF(AND($B123&lt;&gt;"",ISNA(MATCH($B123,机构表,0))),"※机构不在【资料】里",IF(AND($D123&lt;&gt;"",ISNA(MATCH($D123,状态表,0))),"※状态不在【资料】里",IF(N($M123)&gt;N($L123),"※已还本金大于典当金额",IF(AND($I123&lt;&gt;"",$J123&lt;&gt;"",$J123&lt;$I123),"※到期日早于当票日期",IF(AND($H123&lt;&gt;"",COUNTIF($H$4:$H$403,$H123)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L123&lt;&gt;"",$E123=""),"※有金额没写客户","")))))</f>
+        <f>IF($E123="","",IF(AND($B123&lt;&gt;"",ISNA(MATCH($B123,机构表,0))),"※机构不在【资料】里",IF(AND($D123&lt;&gt;"",ISNA(MATCH($D123,状态表,0))),"※状态不在【资料】里",IF(N($M123)&gt;N($L123),"※已还本金大于典当金额",IF(AND($I123&lt;&gt;"",$J123&lt;&gt;"",$J123&lt;$I123),"※到期日早于当票日期",IF(AND($H123&lt;&gt;"",COUNTIF($H$4:$H$403,$H123)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L123&lt;&gt;"",$E123=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -19753,7 +19816,7 @@
       <c r="V124" s="12" t="n"/>
       <c r="W124" s="12" t="n"/>
       <c r="X124" s="18">
-        <f>IF($E124="","",IF(AND($B124&lt;&gt;"",ISNA(MATCH($B124,机构表,0))),"※机构不在【资料】里",IF(AND($D124&lt;&gt;"",ISNA(MATCH($D124,状态表,0))),"※状态不在【资料】里",IF(N($M124)&gt;N($L124),"※已还本金大于典当金额",IF(AND($I124&lt;&gt;"",$J124&lt;&gt;"",$J124&lt;$I124),"※到期日早于当票日期",IF(AND($H124&lt;&gt;"",COUNTIF($H$4:$H$403,$H124)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L124&lt;&gt;"",$E124=""),"※有金额没写客户","")))))</f>
+        <f>IF($E124="","",IF(AND($B124&lt;&gt;"",ISNA(MATCH($B124,机构表,0))),"※机构不在【资料】里",IF(AND($D124&lt;&gt;"",ISNA(MATCH($D124,状态表,0))),"※状态不在【资料】里",IF(N($M124)&gt;N($L124),"※已还本金大于典当金额",IF(AND($I124&lt;&gt;"",$J124&lt;&gt;"",$J124&lt;$I124),"※到期日早于当票日期",IF(AND($H124&lt;&gt;"",COUNTIF($H$4:$H$403,$H124)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L124&lt;&gt;"",$E124=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -19828,7 +19891,7 @@
       </c>
       <c r="W125" s="12" t="n"/>
       <c r="X125" s="18">
-        <f>IF($E125="","",IF(AND($B125&lt;&gt;"",ISNA(MATCH($B125,机构表,0))),"※机构不在【资料】里",IF(AND($D125&lt;&gt;"",ISNA(MATCH($D125,状态表,0))),"※状态不在【资料】里",IF(N($M125)&gt;N($L125),"※已还本金大于典当金额",IF(AND($I125&lt;&gt;"",$J125&lt;&gt;"",$J125&lt;$I125),"※到期日早于当票日期",IF(AND($H125&lt;&gt;"",COUNTIF($H$4:$H$403,$H125)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L125&lt;&gt;"",$E125=""),"※有金额没写客户","")))))</f>
+        <f>IF($E125="","",IF(AND($B125&lt;&gt;"",ISNA(MATCH($B125,机构表,0))),"※机构不在【资料】里",IF(AND($D125&lt;&gt;"",ISNA(MATCH($D125,状态表,0))),"※状态不在【资料】里",IF(N($M125)&gt;N($L125),"※已还本金大于典当金额",IF(AND($I125&lt;&gt;"",$J125&lt;&gt;"",$J125&lt;$I125),"※到期日早于当票日期",IF(AND($H125&lt;&gt;"",COUNTIF($H$4:$H$403,$H125)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L125&lt;&gt;"",$E125=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -19895,7 +19958,7 @@
       <c r="V126" s="12" t="n"/>
       <c r="W126" s="12" t="n"/>
       <c r="X126" s="18">
-        <f>IF($E126="","",IF(AND($B126&lt;&gt;"",ISNA(MATCH($B126,机构表,0))),"※机构不在【资料】里",IF(AND($D126&lt;&gt;"",ISNA(MATCH($D126,状态表,0))),"※状态不在【资料】里",IF(N($M126)&gt;N($L126),"※已还本金大于典当金额",IF(AND($I126&lt;&gt;"",$J126&lt;&gt;"",$J126&lt;$I126),"※到期日早于当票日期",IF(AND($H126&lt;&gt;"",COUNTIF($H$4:$H$403,$H126)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L126&lt;&gt;"",$E126=""),"※有金额没写客户","")))))</f>
+        <f>IF($E126="","",IF(AND($B126&lt;&gt;"",ISNA(MATCH($B126,机构表,0))),"※机构不在【资料】里",IF(AND($D126&lt;&gt;"",ISNA(MATCH($D126,状态表,0))),"※状态不在【资料】里",IF(N($M126)&gt;N($L126),"※已还本金大于典当金额",IF(AND($I126&lt;&gt;"",$J126&lt;&gt;"",$J126&lt;$I126),"※到期日早于当票日期",IF(AND($H126&lt;&gt;"",COUNTIF($H$4:$H$403,$H126)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L126&lt;&gt;"",$E126=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -19958,7 +20021,7 @@
       <c r="V127" s="12" t="n"/>
       <c r="W127" s="12" t="n"/>
       <c r="X127" s="18">
-        <f>IF($E127="","",IF(AND($B127&lt;&gt;"",ISNA(MATCH($B127,机构表,0))),"※机构不在【资料】里",IF(AND($D127&lt;&gt;"",ISNA(MATCH($D127,状态表,0))),"※状态不在【资料】里",IF(N($M127)&gt;N($L127),"※已还本金大于典当金额",IF(AND($I127&lt;&gt;"",$J127&lt;&gt;"",$J127&lt;$I127),"※到期日早于当票日期",IF(AND($H127&lt;&gt;"",COUNTIF($H$4:$H$403,$H127)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L127&lt;&gt;"",$E127=""),"※有金额没写客户","")))))</f>
+        <f>IF($E127="","",IF(AND($B127&lt;&gt;"",ISNA(MATCH($B127,机构表,0))),"※机构不在【资料】里",IF(AND($D127&lt;&gt;"",ISNA(MATCH($D127,状态表,0))),"※状态不在【资料】里",IF(N($M127)&gt;N($L127),"※已还本金大于典当金额",IF(AND($I127&lt;&gt;"",$J127&lt;&gt;"",$J127&lt;$I127),"※到期日早于当票日期",IF(AND($H127&lt;&gt;"",COUNTIF($H$4:$H$403,$H127)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L127&lt;&gt;"",$E127=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -20021,7 +20084,7 @@
       <c r="V128" s="12" t="n"/>
       <c r="W128" s="12" t="n"/>
       <c r="X128" s="18">
-        <f>IF($E128="","",IF(AND($B128&lt;&gt;"",ISNA(MATCH($B128,机构表,0))),"※机构不在【资料】里",IF(AND($D128&lt;&gt;"",ISNA(MATCH($D128,状态表,0))),"※状态不在【资料】里",IF(N($M128)&gt;N($L128),"※已还本金大于典当金额",IF(AND($I128&lt;&gt;"",$J128&lt;&gt;"",$J128&lt;$I128),"※到期日早于当票日期",IF(AND($H128&lt;&gt;"",COUNTIF($H$4:$H$403,$H128)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L128&lt;&gt;"",$E128=""),"※有金额没写客户","")))))</f>
+        <f>IF($E128="","",IF(AND($B128&lt;&gt;"",ISNA(MATCH($B128,机构表,0))),"※机构不在【资料】里",IF(AND($D128&lt;&gt;"",ISNA(MATCH($D128,状态表,0))),"※状态不在【资料】里",IF(N($M128)&gt;N($L128),"※已还本金大于典当金额",IF(AND($I128&lt;&gt;"",$J128&lt;&gt;"",$J128&lt;$I128),"※到期日早于当票日期",IF(AND($H128&lt;&gt;"",COUNTIF($H$4:$H$403,$H128)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L128&lt;&gt;"",$E128=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -20080,7 +20143,7 @@
         </is>
       </c>
       <c r="X129" s="18">
-        <f>IF($E129="","",IF(AND($B129&lt;&gt;"",ISNA(MATCH($B129,机构表,0))),"※机构不在【资料】里",IF(AND($D129&lt;&gt;"",ISNA(MATCH($D129,状态表,0))),"※状态不在【资料】里",IF(N($M129)&gt;N($L129),"※已还本金大于典当金额",IF(AND($I129&lt;&gt;"",$J129&lt;&gt;"",$J129&lt;$I129),"※到期日早于当票日期",IF(AND($H129&lt;&gt;"",COUNTIF($H$4:$H$403,$H129)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L129&lt;&gt;"",$E129=""),"※有金额没写客户","")))))</f>
+        <f>IF($E129="","",IF(AND($B129&lt;&gt;"",ISNA(MATCH($B129,机构表,0))),"※机构不在【资料】里",IF(AND($D129&lt;&gt;"",ISNA(MATCH($D129,状态表,0))),"※状态不在【资料】里",IF(N($M129)&gt;N($L129),"※已还本金大于典当金额",IF(AND($I129&lt;&gt;"",$J129&lt;&gt;"",$J129&lt;$I129),"※到期日早于当票日期",IF(AND($H129&lt;&gt;"",COUNTIF($H$4:$H$403,$H129)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L129&lt;&gt;"",$E129=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -20145,7 +20208,7 @@
       <c r="V130" s="12" t="n"/>
       <c r="W130" s="12" t="n"/>
       <c r="X130" s="18">
-        <f>IF($E130="","",IF(AND($B130&lt;&gt;"",ISNA(MATCH($B130,机构表,0))),"※机构不在【资料】里",IF(AND($D130&lt;&gt;"",ISNA(MATCH($D130,状态表,0))),"※状态不在【资料】里",IF(N($M130)&gt;N($L130),"※已还本金大于典当金额",IF(AND($I130&lt;&gt;"",$J130&lt;&gt;"",$J130&lt;$I130),"※到期日早于当票日期",IF(AND($H130&lt;&gt;"",COUNTIF($H$4:$H$403,$H130)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L130&lt;&gt;"",$E130=""),"※有金额没写客户","")))))</f>
+        <f>IF($E130="","",IF(AND($B130&lt;&gt;"",ISNA(MATCH($B130,机构表,0))),"※机构不在【资料】里",IF(AND($D130&lt;&gt;"",ISNA(MATCH($D130,状态表,0))),"※状态不在【资料】里",IF(N($M130)&gt;N($L130),"※已还本金大于典当金额",IF(AND($I130&lt;&gt;"",$J130&lt;&gt;"",$J130&lt;$I130),"※到期日早于当票日期",IF(AND($H130&lt;&gt;"",COUNTIF($H$4:$H$403,$H130)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L130&lt;&gt;"",$E130=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -20208,7 +20271,7 @@
       <c r="V131" s="12" t="n"/>
       <c r="W131" s="12" t="n"/>
       <c r="X131" s="18">
-        <f>IF($E131="","",IF(AND($B131&lt;&gt;"",ISNA(MATCH($B131,机构表,0))),"※机构不在【资料】里",IF(AND($D131&lt;&gt;"",ISNA(MATCH($D131,状态表,0))),"※状态不在【资料】里",IF(N($M131)&gt;N($L131),"※已还本金大于典当金额",IF(AND($I131&lt;&gt;"",$J131&lt;&gt;"",$J131&lt;$I131),"※到期日早于当票日期",IF(AND($H131&lt;&gt;"",COUNTIF($H$4:$H$403,$H131)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L131&lt;&gt;"",$E131=""),"※有金额没写客户","")))))</f>
+        <f>IF($E131="","",IF(AND($B131&lt;&gt;"",ISNA(MATCH($B131,机构表,0))),"※机构不在【资料】里",IF(AND($D131&lt;&gt;"",ISNA(MATCH($D131,状态表,0))),"※状态不在【资料】里",IF(N($M131)&gt;N($L131),"※已还本金大于典当金额",IF(AND($I131&lt;&gt;"",$J131&lt;&gt;"",$J131&lt;$I131),"※到期日早于当票日期",IF(AND($H131&lt;&gt;"",COUNTIF($H$4:$H$403,$H131)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L131&lt;&gt;"",$E131=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -20285,7 +20348,7 @@
       </c>
       <c r="W132" s="12" t="n"/>
       <c r="X132" s="18">
-        <f>IF($E132="","",IF(AND($B132&lt;&gt;"",ISNA(MATCH($B132,机构表,0))),"※机构不在【资料】里",IF(AND($D132&lt;&gt;"",ISNA(MATCH($D132,状态表,0))),"※状态不在【资料】里",IF(N($M132)&gt;N($L132),"※已还本金大于典当金额",IF(AND($I132&lt;&gt;"",$J132&lt;&gt;"",$J132&lt;$I132),"※到期日早于当票日期",IF(AND($H132&lt;&gt;"",COUNTIF($H$4:$H$403,$H132)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L132&lt;&gt;"",$E132=""),"※有金额没写客户","")))))</f>
+        <f>IF($E132="","",IF(AND($B132&lt;&gt;"",ISNA(MATCH($B132,机构表,0))),"※机构不在【资料】里",IF(AND($D132&lt;&gt;"",ISNA(MATCH($D132,状态表,0))),"※状态不在【资料】里",IF(N($M132)&gt;N($L132),"※已还本金大于典当金额",IF(AND($I132&lt;&gt;"",$J132&lt;&gt;"",$J132&lt;$I132),"※到期日早于当票日期",IF(AND($H132&lt;&gt;"",COUNTIF($H$4:$H$403,$H132)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L132&lt;&gt;"",$E132=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -20360,7 +20423,7 @@
         </is>
       </c>
       <c r="X133" s="18">
-        <f>IF($E133="","",IF(AND($B133&lt;&gt;"",ISNA(MATCH($B133,机构表,0))),"※机构不在【资料】里",IF(AND($D133&lt;&gt;"",ISNA(MATCH($D133,状态表,0))),"※状态不在【资料】里",IF(N($M133)&gt;N($L133),"※已还本金大于典当金额",IF(AND($I133&lt;&gt;"",$J133&lt;&gt;"",$J133&lt;$I133),"※到期日早于当票日期",IF(AND($H133&lt;&gt;"",COUNTIF($H$4:$H$403,$H133)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L133&lt;&gt;"",$E133=""),"※有金额没写客户","")))))</f>
+        <f>IF($E133="","",IF(AND($B133&lt;&gt;"",ISNA(MATCH($B133,机构表,0))),"※机构不在【资料】里",IF(AND($D133&lt;&gt;"",ISNA(MATCH($D133,状态表,0))),"※状态不在【资料】里",IF(N($M133)&gt;N($L133),"※已还本金大于典当金额",IF(AND($I133&lt;&gt;"",$J133&lt;&gt;"",$J133&lt;$I133),"※到期日早于当票日期",IF(AND($H133&lt;&gt;"",COUNTIF($H$4:$H$403,$H133)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L133&lt;&gt;"",$E133=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -20423,7 +20486,7 @@
       <c r="V134" s="12" t="n"/>
       <c r="W134" s="12" t="n"/>
       <c r="X134" s="18">
-        <f>IF($E134="","",IF(AND($B134&lt;&gt;"",ISNA(MATCH($B134,机构表,0))),"※机构不在【资料】里",IF(AND($D134&lt;&gt;"",ISNA(MATCH($D134,状态表,0))),"※状态不在【资料】里",IF(N($M134)&gt;N($L134),"※已还本金大于典当金额",IF(AND($I134&lt;&gt;"",$J134&lt;&gt;"",$J134&lt;$I134),"※到期日早于当票日期",IF(AND($H134&lt;&gt;"",COUNTIF($H$4:$H$403,$H134)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L134&lt;&gt;"",$E134=""),"※有金额没写客户","")))))</f>
+        <f>IF($E134="","",IF(AND($B134&lt;&gt;"",ISNA(MATCH($B134,机构表,0))),"※机构不在【资料】里",IF(AND($D134&lt;&gt;"",ISNA(MATCH($D134,状态表,0))),"※状态不在【资料】里",IF(N($M134)&gt;N($L134),"※已还本金大于典当金额",IF(AND($I134&lt;&gt;"",$J134&lt;&gt;"",$J134&lt;$I134),"※到期日早于当票日期",IF(AND($H134&lt;&gt;"",COUNTIF($H$4:$H$403,$H134)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L134&lt;&gt;"",$E134=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -20484,7 +20547,7 @@
       <c r="V135" s="12" t="n"/>
       <c r="W135" s="12" t="n"/>
       <c r="X135" s="18">
-        <f>IF($E135="","",IF(AND($B135&lt;&gt;"",ISNA(MATCH($B135,机构表,0))),"※机构不在【资料】里",IF(AND($D135&lt;&gt;"",ISNA(MATCH($D135,状态表,0))),"※状态不在【资料】里",IF(N($M135)&gt;N($L135),"※已还本金大于典当金额",IF(AND($I135&lt;&gt;"",$J135&lt;&gt;"",$J135&lt;$I135),"※到期日早于当票日期",IF(AND($H135&lt;&gt;"",COUNTIF($H$4:$H$403,$H135)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L135&lt;&gt;"",$E135=""),"※有金额没写客户","")))))</f>
+        <f>IF($E135="","",IF(AND($B135&lt;&gt;"",ISNA(MATCH($B135,机构表,0))),"※机构不在【资料】里",IF(AND($D135&lt;&gt;"",ISNA(MATCH($D135,状态表,0))),"※状态不在【资料】里",IF(N($M135)&gt;N($L135),"※已还本金大于典当金额",IF(AND($I135&lt;&gt;"",$J135&lt;&gt;"",$J135&lt;$I135),"※到期日早于当票日期",IF(AND($H135&lt;&gt;"",COUNTIF($H$4:$H$403,$H135)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L135&lt;&gt;"",$E135=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -20547,7 +20610,7 @@
       <c r="V136" s="12" t="n"/>
       <c r="W136" s="12" t="n"/>
       <c r="X136" s="18">
-        <f>IF($E136="","",IF(AND($B136&lt;&gt;"",ISNA(MATCH($B136,机构表,0))),"※机构不在【资料】里",IF(AND($D136&lt;&gt;"",ISNA(MATCH($D136,状态表,0))),"※状态不在【资料】里",IF(N($M136)&gt;N($L136),"※已还本金大于典当金额",IF(AND($I136&lt;&gt;"",$J136&lt;&gt;"",$J136&lt;$I136),"※到期日早于当票日期",IF(AND($H136&lt;&gt;"",COUNTIF($H$4:$H$403,$H136)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L136&lt;&gt;"",$E136=""),"※有金额没写客户","")))))</f>
+        <f>IF($E136="","",IF(AND($B136&lt;&gt;"",ISNA(MATCH($B136,机构表,0))),"※机构不在【资料】里",IF(AND($D136&lt;&gt;"",ISNA(MATCH($D136,状态表,0))),"※状态不在【资料】里",IF(N($M136)&gt;N($L136),"※已还本金大于典当金额",IF(AND($I136&lt;&gt;"",$J136&lt;&gt;"",$J136&lt;$I136),"※到期日早于当票日期",IF(AND($H136&lt;&gt;"",COUNTIF($H$4:$H$403,$H136)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L136&lt;&gt;"",$E136=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -20610,7 +20673,7 @@
       <c r="V137" s="12" t="n"/>
       <c r="W137" s="12" t="n"/>
       <c r="X137" s="18">
-        <f>IF($E137="","",IF(AND($B137&lt;&gt;"",ISNA(MATCH($B137,机构表,0))),"※机构不在【资料】里",IF(AND($D137&lt;&gt;"",ISNA(MATCH($D137,状态表,0))),"※状态不在【资料】里",IF(N($M137)&gt;N($L137),"※已还本金大于典当金额",IF(AND($I137&lt;&gt;"",$J137&lt;&gt;"",$J137&lt;$I137),"※到期日早于当票日期",IF(AND($H137&lt;&gt;"",COUNTIF($H$4:$H$403,$H137)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L137&lt;&gt;"",$E137=""),"※有金额没写客户","")))))</f>
+        <f>IF($E137="","",IF(AND($B137&lt;&gt;"",ISNA(MATCH($B137,机构表,0))),"※机构不在【资料】里",IF(AND($D137&lt;&gt;"",ISNA(MATCH($D137,状态表,0))),"※状态不在【资料】里",IF(N($M137)&gt;N($L137),"※已还本金大于典当金额",IF(AND($I137&lt;&gt;"",$J137&lt;&gt;"",$J137&lt;$I137),"※到期日早于当票日期",IF(AND($H137&lt;&gt;"",COUNTIF($H$4:$H$403,$H137)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L137&lt;&gt;"",$E137=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -20687,7 +20750,7 @@
       </c>
       <c r="W138" s="12" t="n"/>
       <c r="X138" s="18">
-        <f>IF($E138="","",IF(AND($B138&lt;&gt;"",ISNA(MATCH($B138,机构表,0))),"※机构不在【资料】里",IF(AND($D138&lt;&gt;"",ISNA(MATCH($D138,状态表,0))),"※状态不在【资料】里",IF(N($M138)&gt;N($L138),"※已还本金大于典当金额",IF(AND($I138&lt;&gt;"",$J138&lt;&gt;"",$J138&lt;$I138),"※到期日早于当票日期",IF(AND($H138&lt;&gt;"",COUNTIF($H$4:$H$403,$H138)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L138&lt;&gt;"",$E138=""),"※有金额没写客户","")))))</f>
+        <f>IF($E138="","",IF(AND($B138&lt;&gt;"",ISNA(MATCH($B138,机构表,0))),"※机构不在【资料】里",IF(AND($D138&lt;&gt;"",ISNA(MATCH($D138,状态表,0))),"※状态不在【资料】里",IF(N($M138)&gt;N($L138),"※已还本金大于典当金额",IF(AND($I138&lt;&gt;"",$J138&lt;&gt;"",$J138&lt;$I138),"※到期日早于当票日期",IF(AND($H138&lt;&gt;"",COUNTIF($H$4:$H$403,$H138)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L138&lt;&gt;"",$E138=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -20762,7 +20825,7 @@
       </c>
       <c r="W139" s="12" t="n"/>
       <c r="X139" s="18">
-        <f>IF($E139="","",IF(AND($B139&lt;&gt;"",ISNA(MATCH($B139,机构表,0))),"※机构不在【资料】里",IF(AND($D139&lt;&gt;"",ISNA(MATCH($D139,状态表,0))),"※状态不在【资料】里",IF(N($M139)&gt;N($L139),"※已还本金大于典当金额",IF(AND($I139&lt;&gt;"",$J139&lt;&gt;"",$J139&lt;$I139),"※到期日早于当票日期",IF(AND($H139&lt;&gt;"",COUNTIF($H$4:$H$403,$H139)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L139&lt;&gt;"",$E139=""),"※有金额没写客户","")))))</f>
+        <f>IF($E139="","",IF(AND($B139&lt;&gt;"",ISNA(MATCH($B139,机构表,0))),"※机构不在【资料】里",IF(AND($D139&lt;&gt;"",ISNA(MATCH($D139,状态表,0))),"※状态不在【资料】里",IF(N($M139)&gt;N($L139),"※已还本金大于典当金额",IF(AND($I139&lt;&gt;"",$J139&lt;&gt;"",$J139&lt;$I139),"※到期日早于当票日期",IF(AND($H139&lt;&gt;"",COUNTIF($H$4:$H$403,$H139)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L139&lt;&gt;"",$E139=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -20827,7 +20890,7 @@
       <c r="V140" s="12" t="n"/>
       <c r="W140" s="12" t="n"/>
       <c r="X140" s="18">
-        <f>IF($E140="","",IF(AND($B140&lt;&gt;"",ISNA(MATCH($B140,机构表,0))),"※机构不在【资料】里",IF(AND($D140&lt;&gt;"",ISNA(MATCH($D140,状态表,0))),"※状态不在【资料】里",IF(N($M140)&gt;N($L140),"※已还本金大于典当金额",IF(AND($I140&lt;&gt;"",$J140&lt;&gt;"",$J140&lt;$I140),"※到期日早于当票日期",IF(AND($H140&lt;&gt;"",COUNTIF($H$4:$H$403,$H140)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L140&lt;&gt;"",$E140=""),"※有金额没写客户","")))))</f>
+        <f>IF($E140="","",IF(AND($B140&lt;&gt;"",ISNA(MATCH($B140,机构表,0))),"※机构不在【资料】里",IF(AND($D140&lt;&gt;"",ISNA(MATCH($D140,状态表,0))),"※状态不在【资料】里",IF(N($M140)&gt;N($L140),"※已还本金大于典当金额",IF(AND($I140&lt;&gt;"",$J140&lt;&gt;"",$J140&lt;$I140),"※到期日早于当票日期",IF(AND($H140&lt;&gt;"",COUNTIF($H$4:$H$403,$H140)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L140&lt;&gt;"",$E140=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -20900,7 +20963,7 @@
       <c r="V141" s="12" t="n"/>
       <c r="W141" s="12" t="n"/>
       <c r="X141" s="18">
-        <f>IF($E141="","",IF(AND($B141&lt;&gt;"",ISNA(MATCH($B141,机构表,0))),"※机构不在【资料】里",IF(AND($D141&lt;&gt;"",ISNA(MATCH($D141,状态表,0))),"※状态不在【资料】里",IF(N($M141)&gt;N($L141),"※已还本金大于典当金额",IF(AND($I141&lt;&gt;"",$J141&lt;&gt;"",$J141&lt;$I141),"※到期日早于当票日期",IF(AND($H141&lt;&gt;"",COUNTIF($H$4:$H$403,$H141)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L141&lt;&gt;"",$E141=""),"※有金额没写客户","")))))</f>
+        <f>IF($E141="","",IF(AND($B141&lt;&gt;"",ISNA(MATCH($B141,机构表,0))),"※机构不在【资料】里",IF(AND($D141&lt;&gt;"",ISNA(MATCH($D141,状态表,0))),"※状态不在【资料】里",IF(N($M141)&gt;N($L141),"※已还本金大于典当金额",IF(AND($I141&lt;&gt;"",$J141&lt;&gt;"",$J141&lt;$I141),"※到期日早于当票日期",IF(AND($H141&lt;&gt;"",COUNTIF($H$4:$H$403,$H141)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L141&lt;&gt;"",$E141=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -20967,7 +21030,7 @@
       <c r="V142" s="12" t="n"/>
       <c r="W142" s="12" t="n"/>
       <c r="X142" s="18">
-        <f>IF($E142="","",IF(AND($B142&lt;&gt;"",ISNA(MATCH($B142,机构表,0))),"※机构不在【资料】里",IF(AND($D142&lt;&gt;"",ISNA(MATCH($D142,状态表,0))),"※状态不在【资料】里",IF(N($M142)&gt;N($L142),"※已还本金大于典当金额",IF(AND($I142&lt;&gt;"",$J142&lt;&gt;"",$J142&lt;$I142),"※到期日早于当票日期",IF(AND($H142&lt;&gt;"",COUNTIF($H$4:$H$403,$H142)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L142&lt;&gt;"",$E142=""),"※有金额没写客户","")))))</f>
+        <f>IF($E142="","",IF(AND($B142&lt;&gt;"",ISNA(MATCH($B142,机构表,0))),"※机构不在【资料】里",IF(AND($D142&lt;&gt;"",ISNA(MATCH($D142,状态表,0))),"※状态不在【资料】里",IF(N($M142)&gt;N($L142),"※已还本金大于典当金额",IF(AND($I142&lt;&gt;"",$J142&lt;&gt;"",$J142&lt;$I142),"※到期日早于当票日期",IF(AND($H142&lt;&gt;"",COUNTIF($H$4:$H$403,$H142)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L142&lt;&gt;"",$E142=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -21030,7 +21093,7 @@
       <c r="V143" s="12" t="n"/>
       <c r="W143" s="12" t="n"/>
       <c r="X143" s="18">
-        <f>IF($E143="","",IF(AND($B143&lt;&gt;"",ISNA(MATCH($B143,机构表,0))),"※机构不在【资料】里",IF(AND($D143&lt;&gt;"",ISNA(MATCH($D143,状态表,0))),"※状态不在【资料】里",IF(N($M143)&gt;N($L143),"※已还本金大于典当金额",IF(AND($I143&lt;&gt;"",$J143&lt;&gt;"",$J143&lt;$I143),"※到期日早于当票日期",IF(AND($H143&lt;&gt;"",COUNTIF($H$4:$H$403,$H143)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L143&lt;&gt;"",$E143=""),"※有金额没写客户","")))))</f>
+        <f>IF($E143="","",IF(AND($B143&lt;&gt;"",ISNA(MATCH($B143,机构表,0))),"※机构不在【资料】里",IF(AND($D143&lt;&gt;"",ISNA(MATCH($D143,状态表,0))),"※状态不在【资料】里",IF(N($M143)&gt;N($L143),"※已还本金大于典当金额",IF(AND($I143&lt;&gt;"",$J143&lt;&gt;"",$J143&lt;$I143),"※到期日早于当票日期",IF(AND($H143&lt;&gt;"",COUNTIF($H$4:$H$403,$H143)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L143&lt;&gt;"",$E143=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -21089,7 +21152,7 @@
         </is>
       </c>
       <c r="X144" s="18">
-        <f>IF($E144="","",IF(AND($B144&lt;&gt;"",ISNA(MATCH($B144,机构表,0))),"※机构不在【资料】里",IF(AND($D144&lt;&gt;"",ISNA(MATCH($D144,状态表,0))),"※状态不在【资料】里",IF(N($M144)&gt;N($L144),"※已还本金大于典当金额",IF(AND($I144&lt;&gt;"",$J144&lt;&gt;"",$J144&lt;$I144),"※到期日早于当票日期",IF(AND($H144&lt;&gt;"",COUNTIF($H$4:$H$403,$H144)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L144&lt;&gt;"",$E144=""),"※有金额没写客户","")))))</f>
+        <f>IF($E144="","",IF(AND($B144&lt;&gt;"",ISNA(MATCH($B144,机构表,0))),"※机构不在【资料】里",IF(AND($D144&lt;&gt;"",ISNA(MATCH($D144,状态表,0))),"※状态不在【资料】里",IF(N($M144)&gt;N($L144),"※已还本金大于典当金额",IF(AND($I144&lt;&gt;"",$J144&lt;&gt;"",$J144&lt;$I144),"※到期日早于当票日期",IF(AND($H144&lt;&gt;"",COUNTIF($H$4:$H$403,$H144)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L144&lt;&gt;"",$E144=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -21152,7 +21215,7 @@
       <c r="V145" s="12" t="n"/>
       <c r="W145" s="12" t="n"/>
       <c r="X145" s="18">
-        <f>IF($E145="","",IF(AND($B145&lt;&gt;"",ISNA(MATCH($B145,机构表,0))),"※机构不在【资料】里",IF(AND($D145&lt;&gt;"",ISNA(MATCH($D145,状态表,0))),"※状态不在【资料】里",IF(N($M145)&gt;N($L145),"※已还本金大于典当金额",IF(AND($I145&lt;&gt;"",$J145&lt;&gt;"",$J145&lt;$I145),"※到期日早于当票日期",IF(AND($H145&lt;&gt;"",COUNTIF($H$4:$H$403,$H145)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L145&lt;&gt;"",$E145=""),"※有金额没写客户","")))))</f>
+        <f>IF($E145="","",IF(AND($B145&lt;&gt;"",ISNA(MATCH($B145,机构表,0))),"※机构不在【资料】里",IF(AND($D145&lt;&gt;"",ISNA(MATCH($D145,状态表,0))),"※状态不在【资料】里",IF(N($M145)&gt;N($L145),"※已还本金大于典当金额",IF(AND($I145&lt;&gt;"",$J145&lt;&gt;"",$J145&lt;$I145),"※到期日早于当票日期",IF(AND($H145&lt;&gt;"",COUNTIF($H$4:$H$403,$H145)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L145&lt;&gt;"",$E145=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -21215,7 +21278,7 @@
       <c r="V146" s="12" t="n"/>
       <c r="W146" s="12" t="n"/>
       <c r="X146" s="18">
-        <f>IF($E146="","",IF(AND($B146&lt;&gt;"",ISNA(MATCH($B146,机构表,0))),"※机构不在【资料】里",IF(AND($D146&lt;&gt;"",ISNA(MATCH($D146,状态表,0))),"※状态不在【资料】里",IF(N($M146)&gt;N($L146),"※已还本金大于典当金额",IF(AND($I146&lt;&gt;"",$J146&lt;&gt;"",$J146&lt;$I146),"※到期日早于当票日期",IF(AND($H146&lt;&gt;"",COUNTIF($H$4:$H$403,$H146)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L146&lt;&gt;"",$E146=""),"※有金额没写客户","")))))</f>
+        <f>IF($E146="","",IF(AND($B146&lt;&gt;"",ISNA(MATCH($B146,机构表,0))),"※机构不在【资料】里",IF(AND($D146&lt;&gt;"",ISNA(MATCH($D146,状态表,0))),"※状态不在【资料】里",IF(N($M146)&gt;N($L146),"※已还本金大于典当金额",IF(AND($I146&lt;&gt;"",$J146&lt;&gt;"",$J146&lt;$I146),"※到期日早于当票日期",IF(AND($H146&lt;&gt;"",COUNTIF($H$4:$H$403,$H146)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L146&lt;&gt;"",$E146=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -21288,7 +21351,7 @@
       </c>
       <c r="W147" s="12" t="n"/>
       <c r="X147" s="18">
-        <f>IF($E147="","",IF(AND($B147&lt;&gt;"",ISNA(MATCH($B147,机构表,0))),"※机构不在【资料】里",IF(AND($D147&lt;&gt;"",ISNA(MATCH($D147,状态表,0))),"※状态不在【资料】里",IF(N($M147)&gt;N($L147),"※已还本金大于典当金额",IF(AND($I147&lt;&gt;"",$J147&lt;&gt;"",$J147&lt;$I147),"※到期日早于当票日期",IF(AND($H147&lt;&gt;"",COUNTIF($H$4:$H$403,$H147)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L147&lt;&gt;"",$E147=""),"※有金额没写客户","")))))</f>
+        <f>IF($E147="","",IF(AND($B147&lt;&gt;"",ISNA(MATCH($B147,机构表,0))),"※机构不在【资料】里",IF(AND($D147&lt;&gt;"",ISNA(MATCH($D147,状态表,0))),"※状态不在【资料】里",IF(N($M147)&gt;N($L147),"※已还本金大于典当金额",IF(AND($I147&lt;&gt;"",$J147&lt;&gt;"",$J147&lt;$I147),"※到期日早于当票日期",IF(AND($H147&lt;&gt;"",COUNTIF($H$4:$H$403,$H147)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L147&lt;&gt;"",$E147=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -21361,7 +21424,7 @@
       </c>
       <c r="W148" s="12" t="n"/>
       <c r="X148" s="18">
-        <f>IF($E148="","",IF(AND($B148&lt;&gt;"",ISNA(MATCH($B148,机构表,0))),"※机构不在【资料】里",IF(AND($D148&lt;&gt;"",ISNA(MATCH($D148,状态表,0))),"※状态不在【资料】里",IF(N($M148)&gt;N($L148),"※已还本金大于典当金额",IF(AND($I148&lt;&gt;"",$J148&lt;&gt;"",$J148&lt;$I148),"※到期日早于当票日期",IF(AND($H148&lt;&gt;"",COUNTIF($H$4:$H$403,$H148)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L148&lt;&gt;"",$E148=""),"※有金额没写客户","")))))</f>
+        <f>IF($E148="","",IF(AND($B148&lt;&gt;"",ISNA(MATCH($B148,机构表,0))),"※机构不在【资料】里",IF(AND($D148&lt;&gt;"",ISNA(MATCH($D148,状态表,0))),"※状态不在【资料】里",IF(N($M148)&gt;N($L148),"※已还本金大于典当金额",IF(AND($I148&lt;&gt;"",$J148&lt;&gt;"",$J148&lt;$I148),"※到期日早于当票日期",IF(AND($H148&lt;&gt;"",COUNTIF($H$4:$H$403,$H148)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L148&lt;&gt;"",$E148=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -21424,7 +21487,7 @@
       <c r="V149" s="12" t="n"/>
       <c r="W149" s="12" t="n"/>
       <c r="X149" s="18">
-        <f>IF($E149="","",IF(AND($B149&lt;&gt;"",ISNA(MATCH($B149,机构表,0))),"※机构不在【资料】里",IF(AND($D149&lt;&gt;"",ISNA(MATCH($D149,状态表,0))),"※状态不在【资料】里",IF(N($M149)&gt;N($L149),"※已还本金大于典当金额",IF(AND($I149&lt;&gt;"",$J149&lt;&gt;"",$J149&lt;$I149),"※到期日早于当票日期",IF(AND($H149&lt;&gt;"",COUNTIF($H$4:$H$403,$H149)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L149&lt;&gt;"",$E149=""),"※有金额没写客户","")))))</f>
+        <f>IF($E149="","",IF(AND($B149&lt;&gt;"",ISNA(MATCH($B149,机构表,0))),"※机构不在【资料】里",IF(AND($D149&lt;&gt;"",ISNA(MATCH($D149,状态表,0))),"※状态不在【资料】里",IF(N($M149)&gt;N($L149),"※已还本金大于典当金额",IF(AND($I149&lt;&gt;"",$J149&lt;&gt;"",$J149&lt;$I149),"※到期日早于当票日期",IF(AND($H149&lt;&gt;"",COUNTIF($H$4:$H$403,$H149)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L149&lt;&gt;"",$E149=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -21487,7 +21550,7 @@
       <c r="V150" s="12" t="n"/>
       <c r="W150" s="12" t="n"/>
       <c r="X150" s="18">
-        <f>IF($E150="","",IF(AND($B150&lt;&gt;"",ISNA(MATCH($B150,机构表,0))),"※机构不在【资料】里",IF(AND($D150&lt;&gt;"",ISNA(MATCH($D150,状态表,0))),"※状态不在【资料】里",IF(N($M150)&gt;N($L150),"※已还本金大于典当金额",IF(AND($I150&lt;&gt;"",$J150&lt;&gt;"",$J150&lt;$I150),"※到期日早于当票日期",IF(AND($H150&lt;&gt;"",COUNTIF($H$4:$H$403,$H150)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L150&lt;&gt;"",$E150=""),"※有金额没写客户","")))))</f>
+        <f>IF($E150="","",IF(AND($B150&lt;&gt;"",ISNA(MATCH($B150,机构表,0))),"※机构不在【资料】里",IF(AND($D150&lt;&gt;"",ISNA(MATCH($D150,状态表,0))),"※状态不在【资料】里",IF(N($M150)&gt;N($L150),"※已还本金大于典当金额",IF(AND($I150&lt;&gt;"",$J150&lt;&gt;"",$J150&lt;$I150),"※到期日早于当票日期",IF(AND($H150&lt;&gt;"",COUNTIF($H$4:$H$403,$H150)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L150&lt;&gt;"",$E150=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -21552,7 +21615,7 @@
       <c r="V151" s="12" t="n"/>
       <c r="W151" s="12" t="n"/>
       <c r="X151" s="18">
-        <f>IF($E151="","",IF(AND($B151&lt;&gt;"",ISNA(MATCH($B151,机构表,0))),"※机构不在【资料】里",IF(AND($D151&lt;&gt;"",ISNA(MATCH($D151,状态表,0))),"※状态不在【资料】里",IF(N($M151)&gt;N($L151),"※已还本金大于典当金额",IF(AND($I151&lt;&gt;"",$J151&lt;&gt;"",$J151&lt;$I151),"※到期日早于当票日期",IF(AND($H151&lt;&gt;"",COUNTIF($H$4:$H$403,$H151)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L151&lt;&gt;"",$E151=""),"※有金额没写客户","")))))</f>
+        <f>IF($E151="","",IF(AND($B151&lt;&gt;"",ISNA(MATCH($B151,机构表,0))),"※机构不在【资料】里",IF(AND($D151&lt;&gt;"",ISNA(MATCH($D151,状态表,0))),"※状态不在【资料】里",IF(N($M151)&gt;N($L151),"※已还本金大于典当金额",IF(AND($I151&lt;&gt;"",$J151&lt;&gt;"",$J151&lt;$I151),"※到期日早于当票日期",IF(AND($H151&lt;&gt;"",COUNTIF($H$4:$H$403,$H151)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L151&lt;&gt;"",$E151=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -21615,7 +21678,7 @@
       <c r="V152" s="12" t="n"/>
       <c r="W152" s="12" t="n"/>
       <c r="X152" s="18">
-        <f>IF($E152="","",IF(AND($B152&lt;&gt;"",ISNA(MATCH($B152,机构表,0))),"※机构不在【资料】里",IF(AND($D152&lt;&gt;"",ISNA(MATCH($D152,状态表,0))),"※状态不在【资料】里",IF(N($M152)&gt;N($L152),"※已还本金大于典当金额",IF(AND($I152&lt;&gt;"",$J152&lt;&gt;"",$J152&lt;$I152),"※到期日早于当票日期",IF(AND($H152&lt;&gt;"",COUNTIF($H$4:$H$403,$H152)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L152&lt;&gt;"",$E152=""),"※有金额没写客户","")))))</f>
+        <f>IF($E152="","",IF(AND($B152&lt;&gt;"",ISNA(MATCH($B152,机构表,0))),"※机构不在【资料】里",IF(AND($D152&lt;&gt;"",ISNA(MATCH($D152,状态表,0))),"※状态不在【资料】里",IF(N($M152)&gt;N($L152),"※已还本金大于典当金额",IF(AND($I152&lt;&gt;"",$J152&lt;&gt;"",$J152&lt;$I152),"※到期日早于当票日期",IF(AND($H152&lt;&gt;"",COUNTIF($H$4:$H$403,$H152)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L152&lt;&gt;"",$E152=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -21682,7 +21745,7 @@
         </is>
       </c>
       <c r="X153" s="18">
-        <f>IF($E153="","",IF(AND($B153&lt;&gt;"",ISNA(MATCH($B153,机构表,0))),"※机构不在【资料】里",IF(AND($D153&lt;&gt;"",ISNA(MATCH($D153,状态表,0))),"※状态不在【资料】里",IF(N($M153)&gt;N($L153),"※已还本金大于典当金额",IF(AND($I153&lt;&gt;"",$J153&lt;&gt;"",$J153&lt;$I153),"※到期日早于当票日期",IF(AND($H153&lt;&gt;"",COUNTIF($H$4:$H$403,$H153)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L153&lt;&gt;"",$E153=""),"※有金额没写客户","")))))</f>
+        <f>IF($E153="","",IF(AND($B153&lt;&gt;"",ISNA(MATCH($B153,机构表,0))),"※机构不在【资料】里",IF(AND($D153&lt;&gt;"",ISNA(MATCH($D153,状态表,0))),"※状态不在【资料】里",IF(N($M153)&gt;N($L153),"※已还本金大于典当金额",IF(AND($I153&lt;&gt;"",$J153&lt;&gt;"",$J153&lt;$I153),"※到期日早于当票日期",IF(AND($H153&lt;&gt;"",COUNTIF($H$4:$H$403,$H153)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L153&lt;&gt;"",$E153=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -21745,7 +21808,7 @@
       <c r="V154" s="12" t="n"/>
       <c r="W154" s="12" t="n"/>
       <c r="X154" s="18">
-        <f>IF($E154="","",IF(AND($B154&lt;&gt;"",ISNA(MATCH($B154,机构表,0))),"※机构不在【资料】里",IF(AND($D154&lt;&gt;"",ISNA(MATCH($D154,状态表,0))),"※状态不在【资料】里",IF(N($M154)&gt;N($L154),"※已还本金大于典当金额",IF(AND($I154&lt;&gt;"",$J154&lt;&gt;"",$J154&lt;$I154),"※到期日早于当票日期",IF(AND($H154&lt;&gt;"",COUNTIF($H$4:$H$403,$H154)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L154&lt;&gt;"",$E154=""),"※有金额没写客户","")))))</f>
+        <f>IF($E154="","",IF(AND($B154&lt;&gt;"",ISNA(MATCH($B154,机构表,0))),"※机构不在【资料】里",IF(AND($D154&lt;&gt;"",ISNA(MATCH($D154,状态表,0))),"※状态不在【资料】里",IF(N($M154)&gt;N($L154),"※已还本金大于典当金额",IF(AND($I154&lt;&gt;"",$J154&lt;&gt;"",$J154&lt;$I154),"※到期日早于当票日期",IF(AND($H154&lt;&gt;"",COUNTIF($H$4:$H$403,$H154)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L154&lt;&gt;"",$E154=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -21810,7 +21873,7 @@
       <c r="V155" s="12" t="n"/>
       <c r="W155" s="12" t="n"/>
       <c r="X155" s="18">
-        <f>IF($E155="","",IF(AND($B155&lt;&gt;"",ISNA(MATCH($B155,机构表,0))),"※机构不在【资料】里",IF(AND($D155&lt;&gt;"",ISNA(MATCH($D155,状态表,0))),"※状态不在【资料】里",IF(N($M155)&gt;N($L155),"※已还本金大于典当金额",IF(AND($I155&lt;&gt;"",$J155&lt;&gt;"",$J155&lt;$I155),"※到期日早于当票日期",IF(AND($H155&lt;&gt;"",COUNTIF($H$4:$H$403,$H155)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L155&lt;&gt;"",$E155=""),"※有金额没写客户","")))))</f>
+        <f>IF($E155="","",IF(AND($B155&lt;&gt;"",ISNA(MATCH($B155,机构表,0))),"※机构不在【资料】里",IF(AND($D155&lt;&gt;"",ISNA(MATCH($D155,状态表,0))),"※状态不在【资料】里",IF(N($M155)&gt;N($L155),"※已还本金大于典当金额",IF(AND($I155&lt;&gt;"",$J155&lt;&gt;"",$J155&lt;$I155),"※到期日早于当票日期",IF(AND($H155&lt;&gt;"",COUNTIF($H$4:$H$403,$H155)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L155&lt;&gt;"",$E155=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -21875,7 +21938,7 @@
       <c r="V156" s="12" t="n"/>
       <c r="W156" s="12" t="n"/>
       <c r="X156" s="18">
-        <f>IF($E156="","",IF(AND($B156&lt;&gt;"",ISNA(MATCH($B156,机构表,0))),"※机构不在【资料】里",IF(AND($D156&lt;&gt;"",ISNA(MATCH($D156,状态表,0))),"※状态不在【资料】里",IF(N($M156)&gt;N($L156),"※已还本金大于典当金额",IF(AND($I156&lt;&gt;"",$J156&lt;&gt;"",$J156&lt;$I156),"※到期日早于当票日期",IF(AND($H156&lt;&gt;"",COUNTIF($H$4:$H$403,$H156)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L156&lt;&gt;"",$E156=""),"※有金额没写客户","")))))</f>
+        <f>IF($E156="","",IF(AND($B156&lt;&gt;"",ISNA(MATCH($B156,机构表,0))),"※机构不在【资料】里",IF(AND($D156&lt;&gt;"",ISNA(MATCH($D156,状态表,0))),"※状态不在【资料】里",IF(N($M156)&gt;N($L156),"※已还本金大于典当金额",IF(AND($I156&lt;&gt;"",$J156&lt;&gt;"",$J156&lt;$I156),"※到期日早于当票日期",IF(AND($H156&lt;&gt;"",COUNTIF($H$4:$H$403,$H156)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L156&lt;&gt;"",$E156=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -21950,7 +22013,7 @@
       </c>
       <c r="W157" s="12" t="n"/>
       <c r="X157" s="18">
-        <f>IF($E157="","",IF(AND($B157&lt;&gt;"",ISNA(MATCH($B157,机构表,0))),"※机构不在【资料】里",IF(AND($D157&lt;&gt;"",ISNA(MATCH($D157,状态表,0))),"※状态不在【资料】里",IF(N($M157)&gt;N($L157),"※已还本金大于典当金额",IF(AND($I157&lt;&gt;"",$J157&lt;&gt;"",$J157&lt;$I157),"※到期日早于当票日期",IF(AND($H157&lt;&gt;"",COUNTIF($H$4:$H$403,$H157)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L157&lt;&gt;"",$E157=""),"※有金额没写客户","")))))</f>
+        <f>IF($E157="","",IF(AND($B157&lt;&gt;"",ISNA(MATCH($B157,机构表,0))),"※机构不在【资料】里",IF(AND($D157&lt;&gt;"",ISNA(MATCH($D157,状态表,0))),"※状态不在【资料】里",IF(N($M157)&gt;N($L157),"※已还本金大于典当金额",IF(AND($I157&lt;&gt;"",$J157&lt;&gt;"",$J157&lt;$I157),"※到期日早于当票日期",IF(AND($H157&lt;&gt;"",COUNTIF($H$4:$H$403,$H157)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L157&lt;&gt;"",$E157=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -22025,7 +22088,7 @@
       </c>
       <c r="W158" s="12" t="n"/>
       <c r="X158" s="18">
-        <f>IF($E158="","",IF(AND($B158&lt;&gt;"",ISNA(MATCH($B158,机构表,0))),"※机构不在【资料】里",IF(AND($D158&lt;&gt;"",ISNA(MATCH($D158,状态表,0))),"※状态不在【资料】里",IF(N($M158)&gt;N($L158),"※已还本金大于典当金额",IF(AND($I158&lt;&gt;"",$J158&lt;&gt;"",$J158&lt;$I158),"※到期日早于当票日期",IF(AND($H158&lt;&gt;"",COUNTIF($H$4:$H$403,$H158)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L158&lt;&gt;"",$E158=""),"※有金额没写客户","")))))</f>
+        <f>IF($E158="","",IF(AND($B158&lt;&gt;"",ISNA(MATCH($B158,机构表,0))),"※机构不在【资料】里",IF(AND($D158&lt;&gt;"",ISNA(MATCH($D158,状态表,0))),"※状态不在【资料】里",IF(N($M158)&gt;N($L158),"※已还本金大于典当金额",IF(AND($I158&lt;&gt;"",$J158&lt;&gt;"",$J158&lt;$I158),"※到期日早于当票日期",IF(AND($H158&lt;&gt;"",COUNTIF($H$4:$H$403,$H158)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L158&lt;&gt;"",$E158=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -22090,7 +22153,7 @@
       <c r="V159" s="12" t="n"/>
       <c r="W159" s="12" t="n"/>
       <c r="X159" s="18">
-        <f>IF($E159="","",IF(AND($B159&lt;&gt;"",ISNA(MATCH($B159,机构表,0))),"※机构不在【资料】里",IF(AND($D159&lt;&gt;"",ISNA(MATCH($D159,状态表,0))),"※状态不在【资料】里",IF(N($M159)&gt;N($L159),"※已还本金大于典当金额",IF(AND($I159&lt;&gt;"",$J159&lt;&gt;"",$J159&lt;$I159),"※到期日早于当票日期",IF(AND($H159&lt;&gt;"",COUNTIF($H$4:$H$403,$H159)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L159&lt;&gt;"",$E159=""),"※有金额没写客户","")))))</f>
+        <f>IF($E159="","",IF(AND($B159&lt;&gt;"",ISNA(MATCH($B159,机构表,0))),"※机构不在【资料】里",IF(AND($D159&lt;&gt;"",ISNA(MATCH($D159,状态表,0))),"※状态不在【资料】里",IF(N($M159)&gt;N($L159),"※已还本金大于典当金额",IF(AND($I159&lt;&gt;"",$J159&lt;&gt;"",$J159&lt;$I159),"※到期日早于当票日期",IF(AND($H159&lt;&gt;"",COUNTIF($H$4:$H$403,$H159)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L159&lt;&gt;"",$E159=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -22167,7 +22230,7 @@
       </c>
       <c r="W160" s="12" t="n"/>
       <c r="X160" s="18">
-        <f>IF($E160="","",IF(AND($B160&lt;&gt;"",ISNA(MATCH($B160,机构表,0))),"※机构不在【资料】里",IF(AND($D160&lt;&gt;"",ISNA(MATCH($D160,状态表,0))),"※状态不在【资料】里",IF(N($M160)&gt;N($L160),"※已还本金大于典当金额",IF(AND($I160&lt;&gt;"",$J160&lt;&gt;"",$J160&lt;$I160),"※到期日早于当票日期",IF(AND($H160&lt;&gt;"",COUNTIF($H$4:$H$403,$H160)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L160&lt;&gt;"",$E160=""),"※有金额没写客户","")))))</f>
+        <f>IF($E160="","",IF(AND($B160&lt;&gt;"",ISNA(MATCH($B160,机构表,0))),"※机构不在【资料】里",IF(AND($D160&lt;&gt;"",ISNA(MATCH($D160,状态表,0))),"※状态不在【资料】里",IF(N($M160)&gt;N($L160),"※已还本金大于典当金额",IF(AND($I160&lt;&gt;"",$J160&lt;&gt;"",$J160&lt;$I160),"※到期日早于当票日期",IF(AND($H160&lt;&gt;"",COUNTIF($H$4:$H$403,$H160)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L160&lt;&gt;"",$E160=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -22230,7 +22293,7 @@
       <c r="V161" s="12" t="n"/>
       <c r="W161" s="12" t="n"/>
       <c r="X161" s="18">
-        <f>IF($E161="","",IF(AND($B161&lt;&gt;"",ISNA(MATCH($B161,机构表,0))),"※机构不在【资料】里",IF(AND($D161&lt;&gt;"",ISNA(MATCH($D161,状态表,0))),"※状态不在【资料】里",IF(N($M161)&gt;N($L161),"※已还本金大于典当金额",IF(AND($I161&lt;&gt;"",$J161&lt;&gt;"",$J161&lt;$I161),"※到期日早于当票日期",IF(AND($H161&lt;&gt;"",COUNTIF($H$4:$H$403,$H161)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L161&lt;&gt;"",$E161=""),"※有金额没写客户","")))))</f>
+        <f>IF($E161="","",IF(AND($B161&lt;&gt;"",ISNA(MATCH($B161,机构表,0))),"※机构不在【资料】里",IF(AND($D161&lt;&gt;"",ISNA(MATCH($D161,状态表,0))),"※状态不在【资料】里",IF(N($M161)&gt;N($L161),"※已还本金大于典当金额",IF(AND($I161&lt;&gt;"",$J161&lt;&gt;"",$J161&lt;$I161),"※到期日早于当票日期",IF(AND($H161&lt;&gt;"",COUNTIF($H$4:$H$403,$H161)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L161&lt;&gt;"",$E161=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -22293,7 +22356,7 @@
       <c r="V162" s="12" t="n"/>
       <c r="W162" s="12" t="n"/>
       <c r="X162" s="18">
-        <f>IF($E162="","",IF(AND($B162&lt;&gt;"",ISNA(MATCH($B162,机构表,0))),"※机构不在【资料】里",IF(AND($D162&lt;&gt;"",ISNA(MATCH($D162,状态表,0))),"※状态不在【资料】里",IF(N($M162)&gt;N($L162),"※已还本金大于典当金额",IF(AND($I162&lt;&gt;"",$J162&lt;&gt;"",$J162&lt;$I162),"※到期日早于当票日期",IF(AND($H162&lt;&gt;"",COUNTIF($H$4:$H$403,$H162)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L162&lt;&gt;"",$E162=""),"※有金额没写客户","")))))</f>
+        <f>IF($E162="","",IF(AND($B162&lt;&gt;"",ISNA(MATCH($B162,机构表,0))),"※机构不在【资料】里",IF(AND($D162&lt;&gt;"",ISNA(MATCH($D162,状态表,0))),"※状态不在【资料】里",IF(N($M162)&gt;N($L162),"※已还本金大于典当金额",IF(AND($I162&lt;&gt;"",$J162&lt;&gt;"",$J162&lt;$I162),"※到期日早于当票日期",IF(AND($H162&lt;&gt;"",COUNTIF($H$4:$H$403,$H162)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L162&lt;&gt;"",$E162=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -22366,7 +22429,7 @@
       <c r="V163" s="12" t="n"/>
       <c r="W163" s="12" t="n"/>
       <c r="X163" s="18">
-        <f>IF($E163="","",IF(AND($B163&lt;&gt;"",ISNA(MATCH($B163,机构表,0))),"※机构不在【资料】里",IF(AND($D163&lt;&gt;"",ISNA(MATCH($D163,状态表,0))),"※状态不在【资料】里",IF(N($M163)&gt;N($L163),"※已还本金大于典当金额",IF(AND($I163&lt;&gt;"",$J163&lt;&gt;"",$J163&lt;$I163),"※到期日早于当票日期",IF(AND($H163&lt;&gt;"",COUNTIF($H$4:$H$403,$H163)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L163&lt;&gt;"",$E163=""),"※有金额没写客户","")))))</f>
+        <f>IF($E163="","",IF(AND($B163&lt;&gt;"",ISNA(MATCH($B163,机构表,0))),"※机构不在【资料】里",IF(AND($D163&lt;&gt;"",ISNA(MATCH($D163,状态表,0))),"※状态不在【资料】里",IF(N($M163)&gt;N($L163),"※已还本金大于典当金额",IF(AND($I163&lt;&gt;"",$J163&lt;&gt;"",$J163&lt;$I163),"※到期日早于当票日期",IF(AND($H163&lt;&gt;"",COUNTIF($H$4:$H$403,$H163)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L163&lt;&gt;"",$E163=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -22431,7 +22494,7 @@
       <c r="V164" s="12" t="n"/>
       <c r="W164" s="12" t="n"/>
       <c r="X164" s="18">
-        <f>IF($E164="","",IF(AND($B164&lt;&gt;"",ISNA(MATCH($B164,机构表,0))),"※机构不在【资料】里",IF(AND($D164&lt;&gt;"",ISNA(MATCH($D164,状态表,0))),"※状态不在【资料】里",IF(N($M164)&gt;N($L164),"※已还本金大于典当金额",IF(AND($I164&lt;&gt;"",$J164&lt;&gt;"",$J164&lt;$I164),"※到期日早于当票日期",IF(AND($H164&lt;&gt;"",COUNTIF($H$4:$H$403,$H164)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L164&lt;&gt;"",$E164=""),"※有金额没写客户","")))))</f>
+        <f>IF($E164="","",IF(AND($B164&lt;&gt;"",ISNA(MATCH($B164,机构表,0))),"※机构不在【资料】里",IF(AND($D164&lt;&gt;"",ISNA(MATCH($D164,状态表,0))),"※状态不在【资料】里",IF(N($M164)&gt;N($L164),"※已还本金大于典当金额",IF(AND($I164&lt;&gt;"",$J164&lt;&gt;"",$J164&lt;$I164),"※到期日早于当票日期",IF(AND($H164&lt;&gt;"",COUNTIF($H$4:$H$403,$H164)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L164&lt;&gt;"",$E164=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -22496,7 +22559,7 @@
       <c r="V165" s="12" t="n"/>
       <c r="W165" s="12" t="n"/>
       <c r="X165" s="18">
-        <f>IF($E165="","",IF(AND($B165&lt;&gt;"",ISNA(MATCH($B165,机构表,0))),"※机构不在【资料】里",IF(AND($D165&lt;&gt;"",ISNA(MATCH($D165,状态表,0))),"※状态不在【资料】里",IF(N($M165)&gt;N($L165),"※已还本金大于典当金额",IF(AND($I165&lt;&gt;"",$J165&lt;&gt;"",$J165&lt;$I165),"※到期日早于当票日期",IF(AND($H165&lt;&gt;"",COUNTIF($H$4:$H$403,$H165)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L165&lt;&gt;"",$E165=""),"※有金额没写客户","")))))</f>
+        <f>IF($E165="","",IF(AND($B165&lt;&gt;"",ISNA(MATCH($B165,机构表,0))),"※机构不在【资料】里",IF(AND($D165&lt;&gt;"",ISNA(MATCH($D165,状态表,0))),"※状态不在【资料】里",IF(N($M165)&gt;N($L165),"※已还本金大于典当金额",IF(AND($I165&lt;&gt;"",$J165&lt;&gt;"",$J165&lt;$I165),"※到期日早于当票日期",IF(AND($H165&lt;&gt;"",COUNTIF($H$4:$H$403,$H165)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L165&lt;&gt;"",$E165=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -22561,7 +22624,7 @@
       <c r="V166" s="12" t="n"/>
       <c r="W166" s="12" t="n"/>
       <c r="X166" s="18">
-        <f>IF($E166="","",IF(AND($B166&lt;&gt;"",ISNA(MATCH($B166,机构表,0))),"※机构不在【资料】里",IF(AND($D166&lt;&gt;"",ISNA(MATCH($D166,状态表,0))),"※状态不在【资料】里",IF(N($M166)&gt;N($L166),"※已还本金大于典当金额",IF(AND($I166&lt;&gt;"",$J166&lt;&gt;"",$J166&lt;$I166),"※到期日早于当票日期",IF(AND($H166&lt;&gt;"",COUNTIF($H$4:$H$403,$H166)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L166&lt;&gt;"",$E166=""),"※有金额没写客户","")))))</f>
+        <f>IF($E166="","",IF(AND($B166&lt;&gt;"",ISNA(MATCH($B166,机构表,0))),"※机构不在【资料】里",IF(AND($D166&lt;&gt;"",ISNA(MATCH($D166,状态表,0))),"※状态不在【资料】里",IF(N($M166)&gt;N($L166),"※已还本金大于典当金额",IF(AND($I166&lt;&gt;"",$J166&lt;&gt;"",$J166&lt;$I166),"※到期日早于当票日期",IF(AND($H166&lt;&gt;"",COUNTIF($H$4:$H$403,$H166)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L166&lt;&gt;"",$E166=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -22632,7 +22695,7 @@
       <c r="V167" s="12" t="n"/>
       <c r="W167" s="12" t="n"/>
       <c r="X167" s="18">
-        <f>IF($E167="","",IF(AND($B167&lt;&gt;"",ISNA(MATCH($B167,机构表,0))),"※机构不在【资料】里",IF(AND($D167&lt;&gt;"",ISNA(MATCH($D167,状态表,0))),"※状态不在【资料】里",IF(N($M167)&gt;N($L167),"※已还本金大于典当金额",IF(AND($I167&lt;&gt;"",$J167&lt;&gt;"",$J167&lt;$I167),"※到期日早于当票日期",IF(AND($H167&lt;&gt;"",COUNTIF($H$4:$H$403,$H167)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L167&lt;&gt;"",$E167=""),"※有金额没写客户","")))))</f>
+        <f>IF($E167="","",IF(AND($B167&lt;&gt;"",ISNA(MATCH($B167,机构表,0))),"※机构不在【资料】里",IF(AND($D167&lt;&gt;"",ISNA(MATCH($D167,状态表,0))),"※状态不在【资料】里",IF(N($M167)&gt;N($L167),"※已还本金大于典当金额",IF(AND($I167&lt;&gt;"",$J167&lt;&gt;"",$J167&lt;$I167),"※到期日早于当票日期",IF(AND($H167&lt;&gt;"",COUNTIF($H$4:$H$403,$H167)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L167&lt;&gt;"",$E167=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -22697,7 +22760,7 @@
       <c r="V168" s="12" t="n"/>
       <c r="W168" s="12" t="n"/>
       <c r="X168" s="18">
-        <f>IF($E168="","",IF(AND($B168&lt;&gt;"",ISNA(MATCH($B168,机构表,0))),"※机构不在【资料】里",IF(AND($D168&lt;&gt;"",ISNA(MATCH($D168,状态表,0))),"※状态不在【资料】里",IF(N($M168)&gt;N($L168),"※已还本金大于典当金额",IF(AND($I168&lt;&gt;"",$J168&lt;&gt;"",$J168&lt;$I168),"※到期日早于当票日期",IF(AND($H168&lt;&gt;"",COUNTIF($H$4:$H$403,$H168)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L168&lt;&gt;"",$E168=""),"※有金额没写客户","")))))</f>
+        <f>IF($E168="","",IF(AND($B168&lt;&gt;"",ISNA(MATCH($B168,机构表,0))),"※机构不在【资料】里",IF(AND($D168&lt;&gt;"",ISNA(MATCH($D168,状态表,0))),"※状态不在【资料】里",IF(N($M168)&gt;N($L168),"※已还本金大于典当金额",IF(AND($I168&lt;&gt;"",$J168&lt;&gt;"",$J168&lt;$I168),"※到期日早于当票日期",IF(AND($H168&lt;&gt;"",COUNTIF($H$4:$H$403,$H168)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L168&lt;&gt;"",$E168=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -22762,7 +22825,7 @@
       <c r="V169" s="12" t="n"/>
       <c r="W169" s="12" t="n"/>
       <c r="X169" s="18">
-        <f>IF($E169="","",IF(AND($B169&lt;&gt;"",ISNA(MATCH($B169,机构表,0))),"※机构不在【资料】里",IF(AND($D169&lt;&gt;"",ISNA(MATCH($D169,状态表,0))),"※状态不在【资料】里",IF(N($M169)&gt;N($L169),"※已还本金大于典当金额",IF(AND($I169&lt;&gt;"",$J169&lt;&gt;"",$J169&lt;$I169),"※到期日早于当票日期",IF(AND($H169&lt;&gt;"",COUNTIF($H$4:$H$403,$H169)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L169&lt;&gt;"",$E169=""),"※有金额没写客户","")))))</f>
+        <f>IF($E169="","",IF(AND($B169&lt;&gt;"",ISNA(MATCH($B169,机构表,0))),"※机构不在【资料】里",IF(AND($D169&lt;&gt;"",ISNA(MATCH($D169,状态表,0))),"※状态不在【资料】里",IF(N($M169)&gt;N($L169),"※已还本金大于典当金额",IF(AND($I169&lt;&gt;"",$J169&lt;&gt;"",$J169&lt;$I169),"※到期日早于当票日期",IF(AND($H169&lt;&gt;"",COUNTIF($H$4:$H$403,$H169)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L169&lt;&gt;"",$E169=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -22825,7 +22888,7 @@
       <c r="V170" s="12" t="n"/>
       <c r="W170" s="12" t="n"/>
       <c r="X170" s="18">
-        <f>IF($E170="","",IF(AND($B170&lt;&gt;"",ISNA(MATCH($B170,机构表,0))),"※机构不在【资料】里",IF(AND($D170&lt;&gt;"",ISNA(MATCH($D170,状态表,0))),"※状态不在【资料】里",IF(N($M170)&gt;N($L170),"※已还本金大于典当金额",IF(AND($I170&lt;&gt;"",$J170&lt;&gt;"",$J170&lt;$I170),"※到期日早于当票日期",IF(AND($H170&lt;&gt;"",COUNTIF($H$4:$H$403,$H170)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L170&lt;&gt;"",$E170=""),"※有金额没写客户","")))))</f>
+        <f>IF($E170="","",IF(AND($B170&lt;&gt;"",ISNA(MATCH($B170,机构表,0))),"※机构不在【资料】里",IF(AND($D170&lt;&gt;"",ISNA(MATCH($D170,状态表,0))),"※状态不在【资料】里",IF(N($M170)&gt;N($L170),"※已还本金大于典当金额",IF(AND($I170&lt;&gt;"",$J170&lt;&gt;"",$J170&lt;$I170),"※到期日早于当票日期",IF(AND($H170&lt;&gt;"",COUNTIF($H$4:$H$403,$H170)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L170&lt;&gt;"",$E170=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -22898,7 +22961,7 @@
       <c r="V171" s="12" t="n"/>
       <c r="W171" s="12" t="n"/>
       <c r="X171" s="18">
-        <f>IF($E171="","",IF(AND($B171&lt;&gt;"",ISNA(MATCH($B171,机构表,0))),"※机构不在【资料】里",IF(AND($D171&lt;&gt;"",ISNA(MATCH($D171,状态表,0))),"※状态不在【资料】里",IF(N($M171)&gt;N($L171),"※已还本金大于典当金额",IF(AND($I171&lt;&gt;"",$J171&lt;&gt;"",$J171&lt;$I171),"※到期日早于当票日期",IF(AND($H171&lt;&gt;"",COUNTIF($H$4:$H$403,$H171)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L171&lt;&gt;"",$E171=""),"※有金额没写客户","")))))</f>
+        <f>IF($E171="","",IF(AND($B171&lt;&gt;"",ISNA(MATCH($B171,机构表,0))),"※机构不在【资料】里",IF(AND($D171&lt;&gt;"",ISNA(MATCH($D171,状态表,0))),"※状态不在【资料】里",IF(N($M171)&gt;N($L171),"※已还本金大于典当金额",IF(AND($I171&lt;&gt;"",$J171&lt;&gt;"",$J171&lt;$I171),"※到期日早于当票日期",IF(AND($H171&lt;&gt;"",COUNTIF($H$4:$H$403,$H171)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L171&lt;&gt;"",$E171=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -22963,7 +23026,7 @@
       <c r="V172" s="12" t="n"/>
       <c r="W172" s="12" t="n"/>
       <c r="X172" s="18">
-        <f>IF($E172="","",IF(AND($B172&lt;&gt;"",ISNA(MATCH($B172,机构表,0))),"※机构不在【资料】里",IF(AND($D172&lt;&gt;"",ISNA(MATCH($D172,状态表,0))),"※状态不在【资料】里",IF(N($M172)&gt;N($L172),"※已还本金大于典当金额",IF(AND($I172&lt;&gt;"",$J172&lt;&gt;"",$J172&lt;$I172),"※到期日早于当票日期",IF(AND($H172&lt;&gt;"",COUNTIF($H$4:$H$403,$H172)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L172&lt;&gt;"",$E172=""),"※有金额没写客户","")))))</f>
+        <f>IF($E172="","",IF(AND($B172&lt;&gt;"",ISNA(MATCH($B172,机构表,0))),"※机构不在【资料】里",IF(AND($D172&lt;&gt;"",ISNA(MATCH($D172,状态表,0))),"※状态不在【资料】里",IF(N($M172)&gt;N($L172),"※已还本金大于典当金额",IF(AND($I172&lt;&gt;"",$J172&lt;&gt;"",$J172&lt;$I172),"※到期日早于当票日期",IF(AND($H172&lt;&gt;"",COUNTIF($H$4:$H$403,$H172)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L172&lt;&gt;"",$E172=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -23028,7 +23091,7 @@
       <c r="V173" s="12" t="n"/>
       <c r="W173" s="12" t="n"/>
       <c r="X173" s="18">
-        <f>IF($E173="","",IF(AND($B173&lt;&gt;"",ISNA(MATCH($B173,机构表,0))),"※机构不在【资料】里",IF(AND($D173&lt;&gt;"",ISNA(MATCH($D173,状态表,0))),"※状态不在【资料】里",IF(N($M173)&gt;N($L173),"※已还本金大于典当金额",IF(AND($I173&lt;&gt;"",$J173&lt;&gt;"",$J173&lt;$I173),"※到期日早于当票日期",IF(AND($H173&lt;&gt;"",COUNTIF($H$4:$H$403,$H173)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L173&lt;&gt;"",$E173=""),"※有金额没写客户","")))))</f>
+        <f>IF($E173="","",IF(AND($B173&lt;&gt;"",ISNA(MATCH($B173,机构表,0))),"※机构不在【资料】里",IF(AND($D173&lt;&gt;"",ISNA(MATCH($D173,状态表,0))),"※状态不在【资料】里",IF(N($M173)&gt;N($L173),"※已还本金大于典当金额",IF(AND($I173&lt;&gt;"",$J173&lt;&gt;"",$J173&lt;$I173),"※到期日早于当票日期",IF(AND($H173&lt;&gt;"",COUNTIF($H$4:$H$403,$H173)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L173&lt;&gt;"",$E173=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -23093,7 +23156,7 @@
       <c r="V174" s="12" t="n"/>
       <c r="W174" s="12" t="n"/>
       <c r="X174" s="18">
-        <f>IF($E174="","",IF(AND($B174&lt;&gt;"",ISNA(MATCH($B174,机构表,0))),"※机构不在【资料】里",IF(AND($D174&lt;&gt;"",ISNA(MATCH($D174,状态表,0))),"※状态不在【资料】里",IF(N($M174)&gt;N($L174),"※已还本金大于典当金额",IF(AND($I174&lt;&gt;"",$J174&lt;&gt;"",$J174&lt;$I174),"※到期日早于当票日期",IF(AND($H174&lt;&gt;"",COUNTIF($H$4:$H$403,$H174)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L174&lt;&gt;"",$E174=""),"※有金额没写客户","")))))</f>
+        <f>IF($E174="","",IF(AND($B174&lt;&gt;"",ISNA(MATCH($B174,机构表,0))),"※机构不在【资料】里",IF(AND($D174&lt;&gt;"",ISNA(MATCH($D174,状态表,0))),"※状态不在【资料】里",IF(N($M174)&gt;N($L174),"※已还本金大于典当金额",IF(AND($I174&lt;&gt;"",$J174&lt;&gt;"",$J174&lt;$I174),"※到期日早于当票日期",IF(AND($H174&lt;&gt;"",COUNTIF($H$4:$H$403,$H174)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L174&lt;&gt;"",$E174=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -23158,7 +23221,7 @@
       <c r="V175" s="12" t="n"/>
       <c r="W175" s="12" t="n"/>
       <c r="X175" s="18">
-        <f>IF($E175="","",IF(AND($B175&lt;&gt;"",ISNA(MATCH($B175,机构表,0))),"※机构不在【资料】里",IF(AND($D175&lt;&gt;"",ISNA(MATCH($D175,状态表,0))),"※状态不在【资料】里",IF(N($M175)&gt;N($L175),"※已还本金大于典当金额",IF(AND($I175&lt;&gt;"",$J175&lt;&gt;"",$J175&lt;$I175),"※到期日早于当票日期",IF(AND($H175&lt;&gt;"",COUNTIF($H$4:$H$403,$H175)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L175&lt;&gt;"",$E175=""),"※有金额没写客户","")))))</f>
+        <f>IF($E175="","",IF(AND($B175&lt;&gt;"",ISNA(MATCH($B175,机构表,0))),"※机构不在【资料】里",IF(AND($D175&lt;&gt;"",ISNA(MATCH($D175,状态表,0))),"※状态不在【资料】里",IF(N($M175)&gt;N($L175),"※已还本金大于典当金额",IF(AND($I175&lt;&gt;"",$J175&lt;&gt;"",$J175&lt;$I175),"※到期日早于当票日期",IF(AND($H175&lt;&gt;"",COUNTIF($H$4:$H$403,$H175)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L175&lt;&gt;"",$E175=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -23217,7 +23280,7 @@
       <c r="V176" s="12" t="n"/>
       <c r="W176" s="12" t="n"/>
       <c r="X176" s="18">
-        <f>IF($E176="","",IF(AND($B176&lt;&gt;"",ISNA(MATCH($B176,机构表,0))),"※机构不在【资料】里",IF(AND($D176&lt;&gt;"",ISNA(MATCH($D176,状态表,0))),"※状态不在【资料】里",IF(N($M176)&gt;N($L176),"※已还本金大于典当金额",IF(AND($I176&lt;&gt;"",$J176&lt;&gt;"",$J176&lt;$I176),"※到期日早于当票日期",IF(AND($H176&lt;&gt;"",COUNTIF($H$4:$H$403,$H176)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L176&lt;&gt;"",$E176=""),"※有金额没写客户","")))))</f>
+        <f>IF($E176="","",IF(AND($B176&lt;&gt;"",ISNA(MATCH($B176,机构表,0))),"※机构不在【资料】里",IF(AND($D176&lt;&gt;"",ISNA(MATCH($D176,状态表,0))),"※状态不在【资料】里",IF(N($M176)&gt;N($L176),"※已还本金大于典当金额",IF(AND($I176&lt;&gt;"",$J176&lt;&gt;"",$J176&lt;$I176),"※到期日早于当票日期",IF(AND($H176&lt;&gt;"",COUNTIF($H$4:$H$403,$H176)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L176&lt;&gt;"",$E176=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -23276,7 +23339,7 @@
       <c r="V177" s="12" t="n"/>
       <c r="W177" s="12" t="n"/>
       <c r="X177" s="18">
-        <f>IF($E177="","",IF(AND($B177&lt;&gt;"",ISNA(MATCH($B177,机构表,0))),"※机构不在【资料】里",IF(AND($D177&lt;&gt;"",ISNA(MATCH($D177,状态表,0))),"※状态不在【资料】里",IF(N($M177)&gt;N($L177),"※已还本金大于典当金额",IF(AND($I177&lt;&gt;"",$J177&lt;&gt;"",$J177&lt;$I177),"※到期日早于当票日期",IF(AND($H177&lt;&gt;"",COUNTIF($H$4:$H$403,$H177)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L177&lt;&gt;"",$E177=""),"※有金额没写客户","")))))</f>
+        <f>IF($E177="","",IF(AND($B177&lt;&gt;"",ISNA(MATCH($B177,机构表,0))),"※机构不在【资料】里",IF(AND($D177&lt;&gt;"",ISNA(MATCH($D177,状态表,0))),"※状态不在【资料】里",IF(N($M177)&gt;N($L177),"※已还本金大于典当金额",IF(AND($I177&lt;&gt;"",$J177&lt;&gt;"",$J177&lt;$I177),"※到期日早于当票日期",IF(AND($H177&lt;&gt;"",COUNTIF($H$4:$H$403,$H177)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L177&lt;&gt;"",$E177=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -23343,7 +23406,7 @@
         </is>
       </c>
       <c r="X178" s="18">
-        <f>IF($E178="","",IF(AND($B178&lt;&gt;"",ISNA(MATCH($B178,机构表,0))),"※机构不在【资料】里",IF(AND($D178&lt;&gt;"",ISNA(MATCH($D178,状态表,0))),"※状态不在【资料】里",IF(N($M178)&gt;N($L178),"※已还本金大于典当金额",IF(AND($I178&lt;&gt;"",$J178&lt;&gt;"",$J178&lt;$I178),"※到期日早于当票日期",IF(AND($H178&lt;&gt;"",COUNTIF($H$4:$H$403,$H178)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L178&lt;&gt;"",$E178=""),"※有金额没写客户","")))))</f>
+        <f>IF($E178="","",IF(AND($B178&lt;&gt;"",ISNA(MATCH($B178,机构表,0))),"※机构不在【资料】里",IF(AND($D178&lt;&gt;"",ISNA(MATCH($D178,状态表,0))),"※状态不在【资料】里",IF(N($M178)&gt;N($L178),"※已还本金大于典当金额",IF(AND($I178&lt;&gt;"",$J178&lt;&gt;"",$J178&lt;$I178),"※到期日早于当票日期",IF(AND($H178&lt;&gt;"",COUNTIF($H$4:$H$403,$H178)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L178&lt;&gt;"",$E178=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -23406,7 +23469,7 @@
       <c r="V179" s="12" t="n"/>
       <c r="W179" s="12" t="n"/>
       <c r="X179" s="18">
-        <f>IF($E179="","",IF(AND($B179&lt;&gt;"",ISNA(MATCH($B179,机构表,0))),"※机构不在【资料】里",IF(AND($D179&lt;&gt;"",ISNA(MATCH($D179,状态表,0))),"※状态不在【资料】里",IF(N($M179)&gt;N($L179),"※已还本金大于典当金额",IF(AND($I179&lt;&gt;"",$J179&lt;&gt;"",$J179&lt;$I179),"※到期日早于当票日期",IF(AND($H179&lt;&gt;"",COUNTIF($H$4:$H$403,$H179)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L179&lt;&gt;"",$E179=""),"※有金额没写客户","")))))</f>
+        <f>IF($E179="","",IF(AND($B179&lt;&gt;"",ISNA(MATCH($B179,机构表,0))),"※机构不在【资料】里",IF(AND($D179&lt;&gt;"",ISNA(MATCH($D179,状态表,0))),"※状态不在【资料】里",IF(N($M179)&gt;N($L179),"※已还本金大于典当金额",IF(AND($I179&lt;&gt;"",$J179&lt;&gt;"",$J179&lt;$I179),"※到期日早于当票日期",IF(AND($H179&lt;&gt;"",COUNTIF($H$4:$H$403,$H179)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L179&lt;&gt;"",$E179=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -23469,7 +23532,7 @@
       <c r="V180" s="12" t="n"/>
       <c r="W180" s="12" t="n"/>
       <c r="X180" s="18">
-        <f>IF($E180="","",IF(AND($B180&lt;&gt;"",ISNA(MATCH($B180,机构表,0))),"※机构不在【资料】里",IF(AND($D180&lt;&gt;"",ISNA(MATCH($D180,状态表,0))),"※状态不在【资料】里",IF(N($M180)&gt;N($L180),"※已还本金大于典当金额",IF(AND($I180&lt;&gt;"",$J180&lt;&gt;"",$J180&lt;$I180),"※到期日早于当票日期",IF(AND($H180&lt;&gt;"",COUNTIF($H$4:$H$403,$H180)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L180&lt;&gt;"",$E180=""),"※有金额没写客户","")))))</f>
+        <f>IF($E180="","",IF(AND($B180&lt;&gt;"",ISNA(MATCH($B180,机构表,0))),"※机构不在【资料】里",IF(AND($D180&lt;&gt;"",ISNA(MATCH($D180,状态表,0))),"※状态不在【资料】里",IF(N($M180)&gt;N($L180),"※已还本金大于典当金额",IF(AND($I180&lt;&gt;"",$J180&lt;&gt;"",$J180&lt;$I180),"※到期日早于当票日期",IF(AND($H180&lt;&gt;"",COUNTIF($H$4:$H$403,$H180)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L180&lt;&gt;"",$E180=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -23544,7 +23607,7 @@
       </c>
       <c r="W181" s="12" t="n"/>
       <c r="X181" s="18">
-        <f>IF($E181="","",IF(AND($B181&lt;&gt;"",ISNA(MATCH($B181,机构表,0))),"※机构不在【资料】里",IF(AND($D181&lt;&gt;"",ISNA(MATCH($D181,状态表,0))),"※状态不在【资料】里",IF(N($M181)&gt;N($L181),"※已还本金大于典当金额",IF(AND($I181&lt;&gt;"",$J181&lt;&gt;"",$J181&lt;$I181),"※到期日早于当票日期",IF(AND($H181&lt;&gt;"",COUNTIF($H$4:$H$403,$H181)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L181&lt;&gt;"",$E181=""),"※有金额没写客户","")))))</f>
+        <f>IF($E181="","",IF(AND($B181&lt;&gt;"",ISNA(MATCH($B181,机构表,0))),"※机构不在【资料】里",IF(AND($D181&lt;&gt;"",ISNA(MATCH($D181,状态表,0))),"※状态不在【资料】里",IF(N($M181)&gt;N($L181),"※已还本金大于典当金额",IF(AND($I181&lt;&gt;"",$J181&lt;&gt;"",$J181&lt;$I181),"※到期日早于当票日期",IF(AND($H181&lt;&gt;"",COUNTIF($H$4:$H$403,$H181)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L181&lt;&gt;"",$E181=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -23607,7 +23670,7 @@
       <c r="V182" s="12" t="n"/>
       <c r="W182" s="12" t="n"/>
       <c r="X182" s="18">
-        <f>IF($E182="","",IF(AND($B182&lt;&gt;"",ISNA(MATCH($B182,机构表,0))),"※机构不在【资料】里",IF(AND($D182&lt;&gt;"",ISNA(MATCH($D182,状态表,0))),"※状态不在【资料】里",IF(N($M182)&gt;N($L182),"※已还本金大于典当金额",IF(AND($I182&lt;&gt;"",$J182&lt;&gt;"",$J182&lt;$I182),"※到期日早于当票日期",IF(AND($H182&lt;&gt;"",COUNTIF($H$4:$H$403,$H182)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L182&lt;&gt;"",$E182=""),"※有金额没写客户","")))))</f>
+        <f>IF($E182="","",IF(AND($B182&lt;&gt;"",ISNA(MATCH($B182,机构表,0))),"※机构不在【资料】里",IF(AND($D182&lt;&gt;"",ISNA(MATCH($D182,状态表,0))),"※状态不在【资料】里",IF(N($M182)&gt;N($L182),"※已还本金大于典当金额",IF(AND($I182&lt;&gt;"",$J182&lt;&gt;"",$J182&lt;$I182),"※到期日早于当票日期",IF(AND($H182&lt;&gt;"",COUNTIF($H$4:$H$403,$H182)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L182&lt;&gt;"",$E182=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -23684,7 +23747,7 @@
       </c>
       <c r="W183" s="12" t="n"/>
       <c r="X183" s="18">
-        <f>IF($E183="","",IF(AND($B183&lt;&gt;"",ISNA(MATCH($B183,机构表,0))),"※机构不在【资料】里",IF(AND($D183&lt;&gt;"",ISNA(MATCH($D183,状态表,0))),"※状态不在【资料】里",IF(N($M183)&gt;N($L183),"※已还本金大于典当金额",IF(AND($I183&lt;&gt;"",$J183&lt;&gt;"",$J183&lt;$I183),"※到期日早于当票日期",IF(AND($H183&lt;&gt;"",COUNTIF($H$4:$H$403,$H183)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L183&lt;&gt;"",$E183=""),"※有金额没写客户","")))))</f>
+        <f>IF($E183="","",IF(AND($B183&lt;&gt;"",ISNA(MATCH($B183,机构表,0))),"※机构不在【资料】里",IF(AND($D183&lt;&gt;"",ISNA(MATCH($D183,状态表,0))),"※状态不在【资料】里",IF(N($M183)&gt;N($L183),"※已还本金大于典当金额",IF(AND($I183&lt;&gt;"",$J183&lt;&gt;"",$J183&lt;$I183),"※到期日早于当票日期",IF(AND($H183&lt;&gt;"",COUNTIF($H$4:$H$403,$H183)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L183&lt;&gt;"",$E183=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -23749,7 +23812,7 @@
       <c r="V184" s="12" t="n"/>
       <c r="W184" s="12" t="n"/>
       <c r="X184" s="18">
-        <f>IF($E184="","",IF(AND($B184&lt;&gt;"",ISNA(MATCH($B184,机构表,0))),"※机构不在【资料】里",IF(AND($D184&lt;&gt;"",ISNA(MATCH($D184,状态表,0))),"※状态不在【资料】里",IF(N($M184)&gt;N($L184),"※已还本金大于典当金额",IF(AND($I184&lt;&gt;"",$J184&lt;&gt;"",$J184&lt;$I184),"※到期日早于当票日期",IF(AND($H184&lt;&gt;"",COUNTIF($H$4:$H$403,$H184)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L184&lt;&gt;"",$E184=""),"※有金额没写客户","")))))</f>
+        <f>IF($E184="","",IF(AND($B184&lt;&gt;"",ISNA(MATCH($B184,机构表,0))),"※机构不在【资料】里",IF(AND($D184&lt;&gt;"",ISNA(MATCH($D184,状态表,0))),"※状态不在【资料】里",IF(N($M184)&gt;N($L184),"※已还本金大于典当金额",IF(AND($I184&lt;&gt;"",$J184&lt;&gt;"",$J184&lt;$I184),"※到期日早于当票日期",IF(AND($H184&lt;&gt;"",COUNTIF($H$4:$H$403,$H184)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L184&lt;&gt;"",$E184=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -23812,7 +23875,7 @@
       <c r="V185" s="12" t="n"/>
       <c r="W185" s="12" t="n"/>
       <c r="X185" s="18">
-        <f>IF($E185="","",IF(AND($B185&lt;&gt;"",ISNA(MATCH($B185,机构表,0))),"※机构不在【资料】里",IF(AND($D185&lt;&gt;"",ISNA(MATCH($D185,状态表,0))),"※状态不在【资料】里",IF(N($M185)&gt;N($L185),"※已还本金大于典当金额",IF(AND($I185&lt;&gt;"",$J185&lt;&gt;"",$J185&lt;$I185),"※到期日早于当票日期",IF(AND($H185&lt;&gt;"",COUNTIF($H$4:$H$403,$H185)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L185&lt;&gt;"",$E185=""),"※有金额没写客户","")))))</f>
+        <f>IF($E185="","",IF(AND($B185&lt;&gt;"",ISNA(MATCH($B185,机构表,0))),"※机构不在【资料】里",IF(AND($D185&lt;&gt;"",ISNA(MATCH($D185,状态表,0))),"※状态不在【资料】里",IF(N($M185)&gt;N($L185),"※已还本金大于典当金额",IF(AND($I185&lt;&gt;"",$J185&lt;&gt;"",$J185&lt;$I185),"※到期日早于当票日期",IF(AND($H185&lt;&gt;"",COUNTIF($H$4:$H$403,$H185)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L185&lt;&gt;"",$E185=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -23875,7 +23938,7 @@
       <c r="V186" s="12" t="n"/>
       <c r="W186" s="12" t="n"/>
       <c r="X186" s="18">
-        <f>IF($E186="","",IF(AND($B186&lt;&gt;"",ISNA(MATCH($B186,机构表,0))),"※机构不在【资料】里",IF(AND($D186&lt;&gt;"",ISNA(MATCH($D186,状态表,0))),"※状态不在【资料】里",IF(N($M186)&gt;N($L186),"※已还本金大于典当金额",IF(AND($I186&lt;&gt;"",$J186&lt;&gt;"",$J186&lt;$I186),"※到期日早于当票日期",IF(AND($H186&lt;&gt;"",COUNTIF($H$4:$H$403,$H186)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L186&lt;&gt;"",$E186=""),"※有金额没写客户","")))))</f>
+        <f>IF($E186="","",IF(AND($B186&lt;&gt;"",ISNA(MATCH($B186,机构表,0))),"※机构不在【资料】里",IF(AND($D186&lt;&gt;"",ISNA(MATCH($D186,状态表,0))),"※状态不在【资料】里",IF(N($M186)&gt;N($L186),"※已还本金大于典当金额",IF(AND($I186&lt;&gt;"",$J186&lt;&gt;"",$J186&lt;$I186),"※到期日早于当票日期",IF(AND($H186&lt;&gt;"",COUNTIF($H$4:$H$403,$H186)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L186&lt;&gt;"",$E186=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -23938,7 +24001,7 @@
       <c r="V187" s="12" t="n"/>
       <c r="W187" s="12" t="n"/>
       <c r="X187" s="18">
-        <f>IF($E187="","",IF(AND($B187&lt;&gt;"",ISNA(MATCH($B187,机构表,0))),"※机构不在【资料】里",IF(AND($D187&lt;&gt;"",ISNA(MATCH($D187,状态表,0))),"※状态不在【资料】里",IF(N($M187)&gt;N($L187),"※已还本金大于典当金额",IF(AND($I187&lt;&gt;"",$J187&lt;&gt;"",$J187&lt;$I187),"※到期日早于当票日期",IF(AND($H187&lt;&gt;"",COUNTIF($H$4:$H$403,$H187)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L187&lt;&gt;"",$E187=""),"※有金额没写客户","")))))</f>
+        <f>IF($E187="","",IF(AND($B187&lt;&gt;"",ISNA(MATCH($B187,机构表,0))),"※机构不在【资料】里",IF(AND($D187&lt;&gt;"",ISNA(MATCH($D187,状态表,0))),"※状态不在【资料】里",IF(N($M187)&gt;N($L187),"※已还本金大于典当金额",IF(AND($I187&lt;&gt;"",$J187&lt;&gt;"",$J187&lt;$I187),"※到期日早于当票日期",IF(AND($H187&lt;&gt;"",COUNTIF($H$4:$H$403,$H187)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L187&lt;&gt;"",$E187=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -24001,7 +24064,7 @@
       <c r="V188" s="12" t="n"/>
       <c r="W188" s="12" t="n"/>
       <c r="X188" s="18">
-        <f>IF($E188="","",IF(AND($B188&lt;&gt;"",ISNA(MATCH($B188,机构表,0))),"※机构不在【资料】里",IF(AND($D188&lt;&gt;"",ISNA(MATCH($D188,状态表,0))),"※状态不在【资料】里",IF(N($M188)&gt;N($L188),"※已还本金大于典当金额",IF(AND($I188&lt;&gt;"",$J188&lt;&gt;"",$J188&lt;$I188),"※到期日早于当票日期",IF(AND($H188&lt;&gt;"",COUNTIF($H$4:$H$403,$H188)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L188&lt;&gt;"",$E188=""),"※有金额没写客户","")))))</f>
+        <f>IF($E188="","",IF(AND($B188&lt;&gt;"",ISNA(MATCH($B188,机构表,0))),"※机构不在【资料】里",IF(AND($D188&lt;&gt;"",ISNA(MATCH($D188,状态表,0))),"※状态不在【资料】里",IF(N($M188)&gt;N($L188),"※已还本金大于典当金额",IF(AND($I188&lt;&gt;"",$J188&lt;&gt;"",$J188&lt;$I188),"※到期日早于当票日期",IF(AND($H188&lt;&gt;"",COUNTIF($H$4:$H$403,$H188)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L188&lt;&gt;"",$E188=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -24064,7 +24127,7 @@
       <c r="V189" s="12" t="n"/>
       <c r="W189" s="12" t="n"/>
       <c r="X189" s="18">
-        <f>IF($E189="","",IF(AND($B189&lt;&gt;"",ISNA(MATCH($B189,机构表,0))),"※机构不在【资料】里",IF(AND($D189&lt;&gt;"",ISNA(MATCH($D189,状态表,0))),"※状态不在【资料】里",IF(N($M189)&gt;N($L189),"※已还本金大于典当金额",IF(AND($I189&lt;&gt;"",$J189&lt;&gt;"",$J189&lt;$I189),"※到期日早于当票日期",IF(AND($H189&lt;&gt;"",COUNTIF($H$4:$H$403,$H189)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L189&lt;&gt;"",$E189=""),"※有金额没写客户","")))))</f>
+        <f>IF($E189="","",IF(AND($B189&lt;&gt;"",ISNA(MATCH($B189,机构表,0))),"※机构不在【资料】里",IF(AND($D189&lt;&gt;"",ISNA(MATCH($D189,状态表,0))),"※状态不在【资料】里",IF(N($M189)&gt;N($L189),"※已还本金大于典当金额",IF(AND($I189&lt;&gt;"",$J189&lt;&gt;"",$J189&lt;$I189),"※到期日早于当票日期",IF(AND($H189&lt;&gt;"",COUNTIF($H$4:$H$403,$H189)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L189&lt;&gt;"",$E189=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -24127,7 +24190,7 @@
       <c r="V190" s="12" t="n"/>
       <c r="W190" s="12" t="n"/>
       <c r="X190" s="18">
-        <f>IF($E190="","",IF(AND($B190&lt;&gt;"",ISNA(MATCH($B190,机构表,0))),"※机构不在【资料】里",IF(AND($D190&lt;&gt;"",ISNA(MATCH($D190,状态表,0))),"※状态不在【资料】里",IF(N($M190)&gt;N($L190),"※已还本金大于典当金额",IF(AND($I190&lt;&gt;"",$J190&lt;&gt;"",$J190&lt;$I190),"※到期日早于当票日期",IF(AND($H190&lt;&gt;"",COUNTIF($H$4:$H$403,$H190)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L190&lt;&gt;"",$E190=""),"※有金额没写客户","")))))</f>
+        <f>IF($E190="","",IF(AND($B190&lt;&gt;"",ISNA(MATCH($B190,机构表,0))),"※机构不在【资料】里",IF(AND($D190&lt;&gt;"",ISNA(MATCH($D190,状态表,0))),"※状态不在【资料】里",IF(N($M190)&gt;N($L190),"※已还本金大于典当金额",IF(AND($I190&lt;&gt;"",$J190&lt;&gt;"",$J190&lt;$I190),"※到期日早于当票日期",IF(AND($H190&lt;&gt;"",COUNTIF($H$4:$H$403,$H190)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L190&lt;&gt;"",$E190=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -24192,7 +24255,7 @@
       <c r="V191" s="12" t="n"/>
       <c r="W191" s="12" t="n"/>
       <c r="X191" s="18">
-        <f>IF($E191="","",IF(AND($B191&lt;&gt;"",ISNA(MATCH($B191,机构表,0))),"※机构不在【资料】里",IF(AND($D191&lt;&gt;"",ISNA(MATCH($D191,状态表,0))),"※状态不在【资料】里",IF(N($M191)&gt;N($L191),"※已还本金大于典当金额",IF(AND($I191&lt;&gt;"",$J191&lt;&gt;"",$J191&lt;$I191),"※到期日早于当票日期",IF(AND($H191&lt;&gt;"",COUNTIF($H$4:$H$403,$H191)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L191&lt;&gt;"",$E191=""),"※有金额没写客户","")))))</f>
+        <f>IF($E191="","",IF(AND($B191&lt;&gt;"",ISNA(MATCH($B191,机构表,0))),"※机构不在【资料】里",IF(AND($D191&lt;&gt;"",ISNA(MATCH($D191,状态表,0))),"※状态不在【资料】里",IF(N($M191)&gt;N($L191),"※已还本金大于典当金额",IF(AND($I191&lt;&gt;"",$J191&lt;&gt;"",$J191&lt;$I191),"※到期日早于当票日期",IF(AND($H191&lt;&gt;"",COUNTIF($H$4:$H$403,$H191)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L191&lt;&gt;"",$E191=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -24253,7 +24316,7 @@
         </is>
       </c>
       <c r="X192" s="18">
-        <f>IF($E192="","",IF(AND($B192&lt;&gt;"",ISNA(MATCH($B192,机构表,0))),"※机构不在【资料】里",IF(AND($D192&lt;&gt;"",ISNA(MATCH($D192,状态表,0))),"※状态不在【资料】里",IF(N($M192)&gt;N($L192),"※已还本金大于典当金额",IF(AND($I192&lt;&gt;"",$J192&lt;&gt;"",$J192&lt;$I192),"※到期日早于当票日期",IF(AND($H192&lt;&gt;"",COUNTIF($H$4:$H$403,$H192)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L192&lt;&gt;"",$E192=""),"※有金额没写客户","")))))</f>
+        <f>IF($E192="","",IF(AND($B192&lt;&gt;"",ISNA(MATCH($B192,机构表,0))),"※机构不在【资料】里",IF(AND($D192&lt;&gt;"",ISNA(MATCH($D192,状态表,0))),"※状态不在【资料】里",IF(N($M192)&gt;N($L192),"※已还本金大于典当金额",IF(AND($I192&lt;&gt;"",$J192&lt;&gt;"",$J192&lt;$I192),"※到期日早于当票日期",IF(AND($H192&lt;&gt;"",COUNTIF($H$4:$H$403,$H192)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L192&lt;&gt;"",$E192=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -24322,7 +24385,7 @@
       </c>
       <c r="W193" s="12" t="n"/>
       <c r="X193" s="18">
-        <f>IF($E193="","",IF(AND($B193&lt;&gt;"",ISNA(MATCH($B193,机构表,0))),"※机构不在【资料】里",IF(AND($D193&lt;&gt;"",ISNA(MATCH($D193,状态表,0))),"※状态不在【资料】里",IF(N($M193)&gt;N($L193),"※已还本金大于典当金额",IF(AND($I193&lt;&gt;"",$J193&lt;&gt;"",$J193&lt;$I193),"※到期日早于当票日期",IF(AND($H193&lt;&gt;"",COUNTIF($H$4:$H$403,$H193)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L193&lt;&gt;"",$E193=""),"※有金额没写客户","")))))</f>
+        <f>IF($E193="","",IF(AND($B193&lt;&gt;"",ISNA(MATCH($B193,机构表,0))),"※机构不在【资料】里",IF(AND($D193&lt;&gt;"",ISNA(MATCH($D193,状态表,0))),"※状态不在【资料】里",IF(N($M193)&gt;N($L193),"※已还本金大于典当金额",IF(AND($I193&lt;&gt;"",$J193&lt;&gt;"",$J193&lt;$I193),"※到期日早于当票日期",IF(AND($H193&lt;&gt;"",COUNTIF($H$4:$H$403,$H193)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L193&lt;&gt;"",$E193=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -24389,7 +24452,7 @@
       <c r="V194" s="12" t="n"/>
       <c r="W194" s="12" t="n"/>
       <c r="X194" s="18">
-        <f>IF($E194="","",IF(AND($B194&lt;&gt;"",ISNA(MATCH($B194,机构表,0))),"※机构不在【资料】里",IF(AND($D194&lt;&gt;"",ISNA(MATCH($D194,状态表,0))),"※状态不在【资料】里",IF(N($M194)&gt;N($L194),"※已还本金大于典当金额",IF(AND($I194&lt;&gt;"",$J194&lt;&gt;"",$J194&lt;$I194),"※到期日早于当票日期",IF(AND($H194&lt;&gt;"",COUNTIF($H$4:$H$403,$H194)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L194&lt;&gt;"",$E194=""),"※有金额没写客户","")))))</f>
+        <f>IF($E194="","",IF(AND($B194&lt;&gt;"",ISNA(MATCH($B194,机构表,0))),"※机构不在【资料】里",IF(AND($D194&lt;&gt;"",ISNA(MATCH($D194,状态表,0))),"※状态不在【资料】里",IF(N($M194)&gt;N($L194),"※已还本金大于典当金额",IF(AND($I194&lt;&gt;"",$J194&lt;&gt;"",$J194&lt;$I194),"※到期日早于当票日期",IF(AND($H194&lt;&gt;"",COUNTIF($H$4:$H$403,$H194)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L194&lt;&gt;"",$E194=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -24464,7 +24527,7 @@
       </c>
       <c r="W195" s="12" t="n"/>
       <c r="X195" s="18">
-        <f>IF($E195="","",IF(AND($B195&lt;&gt;"",ISNA(MATCH($B195,机构表,0))),"※机构不在【资料】里",IF(AND($D195&lt;&gt;"",ISNA(MATCH($D195,状态表,0))),"※状态不在【资料】里",IF(N($M195)&gt;N($L195),"※已还本金大于典当金额",IF(AND($I195&lt;&gt;"",$J195&lt;&gt;"",$J195&lt;$I195),"※到期日早于当票日期",IF(AND($H195&lt;&gt;"",COUNTIF($H$4:$H$403,$H195)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L195&lt;&gt;"",$E195=""),"※有金额没写客户","")))))</f>
+        <f>IF($E195="","",IF(AND($B195&lt;&gt;"",ISNA(MATCH($B195,机构表,0))),"※机构不在【资料】里",IF(AND($D195&lt;&gt;"",ISNA(MATCH($D195,状态表,0))),"※状态不在【资料】里",IF(N($M195)&gt;N($L195),"※已还本金大于典当金额",IF(AND($I195&lt;&gt;"",$J195&lt;&gt;"",$J195&lt;$I195),"※到期日早于当票日期",IF(AND($H195&lt;&gt;"",COUNTIF($H$4:$H$403,$H195)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L195&lt;&gt;"",$E195=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -24539,7 +24602,7 @@
       </c>
       <c r="W196" s="12" t="n"/>
       <c r="X196" s="18">
-        <f>IF($E196="","",IF(AND($B196&lt;&gt;"",ISNA(MATCH($B196,机构表,0))),"※机构不在【资料】里",IF(AND($D196&lt;&gt;"",ISNA(MATCH($D196,状态表,0))),"※状态不在【资料】里",IF(N($M196)&gt;N($L196),"※已还本金大于典当金额",IF(AND($I196&lt;&gt;"",$J196&lt;&gt;"",$J196&lt;$I196),"※到期日早于当票日期",IF(AND($H196&lt;&gt;"",COUNTIF($H$4:$H$403,$H196)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L196&lt;&gt;"",$E196=""),"※有金额没写客户","")))))</f>
+        <f>IF($E196="","",IF(AND($B196&lt;&gt;"",ISNA(MATCH($B196,机构表,0))),"※机构不在【资料】里",IF(AND($D196&lt;&gt;"",ISNA(MATCH($D196,状态表,0))),"※状态不在【资料】里",IF(N($M196)&gt;N($L196),"※已还本金大于典当金额",IF(AND($I196&lt;&gt;"",$J196&lt;&gt;"",$J196&lt;$I196),"※到期日早于当票日期",IF(AND($H196&lt;&gt;"",COUNTIF($H$4:$H$403,$H196)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L196&lt;&gt;"",$E196=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -24602,7 +24665,7 @@
       <c r="V197" s="12" t="n"/>
       <c r="W197" s="12" t="n"/>
       <c r="X197" s="18">
-        <f>IF($E197="","",IF(AND($B197&lt;&gt;"",ISNA(MATCH($B197,机构表,0))),"※机构不在【资料】里",IF(AND($D197&lt;&gt;"",ISNA(MATCH($D197,状态表,0))),"※状态不在【资料】里",IF(N($M197)&gt;N($L197),"※已还本金大于典当金额",IF(AND($I197&lt;&gt;"",$J197&lt;&gt;"",$J197&lt;$I197),"※到期日早于当票日期",IF(AND($H197&lt;&gt;"",COUNTIF($H$4:$H$403,$H197)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L197&lt;&gt;"",$E197=""),"※有金额没写客户","")))))</f>
+        <f>IF($E197="","",IF(AND($B197&lt;&gt;"",ISNA(MATCH($B197,机构表,0))),"※机构不在【资料】里",IF(AND($D197&lt;&gt;"",ISNA(MATCH($D197,状态表,0))),"※状态不在【资料】里",IF(N($M197)&gt;N($L197),"※已还本金大于典当金额",IF(AND($I197&lt;&gt;"",$J197&lt;&gt;"",$J197&lt;$I197),"※到期日早于当票日期",IF(AND($H197&lt;&gt;"",COUNTIF($H$4:$H$403,$H197)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L197&lt;&gt;"",$E197=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -24667,7 +24730,7 @@
       <c r="V198" s="12" t="n"/>
       <c r="W198" s="12" t="n"/>
       <c r="X198" s="18">
-        <f>IF($E198="","",IF(AND($B198&lt;&gt;"",ISNA(MATCH($B198,机构表,0))),"※机构不在【资料】里",IF(AND($D198&lt;&gt;"",ISNA(MATCH($D198,状态表,0))),"※状态不在【资料】里",IF(N($M198)&gt;N($L198),"※已还本金大于典当金额",IF(AND($I198&lt;&gt;"",$J198&lt;&gt;"",$J198&lt;$I198),"※到期日早于当票日期",IF(AND($H198&lt;&gt;"",COUNTIF($H$4:$H$403,$H198)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L198&lt;&gt;"",$E198=""),"※有金额没写客户","")))))</f>
+        <f>IF($E198="","",IF(AND($B198&lt;&gt;"",ISNA(MATCH($B198,机构表,0))),"※机构不在【资料】里",IF(AND($D198&lt;&gt;"",ISNA(MATCH($D198,状态表,0))),"※状态不在【资料】里",IF(N($M198)&gt;N($L198),"※已还本金大于典当金额",IF(AND($I198&lt;&gt;"",$J198&lt;&gt;"",$J198&lt;$I198),"※到期日早于当票日期",IF(AND($H198&lt;&gt;"",COUNTIF($H$4:$H$403,$H198)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L198&lt;&gt;"",$E198=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -24744,7 +24807,7 @@
       </c>
       <c r="W199" s="12" t="n"/>
       <c r="X199" s="18">
-        <f>IF($E199="","",IF(AND($B199&lt;&gt;"",ISNA(MATCH($B199,机构表,0))),"※机构不在【资料】里",IF(AND($D199&lt;&gt;"",ISNA(MATCH($D199,状态表,0))),"※状态不在【资料】里",IF(N($M199)&gt;N($L199),"※已还本金大于典当金额",IF(AND($I199&lt;&gt;"",$J199&lt;&gt;"",$J199&lt;$I199),"※到期日早于当票日期",IF(AND($H199&lt;&gt;"",COUNTIF($H$4:$H$403,$H199)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L199&lt;&gt;"",$E199=""),"※有金额没写客户","")))))</f>
+        <f>IF($E199="","",IF(AND($B199&lt;&gt;"",ISNA(MATCH($B199,机构表,0))),"※机构不在【资料】里",IF(AND($D199&lt;&gt;"",ISNA(MATCH($D199,状态表,0))),"※状态不在【资料】里",IF(N($M199)&gt;N($L199),"※已还本金大于典当金额",IF(AND($I199&lt;&gt;"",$J199&lt;&gt;"",$J199&lt;$I199),"※到期日早于当票日期",IF(AND($H199&lt;&gt;"",COUNTIF($H$4:$H$403,$H199)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L199&lt;&gt;"",$E199=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -24807,7 +24870,7 @@
       <c r="V200" s="12" t="n"/>
       <c r="W200" s="12" t="n"/>
       <c r="X200" s="18">
-        <f>IF($E200="","",IF(AND($B200&lt;&gt;"",ISNA(MATCH($B200,机构表,0))),"※机构不在【资料】里",IF(AND($D200&lt;&gt;"",ISNA(MATCH($D200,状态表,0))),"※状态不在【资料】里",IF(N($M200)&gt;N($L200),"※已还本金大于典当金额",IF(AND($I200&lt;&gt;"",$J200&lt;&gt;"",$J200&lt;$I200),"※到期日早于当票日期",IF(AND($H200&lt;&gt;"",COUNTIF($H$4:$H$403,$H200)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L200&lt;&gt;"",$E200=""),"※有金额没写客户","")))))</f>
+        <f>IF($E200="","",IF(AND($B200&lt;&gt;"",ISNA(MATCH($B200,机构表,0))),"※机构不在【资料】里",IF(AND($D200&lt;&gt;"",ISNA(MATCH($D200,状态表,0))),"※状态不在【资料】里",IF(N($M200)&gt;N($L200),"※已还本金大于典当金额",IF(AND($I200&lt;&gt;"",$J200&lt;&gt;"",$J200&lt;$I200),"※到期日早于当票日期",IF(AND($H200&lt;&gt;"",COUNTIF($H$4:$H$403,$H200)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L200&lt;&gt;"",$E200=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -24884,7 +24947,7 @@
       </c>
       <c r="W201" s="12" t="n"/>
       <c r="X201" s="18">
-        <f>IF($E201="","",IF(AND($B201&lt;&gt;"",ISNA(MATCH($B201,机构表,0))),"※机构不在【资料】里",IF(AND($D201&lt;&gt;"",ISNA(MATCH($D201,状态表,0))),"※状态不在【资料】里",IF(N($M201)&gt;N($L201),"※已还本金大于典当金额",IF(AND($I201&lt;&gt;"",$J201&lt;&gt;"",$J201&lt;$I201),"※到期日早于当票日期",IF(AND($H201&lt;&gt;"",COUNTIF($H$4:$H$403,$H201)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L201&lt;&gt;"",$E201=""),"※有金额没写客户","")))))</f>
+        <f>IF($E201="","",IF(AND($B201&lt;&gt;"",ISNA(MATCH($B201,机构表,0))),"※机构不在【资料】里",IF(AND($D201&lt;&gt;"",ISNA(MATCH($D201,状态表,0))),"※状态不在【资料】里",IF(N($M201)&gt;N($L201),"※已还本金大于典当金额",IF(AND($I201&lt;&gt;"",$J201&lt;&gt;"",$J201&lt;$I201),"※到期日早于当票日期",IF(AND($H201&lt;&gt;"",COUNTIF($H$4:$H$403,$H201)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L201&lt;&gt;"",$E201=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -24957,7 +25020,7 @@
       </c>
       <c r="W202" s="12" t="n"/>
       <c r="X202" s="18">
-        <f>IF($E202="","",IF(AND($B202&lt;&gt;"",ISNA(MATCH($B202,机构表,0))),"※机构不在【资料】里",IF(AND($D202&lt;&gt;"",ISNA(MATCH($D202,状态表,0))),"※状态不在【资料】里",IF(N($M202)&gt;N($L202),"※已还本金大于典当金额",IF(AND($I202&lt;&gt;"",$J202&lt;&gt;"",$J202&lt;$I202),"※到期日早于当票日期",IF(AND($H202&lt;&gt;"",COUNTIF($H$4:$H$403,$H202)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L202&lt;&gt;"",$E202=""),"※有金额没写客户","")))))</f>
+        <f>IF($E202="","",IF(AND($B202&lt;&gt;"",ISNA(MATCH($B202,机构表,0))),"※机构不在【资料】里",IF(AND($D202&lt;&gt;"",ISNA(MATCH($D202,状态表,0))),"※状态不在【资料】里",IF(N($M202)&gt;N($L202),"※已还本金大于典当金额",IF(AND($I202&lt;&gt;"",$J202&lt;&gt;"",$J202&lt;$I202),"※到期日早于当票日期",IF(AND($H202&lt;&gt;"",COUNTIF($H$4:$H$403,$H202)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L202&lt;&gt;"",$E202=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25020,7 +25083,7 @@
       <c r="V203" s="12" t="n"/>
       <c r="W203" s="12" t="n"/>
       <c r="X203" s="18">
-        <f>IF($E203="","",IF(AND($B203&lt;&gt;"",ISNA(MATCH($B203,机构表,0))),"※机构不在【资料】里",IF(AND($D203&lt;&gt;"",ISNA(MATCH($D203,状态表,0))),"※状态不在【资料】里",IF(N($M203)&gt;N($L203),"※已还本金大于典当金额",IF(AND($I203&lt;&gt;"",$J203&lt;&gt;"",$J203&lt;$I203),"※到期日早于当票日期",IF(AND($H203&lt;&gt;"",COUNTIF($H$4:$H$403,$H203)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L203&lt;&gt;"",$E203=""),"※有金额没写客户","")))))</f>
+        <f>IF($E203="","",IF(AND($B203&lt;&gt;"",ISNA(MATCH($B203,机构表,0))),"※机构不在【资料】里",IF(AND($D203&lt;&gt;"",ISNA(MATCH($D203,状态表,0))),"※状态不在【资料】里",IF(N($M203)&gt;N($L203),"※已还本金大于典当金额",IF(AND($I203&lt;&gt;"",$J203&lt;&gt;"",$J203&lt;$I203),"※到期日早于当票日期",IF(AND($H203&lt;&gt;"",COUNTIF($H$4:$H$403,$H203)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L203&lt;&gt;"",$E203=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25079,7 +25142,7 @@
         </is>
       </c>
       <c r="X204" s="18">
-        <f>IF($E204="","",IF(AND($B204&lt;&gt;"",ISNA(MATCH($B204,机构表,0))),"※机构不在【资料】里",IF(AND($D204&lt;&gt;"",ISNA(MATCH($D204,状态表,0))),"※状态不在【资料】里",IF(N($M204)&gt;N($L204),"※已还本金大于典当金额",IF(AND($I204&lt;&gt;"",$J204&lt;&gt;"",$J204&lt;$I204),"※到期日早于当票日期",IF(AND($H204&lt;&gt;"",COUNTIF($H$4:$H$403,$H204)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L204&lt;&gt;"",$E204=""),"※有金额没写客户","")))))</f>
+        <f>IF($E204="","",IF(AND($B204&lt;&gt;"",ISNA(MATCH($B204,机构表,0))),"※机构不在【资料】里",IF(AND($D204&lt;&gt;"",ISNA(MATCH($D204,状态表,0))),"※状态不在【资料】里",IF(N($M204)&gt;N($L204),"※已还本金大于典当金额",IF(AND($I204&lt;&gt;"",$J204&lt;&gt;"",$J204&lt;$I204),"※到期日早于当票日期",IF(AND($H204&lt;&gt;"",COUNTIF($H$4:$H$403,$H204)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L204&lt;&gt;"",$E204=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25114,7 +25177,7 @@
       <c r="V205" s="12" t="n"/>
       <c r="W205" s="12" t="n"/>
       <c r="X205" s="18">
-        <f>IF($E205="","",IF(AND($B205&lt;&gt;"",ISNA(MATCH($B205,机构表,0))),"※机构不在【资料】里",IF(AND($D205&lt;&gt;"",ISNA(MATCH($D205,状态表,0))),"※状态不在【资料】里",IF(N($M205)&gt;N($L205),"※已还本金大于典当金额",IF(AND($I205&lt;&gt;"",$J205&lt;&gt;"",$J205&lt;$I205),"※到期日早于当票日期",IF(AND($H205&lt;&gt;"",COUNTIF($H$4:$H$403,$H205)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L205&lt;&gt;"",$E205=""),"※有金额没写客户","")))))</f>
+        <f>IF($E205="","",IF(AND($B205&lt;&gt;"",ISNA(MATCH($B205,机构表,0))),"※机构不在【资料】里",IF(AND($D205&lt;&gt;"",ISNA(MATCH($D205,状态表,0))),"※状态不在【资料】里",IF(N($M205)&gt;N($L205),"※已还本金大于典当金额",IF(AND($I205&lt;&gt;"",$J205&lt;&gt;"",$J205&lt;$I205),"※到期日早于当票日期",IF(AND($H205&lt;&gt;"",COUNTIF($H$4:$H$403,$H205)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L205&lt;&gt;"",$E205=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25149,7 +25212,7 @@
       <c r="V206" s="12" t="n"/>
       <c r="W206" s="12" t="n"/>
       <c r="X206" s="18">
-        <f>IF($E206="","",IF(AND($B206&lt;&gt;"",ISNA(MATCH($B206,机构表,0))),"※机构不在【资料】里",IF(AND($D206&lt;&gt;"",ISNA(MATCH($D206,状态表,0))),"※状态不在【资料】里",IF(N($M206)&gt;N($L206),"※已还本金大于典当金额",IF(AND($I206&lt;&gt;"",$J206&lt;&gt;"",$J206&lt;$I206),"※到期日早于当票日期",IF(AND($H206&lt;&gt;"",COUNTIF($H$4:$H$403,$H206)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L206&lt;&gt;"",$E206=""),"※有金额没写客户","")))))</f>
+        <f>IF($E206="","",IF(AND($B206&lt;&gt;"",ISNA(MATCH($B206,机构表,0))),"※机构不在【资料】里",IF(AND($D206&lt;&gt;"",ISNA(MATCH($D206,状态表,0))),"※状态不在【资料】里",IF(N($M206)&gt;N($L206),"※已还本金大于典当金额",IF(AND($I206&lt;&gt;"",$J206&lt;&gt;"",$J206&lt;$I206),"※到期日早于当票日期",IF(AND($H206&lt;&gt;"",COUNTIF($H$4:$H$403,$H206)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L206&lt;&gt;"",$E206=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25184,7 +25247,7 @@
       <c r="V207" s="12" t="n"/>
       <c r="W207" s="12" t="n"/>
       <c r="X207" s="18">
-        <f>IF($E207="","",IF(AND($B207&lt;&gt;"",ISNA(MATCH($B207,机构表,0))),"※机构不在【资料】里",IF(AND($D207&lt;&gt;"",ISNA(MATCH($D207,状态表,0))),"※状态不在【资料】里",IF(N($M207)&gt;N($L207),"※已还本金大于典当金额",IF(AND($I207&lt;&gt;"",$J207&lt;&gt;"",$J207&lt;$I207),"※到期日早于当票日期",IF(AND($H207&lt;&gt;"",COUNTIF($H$4:$H$403,$H207)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L207&lt;&gt;"",$E207=""),"※有金额没写客户","")))))</f>
+        <f>IF($E207="","",IF(AND($B207&lt;&gt;"",ISNA(MATCH($B207,机构表,0))),"※机构不在【资料】里",IF(AND($D207&lt;&gt;"",ISNA(MATCH($D207,状态表,0))),"※状态不在【资料】里",IF(N($M207)&gt;N($L207),"※已还本金大于典当金额",IF(AND($I207&lt;&gt;"",$J207&lt;&gt;"",$J207&lt;$I207),"※到期日早于当票日期",IF(AND($H207&lt;&gt;"",COUNTIF($H$4:$H$403,$H207)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L207&lt;&gt;"",$E207=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25219,7 +25282,7 @@
       <c r="V208" s="12" t="n"/>
       <c r="W208" s="12" t="n"/>
       <c r="X208" s="18">
-        <f>IF($E208="","",IF(AND($B208&lt;&gt;"",ISNA(MATCH($B208,机构表,0))),"※机构不在【资料】里",IF(AND($D208&lt;&gt;"",ISNA(MATCH($D208,状态表,0))),"※状态不在【资料】里",IF(N($M208)&gt;N($L208),"※已还本金大于典当金额",IF(AND($I208&lt;&gt;"",$J208&lt;&gt;"",$J208&lt;$I208),"※到期日早于当票日期",IF(AND($H208&lt;&gt;"",COUNTIF($H$4:$H$403,$H208)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L208&lt;&gt;"",$E208=""),"※有金额没写客户","")))))</f>
+        <f>IF($E208="","",IF(AND($B208&lt;&gt;"",ISNA(MATCH($B208,机构表,0))),"※机构不在【资料】里",IF(AND($D208&lt;&gt;"",ISNA(MATCH($D208,状态表,0))),"※状态不在【资料】里",IF(N($M208)&gt;N($L208),"※已还本金大于典当金额",IF(AND($I208&lt;&gt;"",$J208&lt;&gt;"",$J208&lt;$I208),"※到期日早于当票日期",IF(AND($H208&lt;&gt;"",COUNTIF($H$4:$H$403,$H208)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L208&lt;&gt;"",$E208=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25254,7 +25317,7 @@
       <c r="V209" s="12" t="n"/>
       <c r="W209" s="12" t="n"/>
       <c r="X209" s="18">
-        <f>IF($E209="","",IF(AND($B209&lt;&gt;"",ISNA(MATCH($B209,机构表,0))),"※机构不在【资料】里",IF(AND($D209&lt;&gt;"",ISNA(MATCH($D209,状态表,0))),"※状态不在【资料】里",IF(N($M209)&gt;N($L209),"※已还本金大于典当金额",IF(AND($I209&lt;&gt;"",$J209&lt;&gt;"",$J209&lt;$I209),"※到期日早于当票日期",IF(AND($H209&lt;&gt;"",COUNTIF($H$4:$H$403,$H209)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L209&lt;&gt;"",$E209=""),"※有金额没写客户","")))))</f>
+        <f>IF($E209="","",IF(AND($B209&lt;&gt;"",ISNA(MATCH($B209,机构表,0))),"※机构不在【资料】里",IF(AND($D209&lt;&gt;"",ISNA(MATCH($D209,状态表,0))),"※状态不在【资料】里",IF(N($M209)&gt;N($L209),"※已还本金大于典当金额",IF(AND($I209&lt;&gt;"",$J209&lt;&gt;"",$J209&lt;$I209),"※到期日早于当票日期",IF(AND($H209&lt;&gt;"",COUNTIF($H$4:$H$403,$H209)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L209&lt;&gt;"",$E209=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25289,7 +25352,7 @@
       <c r="V210" s="12" t="n"/>
       <c r="W210" s="12" t="n"/>
       <c r="X210" s="18">
-        <f>IF($E210="","",IF(AND($B210&lt;&gt;"",ISNA(MATCH($B210,机构表,0))),"※机构不在【资料】里",IF(AND($D210&lt;&gt;"",ISNA(MATCH($D210,状态表,0))),"※状态不在【资料】里",IF(N($M210)&gt;N($L210),"※已还本金大于典当金额",IF(AND($I210&lt;&gt;"",$J210&lt;&gt;"",$J210&lt;$I210),"※到期日早于当票日期",IF(AND($H210&lt;&gt;"",COUNTIF($H$4:$H$403,$H210)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L210&lt;&gt;"",$E210=""),"※有金额没写客户","")))))</f>
+        <f>IF($E210="","",IF(AND($B210&lt;&gt;"",ISNA(MATCH($B210,机构表,0))),"※机构不在【资料】里",IF(AND($D210&lt;&gt;"",ISNA(MATCH($D210,状态表,0))),"※状态不在【资料】里",IF(N($M210)&gt;N($L210),"※已还本金大于典当金额",IF(AND($I210&lt;&gt;"",$J210&lt;&gt;"",$J210&lt;$I210),"※到期日早于当票日期",IF(AND($H210&lt;&gt;"",COUNTIF($H$4:$H$403,$H210)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L210&lt;&gt;"",$E210=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25324,7 +25387,7 @@
       <c r="V211" s="12" t="n"/>
       <c r="W211" s="12" t="n"/>
       <c r="X211" s="18">
-        <f>IF($E211="","",IF(AND($B211&lt;&gt;"",ISNA(MATCH($B211,机构表,0))),"※机构不在【资料】里",IF(AND($D211&lt;&gt;"",ISNA(MATCH($D211,状态表,0))),"※状态不在【资料】里",IF(N($M211)&gt;N($L211),"※已还本金大于典当金额",IF(AND($I211&lt;&gt;"",$J211&lt;&gt;"",$J211&lt;$I211),"※到期日早于当票日期",IF(AND($H211&lt;&gt;"",COUNTIF($H$4:$H$403,$H211)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L211&lt;&gt;"",$E211=""),"※有金额没写客户","")))))</f>
+        <f>IF($E211="","",IF(AND($B211&lt;&gt;"",ISNA(MATCH($B211,机构表,0))),"※机构不在【资料】里",IF(AND($D211&lt;&gt;"",ISNA(MATCH($D211,状态表,0))),"※状态不在【资料】里",IF(N($M211)&gt;N($L211),"※已还本金大于典当金额",IF(AND($I211&lt;&gt;"",$J211&lt;&gt;"",$J211&lt;$I211),"※到期日早于当票日期",IF(AND($H211&lt;&gt;"",COUNTIF($H$4:$H$403,$H211)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L211&lt;&gt;"",$E211=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25359,7 +25422,7 @@
       <c r="V212" s="12" t="n"/>
       <c r="W212" s="12" t="n"/>
       <c r="X212" s="18">
-        <f>IF($E212="","",IF(AND($B212&lt;&gt;"",ISNA(MATCH($B212,机构表,0))),"※机构不在【资料】里",IF(AND($D212&lt;&gt;"",ISNA(MATCH($D212,状态表,0))),"※状态不在【资料】里",IF(N($M212)&gt;N($L212),"※已还本金大于典当金额",IF(AND($I212&lt;&gt;"",$J212&lt;&gt;"",$J212&lt;$I212),"※到期日早于当票日期",IF(AND($H212&lt;&gt;"",COUNTIF($H$4:$H$403,$H212)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L212&lt;&gt;"",$E212=""),"※有金额没写客户","")))))</f>
+        <f>IF($E212="","",IF(AND($B212&lt;&gt;"",ISNA(MATCH($B212,机构表,0))),"※机构不在【资料】里",IF(AND($D212&lt;&gt;"",ISNA(MATCH($D212,状态表,0))),"※状态不在【资料】里",IF(N($M212)&gt;N($L212),"※已还本金大于典当金额",IF(AND($I212&lt;&gt;"",$J212&lt;&gt;"",$J212&lt;$I212),"※到期日早于当票日期",IF(AND($H212&lt;&gt;"",COUNTIF($H$4:$H$403,$H212)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L212&lt;&gt;"",$E212=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25394,7 +25457,7 @@
       <c r="V213" s="12" t="n"/>
       <c r="W213" s="12" t="n"/>
       <c r="X213" s="18">
-        <f>IF($E213="","",IF(AND($B213&lt;&gt;"",ISNA(MATCH($B213,机构表,0))),"※机构不在【资料】里",IF(AND($D213&lt;&gt;"",ISNA(MATCH($D213,状态表,0))),"※状态不在【资料】里",IF(N($M213)&gt;N($L213),"※已还本金大于典当金额",IF(AND($I213&lt;&gt;"",$J213&lt;&gt;"",$J213&lt;$I213),"※到期日早于当票日期",IF(AND($H213&lt;&gt;"",COUNTIF($H$4:$H$403,$H213)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L213&lt;&gt;"",$E213=""),"※有金额没写客户","")))))</f>
+        <f>IF($E213="","",IF(AND($B213&lt;&gt;"",ISNA(MATCH($B213,机构表,0))),"※机构不在【资料】里",IF(AND($D213&lt;&gt;"",ISNA(MATCH($D213,状态表,0))),"※状态不在【资料】里",IF(N($M213)&gt;N($L213),"※已还本金大于典当金额",IF(AND($I213&lt;&gt;"",$J213&lt;&gt;"",$J213&lt;$I213),"※到期日早于当票日期",IF(AND($H213&lt;&gt;"",COUNTIF($H$4:$H$403,$H213)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L213&lt;&gt;"",$E213=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25429,7 +25492,7 @@
       <c r="V214" s="12" t="n"/>
       <c r="W214" s="12" t="n"/>
       <c r="X214" s="18">
-        <f>IF($E214="","",IF(AND($B214&lt;&gt;"",ISNA(MATCH($B214,机构表,0))),"※机构不在【资料】里",IF(AND($D214&lt;&gt;"",ISNA(MATCH($D214,状态表,0))),"※状态不在【资料】里",IF(N($M214)&gt;N($L214),"※已还本金大于典当金额",IF(AND($I214&lt;&gt;"",$J214&lt;&gt;"",$J214&lt;$I214),"※到期日早于当票日期",IF(AND($H214&lt;&gt;"",COUNTIF($H$4:$H$403,$H214)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L214&lt;&gt;"",$E214=""),"※有金额没写客户","")))))</f>
+        <f>IF($E214="","",IF(AND($B214&lt;&gt;"",ISNA(MATCH($B214,机构表,0))),"※机构不在【资料】里",IF(AND($D214&lt;&gt;"",ISNA(MATCH($D214,状态表,0))),"※状态不在【资料】里",IF(N($M214)&gt;N($L214),"※已还本金大于典当金额",IF(AND($I214&lt;&gt;"",$J214&lt;&gt;"",$J214&lt;$I214),"※到期日早于当票日期",IF(AND($H214&lt;&gt;"",COUNTIF($H$4:$H$403,$H214)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L214&lt;&gt;"",$E214=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25464,7 +25527,7 @@
       <c r="V215" s="12" t="n"/>
       <c r="W215" s="12" t="n"/>
       <c r="X215" s="18">
-        <f>IF($E215="","",IF(AND($B215&lt;&gt;"",ISNA(MATCH($B215,机构表,0))),"※机构不在【资料】里",IF(AND($D215&lt;&gt;"",ISNA(MATCH($D215,状态表,0))),"※状态不在【资料】里",IF(N($M215)&gt;N($L215),"※已还本金大于典当金额",IF(AND($I215&lt;&gt;"",$J215&lt;&gt;"",$J215&lt;$I215),"※到期日早于当票日期",IF(AND($H215&lt;&gt;"",COUNTIF($H$4:$H$403,$H215)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L215&lt;&gt;"",$E215=""),"※有金额没写客户","")))))</f>
+        <f>IF($E215="","",IF(AND($B215&lt;&gt;"",ISNA(MATCH($B215,机构表,0))),"※机构不在【资料】里",IF(AND($D215&lt;&gt;"",ISNA(MATCH($D215,状态表,0))),"※状态不在【资料】里",IF(N($M215)&gt;N($L215),"※已还本金大于典当金额",IF(AND($I215&lt;&gt;"",$J215&lt;&gt;"",$J215&lt;$I215),"※到期日早于当票日期",IF(AND($H215&lt;&gt;"",COUNTIF($H$4:$H$403,$H215)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L215&lt;&gt;"",$E215=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25499,7 +25562,7 @@
       <c r="V216" s="12" t="n"/>
       <c r="W216" s="12" t="n"/>
       <c r="X216" s="18">
-        <f>IF($E216="","",IF(AND($B216&lt;&gt;"",ISNA(MATCH($B216,机构表,0))),"※机构不在【资料】里",IF(AND($D216&lt;&gt;"",ISNA(MATCH($D216,状态表,0))),"※状态不在【资料】里",IF(N($M216)&gt;N($L216),"※已还本金大于典当金额",IF(AND($I216&lt;&gt;"",$J216&lt;&gt;"",$J216&lt;$I216),"※到期日早于当票日期",IF(AND($H216&lt;&gt;"",COUNTIF($H$4:$H$403,$H216)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L216&lt;&gt;"",$E216=""),"※有金额没写客户","")))))</f>
+        <f>IF($E216="","",IF(AND($B216&lt;&gt;"",ISNA(MATCH($B216,机构表,0))),"※机构不在【资料】里",IF(AND($D216&lt;&gt;"",ISNA(MATCH($D216,状态表,0))),"※状态不在【资料】里",IF(N($M216)&gt;N($L216),"※已还本金大于典当金额",IF(AND($I216&lt;&gt;"",$J216&lt;&gt;"",$J216&lt;$I216),"※到期日早于当票日期",IF(AND($H216&lt;&gt;"",COUNTIF($H$4:$H$403,$H216)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L216&lt;&gt;"",$E216=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25534,7 +25597,7 @@
       <c r="V217" s="12" t="n"/>
       <c r="W217" s="12" t="n"/>
       <c r="X217" s="18">
-        <f>IF($E217="","",IF(AND($B217&lt;&gt;"",ISNA(MATCH($B217,机构表,0))),"※机构不在【资料】里",IF(AND($D217&lt;&gt;"",ISNA(MATCH($D217,状态表,0))),"※状态不在【资料】里",IF(N($M217)&gt;N($L217),"※已还本金大于典当金额",IF(AND($I217&lt;&gt;"",$J217&lt;&gt;"",$J217&lt;$I217),"※到期日早于当票日期",IF(AND($H217&lt;&gt;"",COUNTIF($H$4:$H$403,$H217)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L217&lt;&gt;"",$E217=""),"※有金额没写客户","")))))</f>
+        <f>IF($E217="","",IF(AND($B217&lt;&gt;"",ISNA(MATCH($B217,机构表,0))),"※机构不在【资料】里",IF(AND($D217&lt;&gt;"",ISNA(MATCH($D217,状态表,0))),"※状态不在【资料】里",IF(N($M217)&gt;N($L217),"※已还本金大于典当金额",IF(AND($I217&lt;&gt;"",$J217&lt;&gt;"",$J217&lt;$I217),"※到期日早于当票日期",IF(AND($H217&lt;&gt;"",COUNTIF($H$4:$H$403,$H217)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L217&lt;&gt;"",$E217=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25569,7 +25632,7 @@
       <c r="V218" s="12" t="n"/>
       <c r="W218" s="12" t="n"/>
       <c r="X218" s="18">
-        <f>IF($E218="","",IF(AND($B218&lt;&gt;"",ISNA(MATCH($B218,机构表,0))),"※机构不在【资料】里",IF(AND($D218&lt;&gt;"",ISNA(MATCH($D218,状态表,0))),"※状态不在【资料】里",IF(N($M218)&gt;N($L218),"※已还本金大于典当金额",IF(AND($I218&lt;&gt;"",$J218&lt;&gt;"",$J218&lt;$I218),"※到期日早于当票日期",IF(AND($H218&lt;&gt;"",COUNTIF($H$4:$H$403,$H218)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L218&lt;&gt;"",$E218=""),"※有金额没写客户","")))))</f>
+        <f>IF($E218="","",IF(AND($B218&lt;&gt;"",ISNA(MATCH($B218,机构表,0))),"※机构不在【资料】里",IF(AND($D218&lt;&gt;"",ISNA(MATCH($D218,状态表,0))),"※状态不在【资料】里",IF(N($M218)&gt;N($L218),"※已还本金大于典当金额",IF(AND($I218&lt;&gt;"",$J218&lt;&gt;"",$J218&lt;$I218),"※到期日早于当票日期",IF(AND($H218&lt;&gt;"",COUNTIF($H$4:$H$403,$H218)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L218&lt;&gt;"",$E218=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25604,7 +25667,7 @@
       <c r="V219" s="12" t="n"/>
       <c r="W219" s="12" t="n"/>
       <c r="X219" s="18">
-        <f>IF($E219="","",IF(AND($B219&lt;&gt;"",ISNA(MATCH($B219,机构表,0))),"※机构不在【资料】里",IF(AND($D219&lt;&gt;"",ISNA(MATCH($D219,状态表,0))),"※状态不在【资料】里",IF(N($M219)&gt;N($L219),"※已还本金大于典当金额",IF(AND($I219&lt;&gt;"",$J219&lt;&gt;"",$J219&lt;$I219),"※到期日早于当票日期",IF(AND($H219&lt;&gt;"",COUNTIF($H$4:$H$403,$H219)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L219&lt;&gt;"",$E219=""),"※有金额没写客户","")))))</f>
+        <f>IF($E219="","",IF(AND($B219&lt;&gt;"",ISNA(MATCH($B219,机构表,0))),"※机构不在【资料】里",IF(AND($D219&lt;&gt;"",ISNA(MATCH($D219,状态表,0))),"※状态不在【资料】里",IF(N($M219)&gt;N($L219),"※已还本金大于典当金额",IF(AND($I219&lt;&gt;"",$J219&lt;&gt;"",$J219&lt;$I219),"※到期日早于当票日期",IF(AND($H219&lt;&gt;"",COUNTIF($H$4:$H$403,$H219)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L219&lt;&gt;"",$E219=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25639,7 +25702,7 @@
       <c r="V220" s="12" t="n"/>
       <c r="W220" s="12" t="n"/>
       <c r="X220" s="18">
-        <f>IF($E220="","",IF(AND($B220&lt;&gt;"",ISNA(MATCH($B220,机构表,0))),"※机构不在【资料】里",IF(AND($D220&lt;&gt;"",ISNA(MATCH($D220,状态表,0))),"※状态不在【资料】里",IF(N($M220)&gt;N($L220),"※已还本金大于典当金额",IF(AND($I220&lt;&gt;"",$J220&lt;&gt;"",$J220&lt;$I220),"※到期日早于当票日期",IF(AND($H220&lt;&gt;"",COUNTIF($H$4:$H$403,$H220)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L220&lt;&gt;"",$E220=""),"※有金额没写客户","")))))</f>
+        <f>IF($E220="","",IF(AND($B220&lt;&gt;"",ISNA(MATCH($B220,机构表,0))),"※机构不在【资料】里",IF(AND($D220&lt;&gt;"",ISNA(MATCH($D220,状态表,0))),"※状态不在【资料】里",IF(N($M220)&gt;N($L220),"※已还本金大于典当金额",IF(AND($I220&lt;&gt;"",$J220&lt;&gt;"",$J220&lt;$I220),"※到期日早于当票日期",IF(AND($H220&lt;&gt;"",COUNTIF($H$4:$H$403,$H220)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L220&lt;&gt;"",$E220=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25674,7 +25737,7 @@
       <c r="V221" s="12" t="n"/>
       <c r="W221" s="12" t="n"/>
       <c r="X221" s="18">
-        <f>IF($E221="","",IF(AND($B221&lt;&gt;"",ISNA(MATCH($B221,机构表,0))),"※机构不在【资料】里",IF(AND($D221&lt;&gt;"",ISNA(MATCH($D221,状态表,0))),"※状态不在【资料】里",IF(N($M221)&gt;N($L221),"※已还本金大于典当金额",IF(AND($I221&lt;&gt;"",$J221&lt;&gt;"",$J221&lt;$I221),"※到期日早于当票日期",IF(AND($H221&lt;&gt;"",COUNTIF($H$4:$H$403,$H221)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L221&lt;&gt;"",$E221=""),"※有金额没写客户","")))))</f>
+        <f>IF($E221="","",IF(AND($B221&lt;&gt;"",ISNA(MATCH($B221,机构表,0))),"※机构不在【资料】里",IF(AND($D221&lt;&gt;"",ISNA(MATCH($D221,状态表,0))),"※状态不在【资料】里",IF(N($M221)&gt;N($L221),"※已还本金大于典当金额",IF(AND($I221&lt;&gt;"",$J221&lt;&gt;"",$J221&lt;$I221),"※到期日早于当票日期",IF(AND($H221&lt;&gt;"",COUNTIF($H$4:$H$403,$H221)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L221&lt;&gt;"",$E221=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25709,7 +25772,7 @@
       <c r="V222" s="12" t="n"/>
       <c r="W222" s="12" t="n"/>
       <c r="X222" s="18">
-        <f>IF($E222="","",IF(AND($B222&lt;&gt;"",ISNA(MATCH($B222,机构表,0))),"※机构不在【资料】里",IF(AND($D222&lt;&gt;"",ISNA(MATCH($D222,状态表,0))),"※状态不在【资料】里",IF(N($M222)&gt;N($L222),"※已还本金大于典当金额",IF(AND($I222&lt;&gt;"",$J222&lt;&gt;"",$J222&lt;$I222),"※到期日早于当票日期",IF(AND($H222&lt;&gt;"",COUNTIF($H$4:$H$403,$H222)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L222&lt;&gt;"",$E222=""),"※有金额没写客户","")))))</f>
+        <f>IF($E222="","",IF(AND($B222&lt;&gt;"",ISNA(MATCH($B222,机构表,0))),"※机构不在【资料】里",IF(AND($D222&lt;&gt;"",ISNA(MATCH($D222,状态表,0))),"※状态不在【资料】里",IF(N($M222)&gt;N($L222),"※已还本金大于典当金额",IF(AND($I222&lt;&gt;"",$J222&lt;&gt;"",$J222&lt;$I222),"※到期日早于当票日期",IF(AND($H222&lt;&gt;"",COUNTIF($H$4:$H$403,$H222)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L222&lt;&gt;"",$E222=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25744,7 +25807,7 @@
       <c r="V223" s="12" t="n"/>
       <c r="W223" s="12" t="n"/>
       <c r="X223" s="18">
-        <f>IF($E223="","",IF(AND($B223&lt;&gt;"",ISNA(MATCH($B223,机构表,0))),"※机构不在【资料】里",IF(AND($D223&lt;&gt;"",ISNA(MATCH($D223,状态表,0))),"※状态不在【资料】里",IF(N($M223)&gt;N($L223),"※已还本金大于典当金额",IF(AND($I223&lt;&gt;"",$J223&lt;&gt;"",$J223&lt;$I223),"※到期日早于当票日期",IF(AND($H223&lt;&gt;"",COUNTIF($H$4:$H$403,$H223)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L223&lt;&gt;"",$E223=""),"※有金额没写客户","")))))</f>
+        <f>IF($E223="","",IF(AND($B223&lt;&gt;"",ISNA(MATCH($B223,机构表,0))),"※机构不在【资料】里",IF(AND($D223&lt;&gt;"",ISNA(MATCH($D223,状态表,0))),"※状态不在【资料】里",IF(N($M223)&gt;N($L223),"※已还本金大于典当金额",IF(AND($I223&lt;&gt;"",$J223&lt;&gt;"",$J223&lt;$I223),"※到期日早于当票日期",IF(AND($H223&lt;&gt;"",COUNTIF($H$4:$H$403,$H223)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L223&lt;&gt;"",$E223=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25779,7 +25842,7 @@
       <c r="V224" s="12" t="n"/>
       <c r="W224" s="12" t="n"/>
       <c r="X224" s="18">
-        <f>IF($E224="","",IF(AND($B224&lt;&gt;"",ISNA(MATCH($B224,机构表,0))),"※机构不在【资料】里",IF(AND($D224&lt;&gt;"",ISNA(MATCH($D224,状态表,0))),"※状态不在【资料】里",IF(N($M224)&gt;N($L224),"※已还本金大于典当金额",IF(AND($I224&lt;&gt;"",$J224&lt;&gt;"",$J224&lt;$I224),"※到期日早于当票日期",IF(AND($H224&lt;&gt;"",COUNTIF($H$4:$H$403,$H224)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L224&lt;&gt;"",$E224=""),"※有金额没写客户","")))))</f>
+        <f>IF($E224="","",IF(AND($B224&lt;&gt;"",ISNA(MATCH($B224,机构表,0))),"※机构不在【资料】里",IF(AND($D224&lt;&gt;"",ISNA(MATCH($D224,状态表,0))),"※状态不在【资料】里",IF(N($M224)&gt;N($L224),"※已还本金大于典当金额",IF(AND($I224&lt;&gt;"",$J224&lt;&gt;"",$J224&lt;$I224),"※到期日早于当票日期",IF(AND($H224&lt;&gt;"",COUNTIF($H$4:$H$403,$H224)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L224&lt;&gt;"",$E224=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25814,7 +25877,7 @@
       <c r="V225" s="12" t="n"/>
       <c r="W225" s="12" t="n"/>
       <c r="X225" s="18">
-        <f>IF($E225="","",IF(AND($B225&lt;&gt;"",ISNA(MATCH($B225,机构表,0))),"※机构不在【资料】里",IF(AND($D225&lt;&gt;"",ISNA(MATCH($D225,状态表,0))),"※状态不在【资料】里",IF(N($M225)&gt;N($L225),"※已还本金大于典当金额",IF(AND($I225&lt;&gt;"",$J225&lt;&gt;"",$J225&lt;$I225),"※到期日早于当票日期",IF(AND($H225&lt;&gt;"",COUNTIF($H$4:$H$403,$H225)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L225&lt;&gt;"",$E225=""),"※有金额没写客户","")))))</f>
+        <f>IF($E225="","",IF(AND($B225&lt;&gt;"",ISNA(MATCH($B225,机构表,0))),"※机构不在【资料】里",IF(AND($D225&lt;&gt;"",ISNA(MATCH($D225,状态表,0))),"※状态不在【资料】里",IF(N($M225)&gt;N($L225),"※已还本金大于典当金额",IF(AND($I225&lt;&gt;"",$J225&lt;&gt;"",$J225&lt;$I225),"※到期日早于当票日期",IF(AND($H225&lt;&gt;"",COUNTIF($H$4:$H$403,$H225)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L225&lt;&gt;"",$E225=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25849,7 +25912,7 @@
       <c r="V226" s="12" t="n"/>
       <c r="W226" s="12" t="n"/>
       <c r="X226" s="18">
-        <f>IF($E226="","",IF(AND($B226&lt;&gt;"",ISNA(MATCH($B226,机构表,0))),"※机构不在【资料】里",IF(AND($D226&lt;&gt;"",ISNA(MATCH($D226,状态表,0))),"※状态不在【资料】里",IF(N($M226)&gt;N($L226),"※已还本金大于典当金额",IF(AND($I226&lt;&gt;"",$J226&lt;&gt;"",$J226&lt;$I226),"※到期日早于当票日期",IF(AND($H226&lt;&gt;"",COUNTIF($H$4:$H$403,$H226)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L226&lt;&gt;"",$E226=""),"※有金额没写客户","")))))</f>
+        <f>IF($E226="","",IF(AND($B226&lt;&gt;"",ISNA(MATCH($B226,机构表,0))),"※机构不在【资料】里",IF(AND($D226&lt;&gt;"",ISNA(MATCH($D226,状态表,0))),"※状态不在【资料】里",IF(N($M226)&gt;N($L226),"※已还本金大于典当金额",IF(AND($I226&lt;&gt;"",$J226&lt;&gt;"",$J226&lt;$I226),"※到期日早于当票日期",IF(AND($H226&lt;&gt;"",COUNTIF($H$4:$H$403,$H226)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L226&lt;&gt;"",$E226=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25884,7 +25947,7 @@
       <c r="V227" s="12" t="n"/>
       <c r="W227" s="12" t="n"/>
       <c r="X227" s="18">
-        <f>IF($E227="","",IF(AND($B227&lt;&gt;"",ISNA(MATCH($B227,机构表,0))),"※机构不在【资料】里",IF(AND($D227&lt;&gt;"",ISNA(MATCH($D227,状态表,0))),"※状态不在【资料】里",IF(N($M227)&gt;N($L227),"※已还本金大于典当金额",IF(AND($I227&lt;&gt;"",$J227&lt;&gt;"",$J227&lt;$I227),"※到期日早于当票日期",IF(AND($H227&lt;&gt;"",COUNTIF($H$4:$H$403,$H227)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L227&lt;&gt;"",$E227=""),"※有金额没写客户","")))))</f>
+        <f>IF($E227="","",IF(AND($B227&lt;&gt;"",ISNA(MATCH($B227,机构表,0))),"※机构不在【资料】里",IF(AND($D227&lt;&gt;"",ISNA(MATCH($D227,状态表,0))),"※状态不在【资料】里",IF(N($M227)&gt;N($L227),"※已还本金大于典当金额",IF(AND($I227&lt;&gt;"",$J227&lt;&gt;"",$J227&lt;$I227),"※到期日早于当票日期",IF(AND($H227&lt;&gt;"",COUNTIF($H$4:$H$403,$H227)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L227&lt;&gt;"",$E227=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25919,7 +25982,7 @@
       <c r="V228" s="12" t="n"/>
       <c r="W228" s="12" t="n"/>
       <c r="X228" s="18">
-        <f>IF($E228="","",IF(AND($B228&lt;&gt;"",ISNA(MATCH($B228,机构表,0))),"※机构不在【资料】里",IF(AND($D228&lt;&gt;"",ISNA(MATCH($D228,状态表,0))),"※状态不在【资料】里",IF(N($M228)&gt;N($L228),"※已还本金大于典当金额",IF(AND($I228&lt;&gt;"",$J228&lt;&gt;"",$J228&lt;$I228),"※到期日早于当票日期",IF(AND($H228&lt;&gt;"",COUNTIF($H$4:$H$403,$H228)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L228&lt;&gt;"",$E228=""),"※有金额没写客户","")))))</f>
+        <f>IF($E228="","",IF(AND($B228&lt;&gt;"",ISNA(MATCH($B228,机构表,0))),"※机构不在【资料】里",IF(AND($D228&lt;&gt;"",ISNA(MATCH($D228,状态表,0))),"※状态不在【资料】里",IF(N($M228)&gt;N($L228),"※已还本金大于典当金额",IF(AND($I228&lt;&gt;"",$J228&lt;&gt;"",$J228&lt;$I228),"※到期日早于当票日期",IF(AND($H228&lt;&gt;"",COUNTIF($H$4:$H$403,$H228)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L228&lt;&gt;"",$E228=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25954,7 +26017,7 @@
       <c r="V229" s="12" t="n"/>
       <c r="W229" s="12" t="n"/>
       <c r="X229" s="18">
-        <f>IF($E229="","",IF(AND($B229&lt;&gt;"",ISNA(MATCH($B229,机构表,0))),"※机构不在【资料】里",IF(AND($D229&lt;&gt;"",ISNA(MATCH($D229,状态表,0))),"※状态不在【资料】里",IF(N($M229)&gt;N($L229),"※已还本金大于典当金额",IF(AND($I229&lt;&gt;"",$J229&lt;&gt;"",$J229&lt;$I229),"※到期日早于当票日期",IF(AND($H229&lt;&gt;"",COUNTIF($H$4:$H$403,$H229)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L229&lt;&gt;"",$E229=""),"※有金额没写客户","")))))</f>
+        <f>IF($E229="","",IF(AND($B229&lt;&gt;"",ISNA(MATCH($B229,机构表,0))),"※机构不在【资料】里",IF(AND($D229&lt;&gt;"",ISNA(MATCH($D229,状态表,0))),"※状态不在【资料】里",IF(N($M229)&gt;N($L229),"※已还本金大于典当金额",IF(AND($I229&lt;&gt;"",$J229&lt;&gt;"",$J229&lt;$I229),"※到期日早于当票日期",IF(AND($H229&lt;&gt;"",COUNTIF($H$4:$H$403,$H229)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L229&lt;&gt;"",$E229=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -25989,7 +26052,7 @@
       <c r="V230" s="12" t="n"/>
       <c r="W230" s="12" t="n"/>
       <c r="X230" s="18">
-        <f>IF($E230="","",IF(AND($B230&lt;&gt;"",ISNA(MATCH($B230,机构表,0))),"※机构不在【资料】里",IF(AND($D230&lt;&gt;"",ISNA(MATCH($D230,状态表,0))),"※状态不在【资料】里",IF(N($M230)&gt;N($L230),"※已还本金大于典当金额",IF(AND($I230&lt;&gt;"",$J230&lt;&gt;"",$J230&lt;$I230),"※到期日早于当票日期",IF(AND($H230&lt;&gt;"",COUNTIF($H$4:$H$403,$H230)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L230&lt;&gt;"",$E230=""),"※有金额没写客户","")))))</f>
+        <f>IF($E230="","",IF(AND($B230&lt;&gt;"",ISNA(MATCH($B230,机构表,0))),"※机构不在【资料】里",IF(AND($D230&lt;&gt;"",ISNA(MATCH($D230,状态表,0))),"※状态不在【资料】里",IF(N($M230)&gt;N($L230),"※已还本金大于典当金额",IF(AND($I230&lt;&gt;"",$J230&lt;&gt;"",$J230&lt;$I230),"※到期日早于当票日期",IF(AND($H230&lt;&gt;"",COUNTIF($H$4:$H$403,$H230)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L230&lt;&gt;"",$E230=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26024,7 +26087,7 @@
       <c r="V231" s="12" t="n"/>
       <c r="W231" s="12" t="n"/>
       <c r="X231" s="18">
-        <f>IF($E231="","",IF(AND($B231&lt;&gt;"",ISNA(MATCH($B231,机构表,0))),"※机构不在【资料】里",IF(AND($D231&lt;&gt;"",ISNA(MATCH($D231,状态表,0))),"※状态不在【资料】里",IF(N($M231)&gt;N($L231),"※已还本金大于典当金额",IF(AND($I231&lt;&gt;"",$J231&lt;&gt;"",$J231&lt;$I231),"※到期日早于当票日期",IF(AND($H231&lt;&gt;"",COUNTIF($H$4:$H$403,$H231)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L231&lt;&gt;"",$E231=""),"※有金额没写客户","")))))</f>
+        <f>IF($E231="","",IF(AND($B231&lt;&gt;"",ISNA(MATCH($B231,机构表,0))),"※机构不在【资料】里",IF(AND($D231&lt;&gt;"",ISNA(MATCH($D231,状态表,0))),"※状态不在【资料】里",IF(N($M231)&gt;N($L231),"※已还本金大于典当金额",IF(AND($I231&lt;&gt;"",$J231&lt;&gt;"",$J231&lt;$I231),"※到期日早于当票日期",IF(AND($H231&lt;&gt;"",COUNTIF($H$4:$H$403,$H231)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L231&lt;&gt;"",$E231=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26059,7 +26122,7 @@
       <c r="V232" s="12" t="n"/>
       <c r="W232" s="12" t="n"/>
       <c r="X232" s="18">
-        <f>IF($E232="","",IF(AND($B232&lt;&gt;"",ISNA(MATCH($B232,机构表,0))),"※机构不在【资料】里",IF(AND($D232&lt;&gt;"",ISNA(MATCH($D232,状态表,0))),"※状态不在【资料】里",IF(N($M232)&gt;N($L232),"※已还本金大于典当金额",IF(AND($I232&lt;&gt;"",$J232&lt;&gt;"",$J232&lt;$I232),"※到期日早于当票日期",IF(AND($H232&lt;&gt;"",COUNTIF($H$4:$H$403,$H232)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L232&lt;&gt;"",$E232=""),"※有金额没写客户","")))))</f>
+        <f>IF($E232="","",IF(AND($B232&lt;&gt;"",ISNA(MATCH($B232,机构表,0))),"※机构不在【资料】里",IF(AND($D232&lt;&gt;"",ISNA(MATCH($D232,状态表,0))),"※状态不在【资料】里",IF(N($M232)&gt;N($L232),"※已还本金大于典当金额",IF(AND($I232&lt;&gt;"",$J232&lt;&gt;"",$J232&lt;$I232),"※到期日早于当票日期",IF(AND($H232&lt;&gt;"",COUNTIF($H$4:$H$403,$H232)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L232&lt;&gt;"",$E232=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26094,7 +26157,7 @@
       <c r="V233" s="12" t="n"/>
       <c r="W233" s="12" t="n"/>
       <c r="X233" s="18">
-        <f>IF($E233="","",IF(AND($B233&lt;&gt;"",ISNA(MATCH($B233,机构表,0))),"※机构不在【资料】里",IF(AND($D233&lt;&gt;"",ISNA(MATCH($D233,状态表,0))),"※状态不在【资料】里",IF(N($M233)&gt;N($L233),"※已还本金大于典当金额",IF(AND($I233&lt;&gt;"",$J233&lt;&gt;"",$J233&lt;$I233),"※到期日早于当票日期",IF(AND($H233&lt;&gt;"",COUNTIF($H$4:$H$403,$H233)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L233&lt;&gt;"",$E233=""),"※有金额没写客户","")))))</f>
+        <f>IF($E233="","",IF(AND($B233&lt;&gt;"",ISNA(MATCH($B233,机构表,0))),"※机构不在【资料】里",IF(AND($D233&lt;&gt;"",ISNA(MATCH($D233,状态表,0))),"※状态不在【资料】里",IF(N($M233)&gt;N($L233),"※已还本金大于典当金额",IF(AND($I233&lt;&gt;"",$J233&lt;&gt;"",$J233&lt;$I233),"※到期日早于当票日期",IF(AND($H233&lt;&gt;"",COUNTIF($H$4:$H$403,$H233)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L233&lt;&gt;"",$E233=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26129,7 +26192,7 @@
       <c r="V234" s="12" t="n"/>
       <c r="W234" s="12" t="n"/>
       <c r="X234" s="18">
-        <f>IF($E234="","",IF(AND($B234&lt;&gt;"",ISNA(MATCH($B234,机构表,0))),"※机构不在【资料】里",IF(AND($D234&lt;&gt;"",ISNA(MATCH($D234,状态表,0))),"※状态不在【资料】里",IF(N($M234)&gt;N($L234),"※已还本金大于典当金额",IF(AND($I234&lt;&gt;"",$J234&lt;&gt;"",$J234&lt;$I234),"※到期日早于当票日期",IF(AND($H234&lt;&gt;"",COUNTIF($H$4:$H$403,$H234)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L234&lt;&gt;"",$E234=""),"※有金额没写客户","")))))</f>
+        <f>IF($E234="","",IF(AND($B234&lt;&gt;"",ISNA(MATCH($B234,机构表,0))),"※机构不在【资料】里",IF(AND($D234&lt;&gt;"",ISNA(MATCH($D234,状态表,0))),"※状态不在【资料】里",IF(N($M234)&gt;N($L234),"※已还本金大于典当金额",IF(AND($I234&lt;&gt;"",$J234&lt;&gt;"",$J234&lt;$I234),"※到期日早于当票日期",IF(AND($H234&lt;&gt;"",COUNTIF($H$4:$H$403,$H234)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L234&lt;&gt;"",$E234=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26164,7 +26227,7 @@
       <c r="V235" s="12" t="n"/>
       <c r="W235" s="12" t="n"/>
       <c r="X235" s="18">
-        <f>IF($E235="","",IF(AND($B235&lt;&gt;"",ISNA(MATCH($B235,机构表,0))),"※机构不在【资料】里",IF(AND($D235&lt;&gt;"",ISNA(MATCH($D235,状态表,0))),"※状态不在【资料】里",IF(N($M235)&gt;N($L235),"※已还本金大于典当金额",IF(AND($I235&lt;&gt;"",$J235&lt;&gt;"",$J235&lt;$I235),"※到期日早于当票日期",IF(AND($H235&lt;&gt;"",COUNTIF($H$4:$H$403,$H235)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L235&lt;&gt;"",$E235=""),"※有金额没写客户","")))))</f>
+        <f>IF($E235="","",IF(AND($B235&lt;&gt;"",ISNA(MATCH($B235,机构表,0))),"※机构不在【资料】里",IF(AND($D235&lt;&gt;"",ISNA(MATCH($D235,状态表,0))),"※状态不在【资料】里",IF(N($M235)&gt;N($L235),"※已还本金大于典当金额",IF(AND($I235&lt;&gt;"",$J235&lt;&gt;"",$J235&lt;$I235),"※到期日早于当票日期",IF(AND($H235&lt;&gt;"",COUNTIF($H$4:$H$403,$H235)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L235&lt;&gt;"",$E235=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26199,7 +26262,7 @@
       <c r="V236" s="12" t="n"/>
       <c r="W236" s="12" t="n"/>
       <c r="X236" s="18">
-        <f>IF($E236="","",IF(AND($B236&lt;&gt;"",ISNA(MATCH($B236,机构表,0))),"※机构不在【资料】里",IF(AND($D236&lt;&gt;"",ISNA(MATCH($D236,状态表,0))),"※状态不在【资料】里",IF(N($M236)&gt;N($L236),"※已还本金大于典当金额",IF(AND($I236&lt;&gt;"",$J236&lt;&gt;"",$J236&lt;$I236),"※到期日早于当票日期",IF(AND($H236&lt;&gt;"",COUNTIF($H$4:$H$403,$H236)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L236&lt;&gt;"",$E236=""),"※有金额没写客户","")))))</f>
+        <f>IF($E236="","",IF(AND($B236&lt;&gt;"",ISNA(MATCH($B236,机构表,0))),"※机构不在【资料】里",IF(AND($D236&lt;&gt;"",ISNA(MATCH($D236,状态表,0))),"※状态不在【资料】里",IF(N($M236)&gt;N($L236),"※已还本金大于典当金额",IF(AND($I236&lt;&gt;"",$J236&lt;&gt;"",$J236&lt;$I236),"※到期日早于当票日期",IF(AND($H236&lt;&gt;"",COUNTIF($H$4:$H$403,$H236)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L236&lt;&gt;"",$E236=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26234,7 +26297,7 @@
       <c r="V237" s="12" t="n"/>
       <c r="W237" s="12" t="n"/>
       <c r="X237" s="18">
-        <f>IF($E237="","",IF(AND($B237&lt;&gt;"",ISNA(MATCH($B237,机构表,0))),"※机构不在【资料】里",IF(AND($D237&lt;&gt;"",ISNA(MATCH($D237,状态表,0))),"※状态不在【资料】里",IF(N($M237)&gt;N($L237),"※已还本金大于典当金额",IF(AND($I237&lt;&gt;"",$J237&lt;&gt;"",$J237&lt;$I237),"※到期日早于当票日期",IF(AND($H237&lt;&gt;"",COUNTIF($H$4:$H$403,$H237)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L237&lt;&gt;"",$E237=""),"※有金额没写客户","")))))</f>
+        <f>IF($E237="","",IF(AND($B237&lt;&gt;"",ISNA(MATCH($B237,机构表,0))),"※机构不在【资料】里",IF(AND($D237&lt;&gt;"",ISNA(MATCH($D237,状态表,0))),"※状态不在【资料】里",IF(N($M237)&gt;N($L237),"※已还本金大于典当金额",IF(AND($I237&lt;&gt;"",$J237&lt;&gt;"",$J237&lt;$I237),"※到期日早于当票日期",IF(AND($H237&lt;&gt;"",COUNTIF($H$4:$H$403,$H237)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L237&lt;&gt;"",$E237=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26269,7 +26332,7 @@
       <c r="V238" s="12" t="n"/>
       <c r="W238" s="12" t="n"/>
       <c r="X238" s="18">
-        <f>IF($E238="","",IF(AND($B238&lt;&gt;"",ISNA(MATCH($B238,机构表,0))),"※机构不在【资料】里",IF(AND($D238&lt;&gt;"",ISNA(MATCH($D238,状态表,0))),"※状态不在【资料】里",IF(N($M238)&gt;N($L238),"※已还本金大于典当金额",IF(AND($I238&lt;&gt;"",$J238&lt;&gt;"",$J238&lt;$I238),"※到期日早于当票日期",IF(AND($H238&lt;&gt;"",COUNTIF($H$4:$H$403,$H238)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L238&lt;&gt;"",$E238=""),"※有金额没写客户","")))))</f>
+        <f>IF($E238="","",IF(AND($B238&lt;&gt;"",ISNA(MATCH($B238,机构表,0))),"※机构不在【资料】里",IF(AND($D238&lt;&gt;"",ISNA(MATCH($D238,状态表,0))),"※状态不在【资料】里",IF(N($M238)&gt;N($L238),"※已还本金大于典当金额",IF(AND($I238&lt;&gt;"",$J238&lt;&gt;"",$J238&lt;$I238),"※到期日早于当票日期",IF(AND($H238&lt;&gt;"",COUNTIF($H$4:$H$403,$H238)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L238&lt;&gt;"",$E238=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26304,7 +26367,7 @@
       <c r="V239" s="12" t="n"/>
       <c r="W239" s="12" t="n"/>
       <c r="X239" s="18">
-        <f>IF($E239="","",IF(AND($B239&lt;&gt;"",ISNA(MATCH($B239,机构表,0))),"※机构不在【资料】里",IF(AND($D239&lt;&gt;"",ISNA(MATCH($D239,状态表,0))),"※状态不在【资料】里",IF(N($M239)&gt;N($L239),"※已还本金大于典当金额",IF(AND($I239&lt;&gt;"",$J239&lt;&gt;"",$J239&lt;$I239),"※到期日早于当票日期",IF(AND($H239&lt;&gt;"",COUNTIF($H$4:$H$403,$H239)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L239&lt;&gt;"",$E239=""),"※有金额没写客户","")))))</f>
+        <f>IF($E239="","",IF(AND($B239&lt;&gt;"",ISNA(MATCH($B239,机构表,0))),"※机构不在【资料】里",IF(AND($D239&lt;&gt;"",ISNA(MATCH($D239,状态表,0))),"※状态不在【资料】里",IF(N($M239)&gt;N($L239),"※已还本金大于典当金额",IF(AND($I239&lt;&gt;"",$J239&lt;&gt;"",$J239&lt;$I239),"※到期日早于当票日期",IF(AND($H239&lt;&gt;"",COUNTIF($H$4:$H$403,$H239)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L239&lt;&gt;"",$E239=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26339,7 +26402,7 @@
       <c r="V240" s="12" t="n"/>
       <c r="W240" s="12" t="n"/>
       <c r="X240" s="18">
-        <f>IF($E240="","",IF(AND($B240&lt;&gt;"",ISNA(MATCH($B240,机构表,0))),"※机构不在【资料】里",IF(AND($D240&lt;&gt;"",ISNA(MATCH($D240,状态表,0))),"※状态不在【资料】里",IF(N($M240)&gt;N($L240),"※已还本金大于典当金额",IF(AND($I240&lt;&gt;"",$J240&lt;&gt;"",$J240&lt;$I240),"※到期日早于当票日期",IF(AND($H240&lt;&gt;"",COUNTIF($H$4:$H$403,$H240)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L240&lt;&gt;"",$E240=""),"※有金额没写客户","")))))</f>
+        <f>IF($E240="","",IF(AND($B240&lt;&gt;"",ISNA(MATCH($B240,机构表,0))),"※机构不在【资料】里",IF(AND($D240&lt;&gt;"",ISNA(MATCH($D240,状态表,0))),"※状态不在【资料】里",IF(N($M240)&gt;N($L240),"※已还本金大于典当金额",IF(AND($I240&lt;&gt;"",$J240&lt;&gt;"",$J240&lt;$I240),"※到期日早于当票日期",IF(AND($H240&lt;&gt;"",COUNTIF($H$4:$H$403,$H240)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L240&lt;&gt;"",$E240=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26374,7 +26437,7 @@
       <c r="V241" s="12" t="n"/>
       <c r="W241" s="12" t="n"/>
       <c r="X241" s="18">
-        <f>IF($E241="","",IF(AND($B241&lt;&gt;"",ISNA(MATCH($B241,机构表,0))),"※机构不在【资料】里",IF(AND($D241&lt;&gt;"",ISNA(MATCH($D241,状态表,0))),"※状态不在【资料】里",IF(N($M241)&gt;N($L241),"※已还本金大于典当金额",IF(AND($I241&lt;&gt;"",$J241&lt;&gt;"",$J241&lt;$I241),"※到期日早于当票日期",IF(AND($H241&lt;&gt;"",COUNTIF($H$4:$H$403,$H241)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L241&lt;&gt;"",$E241=""),"※有金额没写客户","")))))</f>
+        <f>IF($E241="","",IF(AND($B241&lt;&gt;"",ISNA(MATCH($B241,机构表,0))),"※机构不在【资料】里",IF(AND($D241&lt;&gt;"",ISNA(MATCH($D241,状态表,0))),"※状态不在【资料】里",IF(N($M241)&gt;N($L241),"※已还本金大于典当金额",IF(AND($I241&lt;&gt;"",$J241&lt;&gt;"",$J241&lt;$I241),"※到期日早于当票日期",IF(AND($H241&lt;&gt;"",COUNTIF($H$4:$H$403,$H241)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L241&lt;&gt;"",$E241=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26409,7 +26472,7 @@
       <c r="V242" s="12" t="n"/>
       <c r="W242" s="12" t="n"/>
       <c r="X242" s="18">
-        <f>IF($E242="","",IF(AND($B242&lt;&gt;"",ISNA(MATCH($B242,机构表,0))),"※机构不在【资料】里",IF(AND($D242&lt;&gt;"",ISNA(MATCH($D242,状态表,0))),"※状态不在【资料】里",IF(N($M242)&gt;N($L242),"※已还本金大于典当金额",IF(AND($I242&lt;&gt;"",$J242&lt;&gt;"",$J242&lt;$I242),"※到期日早于当票日期",IF(AND($H242&lt;&gt;"",COUNTIF($H$4:$H$403,$H242)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L242&lt;&gt;"",$E242=""),"※有金额没写客户","")))))</f>
+        <f>IF($E242="","",IF(AND($B242&lt;&gt;"",ISNA(MATCH($B242,机构表,0))),"※机构不在【资料】里",IF(AND($D242&lt;&gt;"",ISNA(MATCH($D242,状态表,0))),"※状态不在【资料】里",IF(N($M242)&gt;N($L242),"※已还本金大于典当金额",IF(AND($I242&lt;&gt;"",$J242&lt;&gt;"",$J242&lt;$I242),"※到期日早于当票日期",IF(AND($H242&lt;&gt;"",COUNTIF($H$4:$H$403,$H242)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L242&lt;&gt;"",$E242=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26444,7 +26507,7 @@
       <c r="V243" s="12" t="n"/>
       <c r="W243" s="12" t="n"/>
       <c r="X243" s="18">
-        <f>IF($E243="","",IF(AND($B243&lt;&gt;"",ISNA(MATCH($B243,机构表,0))),"※机构不在【资料】里",IF(AND($D243&lt;&gt;"",ISNA(MATCH($D243,状态表,0))),"※状态不在【资料】里",IF(N($M243)&gt;N($L243),"※已还本金大于典当金额",IF(AND($I243&lt;&gt;"",$J243&lt;&gt;"",$J243&lt;$I243),"※到期日早于当票日期",IF(AND($H243&lt;&gt;"",COUNTIF($H$4:$H$403,$H243)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L243&lt;&gt;"",$E243=""),"※有金额没写客户","")))))</f>
+        <f>IF($E243="","",IF(AND($B243&lt;&gt;"",ISNA(MATCH($B243,机构表,0))),"※机构不在【资料】里",IF(AND($D243&lt;&gt;"",ISNA(MATCH($D243,状态表,0))),"※状态不在【资料】里",IF(N($M243)&gt;N($L243),"※已还本金大于典当金额",IF(AND($I243&lt;&gt;"",$J243&lt;&gt;"",$J243&lt;$I243),"※到期日早于当票日期",IF(AND($H243&lt;&gt;"",COUNTIF($H$4:$H$403,$H243)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L243&lt;&gt;"",$E243=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26479,7 +26542,7 @@
       <c r="V244" s="12" t="n"/>
       <c r="W244" s="12" t="n"/>
       <c r="X244" s="18">
-        <f>IF($E244="","",IF(AND($B244&lt;&gt;"",ISNA(MATCH($B244,机构表,0))),"※机构不在【资料】里",IF(AND($D244&lt;&gt;"",ISNA(MATCH($D244,状态表,0))),"※状态不在【资料】里",IF(N($M244)&gt;N($L244),"※已还本金大于典当金额",IF(AND($I244&lt;&gt;"",$J244&lt;&gt;"",$J244&lt;$I244),"※到期日早于当票日期",IF(AND($H244&lt;&gt;"",COUNTIF($H$4:$H$403,$H244)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L244&lt;&gt;"",$E244=""),"※有金额没写客户","")))))</f>
+        <f>IF($E244="","",IF(AND($B244&lt;&gt;"",ISNA(MATCH($B244,机构表,0))),"※机构不在【资料】里",IF(AND($D244&lt;&gt;"",ISNA(MATCH($D244,状态表,0))),"※状态不在【资料】里",IF(N($M244)&gt;N($L244),"※已还本金大于典当金额",IF(AND($I244&lt;&gt;"",$J244&lt;&gt;"",$J244&lt;$I244),"※到期日早于当票日期",IF(AND($H244&lt;&gt;"",COUNTIF($H$4:$H$403,$H244)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L244&lt;&gt;"",$E244=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26514,7 +26577,7 @@
       <c r="V245" s="12" t="n"/>
       <c r="W245" s="12" t="n"/>
       <c r="X245" s="18">
-        <f>IF($E245="","",IF(AND($B245&lt;&gt;"",ISNA(MATCH($B245,机构表,0))),"※机构不在【资料】里",IF(AND($D245&lt;&gt;"",ISNA(MATCH($D245,状态表,0))),"※状态不在【资料】里",IF(N($M245)&gt;N($L245),"※已还本金大于典当金额",IF(AND($I245&lt;&gt;"",$J245&lt;&gt;"",$J245&lt;$I245),"※到期日早于当票日期",IF(AND($H245&lt;&gt;"",COUNTIF($H$4:$H$403,$H245)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L245&lt;&gt;"",$E245=""),"※有金额没写客户","")))))</f>
+        <f>IF($E245="","",IF(AND($B245&lt;&gt;"",ISNA(MATCH($B245,机构表,0))),"※机构不在【资料】里",IF(AND($D245&lt;&gt;"",ISNA(MATCH($D245,状态表,0))),"※状态不在【资料】里",IF(N($M245)&gt;N($L245),"※已还本金大于典当金额",IF(AND($I245&lt;&gt;"",$J245&lt;&gt;"",$J245&lt;$I245),"※到期日早于当票日期",IF(AND($H245&lt;&gt;"",COUNTIF($H$4:$H$403,$H245)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L245&lt;&gt;"",$E245=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26549,7 +26612,7 @@
       <c r="V246" s="12" t="n"/>
       <c r="W246" s="12" t="n"/>
       <c r="X246" s="18">
-        <f>IF($E246="","",IF(AND($B246&lt;&gt;"",ISNA(MATCH($B246,机构表,0))),"※机构不在【资料】里",IF(AND($D246&lt;&gt;"",ISNA(MATCH($D246,状态表,0))),"※状态不在【资料】里",IF(N($M246)&gt;N($L246),"※已还本金大于典当金额",IF(AND($I246&lt;&gt;"",$J246&lt;&gt;"",$J246&lt;$I246),"※到期日早于当票日期",IF(AND($H246&lt;&gt;"",COUNTIF($H$4:$H$403,$H246)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L246&lt;&gt;"",$E246=""),"※有金额没写客户","")))))</f>
+        <f>IF($E246="","",IF(AND($B246&lt;&gt;"",ISNA(MATCH($B246,机构表,0))),"※机构不在【资料】里",IF(AND($D246&lt;&gt;"",ISNA(MATCH($D246,状态表,0))),"※状态不在【资料】里",IF(N($M246)&gt;N($L246),"※已还本金大于典当金额",IF(AND($I246&lt;&gt;"",$J246&lt;&gt;"",$J246&lt;$I246),"※到期日早于当票日期",IF(AND($H246&lt;&gt;"",COUNTIF($H$4:$H$403,$H246)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L246&lt;&gt;"",$E246=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26584,7 +26647,7 @@
       <c r="V247" s="12" t="n"/>
       <c r="W247" s="12" t="n"/>
       <c r="X247" s="18">
-        <f>IF($E247="","",IF(AND($B247&lt;&gt;"",ISNA(MATCH($B247,机构表,0))),"※机构不在【资料】里",IF(AND($D247&lt;&gt;"",ISNA(MATCH($D247,状态表,0))),"※状态不在【资料】里",IF(N($M247)&gt;N($L247),"※已还本金大于典当金额",IF(AND($I247&lt;&gt;"",$J247&lt;&gt;"",$J247&lt;$I247),"※到期日早于当票日期",IF(AND($H247&lt;&gt;"",COUNTIF($H$4:$H$403,$H247)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L247&lt;&gt;"",$E247=""),"※有金额没写客户","")))))</f>
+        <f>IF($E247="","",IF(AND($B247&lt;&gt;"",ISNA(MATCH($B247,机构表,0))),"※机构不在【资料】里",IF(AND($D247&lt;&gt;"",ISNA(MATCH($D247,状态表,0))),"※状态不在【资料】里",IF(N($M247)&gt;N($L247),"※已还本金大于典当金额",IF(AND($I247&lt;&gt;"",$J247&lt;&gt;"",$J247&lt;$I247),"※到期日早于当票日期",IF(AND($H247&lt;&gt;"",COUNTIF($H$4:$H$403,$H247)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L247&lt;&gt;"",$E247=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26619,7 +26682,7 @@
       <c r="V248" s="12" t="n"/>
       <c r="W248" s="12" t="n"/>
       <c r="X248" s="18">
-        <f>IF($E248="","",IF(AND($B248&lt;&gt;"",ISNA(MATCH($B248,机构表,0))),"※机构不在【资料】里",IF(AND($D248&lt;&gt;"",ISNA(MATCH($D248,状态表,0))),"※状态不在【资料】里",IF(N($M248)&gt;N($L248),"※已还本金大于典当金额",IF(AND($I248&lt;&gt;"",$J248&lt;&gt;"",$J248&lt;$I248),"※到期日早于当票日期",IF(AND($H248&lt;&gt;"",COUNTIF($H$4:$H$403,$H248)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L248&lt;&gt;"",$E248=""),"※有金额没写客户","")))))</f>
+        <f>IF($E248="","",IF(AND($B248&lt;&gt;"",ISNA(MATCH($B248,机构表,0))),"※机构不在【资料】里",IF(AND($D248&lt;&gt;"",ISNA(MATCH($D248,状态表,0))),"※状态不在【资料】里",IF(N($M248)&gt;N($L248),"※已还本金大于典当金额",IF(AND($I248&lt;&gt;"",$J248&lt;&gt;"",$J248&lt;$I248),"※到期日早于当票日期",IF(AND($H248&lt;&gt;"",COUNTIF($H$4:$H$403,$H248)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L248&lt;&gt;"",$E248=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26654,7 +26717,7 @@
       <c r="V249" s="12" t="n"/>
       <c r="W249" s="12" t="n"/>
       <c r="X249" s="18">
-        <f>IF($E249="","",IF(AND($B249&lt;&gt;"",ISNA(MATCH($B249,机构表,0))),"※机构不在【资料】里",IF(AND($D249&lt;&gt;"",ISNA(MATCH($D249,状态表,0))),"※状态不在【资料】里",IF(N($M249)&gt;N($L249),"※已还本金大于典当金额",IF(AND($I249&lt;&gt;"",$J249&lt;&gt;"",$J249&lt;$I249),"※到期日早于当票日期",IF(AND($H249&lt;&gt;"",COUNTIF($H$4:$H$403,$H249)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L249&lt;&gt;"",$E249=""),"※有金额没写客户","")))))</f>
+        <f>IF($E249="","",IF(AND($B249&lt;&gt;"",ISNA(MATCH($B249,机构表,0))),"※机构不在【资料】里",IF(AND($D249&lt;&gt;"",ISNA(MATCH($D249,状态表,0))),"※状态不在【资料】里",IF(N($M249)&gt;N($L249),"※已还本金大于典当金额",IF(AND($I249&lt;&gt;"",$J249&lt;&gt;"",$J249&lt;$I249),"※到期日早于当票日期",IF(AND($H249&lt;&gt;"",COUNTIF($H$4:$H$403,$H249)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L249&lt;&gt;"",$E249=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26689,7 +26752,7 @@
       <c r="V250" s="12" t="n"/>
       <c r="W250" s="12" t="n"/>
       <c r="X250" s="18">
-        <f>IF($E250="","",IF(AND($B250&lt;&gt;"",ISNA(MATCH($B250,机构表,0))),"※机构不在【资料】里",IF(AND($D250&lt;&gt;"",ISNA(MATCH($D250,状态表,0))),"※状态不在【资料】里",IF(N($M250)&gt;N($L250),"※已还本金大于典当金额",IF(AND($I250&lt;&gt;"",$J250&lt;&gt;"",$J250&lt;$I250),"※到期日早于当票日期",IF(AND($H250&lt;&gt;"",COUNTIF($H$4:$H$403,$H250)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L250&lt;&gt;"",$E250=""),"※有金额没写客户","")))))</f>
+        <f>IF($E250="","",IF(AND($B250&lt;&gt;"",ISNA(MATCH($B250,机构表,0))),"※机构不在【资料】里",IF(AND($D250&lt;&gt;"",ISNA(MATCH($D250,状态表,0))),"※状态不在【资料】里",IF(N($M250)&gt;N($L250),"※已还本金大于典当金额",IF(AND($I250&lt;&gt;"",$J250&lt;&gt;"",$J250&lt;$I250),"※到期日早于当票日期",IF(AND($H250&lt;&gt;"",COUNTIF($H$4:$H$403,$H250)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L250&lt;&gt;"",$E250=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26724,7 +26787,7 @@
       <c r="V251" s="12" t="n"/>
       <c r="W251" s="12" t="n"/>
       <c r="X251" s="18">
-        <f>IF($E251="","",IF(AND($B251&lt;&gt;"",ISNA(MATCH($B251,机构表,0))),"※机构不在【资料】里",IF(AND($D251&lt;&gt;"",ISNA(MATCH($D251,状态表,0))),"※状态不在【资料】里",IF(N($M251)&gt;N($L251),"※已还本金大于典当金额",IF(AND($I251&lt;&gt;"",$J251&lt;&gt;"",$J251&lt;$I251),"※到期日早于当票日期",IF(AND($H251&lt;&gt;"",COUNTIF($H$4:$H$403,$H251)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L251&lt;&gt;"",$E251=""),"※有金额没写客户","")))))</f>
+        <f>IF($E251="","",IF(AND($B251&lt;&gt;"",ISNA(MATCH($B251,机构表,0))),"※机构不在【资料】里",IF(AND($D251&lt;&gt;"",ISNA(MATCH($D251,状态表,0))),"※状态不在【资料】里",IF(N($M251)&gt;N($L251),"※已还本金大于典当金额",IF(AND($I251&lt;&gt;"",$J251&lt;&gt;"",$J251&lt;$I251),"※到期日早于当票日期",IF(AND($H251&lt;&gt;"",COUNTIF($H$4:$H$403,$H251)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L251&lt;&gt;"",$E251=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26759,7 +26822,7 @@
       <c r="V252" s="12" t="n"/>
       <c r="W252" s="12" t="n"/>
       <c r="X252" s="18">
-        <f>IF($E252="","",IF(AND($B252&lt;&gt;"",ISNA(MATCH($B252,机构表,0))),"※机构不在【资料】里",IF(AND($D252&lt;&gt;"",ISNA(MATCH($D252,状态表,0))),"※状态不在【资料】里",IF(N($M252)&gt;N($L252),"※已还本金大于典当金额",IF(AND($I252&lt;&gt;"",$J252&lt;&gt;"",$J252&lt;$I252),"※到期日早于当票日期",IF(AND($H252&lt;&gt;"",COUNTIF($H$4:$H$403,$H252)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L252&lt;&gt;"",$E252=""),"※有金额没写客户","")))))</f>
+        <f>IF($E252="","",IF(AND($B252&lt;&gt;"",ISNA(MATCH($B252,机构表,0))),"※机构不在【资料】里",IF(AND($D252&lt;&gt;"",ISNA(MATCH($D252,状态表,0))),"※状态不在【资料】里",IF(N($M252)&gt;N($L252),"※已还本金大于典当金额",IF(AND($I252&lt;&gt;"",$J252&lt;&gt;"",$J252&lt;$I252),"※到期日早于当票日期",IF(AND($H252&lt;&gt;"",COUNTIF($H$4:$H$403,$H252)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L252&lt;&gt;"",$E252=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26794,7 +26857,7 @@
       <c r="V253" s="12" t="n"/>
       <c r="W253" s="12" t="n"/>
       <c r="X253" s="18">
-        <f>IF($E253="","",IF(AND($B253&lt;&gt;"",ISNA(MATCH($B253,机构表,0))),"※机构不在【资料】里",IF(AND($D253&lt;&gt;"",ISNA(MATCH($D253,状态表,0))),"※状态不在【资料】里",IF(N($M253)&gt;N($L253),"※已还本金大于典当金额",IF(AND($I253&lt;&gt;"",$J253&lt;&gt;"",$J253&lt;$I253),"※到期日早于当票日期",IF(AND($H253&lt;&gt;"",COUNTIF($H$4:$H$403,$H253)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L253&lt;&gt;"",$E253=""),"※有金额没写客户","")))))</f>
+        <f>IF($E253="","",IF(AND($B253&lt;&gt;"",ISNA(MATCH($B253,机构表,0))),"※机构不在【资料】里",IF(AND($D253&lt;&gt;"",ISNA(MATCH($D253,状态表,0))),"※状态不在【资料】里",IF(N($M253)&gt;N($L253),"※已还本金大于典当金额",IF(AND($I253&lt;&gt;"",$J253&lt;&gt;"",$J253&lt;$I253),"※到期日早于当票日期",IF(AND($H253&lt;&gt;"",COUNTIF($H$4:$H$403,$H253)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L253&lt;&gt;"",$E253=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26829,7 +26892,7 @@
       <c r="V254" s="12" t="n"/>
       <c r="W254" s="12" t="n"/>
       <c r="X254" s="18">
-        <f>IF($E254="","",IF(AND($B254&lt;&gt;"",ISNA(MATCH($B254,机构表,0))),"※机构不在【资料】里",IF(AND($D254&lt;&gt;"",ISNA(MATCH($D254,状态表,0))),"※状态不在【资料】里",IF(N($M254)&gt;N($L254),"※已还本金大于典当金额",IF(AND($I254&lt;&gt;"",$J254&lt;&gt;"",$J254&lt;$I254),"※到期日早于当票日期",IF(AND($H254&lt;&gt;"",COUNTIF($H$4:$H$403,$H254)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L254&lt;&gt;"",$E254=""),"※有金额没写客户","")))))</f>
+        <f>IF($E254="","",IF(AND($B254&lt;&gt;"",ISNA(MATCH($B254,机构表,0))),"※机构不在【资料】里",IF(AND($D254&lt;&gt;"",ISNA(MATCH($D254,状态表,0))),"※状态不在【资料】里",IF(N($M254)&gt;N($L254),"※已还本金大于典当金额",IF(AND($I254&lt;&gt;"",$J254&lt;&gt;"",$J254&lt;$I254),"※到期日早于当票日期",IF(AND($H254&lt;&gt;"",COUNTIF($H$4:$H$403,$H254)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L254&lt;&gt;"",$E254=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26864,7 +26927,7 @@
       <c r="V255" s="12" t="n"/>
       <c r="W255" s="12" t="n"/>
       <c r="X255" s="18">
-        <f>IF($E255="","",IF(AND($B255&lt;&gt;"",ISNA(MATCH($B255,机构表,0))),"※机构不在【资料】里",IF(AND($D255&lt;&gt;"",ISNA(MATCH($D255,状态表,0))),"※状态不在【资料】里",IF(N($M255)&gt;N($L255),"※已还本金大于典当金额",IF(AND($I255&lt;&gt;"",$J255&lt;&gt;"",$J255&lt;$I255),"※到期日早于当票日期",IF(AND($H255&lt;&gt;"",COUNTIF($H$4:$H$403,$H255)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L255&lt;&gt;"",$E255=""),"※有金额没写客户","")))))</f>
+        <f>IF($E255="","",IF(AND($B255&lt;&gt;"",ISNA(MATCH($B255,机构表,0))),"※机构不在【资料】里",IF(AND($D255&lt;&gt;"",ISNA(MATCH($D255,状态表,0))),"※状态不在【资料】里",IF(N($M255)&gt;N($L255),"※已还本金大于典当金额",IF(AND($I255&lt;&gt;"",$J255&lt;&gt;"",$J255&lt;$I255),"※到期日早于当票日期",IF(AND($H255&lt;&gt;"",COUNTIF($H$4:$H$403,$H255)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L255&lt;&gt;"",$E255=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26899,7 +26962,7 @@
       <c r="V256" s="12" t="n"/>
       <c r="W256" s="12" t="n"/>
       <c r="X256" s="18">
-        <f>IF($E256="","",IF(AND($B256&lt;&gt;"",ISNA(MATCH($B256,机构表,0))),"※机构不在【资料】里",IF(AND($D256&lt;&gt;"",ISNA(MATCH($D256,状态表,0))),"※状态不在【资料】里",IF(N($M256)&gt;N($L256),"※已还本金大于典当金额",IF(AND($I256&lt;&gt;"",$J256&lt;&gt;"",$J256&lt;$I256),"※到期日早于当票日期",IF(AND($H256&lt;&gt;"",COUNTIF($H$4:$H$403,$H256)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L256&lt;&gt;"",$E256=""),"※有金额没写客户","")))))</f>
+        <f>IF($E256="","",IF(AND($B256&lt;&gt;"",ISNA(MATCH($B256,机构表,0))),"※机构不在【资料】里",IF(AND($D256&lt;&gt;"",ISNA(MATCH($D256,状态表,0))),"※状态不在【资料】里",IF(N($M256)&gt;N($L256),"※已还本金大于典当金额",IF(AND($I256&lt;&gt;"",$J256&lt;&gt;"",$J256&lt;$I256),"※到期日早于当票日期",IF(AND($H256&lt;&gt;"",COUNTIF($H$4:$H$403,$H256)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L256&lt;&gt;"",$E256=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26934,7 +26997,7 @@
       <c r="V257" s="12" t="n"/>
       <c r="W257" s="12" t="n"/>
       <c r="X257" s="18">
-        <f>IF($E257="","",IF(AND($B257&lt;&gt;"",ISNA(MATCH($B257,机构表,0))),"※机构不在【资料】里",IF(AND($D257&lt;&gt;"",ISNA(MATCH($D257,状态表,0))),"※状态不在【资料】里",IF(N($M257)&gt;N($L257),"※已还本金大于典当金额",IF(AND($I257&lt;&gt;"",$J257&lt;&gt;"",$J257&lt;$I257),"※到期日早于当票日期",IF(AND($H257&lt;&gt;"",COUNTIF($H$4:$H$403,$H257)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L257&lt;&gt;"",$E257=""),"※有金额没写客户","")))))</f>
+        <f>IF($E257="","",IF(AND($B257&lt;&gt;"",ISNA(MATCH($B257,机构表,0))),"※机构不在【资料】里",IF(AND($D257&lt;&gt;"",ISNA(MATCH($D257,状态表,0))),"※状态不在【资料】里",IF(N($M257)&gt;N($L257),"※已还本金大于典当金额",IF(AND($I257&lt;&gt;"",$J257&lt;&gt;"",$J257&lt;$I257),"※到期日早于当票日期",IF(AND($H257&lt;&gt;"",COUNTIF($H$4:$H$403,$H257)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L257&lt;&gt;"",$E257=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -26969,7 +27032,7 @@
       <c r="V258" s="12" t="n"/>
       <c r="W258" s="12" t="n"/>
       <c r="X258" s="18">
-        <f>IF($E258="","",IF(AND($B258&lt;&gt;"",ISNA(MATCH($B258,机构表,0))),"※机构不在【资料】里",IF(AND($D258&lt;&gt;"",ISNA(MATCH($D258,状态表,0))),"※状态不在【资料】里",IF(N($M258)&gt;N($L258),"※已还本金大于典当金额",IF(AND($I258&lt;&gt;"",$J258&lt;&gt;"",$J258&lt;$I258),"※到期日早于当票日期",IF(AND($H258&lt;&gt;"",COUNTIF($H$4:$H$403,$H258)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L258&lt;&gt;"",$E258=""),"※有金额没写客户","")))))</f>
+        <f>IF($E258="","",IF(AND($B258&lt;&gt;"",ISNA(MATCH($B258,机构表,0))),"※机构不在【资料】里",IF(AND($D258&lt;&gt;"",ISNA(MATCH($D258,状态表,0))),"※状态不在【资料】里",IF(N($M258)&gt;N($L258),"※已还本金大于典当金额",IF(AND($I258&lt;&gt;"",$J258&lt;&gt;"",$J258&lt;$I258),"※到期日早于当票日期",IF(AND($H258&lt;&gt;"",COUNTIF($H$4:$H$403,$H258)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L258&lt;&gt;"",$E258=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27004,7 +27067,7 @@
       <c r="V259" s="12" t="n"/>
       <c r="W259" s="12" t="n"/>
       <c r="X259" s="18">
-        <f>IF($E259="","",IF(AND($B259&lt;&gt;"",ISNA(MATCH($B259,机构表,0))),"※机构不在【资料】里",IF(AND($D259&lt;&gt;"",ISNA(MATCH($D259,状态表,0))),"※状态不在【资料】里",IF(N($M259)&gt;N($L259),"※已还本金大于典当金额",IF(AND($I259&lt;&gt;"",$J259&lt;&gt;"",$J259&lt;$I259),"※到期日早于当票日期",IF(AND($H259&lt;&gt;"",COUNTIF($H$4:$H$403,$H259)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L259&lt;&gt;"",$E259=""),"※有金额没写客户","")))))</f>
+        <f>IF($E259="","",IF(AND($B259&lt;&gt;"",ISNA(MATCH($B259,机构表,0))),"※机构不在【资料】里",IF(AND($D259&lt;&gt;"",ISNA(MATCH($D259,状态表,0))),"※状态不在【资料】里",IF(N($M259)&gt;N($L259),"※已还本金大于典当金额",IF(AND($I259&lt;&gt;"",$J259&lt;&gt;"",$J259&lt;$I259),"※到期日早于当票日期",IF(AND($H259&lt;&gt;"",COUNTIF($H$4:$H$403,$H259)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L259&lt;&gt;"",$E259=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27039,7 +27102,7 @@
       <c r="V260" s="12" t="n"/>
       <c r="W260" s="12" t="n"/>
       <c r="X260" s="18">
-        <f>IF($E260="","",IF(AND($B260&lt;&gt;"",ISNA(MATCH($B260,机构表,0))),"※机构不在【资料】里",IF(AND($D260&lt;&gt;"",ISNA(MATCH($D260,状态表,0))),"※状态不在【资料】里",IF(N($M260)&gt;N($L260),"※已还本金大于典当金额",IF(AND($I260&lt;&gt;"",$J260&lt;&gt;"",$J260&lt;$I260),"※到期日早于当票日期",IF(AND($H260&lt;&gt;"",COUNTIF($H$4:$H$403,$H260)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L260&lt;&gt;"",$E260=""),"※有金额没写客户","")))))</f>
+        <f>IF($E260="","",IF(AND($B260&lt;&gt;"",ISNA(MATCH($B260,机构表,0))),"※机构不在【资料】里",IF(AND($D260&lt;&gt;"",ISNA(MATCH($D260,状态表,0))),"※状态不在【资料】里",IF(N($M260)&gt;N($L260),"※已还本金大于典当金额",IF(AND($I260&lt;&gt;"",$J260&lt;&gt;"",$J260&lt;$I260),"※到期日早于当票日期",IF(AND($H260&lt;&gt;"",COUNTIF($H$4:$H$403,$H260)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L260&lt;&gt;"",$E260=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27074,7 +27137,7 @@
       <c r="V261" s="12" t="n"/>
       <c r="W261" s="12" t="n"/>
       <c r="X261" s="18">
-        <f>IF($E261="","",IF(AND($B261&lt;&gt;"",ISNA(MATCH($B261,机构表,0))),"※机构不在【资料】里",IF(AND($D261&lt;&gt;"",ISNA(MATCH($D261,状态表,0))),"※状态不在【资料】里",IF(N($M261)&gt;N($L261),"※已还本金大于典当金额",IF(AND($I261&lt;&gt;"",$J261&lt;&gt;"",$J261&lt;$I261),"※到期日早于当票日期",IF(AND($H261&lt;&gt;"",COUNTIF($H$4:$H$403,$H261)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L261&lt;&gt;"",$E261=""),"※有金额没写客户","")))))</f>
+        <f>IF($E261="","",IF(AND($B261&lt;&gt;"",ISNA(MATCH($B261,机构表,0))),"※机构不在【资料】里",IF(AND($D261&lt;&gt;"",ISNA(MATCH($D261,状态表,0))),"※状态不在【资料】里",IF(N($M261)&gt;N($L261),"※已还本金大于典当金额",IF(AND($I261&lt;&gt;"",$J261&lt;&gt;"",$J261&lt;$I261),"※到期日早于当票日期",IF(AND($H261&lt;&gt;"",COUNTIF($H$4:$H$403,$H261)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L261&lt;&gt;"",$E261=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27109,7 +27172,7 @@
       <c r="V262" s="12" t="n"/>
       <c r="W262" s="12" t="n"/>
       <c r="X262" s="18">
-        <f>IF($E262="","",IF(AND($B262&lt;&gt;"",ISNA(MATCH($B262,机构表,0))),"※机构不在【资料】里",IF(AND($D262&lt;&gt;"",ISNA(MATCH($D262,状态表,0))),"※状态不在【资料】里",IF(N($M262)&gt;N($L262),"※已还本金大于典当金额",IF(AND($I262&lt;&gt;"",$J262&lt;&gt;"",$J262&lt;$I262),"※到期日早于当票日期",IF(AND($H262&lt;&gt;"",COUNTIF($H$4:$H$403,$H262)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L262&lt;&gt;"",$E262=""),"※有金额没写客户","")))))</f>
+        <f>IF($E262="","",IF(AND($B262&lt;&gt;"",ISNA(MATCH($B262,机构表,0))),"※机构不在【资料】里",IF(AND($D262&lt;&gt;"",ISNA(MATCH($D262,状态表,0))),"※状态不在【资料】里",IF(N($M262)&gt;N($L262),"※已还本金大于典当金额",IF(AND($I262&lt;&gt;"",$J262&lt;&gt;"",$J262&lt;$I262),"※到期日早于当票日期",IF(AND($H262&lt;&gt;"",COUNTIF($H$4:$H$403,$H262)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L262&lt;&gt;"",$E262=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27144,7 +27207,7 @@
       <c r="V263" s="12" t="n"/>
       <c r="W263" s="12" t="n"/>
       <c r="X263" s="18">
-        <f>IF($E263="","",IF(AND($B263&lt;&gt;"",ISNA(MATCH($B263,机构表,0))),"※机构不在【资料】里",IF(AND($D263&lt;&gt;"",ISNA(MATCH($D263,状态表,0))),"※状态不在【资料】里",IF(N($M263)&gt;N($L263),"※已还本金大于典当金额",IF(AND($I263&lt;&gt;"",$J263&lt;&gt;"",$J263&lt;$I263),"※到期日早于当票日期",IF(AND($H263&lt;&gt;"",COUNTIF($H$4:$H$403,$H263)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L263&lt;&gt;"",$E263=""),"※有金额没写客户","")))))</f>
+        <f>IF($E263="","",IF(AND($B263&lt;&gt;"",ISNA(MATCH($B263,机构表,0))),"※机构不在【资料】里",IF(AND($D263&lt;&gt;"",ISNA(MATCH($D263,状态表,0))),"※状态不在【资料】里",IF(N($M263)&gt;N($L263),"※已还本金大于典当金额",IF(AND($I263&lt;&gt;"",$J263&lt;&gt;"",$J263&lt;$I263),"※到期日早于当票日期",IF(AND($H263&lt;&gt;"",COUNTIF($H$4:$H$403,$H263)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L263&lt;&gt;"",$E263=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27179,7 +27242,7 @@
       <c r="V264" s="12" t="n"/>
       <c r="W264" s="12" t="n"/>
       <c r="X264" s="18">
-        <f>IF($E264="","",IF(AND($B264&lt;&gt;"",ISNA(MATCH($B264,机构表,0))),"※机构不在【资料】里",IF(AND($D264&lt;&gt;"",ISNA(MATCH($D264,状态表,0))),"※状态不在【资料】里",IF(N($M264)&gt;N($L264),"※已还本金大于典当金额",IF(AND($I264&lt;&gt;"",$J264&lt;&gt;"",$J264&lt;$I264),"※到期日早于当票日期",IF(AND($H264&lt;&gt;"",COUNTIF($H$4:$H$403,$H264)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L264&lt;&gt;"",$E264=""),"※有金额没写客户","")))))</f>
+        <f>IF($E264="","",IF(AND($B264&lt;&gt;"",ISNA(MATCH($B264,机构表,0))),"※机构不在【资料】里",IF(AND($D264&lt;&gt;"",ISNA(MATCH($D264,状态表,0))),"※状态不在【资料】里",IF(N($M264)&gt;N($L264),"※已还本金大于典当金额",IF(AND($I264&lt;&gt;"",$J264&lt;&gt;"",$J264&lt;$I264),"※到期日早于当票日期",IF(AND($H264&lt;&gt;"",COUNTIF($H$4:$H$403,$H264)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L264&lt;&gt;"",$E264=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27214,7 +27277,7 @@
       <c r="V265" s="12" t="n"/>
       <c r="W265" s="12" t="n"/>
       <c r="X265" s="18">
-        <f>IF($E265="","",IF(AND($B265&lt;&gt;"",ISNA(MATCH($B265,机构表,0))),"※机构不在【资料】里",IF(AND($D265&lt;&gt;"",ISNA(MATCH($D265,状态表,0))),"※状态不在【资料】里",IF(N($M265)&gt;N($L265),"※已还本金大于典当金额",IF(AND($I265&lt;&gt;"",$J265&lt;&gt;"",$J265&lt;$I265),"※到期日早于当票日期",IF(AND($H265&lt;&gt;"",COUNTIF($H$4:$H$403,$H265)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L265&lt;&gt;"",$E265=""),"※有金额没写客户","")))))</f>
+        <f>IF($E265="","",IF(AND($B265&lt;&gt;"",ISNA(MATCH($B265,机构表,0))),"※机构不在【资料】里",IF(AND($D265&lt;&gt;"",ISNA(MATCH($D265,状态表,0))),"※状态不在【资料】里",IF(N($M265)&gt;N($L265),"※已还本金大于典当金额",IF(AND($I265&lt;&gt;"",$J265&lt;&gt;"",$J265&lt;$I265),"※到期日早于当票日期",IF(AND($H265&lt;&gt;"",COUNTIF($H$4:$H$403,$H265)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L265&lt;&gt;"",$E265=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27249,7 +27312,7 @@
       <c r="V266" s="12" t="n"/>
       <c r="W266" s="12" t="n"/>
       <c r="X266" s="18">
-        <f>IF($E266="","",IF(AND($B266&lt;&gt;"",ISNA(MATCH($B266,机构表,0))),"※机构不在【资料】里",IF(AND($D266&lt;&gt;"",ISNA(MATCH($D266,状态表,0))),"※状态不在【资料】里",IF(N($M266)&gt;N($L266),"※已还本金大于典当金额",IF(AND($I266&lt;&gt;"",$J266&lt;&gt;"",$J266&lt;$I266),"※到期日早于当票日期",IF(AND($H266&lt;&gt;"",COUNTIF($H$4:$H$403,$H266)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L266&lt;&gt;"",$E266=""),"※有金额没写客户","")))))</f>
+        <f>IF($E266="","",IF(AND($B266&lt;&gt;"",ISNA(MATCH($B266,机构表,0))),"※机构不在【资料】里",IF(AND($D266&lt;&gt;"",ISNA(MATCH($D266,状态表,0))),"※状态不在【资料】里",IF(N($M266)&gt;N($L266),"※已还本金大于典当金额",IF(AND($I266&lt;&gt;"",$J266&lt;&gt;"",$J266&lt;$I266),"※到期日早于当票日期",IF(AND($H266&lt;&gt;"",COUNTIF($H$4:$H$403,$H266)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L266&lt;&gt;"",$E266=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27284,7 +27347,7 @@
       <c r="V267" s="12" t="n"/>
       <c r="W267" s="12" t="n"/>
       <c r="X267" s="18">
-        <f>IF($E267="","",IF(AND($B267&lt;&gt;"",ISNA(MATCH($B267,机构表,0))),"※机构不在【资料】里",IF(AND($D267&lt;&gt;"",ISNA(MATCH($D267,状态表,0))),"※状态不在【资料】里",IF(N($M267)&gt;N($L267),"※已还本金大于典当金额",IF(AND($I267&lt;&gt;"",$J267&lt;&gt;"",$J267&lt;$I267),"※到期日早于当票日期",IF(AND($H267&lt;&gt;"",COUNTIF($H$4:$H$403,$H267)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L267&lt;&gt;"",$E267=""),"※有金额没写客户","")))))</f>
+        <f>IF($E267="","",IF(AND($B267&lt;&gt;"",ISNA(MATCH($B267,机构表,0))),"※机构不在【资料】里",IF(AND($D267&lt;&gt;"",ISNA(MATCH($D267,状态表,0))),"※状态不在【资料】里",IF(N($M267)&gt;N($L267),"※已还本金大于典当金额",IF(AND($I267&lt;&gt;"",$J267&lt;&gt;"",$J267&lt;$I267),"※到期日早于当票日期",IF(AND($H267&lt;&gt;"",COUNTIF($H$4:$H$403,$H267)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L267&lt;&gt;"",$E267=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27319,7 +27382,7 @@
       <c r="V268" s="12" t="n"/>
       <c r="W268" s="12" t="n"/>
       <c r="X268" s="18">
-        <f>IF($E268="","",IF(AND($B268&lt;&gt;"",ISNA(MATCH($B268,机构表,0))),"※机构不在【资料】里",IF(AND($D268&lt;&gt;"",ISNA(MATCH($D268,状态表,0))),"※状态不在【资料】里",IF(N($M268)&gt;N($L268),"※已还本金大于典当金额",IF(AND($I268&lt;&gt;"",$J268&lt;&gt;"",$J268&lt;$I268),"※到期日早于当票日期",IF(AND($H268&lt;&gt;"",COUNTIF($H$4:$H$403,$H268)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L268&lt;&gt;"",$E268=""),"※有金额没写客户","")))))</f>
+        <f>IF($E268="","",IF(AND($B268&lt;&gt;"",ISNA(MATCH($B268,机构表,0))),"※机构不在【资料】里",IF(AND($D268&lt;&gt;"",ISNA(MATCH($D268,状态表,0))),"※状态不在【资料】里",IF(N($M268)&gt;N($L268),"※已还本金大于典当金额",IF(AND($I268&lt;&gt;"",$J268&lt;&gt;"",$J268&lt;$I268),"※到期日早于当票日期",IF(AND($H268&lt;&gt;"",COUNTIF($H$4:$H$403,$H268)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L268&lt;&gt;"",$E268=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27354,7 +27417,7 @@
       <c r="V269" s="12" t="n"/>
       <c r="W269" s="12" t="n"/>
       <c r="X269" s="18">
-        <f>IF($E269="","",IF(AND($B269&lt;&gt;"",ISNA(MATCH($B269,机构表,0))),"※机构不在【资料】里",IF(AND($D269&lt;&gt;"",ISNA(MATCH($D269,状态表,0))),"※状态不在【资料】里",IF(N($M269)&gt;N($L269),"※已还本金大于典当金额",IF(AND($I269&lt;&gt;"",$J269&lt;&gt;"",$J269&lt;$I269),"※到期日早于当票日期",IF(AND($H269&lt;&gt;"",COUNTIF($H$4:$H$403,$H269)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L269&lt;&gt;"",$E269=""),"※有金额没写客户","")))))</f>
+        <f>IF($E269="","",IF(AND($B269&lt;&gt;"",ISNA(MATCH($B269,机构表,0))),"※机构不在【资料】里",IF(AND($D269&lt;&gt;"",ISNA(MATCH($D269,状态表,0))),"※状态不在【资料】里",IF(N($M269)&gt;N($L269),"※已还本金大于典当金额",IF(AND($I269&lt;&gt;"",$J269&lt;&gt;"",$J269&lt;$I269),"※到期日早于当票日期",IF(AND($H269&lt;&gt;"",COUNTIF($H$4:$H$403,$H269)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L269&lt;&gt;"",$E269=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27389,7 +27452,7 @@
       <c r="V270" s="12" t="n"/>
       <c r="W270" s="12" t="n"/>
       <c r="X270" s="18">
-        <f>IF($E270="","",IF(AND($B270&lt;&gt;"",ISNA(MATCH($B270,机构表,0))),"※机构不在【资料】里",IF(AND($D270&lt;&gt;"",ISNA(MATCH($D270,状态表,0))),"※状态不在【资料】里",IF(N($M270)&gt;N($L270),"※已还本金大于典当金额",IF(AND($I270&lt;&gt;"",$J270&lt;&gt;"",$J270&lt;$I270),"※到期日早于当票日期",IF(AND($H270&lt;&gt;"",COUNTIF($H$4:$H$403,$H270)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L270&lt;&gt;"",$E270=""),"※有金额没写客户","")))))</f>
+        <f>IF($E270="","",IF(AND($B270&lt;&gt;"",ISNA(MATCH($B270,机构表,0))),"※机构不在【资料】里",IF(AND($D270&lt;&gt;"",ISNA(MATCH($D270,状态表,0))),"※状态不在【资料】里",IF(N($M270)&gt;N($L270),"※已还本金大于典当金额",IF(AND($I270&lt;&gt;"",$J270&lt;&gt;"",$J270&lt;$I270),"※到期日早于当票日期",IF(AND($H270&lt;&gt;"",COUNTIF($H$4:$H$403,$H270)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L270&lt;&gt;"",$E270=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27424,7 +27487,7 @@
       <c r="V271" s="12" t="n"/>
       <c r="W271" s="12" t="n"/>
       <c r="X271" s="18">
-        <f>IF($E271="","",IF(AND($B271&lt;&gt;"",ISNA(MATCH($B271,机构表,0))),"※机构不在【资料】里",IF(AND($D271&lt;&gt;"",ISNA(MATCH($D271,状态表,0))),"※状态不在【资料】里",IF(N($M271)&gt;N($L271),"※已还本金大于典当金额",IF(AND($I271&lt;&gt;"",$J271&lt;&gt;"",$J271&lt;$I271),"※到期日早于当票日期",IF(AND($H271&lt;&gt;"",COUNTIF($H$4:$H$403,$H271)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L271&lt;&gt;"",$E271=""),"※有金额没写客户","")))))</f>
+        <f>IF($E271="","",IF(AND($B271&lt;&gt;"",ISNA(MATCH($B271,机构表,0))),"※机构不在【资料】里",IF(AND($D271&lt;&gt;"",ISNA(MATCH($D271,状态表,0))),"※状态不在【资料】里",IF(N($M271)&gt;N($L271),"※已还本金大于典当金额",IF(AND($I271&lt;&gt;"",$J271&lt;&gt;"",$J271&lt;$I271),"※到期日早于当票日期",IF(AND($H271&lt;&gt;"",COUNTIF($H$4:$H$403,$H271)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L271&lt;&gt;"",$E271=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27459,7 +27522,7 @@
       <c r="V272" s="12" t="n"/>
       <c r="W272" s="12" t="n"/>
       <c r="X272" s="18">
-        <f>IF($E272="","",IF(AND($B272&lt;&gt;"",ISNA(MATCH($B272,机构表,0))),"※机构不在【资料】里",IF(AND($D272&lt;&gt;"",ISNA(MATCH($D272,状态表,0))),"※状态不在【资料】里",IF(N($M272)&gt;N($L272),"※已还本金大于典当金额",IF(AND($I272&lt;&gt;"",$J272&lt;&gt;"",$J272&lt;$I272),"※到期日早于当票日期",IF(AND($H272&lt;&gt;"",COUNTIF($H$4:$H$403,$H272)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L272&lt;&gt;"",$E272=""),"※有金额没写客户","")))))</f>
+        <f>IF($E272="","",IF(AND($B272&lt;&gt;"",ISNA(MATCH($B272,机构表,0))),"※机构不在【资料】里",IF(AND($D272&lt;&gt;"",ISNA(MATCH($D272,状态表,0))),"※状态不在【资料】里",IF(N($M272)&gt;N($L272),"※已还本金大于典当金额",IF(AND($I272&lt;&gt;"",$J272&lt;&gt;"",$J272&lt;$I272),"※到期日早于当票日期",IF(AND($H272&lt;&gt;"",COUNTIF($H$4:$H$403,$H272)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L272&lt;&gt;"",$E272=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27494,7 +27557,7 @@
       <c r="V273" s="12" t="n"/>
       <c r="W273" s="12" t="n"/>
       <c r="X273" s="18">
-        <f>IF($E273="","",IF(AND($B273&lt;&gt;"",ISNA(MATCH($B273,机构表,0))),"※机构不在【资料】里",IF(AND($D273&lt;&gt;"",ISNA(MATCH($D273,状态表,0))),"※状态不在【资料】里",IF(N($M273)&gt;N($L273),"※已还本金大于典当金额",IF(AND($I273&lt;&gt;"",$J273&lt;&gt;"",$J273&lt;$I273),"※到期日早于当票日期",IF(AND($H273&lt;&gt;"",COUNTIF($H$4:$H$403,$H273)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L273&lt;&gt;"",$E273=""),"※有金额没写客户","")))))</f>
+        <f>IF($E273="","",IF(AND($B273&lt;&gt;"",ISNA(MATCH($B273,机构表,0))),"※机构不在【资料】里",IF(AND($D273&lt;&gt;"",ISNA(MATCH($D273,状态表,0))),"※状态不在【资料】里",IF(N($M273)&gt;N($L273),"※已还本金大于典当金额",IF(AND($I273&lt;&gt;"",$J273&lt;&gt;"",$J273&lt;$I273),"※到期日早于当票日期",IF(AND($H273&lt;&gt;"",COUNTIF($H$4:$H$403,$H273)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L273&lt;&gt;"",$E273=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27529,7 +27592,7 @@
       <c r="V274" s="12" t="n"/>
       <c r="W274" s="12" t="n"/>
       <c r="X274" s="18">
-        <f>IF($E274="","",IF(AND($B274&lt;&gt;"",ISNA(MATCH($B274,机构表,0))),"※机构不在【资料】里",IF(AND($D274&lt;&gt;"",ISNA(MATCH($D274,状态表,0))),"※状态不在【资料】里",IF(N($M274)&gt;N($L274),"※已还本金大于典当金额",IF(AND($I274&lt;&gt;"",$J274&lt;&gt;"",$J274&lt;$I274),"※到期日早于当票日期",IF(AND($H274&lt;&gt;"",COUNTIF($H$4:$H$403,$H274)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L274&lt;&gt;"",$E274=""),"※有金额没写客户","")))))</f>
+        <f>IF($E274="","",IF(AND($B274&lt;&gt;"",ISNA(MATCH($B274,机构表,0))),"※机构不在【资料】里",IF(AND($D274&lt;&gt;"",ISNA(MATCH($D274,状态表,0))),"※状态不在【资料】里",IF(N($M274)&gt;N($L274),"※已还本金大于典当金额",IF(AND($I274&lt;&gt;"",$J274&lt;&gt;"",$J274&lt;$I274),"※到期日早于当票日期",IF(AND($H274&lt;&gt;"",COUNTIF($H$4:$H$403,$H274)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L274&lt;&gt;"",$E274=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27564,7 +27627,7 @@
       <c r="V275" s="12" t="n"/>
       <c r="W275" s="12" t="n"/>
       <c r="X275" s="18">
-        <f>IF($E275="","",IF(AND($B275&lt;&gt;"",ISNA(MATCH($B275,机构表,0))),"※机构不在【资料】里",IF(AND($D275&lt;&gt;"",ISNA(MATCH($D275,状态表,0))),"※状态不在【资料】里",IF(N($M275)&gt;N($L275),"※已还本金大于典当金额",IF(AND($I275&lt;&gt;"",$J275&lt;&gt;"",$J275&lt;$I275),"※到期日早于当票日期",IF(AND($H275&lt;&gt;"",COUNTIF($H$4:$H$403,$H275)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L275&lt;&gt;"",$E275=""),"※有金额没写客户","")))))</f>
+        <f>IF($E275="","",IF(AND($B275&lt;&gt;"",ISNA(MATCH($B275,机构表,0))),"※机构不在【资料】里",IF(AND($D275&lt;&gt;"",ISNA(MATCH($D275,状态表,0))),"※状态不在【资料】里",IF(N($M275)&gt;N($L275),"※已还本金大于典当金额",IF(AND($I275&lt;&gt;"",$J275&lt;&gt;"",$J275&lt;$I275),"※到期日早于当票日期",IF(AND($H275&lt;&gt;"",COUNTIF($H$4:$H$403,$H275)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L275&lt;&gt;"",$E275=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27599,7 +27662,7 @@
       <c r="V276" s="12" t="n"/>
       <c r="W276" s="12" t="n"/>
       <c r="X276" s="18">
-        <f>IF($E276="","",IF(AND($B276&lt;&gt;"",ISNA(MATCH($B276,机构表,0))),"※机构不在【资料】里",IF(AND($D276&lt;&gt;"",ISNA(MATCH($D276,状态表,0))),"※状态不在【资料】里",IF(N($M276)&gt;N($L276),"※已还本金大于典当金额",IF(AND($I276&lt;&gt;"",$J276&lt;&gt;"",$J276&lt;$I276),"※到期日早于当票日期",IF(AND($H276&lt;&gt;"",COUNTIF($H$4:$H$403,$H276)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L276&lt;&gt;"",$E276=""),"※有金额没写客户","")))))</f>
+        <f>IF($E276="","",IF(AND($B276&lt;&gt;"",ISNA(MATCH($B276,机构表,0))),"※机构不在【资料】里",IF(AND($D276&lt;&gt;"",ISNA(MATCH($D276,状态表,0))),"※状态不在【资料】里",IF(N($M276)&gt;N($L276),"※已还本金大于典当金额",IF(AND($I276&lt;&gt;"",$J276&lt;&gt;"",$J276&lt;$I276),"※到期日早于当票日期",IF(AND($H276&lt;&gt;"",COUNTIF($H$4:$H$403,$H276)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L276&lt;&gt;"",$E276=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27634,7 +27697,7 @@
       <c r="V277" s="12" t="n"/>
       <c r="W277" s="12" t="n"/>
       <c r="X277" s="18">
-        <f>IF($E277="","",IF(AND($B277&lt;&gt;"",ISNA(MATCH($B277,机构表,0))),"※机构不在【资料】里",IF(AND($D277&lt;&gt;"",ISNA(MATCH($D277,状态表,0))),"※状态不在【资料】里",IF(N($M277)&gt;N($L277),"※已还本金大于典当金额",IF(AND($I277&lt;&gt;"",$J277&lt;&gt;"",$J277&lt;$I277),"※到期日早于当票日期",IF(AND($H277&lt;&gt;"",COUNTIF($H$4:$H$403,$H277)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L277&lt;&gt;"",$E277=""),"※有金额没写客户","")))))</f>
+        <f>IF($E277="","",IF(AND($B277&lt;&gt;"",ISNA(MATCH($B277,机构表,0))),"※机构不在【资料】里",IF(AND($D277&lt;&gt;"",ISNA(MATCH($D277,状态表,0))),"※状态不在【资料】里",IF(N($M277)&gt;N($L277),"※已还本金大于典当金额",IF(AND($I277&lt;&gt;"",$J277&lt;&gt;"",$J277&lt;$I277),"※到期日早于当票日期",IF(AND($H277&lt;&gt;"",COUNTIF($H$4:$H$403,$H277)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L277&lt;&gt;"",$E277=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27669,7 +27732,7 @@
       <c r="V278" s="12" t="n"/>
       <c r="W278" s="12" t="n"/>
       <c r="X278" s="18">
-        <f>IF($E278="","",IF(AND($B278&lt;&gt;"",ISNA(MATCH($B278,机构表,0))),"※机构不在【资料】里",IF(AND($D278&lt;&gt;"",ISNA(MATCH($D278,状态表,0))),"※状态不在【资料】里",IF(N($M278)&gt;N($L278),"※已还本金大于典当金额",IF(AND($I278&lt;&gt;"",$J278&lt;&gt;"",$J278&lt;$I278),"※到期日早于当票日期",IF(AND($H278&lt;&gt;"",COUNTIF($H$4:$H$403,$H278)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L278&lt;&gt;"",$E278=""),"※有金额没写客户","")))))</f>
+        <f>IF($E278="","",IF(AND($B278&lt;&gt;"",ISNA(MATCH($B278,机构表,0))),"※机构不在【资料】里",IF(AND($D278&lt;&gt;"",ISNA(MATCH($D278,状态表,0))),"※状态不在【资料】里",IF(N($M278)&gt;N($L278),"※已还本金大于典当金额",IF(AND($I278&lt;&gt;"",$J278&lt;&gt;"",$J278&lt;$I278),"※到期日早于当票日期",IF(AND($H278&lt;&gt;"",COUNTIF($H$4:$H$403,$H278)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L278&lt;&gt;"",$E278=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27704,7 +27767,7 @@
       <c r="V279" s="12" t="n"/>
       <c r="W279" s="12" t="n"/>
       <c r="X279" s="18">
-        <f>IF($E279="","",IF(AND($B279&lt;&gt;"",ISNA(MATCH($B279,机构表,0))),"※机构不在【资料】里",IF(AND($D279&lt;&gt;"",ISNA(MATCH($D279,状态表,0))),"※状态不在【资料】里",IF(N($M279)&gt;N($L279),"※已还本金大于典当金额",IF(AND($I279&lt;&gt;"",$J279&lt;&gt;"",$J279&lt;$I279),"※到期日早于当票日期",IF(AND($H279&lt;&gt;"",COUNTIF($H$4:$H$403,$H279)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L279&lt;&gt;"",$E279=""),"※有金额没写客户","")))))</f>
+        <f>IF($E279="","",IF(AND($B279&lt;&gt;"",ISNA(MATCH($B279,机构表,0))),"※机构不在【资料】里",IF(AND($D279&lt;&gt;"",ISNA(MATCH($D279,状态表,0))),"※状态不在【资料】里",IF(N($M279)&gt;N($L279),"※已还本金大于典当金额",IF(AND($I279&lt;&gt;"",$J279&lt;&gt;"",$J279&lt;$I279),"※到期日早于当票日期",IF(AND($H279&lt;&gt;"",COUNTIF($H$4:$H$403,$H279)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L279&lt;&gt;"",$E279=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27739,7 +27802,7 @@
       <c r="V280" s="12" t="n"/>
       <c r="W280" s="12" t="n"/>
       <c r="X280" s="18">
-        <f>IF($E280="","",IF(AND($B280&lt;&gt;"",ISNA(MATCH($B280,机构表,0))),"※机构不在【资料】里",IF(AND($D280&lt;&gt;"",ISNA(MATCH($D280,状态表,0))),"※状态不在【资料】里",IF(N($M280)&gt;N($L280),"※已还本金大于典当金额",IF(AND($I280&lt;&gt;"",$J280&lt;&gt;"",$J280&lt;$I280),"※到期日早于当票日期",IF(AND($H280&lt;&gt;"",COUNTIF($H$4:$H$403,$H280)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L280&lt;&gt;"",$E280=""),"※有金额没写客户","")))))</f>
+        <f>IF($E280="","",IF(AND($B280&lt;&gt;"",ISNA(MATCH($B280,机构表,0))),"※机构不在【资料】里",IF(AND($D280&lt;&gt;"",ISNA(MATCH($D280,状态表,0))),"※状态不在【资料】里",IF(N($M280)&gt;N($L280),"※已还本金大于典当金额",IF(AND($I280&lt;&gt;"",$J280&lt;&gt;"",$J280&lt;$I280),"※到期日早于当票日期",IF(AND($H280&lt;&gt;"",COUNTIF($H$4:$H$403,$H280)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L280&lt;&gt;"",$E280=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27774,7 +27837,7 @@
       <c r="V281" s="12" t="n"/>
       <c r="W281" s="12" t="n"/>
       <c r="X281" s="18">
-        <f>IF($E281="","",IF(AND($B281&lt;&gt;"",ISNA(MATCH($B281,机构表,0))),"※机构不在【资料】里",IF(AND($D281&lt;&gt;"",ISNA(MATCH($D281,状态表,0))),"※状态不在【资料】里",IF(N($M281)&gt;N($L281),"※已还本金大于典当金额",IF(AND($I281&lt;&gt;"",$J281&lt;&gt;"",$J281&lt;$I281),"※到期日早于当票日期",IF(AND($H281&lt;&gt;"",COUNTIF($H$4:$H$403,$H281)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L281&lt;&gt;"",$E281=""),"※有金额没写客户","")))))</f>
+        <f>IF($E281="","",IF(AND($B281&lt;&gt;"",ISNA(MATCH($B281,机构表,0))),"※机构不在【资料】里",IF(AND($D281&lt;&gt;"",ISNA(MATCH($D281,状态表,0))),"※状态不在【资料】里",IF(N($M281)&gt;N($L281),"※已还本金大于典当金额",IF(AND($I281&lt;&gt;"",$J281&lt;&gt;"",$J281&lt;$I281),"※到期日早于当票日期",IF(AND($H281&lt;&gt;"",COUNTIF($H$4:$H$403,$H281)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L281&lt;&gt;"",$E281=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27809,7 +27872,7 @@
       <c r="V282" s="12" t="n"/>
       <c r="W282" s="12" t="n"/>
       <c r="X282" s="18">
-        <f>IF($E282="","",IF(AND($B282&lt;&gt;"",ISNA(MATCH($B282,机构表,0))),"※机构不在【资料】里",IF(AND($D282&lt;&gt;"",ISNA(MATCH($D282,状态表,0))),"※状态不在【资料】里",IF(N($M282)&gt;N($L282),"※已还本金大于典当金额",IF(AND($I282&lt;&gt;"",$J282&lt;&gt;"",$J282&lt;$I282),"※到期日早于当票日期",IF(AND($H282&lt;&gt;"",COUNTIF($H$4:$H$403,$H282)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L282&lt;&gt;"",$E282=""),"※有金额没写客户","")))))</f>
+        <f>IF($E282="","",IF(AND($B282&lt;&gt;"",ISNA(MATCH($B282,机构表,0))),"※机构不在【资料】里",IF(AND($D282&lt;&gt;"",ISNA(MATCH($D282,状态表,0))),"※状态不在【资料】里",IF(N($M282)&gt;N($L282),"※已还本金大于典当金额",IF(AND($I282&lt;&gt;"",$J282&lt;&gt;"",$J282&lt;$I282),"※到期日早于当票日期",IF(AND($H282&lt;&gt;"",COUNTIF($H$4:$H$403,$H282)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L282&lt;&gt;"",$E282=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27844,7 +27907,7 @@
       <c r="V283" s="12" t="n"/>
       <c r="W283" s="12" t="n"/>
       <c r="X283" s="18">
-        <f>IF($E283="","",IF(AND($B283&lt;&gt;"",ISNA(MATCH($B283,机构表,0))),"※机构不在【资料】里",IF(AND($D283&lt;&gt;"",ISNA(MATCH($D283,状态表,0))),"※状态不在【资料】里",IF(N($M283)&gt;N($L283),"※已还本金大于典当金额",IF(AND($I283&lt;&gt;"",$J283&lt;&gt;"",$J283&lt;$I283),"※到期日早于当票日期",IF(AND($H283&lt;&gt;"",COUNTIF($H$4:$H$403,$H283)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L283&lt;&gt;"",$E283=""),"※有金额没写客户","")))))</f>
+        <f>IF($E283="","",IF(AND($B283&lt;&gt;"",ISNA(MATCH($B283,机构表,0))),"※机构不在【资料】里",IF(AND($D283&lt;&gt;"",ISNA(MATCH($D283,状态表,0))),"※状态不在【资料】里",IF(N($M283)&gt;N($L283),"※已还本金大于典当金额",IF(AND($I283&lt;&gt;"",$J283&lt;&gt;"",$J283&lt;$I283),"※到期日早于当票日期",IF(AND($H283&lt;&gt;"",COUNTIF($H$4:$H$403,$H283)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L283&lt;&gt;"",$E283=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27879,7 +27942,7 @@
       <c r="V284" s="12" t="n"/>
       <c r="W284" s="12" t="n"/>
       <c r="X284" s="18">
-        <f>IF($E284="","",IF(AND($B284&lt;&gt;"",ISNA(MATCH($B284,机构表,0))),"※机构不在【资料】里",IF(AND($D284&lt;&gt;"",ISNA(MATCH($D284,状态表,0))),"※状态不在【资料】里",IF(N($M284)&gt;N($L284),"※已还本金大于典当金额",IF(AND($I284&lt;&gt;"",$J284&lt;&gt;"",$J284&lt;$I284),"※到期日早于当票日期",IF(AND($H284&lt;&gt;"",COUNTIF($H$4:$H$403,$H284)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L284&lt;&gt;"",$E284=""),"※有金额没写客户","")))))</f>
+        <f>IF($E284="","",IF(AND($B284&lt;&gt;"",ISNA(MATCH($B284,机构表,0))),"※机构不在【资料】里",IF(AND($D284&lt;&gt;"",ISNA(MATCH($D284,状态表,0))),"※状态不在【资料】里",IF(N($M284)&gt;N($L284),"※已还本金大于典当金额",IF(AND($I284&lt;&gt;"",$J284&lt;&gt;"",$J284&lt;$I284),"※到期日早于当票日期",IF(AND($H284&lt;&gt;"",COUNTIF($H$4:$H$403,$H284)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L284&lt;&gt;"",$E284=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27914,7 +27977,7 @@
       <c r="V285" s="12" t="n"/>
       <c r="W285" s="12" t="n"/>
       <c r="X285" s="18">
-        <f>IF($E285="","",IF(AND($B285&lt;&gt;"",ISNA(MATCH($B285,机构表,0))),"※机构不在【资料】里",IF(AND($D285&lt;&gt;"",ISNA(MATCH($D285,状态表,0))),"※状态不在【资料】里",IF(N($M285)&gt;N($L285),"※已还本金大于典当金额",IF(AND($I285&lt;&gt;"",$J285&lt;&gt;"",$J285&lt;$I285),"※到期日早于当票日期",IF(AND($H285&lt;&gt;"",COUNTIF($H$4:$H$403,$H285)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L285&lt;&gt;"",$E285=""),"※有金额没写客户","")))))</f>
+        <f>IF($E285="","",IF(AND($B285&lt;&gt;"",ISNA(MATCH($B285,机构表,0))),"※机构不在【资料】里",IF(AND($D285&lt;&gt;"",ISNA(MATCH($D285,状态表,0))),"※状态不在【资料】里",IF(N($M285)&gt;N($L285),"※已还本金大于典当金额",IF(AND($I285&lt;&gt;"",$J285&lt;&gt;"",$J285&lt;$I285),"※到期日早于当票日期",IF(AND($H285&lt;&gt;"",COUNTIF($H$4:$H$403,$H285)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L285&lt;&gt;"",$E285=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27949,7 +28012,7 @@
       <c r="V286" s="12" t="n"/>
       <c r="W286" s="12" t="n"/>
       <c r="X286" s="18">
-        <f>IF($E286="","",IF(AND($B286&lt;&gt;"",ISNA(MATCH($B286,机构表,0))),"※机构不在【资料】里",IF(AND($D286&lt;&gt;"",ISNA(MATCH($D286,状态表,0))),"※状态不在【资料】里",IF(N($M286)&gt;N($L286),"※已还本金大于典当金额",IF(AND($I286&lt;&gt;"",$J286&lt;&gt;"",$J286&lt;$I286),"※到期日早于当票日期",IF(AND($H286&lt;&gt;"",COUNTIF($H$4:$H$403,$H286)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L286&lt;&gt;"",$E286=""),"※有金额没写客户","")))))</f>
+        <f>IF($E286="","",IF(AND($B286&lt;&gt;"",ISNA(MATCH($B286,机构表,0))),"※机构不在【资料】里",IF(AND($D286&lt;&gt;"",ISNA(MATCH($D286,状态表,0))),"※状态不在【资料】里",IF(N($M286)&gt;N($L286),"※已还本金大于典当金额",IF(AND($I286&lt;&gt;"",$J286&lt;&gt;"",$J286&lt;$I286),"※到期日早于当票日期",IF(AND($H286&lt;&gt;"",COUNTIF($H$4:$H$403,$H286)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L286&lt;&gt;"",$E286=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -27984,7 +28047,7 @@
       <c r="V287" s="12" t="n"/>
       <c r="W287" s="12" t="n"/>
       <c r="X287" s="18">
-        <f>IF($E287="","",IF(AND($B287&lt;&gt;"",ISNA(MATCH($B287,机构表,0))),"※机构不在【资料】里",IF(AND($D287&lt;&gt;"",ISNA(MATCH($D287,状态表,0))),"※状态不在【资料】里",IF(N($M287)&gt;N($L287),"※已还本金大于典当金额",IF(AND($I287&lt;&gt;"",$J287&lt;&gt;"",$J287&lt;$I287),"※到期日早于当票日期",IF(AND($H287&lt;&gt;"",COUNTIF($H$4:$H$403,$H287)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L287&lt;&gt;"",$E287=""),"※有金额没写客户","")))))</f>
+        <f>IF($E287="","",IF(AND($B287&lt;&gt;"",ISNA(MATCH($B287,机构表,0))),"※机构不在【资料】里",IF(AND($D287&lt;&gt;"",ISNA(MATCH($D287,状态表,0))),"※状态不在【资料】里",IF(N($M287)&gt;N($L287),"※已还本金大于典当金额",IF(AND($I287&lt;&gt;"",$J287&lt;&gt;"",$J287&lt;$I287),"※到期日早于当票日期",IF(AND($H287&lt;&gt;"",COUNTIF($H$4:$H$403,$H287)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L287&lt;&gt;"",$E287=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28019,7 +28082,7 @@
       <c r="V288" s="12" t="n"/>
       <c r="W288" s="12" t="n"/>
       <c r="X288" s="18">
-        <f>IF($E288="","",IF(AND($B288&lt;&gt;"",ISNA(MATCH($B288,机构表,0))),"※机构不在【资料】里",IF(AND($D288&lt;&gt;"",ISNA(MATCH($D288,状态表,0))),"※状态不在【资料】里",IF(N($M288)&gt;N($L288),"※已还本金大于典当金额",IF(AND($I288&lt;&gt;"",$J288&lt;&gt;"",$J288&lt;$I288),"※到期日早于当票日期",IF(AND($H288&lt;&gt;"",COUNTIF($H$4:$H$403,$H288)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L288&lt;&gt;"",$E288=""),"※有金额没写客户","")))))</f>
+        <f>IF($E288="","",IF(AND($B288&lt;&gt;"",ISNA(MATCH($B288,机构表,0))),"※机构不在【资料】里",IF(AND($D288&lt;&gt;"",ISNA(MATCH($D288,状态表,0))),"※状态不在【资料】里",IF(N($M288)&gt;N($L288),"※已还本金大于典当金额",IF(AND($I288&lt;&gt;"",$J288&lt;&gt;"",$J288&lt;$I288),"※到期日早于当票日期",IF(AND($H288&lt;&gt;"",COUNTIF($H$4:$H$403,$H288)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L288&lt;&gt;"",$E288=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28054,7 +28117,7 @@
       <c r="V289" s="12" t="n"/>
       <c r="W289" s="12" t="n"/>
       <c r="X289" s="18">
-        <f>IF($E289="","",IF(AND($B289&lt;&gt;"",ISNA(MATCH($B289,机构表,0))),"※机构不在【资料】里",IF(AND($D289&lt;&gt;"",ISNA(MATCH($D289,状态表,0))),"※状态不在【资料】里",IF(N($M289)&gt;N($L289),"※已还本金大于典当金额",IF(AND($I289&lt;&gt;"",$J289&lt;&gt;"",$J289&lt;$I289),"※到期日早于当票日期",IF(AND($H289&lt;&gt;"",COUNTIF($H$4:$H$403,$H289)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L289&lt;&gt;"",$E289=""),"※有金额没写客户","")))))</f>
+        <f>IF($E289="","",IF(AND($B289&lt;&gt;"",ISNA(MATCH($B289,机构表,0))),"※机构不在【资料】里",IF(AND($D289&lt;&gt;"",ISNA(MATCH($D289,状态表,0))),"※状态不在【资料】里",IF(N($M289)&gt;N($L289),"※已还本金大于典当金额",IF(AND($I289&lt;&gt;"",$J289&lt;&gt;"",$J289&lt;$I289),"※到期日早于当票日期",IF(AND($H289&lt;&gt;"",COUNTIF($H$4:$H$403,$H289)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L289&lt;&gt;"",$E289=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28089,7 +28152,7 @@
       <c r="V290" s="12" t="n"/>
       <c r="W290" s="12" t="n"/>
       <c r="X290" s="18">
-        <f>IF($E290="","",IF(AND($B290&lt;&gt;"",ISNA(MATCH($B290,机构表,0))),"※机构不在【资料】里",IF(AND($D290&lt;&gt;"",ISNA(MATCH($D290,状态表,0))),"※状态不在【资料】里",IF(N($M290)&gt;N($L290),"※已还本金大于典当金额",IF(AND($I290&lt;&gt;"",$J290&lt;&gt;"",$J290&lt;$I290),"※到期日早于当票日期",IF(AND($H290&lt;&gt;"",COUNTIF($H$4:$H$403,$H290)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L290&lt;&gt;"",$E290=""),"※有金额没写客户","")))))</f>
+        <f>IF($E290="","",IF(AND($B290&lt;&gt;"",ISNA(MATCH($B290,机构表,0))),"※机构不在【资料】里",IF(AND($D290&lt;&gt;"",ISNA(MATCH($D290,状态表,0))),"※状态不在【资料】里",IF(N($M290)&gt;N($L290),"※已还本金大于典当金额",IF(AND($I290&lt;&gt;"",$J290&lt;&gt;"",$J290&lt;$I290),"※到期日早于当票日期",IF(AND($H290&lt;&gt;"",COUNTIF($H$4:$H$403,$H290)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L290&lt;&gt;"",$E290=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28124,7 +28187,7 @@
       <c r="V291" s="12" t="n"/>
       <c r="W291" s="12" t="n"/>
       <c r="X291" s="18">
-        <f>IF($E291="","",IF(AND($B291&lt;&gt;"",ISNA(MATCH($B291,机构表,0))),"※机构不在【资料】里",IF(AND($D291&lt;&gt;"",ISNA(MATCH($D291,状态表,0))),"※状态不在【资料】里",IF(N($M291)&gt;N($L291),"※已还本金大于典当金额",IF(AND($I291&lt;&gt;"",$J291&lt;&gt;"",$J291&lt;$I291),"※到期日早于当票日期",IF(AND($H291&lt;&gt;"",COUNTIF($H$4:$H$403,$H291)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L291&lt;&gt;"",$E291=""),"※有金额没写客户","")))))</f>
+        <f>IF($E291="","",IF(AND($B291&lt;&gt;"",ISNA(MATCH($B291,机构表,0))),"※机构不在【资料】里",IF(AND($D291&lt;&gt;"",ISNA(MATCH($D291,状态表,0))),"※状态不在【资料】里",IF(N($M291)&gt;N($L291),"※已还本金大于典当金额",IF(AND($I291&lt;&gt;"",$J291&lt;&gt;"",$J291&lt;$I291),"※到期日早于当票日期",IF(AND($H291&lt;&gt;"",COUNTIF($H$4:$H$403,$H291)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L291&lt;&gt;"",$E291=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28159,7 +28222,7 @@
       <c r="V292" s="12" t="n"/>
       <c r="W292" s="12" t="n"/>
       <c r="X292" s="18">
-        <f>IF($E292="","",IF(AND($B292&lt;&gt;"",ISNA(MATCH($B292,机构表,0))),"※机构不在【资料】里",IF(AND($D292&lt;&gt;"",ISNA(MATCH($D292,状态表,0))),"※状态不在【资料】里",IF(N($M292)&gt;N($L292),"※已还本金大于典当金额",IF(AND($I292&lt;&gt;"",$J292&lt;&gt;"",$J292&lt;$I292),"※到期日早于当票日期",IF(AND($H292&lt;&gt;"",COUNTIF($H$4:$H$403,$H292)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L292&lt;&gt;"",$E292=""),"※有金额没写客户","")))))</f>
+        <f>IF($E292="","",IF(AND($B292&lt;&gt;"",ISNA(MATCH($B292,机构表,0))),"※机构不在【资料】里",IF(AND($D292&lt;&gt;"",ISNA(MATCH($D292,状态表,0))),"※状态不在【资料】里",IF(N($M292)&gt;N($L292),"※已还本金大于典当金额",IF(AND($I292&lt;&gt;"",$J292&lt;&gt;"",$J292&lt;$I292),"※到期日早于当票日期",IF(AND($H292&lt;&gt;"",COUNTIF($H$4:$H$403,$H292)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L292&lt;&gt;"",$E292=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28194,7 +28257,7 @@
       <c r="V293" s="12" t="n"/>
       <c r="W293" s="12" t="n"/>
       <c r="X293" s="18">
-        <f>IF($E293="","",IF(AND($B293&lt;&gt;"",ISNA(MATCH($B293,机构表,0))),"※机构不在【资料】里",IF(AND($D293&lt;&gt;"",ISNA(MATCH($D293,状态表,0))),"※状态不在【资料】里",IF(N($M293)&gt;N($L293),"※已还本金大于典当金额",IF(AND($I293&lt;&gt;"",$J293&lt;&gt;"",$J293&lt;$I293),"※到期日早于当票日期",IF(AND($H293&lt;&gt;"",COUNTIF($H$4:$H$403,$H293)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L293&lt;&gt;"",$E293=""),"※有金额没写客户","")))))</f>
+        <f>IF($E293="","",IF(AND($B293&lt;&gt;"",ISNA(MATCH($B293,机构表,0))),"※机构不在【资料】里",IF(AND($D293&lt;&gt;"",ISNA(MATCH($D293,状态表,0))),"※状态不在【资料】里",IF(N($M293)&gt;N($L293),"※已还本金大于典当金额",IF(AND($I293&lt;&gt;"",$J293&lt;&gt;"",$J293&lt;$I293),"※到期日早于当票日期",IF(AND($H293&lt;&gt;"",COUNTIF($H$4:$H$403,$H293)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L293&lt;&gt;"",$E293=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28229,7 +28292,7 @@
       <c r="V294" s="12" t="n"/>
       <c r="W294" s="12" t="n"/>
       <c r="X294" s="18">
-        <f>IF($E294="","",IF(AND($B294&lt;&gt;"",ISNA(MATCH($B294,机构表,0))),"※机构不在【资料】里",IF(AND($D294&lt;&gt;"",ISNA(MATCH($D294,状态表,0))),"※状态不在【资料】里",IF(N($M294)&gt;N($L294),"※已还本金大于典当金额",IF(AND($I294&lt;&gt;"",$J294&lt;&gt;"",$J294&lt;$I294),"※到期日早于当票日期",IF(AND($H294&lt;&gt;"",COUNTIF($H$4:$H$403,$H294)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L294&lt;&gt;"",$E294=""),"※有金额没写客户","")))))</f>
+        <f>IF($E294="","",IF(AND($B294&lt;&gt;"",ISNA(MATCH($B294,机构表,0))),"※机构不在【资料】里",IF(AND($D294&lt;&gt;"",ISNA(MATCH($D294,状态表,0))),"※状态不在【资料】里",IF(N($M294)&gt;N($L294),"※已还本金大于典当金额",IF(AND($I294&lt;&gt;"",$J294&lt;&gt;"",$J294&lt;$I294),"※到期日早于当票日期",IF(AND($H294&lt;&gt;"",COUNTIF($H$4:$H$403,$H294)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L294&lt;&gt;"",$E294=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28264,7 +28327,7 @@
       <c r="V295" s="12" t="n"/>
       <c r="W295" s="12" t="n"/>
       <c r="X295" s="18">
-        <f>IF($E295="","",IF(AND($B295&lt;&gt;"",ISNA(MATCH($B295,机构表,0))),"※机构不在【资料】里",IF(AND($D295&lt;&gt;"",ISNA(MATCH($D295,状态表,0))),"※状态不在【资料】里",IF(N($M295)&gt;N($L295),"※已还本金大于典当金额",IF(AND($I295&lt;&gt;"",$J295&lt;&gt;"",$J295&lt;$I295),"※到期日早于当票日期",IF(AND($H295&lt;&gt;"",COUNTIF($H$4:$H$403,$H295)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L295&lt;&gt;"",$E295=""),"※有金额没写客户","")))))</f>
+        <f>IF($E295="","",IF(AND($B295&lt;&gt;"",ISNA(MATCH($B295,机构表,0))),"※机构不在【资料】里",IF(AND($D295&lt;&gt;"",ISNA(MATCH($D295,状态表,0))),"※状态不在【资料】里",IF(N($M295)&gt;N($L295),"※已还本金大于典当金额",IF(AND($I295&lt;&gt;"",$J295&lt;&gt;"",$J295&lt;$I295),"※到期日早于当票日期",IF(AND($H295&lt;&gt;"",COUNTIF($H$4:$H$403,$H295)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L295&lt;&gt;"",$E295=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28299,7 +28362,7 @@
       <c r="V296" s="12" t="n"/>
       <c r="W296" s="12" t="n"/>
       <c r="X296" s="18">
-        <f>IF($E296="","",IF(AND($B296&lt;&gt;"",ISNA(MATCH($B296,机构表,0))),"※机构不在【资料】里",IF(AND($D296&lt;&gt;"",ISNA(MATCH($D296,状态表,0))),"※状态不在【资料】里",IF(N($M296)&gt;N($L296),"※已还本金大于典当金额",IF(AND($I296&lt;&gt;"",$J296&lt;&gt;"",$J296&lt;$I296),"※到期日早于当票日期",IF(AND($H296&lt;&gt;"",COUNTIF($H$4:$H$403,$H296)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L296&lt;&gt;"",$E296=""),"※有金额没写客户","")))))</f>
+        <f>IF($E296="","",IF(AND($B296&lt;&gt;"",ISNA(MATCH($B296,机构表,0))),"※机构不在【资料】里",IF(AND($D296&lt;&gt;"",ISNA(MATCH($D296,状态表,0))),"※状态不在【资料】里",IF(N($M296)&gt;N($L296),"※已还本金大于典当金额",IF(AND($I296&lt;&gt;"",$J296&lt;&gt;"",$J296&lt;$I296),"※到期日早于当票日期",IF(AND($H296&lt;&gt;"",COUNTIF($H$4:$H$403,$H296)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L296&lt;&gt;"",$E296=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28334,7 +28397,7 @@
       <c r="V297" s="12" t="n"/>
       <c r="W297" s="12" t="n"/>
       <c r="X297" s="18">
-        <f>IF($E297="","",IF(AND($B297&lt;&gt;"",ISNA(MATCH($B297,机构表,0))),"※机构不在【资料】里",IF(AND($D297&lt;&gt;"",ISNA(MATCH($D297,状态表,0))),"※状态不在【资料】里",IF(N($M297)&gt;N($L297),"※已还本金大于典当金额",IF(AND($I297&lt;&gt;"",$J297&lt;&gt;"",$J297&lt;$I297),"※到期日早于当票日期",IF(AND($H297&lt;&gt;"",COUNTIF($H$4:$H$403,$H297)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L297&lt;&gt;"",$E297=""),"※有金额没写客户","")))))</f>
+        <f>IF($E297="","",IF(AND($B297&lt;&gt;"",ISNA(MATCH($B297,机构表,0))),"※机构不在【资料】里",IF(AND($D297&lt;&gt;"",ISNA(MATCH($D297,状态表,0))),"※状态不在【资料】里",IF(N($M297)&gt;N($L297),"※已还本金大于典当金额",IF(AND($I297&lt;&gt;"",$J297&lt;&gt;"",$J297&lt;$I297),"※到期日早于当票日期",IF(AND($H297&lt;&gt;"",COUNTIF($H$4:$H$403,$H297)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L297&lt;&gt;"",$E297=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28369,7 +28432,7 @@
       <c r="V298" s="12" t="n"/>
       <c r="W298" s="12" t="n"/>
       <c r="X298" s="18">
-        <f>IF($E298="","",IF(AND($B298&lt;&gt;"",ISNA(MATCH($B298,机构表,0))),"※机构不在【资料】里",IF(AND($D298&lt;&gt;"",ISNA(MATCH($D298,状态表,0))),"※状态不在【资料】里",IF(N($M298)&gt;N($L298),"※已还本金大于典当金额",IF(AND($I298&lt;&gt;"",$J298&lt;&gt;"",$J298&lt;$I298),"※到期日早于当票日期",IF(AND($H298&lt;&gt;"",COUNTIF($H$4:$H$403,$H298)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L298&lt;&gt;"",$E298=""),"※有金额没写客户","")))))</f>
+        <f>IF($E298="","",IF(AND($B298&lt;&gt;"",ISNA(MATCH($B298,机构表,0))),"※机构不在【资料】里",IF(AND($D298&lt;&gt;"",ISNA(MATCH($D298,状态表,0))),"※状态不在【资料】里",IF(N($M298)&gt;N($L298),"※已还本金大于典当金额",IF(AND($I298&lt;&gt;"",$J298&lt;&gt;"",$J298&lt;$I298),"※到期日早于当票日期",IF(AND($H298&lt;&gt;"",COUNTIF($H$4:$H$403,$H298)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L298&lt;&gt;"",$E298=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28404,7 +28467,7 @@
       <c r="V299" s="12" t="n"/>
       <c r="W299" s="12" t="n"/>
       <c r="X299" s="18">
-        <f>IF($E299="","",IF(AND($B299&lt;&gt;"",ISNA(MATCH($B299,机构表,0))),"※机构不在【资料】里",IF(AND($D299&lt;&gt;"",ISNA(MATCH($D299,状态表,0))),"※状态不在【资料】里",IF(N($M299)&gt;N($L299),"※已还本金大于典当金额",IF(AND($I299&lt;&gt;"",$J299&lt;&gt;"",$J299&lt;$I299),"※到期日早于当票日期",IF(AND($H299&lt;&gt;"",COUNTIF($H$4:$H$403,$H299)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L299&lt;&gt;"",$E299=""),"※有金额没写客户","")))))</f>
+        <f>IF($E299="","",IF(AND($B299&lt;&gt;"",ISNA(MATCH($B299,机构表,0))),"※机构不在【资料】里",IF(AND($D299&lt;&gt;"",ISNA(MATCH($D299,状态表,0))),"※状态不在【资料】里",IF(N($M299)&gt;N($L299),"※已还本金大于典当金额",IF(AND($I299&lt;&gt;"",$J299&lt;&gt;"",$J299&lt;$I299),"※到期日早于当票日期",IF(AND($H299&lt;&gt;"",COUNTIF($H$4:$H$403,$H299)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L299&lt;&gt;"",$E299=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28439,7 +28502,7 @@
       <c r="V300" s="12" t="n"/>
       <c r="W300" s="12" t="n"/>
       <c r="X300" s="18">
-        <f>IF($E300="","",IF(AND($B300&lt;&gt;"",ISNA(MATCH($B300,机构表,0))),"※机构不在【资料】里",IF(AND($D300&lt;&gt;"",ISNA(MATCH($D300,状态表,0))),"※状态不在【资料】里",IF(N($M300)&gt;N($L300),"※已还本金大于典当金额",IF(AND($I300&lt;&gt;"",$J300&lt;&gt;"",$J300&lt;$I300),"※到期日早于当票日期",IF(AND($H300&lt;&gt;"",COUNTIF($H$4:$H$403,$H300)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L300&lt;&gt;"",$E300=""),"※有金额没写客户","")))))</f>
+        <f>IF($E300="","",IF(AND($B300&lt;&gt;"",ISNA(MATCH($B300,机构表,0))),"※机构不在【资料】里",IF(AND($D300&lt;&gt;"",ISNA(MATCH($D300,状态表,0))),"※状态不在【资料】里",IF(N($M300)&gt;N($L300),"※已还本金大于典当金额",IF(AND($I300&lt;&gt;"",$J300&lt;&gt;"",$J300&lt;$I300),"※到期日早于当票日期",IF(AND($H300&lt;&gt;"",COUNTIF($H$4:$H$403,$H300)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L300&lt;&gt;"",$E300=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28474,7 +28537,7 @@
       <c r="V301" s="12" t="n"/>
       <c r="W301" s="12" t="n"/>
       <c r="X301" s="18">
-        <f>IF($E301="","",IF(AND($B301&lt;&gt;"",ISNA(MATCH($B301,机构表,0))),"※机构不在【资料】里",IF(AND($D301&lt;&gt;"",ISNA(MATCH($D301,状态表,0))),"※状态不在【资料】里",IF(N($M301)&gt;N($L301),"※已还本金大于典当金额",IF(AND($I301&lt;&gt;"",$J301&lt;&gt;"",$J301&lt;$I301),"※到期日早于当票日期",IF(AND($H301&lt;&gt;"",COUNTIF($H$4:$H$403,$H301)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L301&lt;&gt;"",$E301=""),"※有金额没写客户","")))))</f>
+        <f>IF($E301="","",IF(AND($B301&lt;&gt;"",ISNA(MATCH($B301,机构表,0))),"※机构不在【资料】里",IF(AND($D301&lt;&gt;"",ISNA(MATCH($D301,状态表,0))),"※状态不在【资料】里",IF(N($M301)&gt;N($L301),"※已还本金大于典当金额",IF(AND($I301&lt;&gt;"",$J301&lt;&gt;"",$J301&lt;$I301),"※到期日早于当票日期",IF(AND($H301&lt;&gt;"",COUNTIF($H$4:$H$403,$H301)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L301&lt;&gt;"",$E301=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28509,7 +28572,7 @@
       <c r="V302" s="12" t="n"/>
       <c r="W302" s="12" t="n"/>
       <c r="X302" s="18">
-        <f>IF($E302="","",IF(AND($B302&lt;&gt;"",ISNA(MATCH($B302,机构表,0))),"※机构不在【资料】里",IF(AND($D302&lt;&gt;"",ISNA(MATCH($D302,状态表,0))),"※状态不在【资料】里",IF(N($M302)&gt;N($L302),"※已还本金大于典当金额",IF(AND($I302&lt;&gt;"",$J302&lt;&gt;"",$J302&lt;$I302),"※到期日早于当票日期",IF(AND($H302&lt;&gt;"",COUNTIF($H$4:$H$403,$H302)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L302&lt;&gt;"",$E302=""),"※有金额没写客户","")))))</f>
+        <f>IF($E302="","",IF(AND($B302&lt;&gt;"",ISNA(MATCH($B302,机构表,0))),"※机构不在【资料】里",IF(AND($D302&lt;&gt;"",ISNA(MATCH($D302,状态表,0))),"※状态不在【资料】里",IF(N($M302)&gt;N($L302),"※已还本金大于典当金额",IF(AND($I302&lt;&gt;"",$J302&lt;&gt;"",$J302&lt;$I302),"※到期日早于当票日期",IF(AND($H302&lt;&gt;"",COUNTIF($H$4:$H$403,$H302)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L302&lt;&gt;"",$E302=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28544,7 +28607,7 @@
       <c r="V303" s="12" t="n"/>
       <c r="W303" s="12" t="n"/>
       <c r="X303" s="18">
-        <f>IF($E303="","",IF(AND($B303&lt;&gt;"",ISNA(MATCH($B303,机构表,0))),"※机构不在【资料】里",IF(AND($D303&lt;&gt;"",ISNA(MATCH($D303,状态表,0))),"※状态不在【资料】里",IF(N($M303)&gt;N($L303),"※已还本金大于典当金额",IF(AND($I303&lt;&gt;"",$J303&lt;&gt;"",$J303&lt;$I303),"※到期日早于当票日期",IF(AND($H303&lt;&gt;"",COUNTIF($H$4:$H$403,$H303)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L303&lt;&gt;"",$E303=""),"※有金额没写客户","")))))</f>
+        <f>IF($E303="","",IF(AND($B303&lt;&gt;"",ISNA(MATCH($B303,机构表,0))),"※机构不在【资料】里",IF(AND($D303&lt;&gt;"",ISNA(MATCH($D303,状态表,0))),"※状态不在【资料】里",IF(N($M303)&gt;N($L303),"※已还本金大于典当金额",IF(AND($I303&lt;&gt;"",$J303&lt;&gt;"",$J303&lt;$I303),"※到期日早于当票日期",IF(AND($H303&lt;&gt;"",COUNTIF($H$4:$H$403,$H303)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L303&lt;&gt;"",$E303=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28579,7 +28642,7 @@
       <c r="V304" s="12" t="n"/>
       <c r="W304" s="12" t="n"/>
       <c r="X304" s="18">
-        <f>IF($E304="","",IF(AND($B304&lt;&gt;"",ISNA(MATCH($B304,机构表,0))),"※机构不在【资料】里",IF(AND($D304&lt;&gt;"",ISNA(MATCH($D304,状态表,0))),"※状态不在【资料】里",IF(N($M304)&gt;N($L304),"※已还本金大于典当金额",IF(AND($I304&lt;&gt;"",$J304&lt;&gt;"",$J304&lt;$I304),"※到期日早于当票日期",IF(AND($H304&lt;&gt;"",COUNTIF($H$4:$H$403,$H304)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L304&lt;&gt;"",$E304=""),"※有金额没写客户","")))))</f>
+        <f>IF($E304="","",IF(AND($B304&lt;&gt;"",ISNA(MATCH($B304,机构表,0))),"※机构不在【资料】里",IF(AND($D304&lt;&gt;"",ISNA(MATCH($D304,状态表,0))),"※状态不在【资料】里",IF(N($M304)&gt;N($L304),"※已还本金大于典当金额",IF(AND($I304&lt;&gt;"",$J304&lt;&gt;"",$J304&lt;$I304),"※到期日早于当票日期",IF(AND($H304&lt;&gt;"",COUNTIF($H$4:$H$403,$H304)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L304&lt;&gt;"",$E304=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28614,7 +28677,7 @@
       <c r="V305" s="12" t="n"/>
       <c r="W305" s="12" t="n"/>
       <c r="X305" s="18">
-        <f>IF($E305="","",IF(AND($B305&lt;&gt;"",ISNA(MATCH($B305,机构表,0))),"※机构不在【资料】里",IF(AND($D305&lt;&gt;"",ISNA(MATCH($D305,状态表,0))),"※状态不在【资料】里",IF(N($M305)&gt;N($L305),"※已还本金大于典当金额",IF(AND($I305&lt;&gt;"",$J305&lt;&gt;"",$J305&lt;$I305),"※到期日早于当票日期",IF(AND($H305&lt;&gt;"",COUNTIF($H$4:$H$403,$H305)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L305&lt;&gt;"",$E305=""),"※有金额没写客户","")))))</f>
+        <f>IF($E305="","",IF(AND($B305&lt;&gt;"",ISNA(MATCH($B305,机构表,0))),"※机构不在【资料】里",IF(AND($D305&lt;&gt;"",ISNA(MATCH($D305,状态表,0))),"※状态不在【资料】里",IF(N($M305)&gt;N($L305),"※已还本金大于典当金额",IF(AND($I305&lt;&gt;"",$J305&lt;&gt;"",$J305&lt;$I305),"※到期日早于当票日期",IF(AND($H305&lt;&gt;"",COUNTIF($H$4:$H$403,$H305)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L305&lt;&gt;"",$E305=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28649,7 +28712,7 @@
       <c r="V306" s="12" t="n"/>
       <c r="W306" s="12" t="n"/>
       <c r="X306" s="18">
-        <f>IF($E306="","",IF(AND($B306&lt;&gt;"",ISNA(MATCH($B306,机构表,0))),"※机构不在【资料】里",IF(AND($D306&lt;&gt;"",ISNA(MATCH($D306,状态表,0))),"※状态不在【资料】里",IF(N($M306)&gt;N($L306),"※已还本金大于典当金额",IF(AND($I306&lt;&gt;"",$J306&lt;&gt;"",$J306&lt;$I306),"※到期日早于当票日期",IF(AND($H306&lt;&gt;"",COUNTIF($H$4:$H$403,$H306)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L306&lt;&gt;"",$E306=""),"※有金额没写客户","")))))</f>
+        <f>IF($E306="","",IF(AND($B306&lt;&gt;"",ISNA(MATCH($B306,机构表,0))),"※机构不在【资料】里",IF(AND($D306&lt;&gt;"",ISNA(MATCH($D306,状态表,0))),"※状态不在【资料】里",IF(N($M306)&gt;N($L306),"※已还本金大于典当金额",IF(AND($I306&lt;&gt;"",$J306&lt;&gt;"",$J306&lt;$I306),"※到期日早于当票日期",IF(AND($H306&lt;&gt;"",COUNTIF($H$4:$H$403,$H306)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L306&lt;&gt;"",$E306=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28684,7 +28747,7 @@
       <c r="V307" s="12" t="n"/>
       <c r="W307" s="12" t="n"/>
       <c r="X307" s="18">
-        <f>IF($E307="","",IF(AND($B307&lt;&gt;"",ISNA(MATCH($B307,机构表,0))),"※机构不在【资料】里",IF(AND($D307&lt;&gt;"",ISNA(MATCH($D307,状态表,0))),"※状态不在【资料】里",IF(N($M307)&gt;N($L307),"※已还本金大于典当金额",IF(AND($I307&lt;&gt;"",$J307&lt;&gt;"",$J307&lt;$I307),"※到期日早于当票日期",IF(AND($H307&lt;&gt;"",COUNTIF($H$4:$H$403,$H307)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L307&lt;&gt;"",$E307=""),"※有金额没写客户","")))))</f>
+        <f>IF($E307="","",IF(AND($B307&lt;&gt;"",ISNA(MATCH($B307,机构表,0))),"※机构不在【资料】里",IF(AND($D307&lt;&gt;"",ISNA(MATCH($D307,状态表,0))),"※状态不在【资料】里",IF(N($M307)&gt;N($L307),"※已还本金大于典当金额",IF(AND($I307&lt;&gt;"",$J307&lt;&gt;"",$J307&lt;$I307),"※到期日早于当票日期",IF(AND($H307&lt;&gt;"",COUNTIF($H$4:$H$403,$H307)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L307&lt;&gt;"",$E307=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28719,7 +28782,7 @@
       <c r="V308" s="12" t="n"/>
       <c r="W308" s="12" t="n"/>
       <c r="X308" s="18">
-        <f>IF($E308="","",IF(AND($B308&lt;&gt;"",ISNA(MATCH($B308,机构表,0))),"※机构不在【资料】里",IF(AND($D308&lt;&gt;"",ISNA(MATCH($D308,状态表,0))),"※状态不在【资料】里",IF(N($M308)&gt;N($L308),"※已还本金大于典当金额",IF(AND($I308&lt;&gt;"",$J308&lt;&gt;"",$J308&lt;$I308),"※到期日早于当票日期",IF(AND($H308&lt;&gt;"",COUNTIF($H$4:$H$403,$H308)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L308&lt;&gt;"",$E308=""),"※有金额没写客户","")))))</f>
+        <f>IF($E308="","",IF(AND($B308&lt;&gt;"",ISNA(MATCH($B308,机构表,0))),"※机构不在【资料】里",IF(AND($D308&lt;&gt;"",ISNA(MATCH($D308,状态表,0))),"※状态不在【资料】里",IF(N($M308)&gt;N($L308),"※已还本金大于典当金额",IF(AND($I308&lt;&gt;"",$J308&lt;&gt;"",$J308&lt;$I308),"※到期日早于当票日期",IF(AND($H308&lt;&gt;"",COUNTIF($H$4:$H$403,$H308)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L308&lt;&gt;"",$E308=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28754,7 +28817,7 @@
       <c r="V309" s="12" t="n"/>
       <c r="W309" s="12" t="n"/>
       <c r="X309" s="18">
-        <f>IF($E309="","",IF(AND($B309&lt;&gt;"",ISNA(MATCH($B309,机构表,0))),"※机构不在【资料】里",IF(AND($D309&lt;&gt;"",ISNA(MATCH($D309,状态表,0))),"※状态不在【资料】里",IF(N($M309)&gt;N($L309),"※已还本金大于典当金额",IF(AND($I309&lt;&gt;"",$J309&lt;&gt;"",$J309&lt;$I309),"※到期日早于当票日期",IF(AND($H309&lt;&gt;"",COUNTIF($H$4:$H$403,$H309)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L309&lt;&gt;"",$E309=""),"※有金额没写客户","")))))</f>
+        <f>IF($E309="","",IF(AND($B309&lt;&gt;"",ISNA(MATCH($B309,机构表,0))),"※机构不在【资料】里",IF(AND($D309&lt;&gt;"",ISNA(MATCH($D309,状态表,0))),"※状态不在【资料】里",IF(N($M309)&gt;N($L309),"※已还本金大于典当金额",IF(AND($I309&lt;&gt;"",$J309&lt;&gt;"",$J309&lt;$I309),"※到期日早于当票日期",IF(AND($H309&lt;&gt;"",COUNTIF($H$4:$H$403,$H309)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L309&lt;&gt;"",$E309=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28789,7 +28852,7 @@
       <c r="V310" s="12" t="n"/>
       <c r="W310" s="12" t="n"/>
       <c r="X310" s="18">
-        <f>IF($E310="","",IF(AND($B310&lt;&gt;"",ISNA(MATCH($B310,机构表,0))),"※机构不在【资料】里",IF(AND($D310&lt;&gt;"",ISNA(MATCH($D310,状态表,0))),"※状态不在【资料】里",IF(N($M310)&gt;N($L310),"※已还本金大于典当金额",IF(AND($I310&lt;&gt;"",$J310&lt;&gt;"",$J310&lt;$I310),"※到期日早于当票日期",IF(AND($H310&lt;&gt;"",COUNTIF($H$4:$H$403,$H310)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L310&lt;&gt;"",$E310=""),"※有金额没写客户","")))))</f>
+        <f>IF($E310="","",IF(AND($B310&lt;&gt;"",ISNA(MATCH($B310,机构表,0))),"※机构不在【资料】里",IF(AND($D310&lt;&gt;"",ISNA(MATCH($D310,状态表,0))),"※状态不在【资料】里",IF(N($M310)&gt;N($L310),"※已还本金大于典当金额",IF(AND($I310&lt;&gt;"",$J310&lt;&gt;"",$J310&lt;$I310),"※到期日早于当票日期",IF(AND($H310&lt;&gt;"",COUNTIF($H$4:$H$403,$H310)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L310&lt;&gt;"",$E310=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28824,7 +28887,7 @@
       <c r="V311" s="12" t="n"/>
       <c r="W311" s="12" t="n"/>
       <c r="X311" s="18">
-        <f>IF($E311="","",IF(AND($B311&lt;&gt;"",ISNA(MATCH($B311,机构表,0))),"※机构不在【资料】里",IF(AND($D311&lt;&gt;"",ISNA(MATCH($D311,状态表,0))),"※状态不在【资料】里",IF(N($M311)&gt;N($L311),"※已还本金大于典当金额",IF(AND($I311&lt;&gt;"",$J311&lt;&gt;"",$J311&lt;$I311),"※到期日早于当票日期",IF(AND($H311&lt;&gt;"",COUNTIF($H$4:$H$403,$H311)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L311&lt;&gt;"",$E311=""),"※有金额没写客户","")))))</f>
+        <f>IF($E311="","",IF(AND($B311&lt;&gt;"",ISNA(MATCH($B311,机构表,0))),"※机构不在【资料】里",IF(AND($D311&lt;&gt;"",ISNA(MATCH($D311,状态表,0))),"※状态不在【资料】里",IF(N($M311)&gt;N($L311),"※已还本金大于典当金额",IF(AND($I311&lt;&gt;"",$J311&lt;&gt;"",$J311&lt;$I311),"※到期日早于当票日期",IF(AND($H311&lt;&gt;"",COUNTIF($H$4:$H$403,$H311)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L311&lt;&gt;"",$E311=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28859,7 +28922,7 @@
       <c r="V312" s="12" t="n"/>
       <c r="W312" s="12" t="n"/>
       <c r="X312" s="18">
-        <f>IF($E312="","",IF(AND($B312&lt;&gt;"",ISNA(MATCH($B312,机构表,0))),"※机构不在【资料】里",IF(AND($D312&lt;&gt;"",ISNA(MATCH($D312,状态表,0))),"※状态不在【资料】里",IF(N($M312)&gt;N($L312),"※已还本金大于典当金额",IF(AND($I312&lt;&gt;"",$J312&lt;&gt;"",$J312&lt;$I312),"※到期日早于当票日期",IF(AND($H312&lt;&gt;"",COUNTIF($H$4:$H$403,$H312)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L312&lt;&gt;"",$E312=""),"※有金额没写客户","")))))</f>
+        <f>IF($E312="","",IF(AND($B312&lt;&gt;"",ISNA(MATCH($B312,机构表,0))),"※机构不在【资料】里",IF(AND($D312&lt;&gt;"",ISNA(MATCH($D312,状态表,0))),"※状态不在【资料】里",IF(N($M312)&gt;N($L312),"※已还本金大于典当金额",IF(AND($I312&lt;&gt;"",$J312&lt;&gt;"",$J312&lt;$I312),"※到期日早于当票日期",IF(AND($H312&lt;&gt;"",COUNTIF($H$4:$H$403,$H312)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L312&lt;&gt;"",$E312=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28894,7 +28957,7 @@
       <c r="V313" s="12" t="n"/>
       <c r="W313" s="12" t="n"/>
       <c r="X313" s="18">
-        <f>IF($E313="","",IF(AND($B313&lt;&gt;"",ISNA(MATCH($B313,机构表,0))),"※机构不在【资料】里",IF(AND($D313&lt;&gt;"",ISNA(MATCH($D313,状态表,0))),"※状态不在【资料】里",IF(N($M313)&gt;N($L313),"※已还本金大于典当金额",IF(AND($I313&lt;&gt;"",$J313&lt;&gt;"",$J313&lt;$I313),"※到期日早于当票日期",IF(AND($H313&lt;&gt;"",COUNTIF($H$4:$H$403,$H313)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L313&lt;&gt;"",$E313=""),"※有金额没写客户","")))))</f>
+        <f>IF($E313="","",IF(AND($B313&lt;&gt;"",ISNA(MATCH($B313,机构表,0))),"※机构不在【资料】里",IF(AND($D313&lt;&gt;"",ISNA(MATCH($D313,状态表,0))),"※状态不在【资料】里",IF(N($M313)&gt;N($L313),"※已还本金大于典当金额",IF(AND($I313&lt;&gt;"",$J313&lt;&gt;"",$J313&lt;$I313),"※到期日早于当票日期",IF(AND($H313&lt;&gt;"",COUNTIF($H$4:$H$403,$H313)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L313&lt;&gt;"",$E313=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28929,7 +28992,7 @@
       <c r="V314" s="12" t="n"/>
       <c r="W314" s="12" t="n"/>
       <c r="X314" s="18">
-        <f>IF($E314="","",IF(AND($B314&lt;&gt;"",ISNA(MATCH($B314,机构表,0))),"※机构不在【资料】里",IF(AND($D314&lt;&gt;"",ISNA(MATCH($D314,状态表,0))),"※状态不在【资料】里",IF(N($M314)&gt;N($L314),"※已还本金大于典当金额",IF(AND($I314&lt;&gt;"",$J314&lt;&gt;"",$J314&lt;$I314),"※到期日早于当票日期",IF(AND($H314&lt;&gt;"",COUNTIF($H$4:$H$403,$H314)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L314&lt;&gt;"",$E314=""),"※有金额没写客户","")))))</f>
+        <f>IF($E314="","",IF(AND($B314&lt;&gt;"",ISNA(MATCH($B314,机构表,0))),"※机构不在【资料】里",IF(AND($D314&lt;&gt;"",ISNA(MATCH($D314,状态表,0))),"※状态不在【资料】里",IF(N($M314)&gt;N($L314),"※已还本金大于典当金额",IF(AND($I314&lt;&gt;"",$J314&lt;&gt;"",$J314&lt;$I314),"※到期日早于当票日期",IF(AND($H314&lt;&gt;"",COUNTIF($H$4:$H$403,$H314)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L314&lt;&gt;"",$E314=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28964,7 +29027,7 @@
       <c r="V315" s="12" t="n"/>
       <c r="W315" s="12" t="n"/>
       <c r="X315" s="18">
-        <f>IF($E315="","",IF(AND($B315&lt;&gt;"",ISNA(MATCH($B315,机构表,0))),"※机构不在【资料】里",IF(AND($D315&lt;&gt;"",ISNA(MATCH($D315,状态表,0))),"※状态不在【资料】里",IF(N($M315)&gt;N($L315),"※已还本金大于典当金额",IF(AND($I315&lt;&gt;"",$J315&lt;&gt;"",$J315&lt;$I315),"※到期日早于当票日期",IF(AND($H315&lt;&gt;"",COUNTIF($H$4:$H$403,$H315)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L315&lt;&gt;"",$E315=""),"※有金额没写客户","")))))</f>
+        <f>IF($E315="","",IF(AND($B315&lt;&gt;"",ISNA(MATCH($B315,机构表,0))),"※机构不在【资料】里",IF(AND($D315&lt;&gt;"",ISNA(MATCH($D315,状态表,0))),"※状态不在【资料】里",IF(N($M315)&gt;N($L315),"※已还本金大于典当金额",IF(AND($I315&lt;&gt;"",$J315&lt;&gt;"",$J315&lt;$I315),"※到期日早于当票日期",IF(AND($H315&lt;&gt;"",COUNTIF($H$4:$H$403,$H315)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L315&lt;&gt;"",$E315=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -28999,7 +29062,7 @@
       <c r="V316" s="12" t="n"/>
       <c r="W316" s="12" t="n"/>
       <c r="X316" s="18">
-        <f>IF($E316="","",IF(AND($B316&lt;&gt;"",ISNA(MATCH($B316,机构表,0))),"※机构不在【资料】里",IF(AND($D316&lt;&gt;"",ISNA(MATCH($D316,状态表,0))),"※状态不在【资料】里",IF(N($M316)&gt;N($L316),"※已还本金大于典当金额",IF(AND($I316&lt;&gt;"",$J316&lt;&gt;"",$J316&lt;$I316),"※到期日早于当票日期",IF(AND($H316&lt;&gt;"",COUNTIF($H$4:$H$403,$H316)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L316&lt;&gt;"",$E316=""),"※有金额没写客户","")))))</f>
+        <f>IF($E316="","",IF(AND($B316&lt;&gt;"",ISNA(MATCH($B316,机构表,0))),"※机构不在【资料】里",IF(AND($D316&lt;&gt;"",ISNA(MATCH($D316,状态表,0))),"※状态不在【资料】里",IF(N($M316)&gt;N($L316),"※已还本金大于典当金额",IF(AND($I316&lt;&gt;"",$J316&lt;&gt;"",$J316&lt;$I316),"※到期日早于当票日期",IF(AND($H316&lt;&gt;"",COUNTIF($H$4:$H$403,$H316)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L316&lt;&gt;"",$E316=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29034,7 +29097,7 @@
       <c r="V317" s="12" t="n"/>
       <c r="W317" s="12" t="n"/>
       <c r="X317" s="18">
-        <f>IF($E317="","",IF(AND($B317&lt;&gt;"",ISNA(MATCH($B317,机构表,0))),"※机构不在【资料】里",IF(AND($D317&lt;&gt;"",ISNA(MATCH($D317,状态表,0))),"※状态不在【资料】里",IF(N($M317)&gt;N($L317),"※已还本金大于典当金额",IF(AND($I317&lt;&gt;"",$J317&lt;&gt;"",$J317&lt;$I317),"※到期日早于当票日期",IF(AND($H317&lt;&gt;"",COUNTIF($H$4:$H$403,$H317)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L317&lt;&gt;"",$E317=""),"※有金额没写客户","")))))</f>
+        <f>IF($E317="","",IF(AND($B317&lt;&gt;"",ISNA(MATCH($B317,机构表,0))),"※机构不在【资料】里",IF(AND($D317&lt;&gt;"",ISNA(MATCH($D317,状态表,0))),"※状态不在【资料】里",IF(N($M317)&gt;N($L317),"※已还本金大于典当金额",IF(AND($I317&lt;&gt;"",$J317&lt;&gt;"",$J317&lt;$I317),"※到期日早于当票日期",IF(AND($H317&lt;&gt;"",COUNTIF($H$4:$H$403,$H317)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L317&lt;&gt;"",$E317=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29069,7 +29132,7 @@
       <c r="V318" s="12" t="n"/>
       <c r="W318" s="12" t="n"/>
       <c r="X318" s="18">
-        <f>IF($E318="","",IF(AND($B318&lt;&gt;"",ISNA(MATCH($B318,机构表,0))),"※机构不在【资料】里",IF(AND($D318&lt;&gt;"",ISNA(MATCH($D318,状态表,0))),"※状态不在【资料】里",IF(N($M318)&gt;N($L318),"※已还本金大于典当金额",IF(AND($I318&lt;&gt;"",$J318&lt;&gt;"",$J318&lt;$I318),"※到期日早于当票日期",IF(AND($H318&lt;&gt;"",COUNTIF($H$4:$H$403,$H318)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L318&lt;&gt;"",$E318=""),"※有金额没写客户","")))))</f>
+        <f>IF($E318="","",IF(AND($B318&lt;&gt;"",ISNA(MATCH($B318,机构表,0))),"※机构不在【资料】里",IF(AND($D318&lt;&gt;"",ISNA(MATCH($D318,状态表,0))),"※状态不在【资料】里",IF(N($M318)&gt;N($L318),"※已还本金大于典当金额",IF(AND($I318&lt;&gt;"",$J318&lt;&gt;"",$J318&lt;$I318),"※到期日早于当票日期",IF(AND($H318&lt;&gt;"",COUNTIF($H$4:$H$403,$H318)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L318&lt;&gt;"",$E318=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29104,7 +29167,7 @@
       <c r="V319" s="12" t="n"/>
       <c r="W319" s="12" t="n"/>
       <c r="X319" s="18">
-        <f>IF($E319="","",IF(AND($B319&lt;&gt;"",ISNA(MATCH($B319,机构表,0))),"※机构不在【资料】里",IF(AND($D319&lt;&gt;"",ISNA(MATCH($D319,状态表,0))),"※状态不在【资料】里",IF(N($M319)&gt;N($L319),"※已还本金大于典当金额",IF(AND($I319&lt;&gt;"",$J319&lt;&gt;"",$J319&lt;$I319),"※到期日早于当票日期",IF(AND($H319&lt;&gt;"",COUNTIF($H$4:$H$403,$H319)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L319&lt;&gt;"",$E319=""),"※有金额没写客户","")))))</f>
+        <f>IF($E319="","",IF(AND($B319&lt;&gt;"",ISNA(MATCH($B319,机构表,0))),"※机构不在【资料】里",IF(AND($D319&lt;&gt;"",ISNA(MATCH($D319,状态表,0))),"※状态不在【资料】里",IF(N($M319)&gt;N($L319),"※已还本金大于典当金额",IF(AND($I319&lt;&gt;"",$J319&lt;&gt;"",$J319&lt;$I319),"※到期日早于当票日期",IF(AND($H319&lt;&gt;"",COUNTIF($H$4:$H$403,$H319)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L319&lt;&gt;"",$E319=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29139,7 +29202,7 @@
       <c r="V320" s="12" t="n"/>
       <c r="W320" s="12" t="n"/>
       <c r="X320" s="18">
-        <f>IF($E320="","",IF(AND($B320&lt;&gt;"",ISNA(MATCH($B320,机构表,0))),"※机构不在【资料】里",IF(AND($D320&lt;&gt;"",ISNA(MATCH($D320,状态表,0))),"※状态不在【资料】里",IF(N($M320)&gt;N($L320),"※已还本金大于典当金额",IF(AND($I320&lt;&gt;"",$J320&lt;&gt;"",$J320&lt;$I320),"※到期日早于当票日期",IF(AND($H320&lt;&gt;"",COUNTIF($H$4:$H$403,$H320)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L320&lt;&gt;"",$E320=""),"※有金额没写客户","")))))</f>
+        <f>IF($E320="","",IF(AND($B320&lt;&gt;"",ISNA(MATCH($B320,机构表,0))),"※机构不在【资料】里",IF(AND($D320&lt;&gt;"",ISNA(MATCH($D320,状态表,0))),"※状态不在【资料】里",IF(N($M320)&gt;N($L320),"※已还本金大于典当金额",IF(AND($I320&lt;&gt;"",$J320&lt;&gt;"",$J320&lt;$I320),"※到期日早于当票日期",IF(AND($H320&lt;&gt;"",COUNTIF($H$4:$H$403,$H320)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L320&lt;&gt;"",$E320=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29174,7 +29237,7 @@
       <c r="V321" s="12" t="n"/>
       <c r="W321" s="12" t="n"/>
       <c r="X321" s="18">
-        <f>IF($E321="","",IF(AND($B321&lt;&gt;"",ISNA(MATCH($B321,机构表,0))),"※机构不在【资料】里",IF(AND($D321&lt;&gt;"",ISNA(MATCH($D321,状态表,0))),"※状态不在【资料】里",IF(N($M321)&gt;N($L321),"※已还本金大于典当金额",IF(AND($I321&lt;&gt;"",$J321&lt;&gt;"",$J321&lt;$I321),"※到期日早于当票日期",IF(AND($H321&lt;&gt;"",COUNTIF($H$4:$H$403,$H321)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L321&lt;&gt;"",$E321=""),"※有金额没写客户","")))))</f>
+        <f>IF($E321="","",IF(AND($B321&lt;&gt;"",ISNA(MATCH($B321,机构表,0))),"※机构不在【资料】里",IF(AND($D321&lt;&gt;"",ISNA(MATCH($D321,状态表,0))),"※状态不在【资料】里",IF(N($M321)&gt;N($L321),"※已还本金大于典当金额",IF(AND($I321&lt;&gt;"",$J321&lt;&gt;"",$J321&lt;$I321),"※到期日早于当票日期",IF(AND($H321&lt;&gt;"",COUNTIF($H$4:$H$403,$H321)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L321&lt;&gt;"",$E321=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29209,7 +29272,7 @@
       <c r="V322" s="12" t="n"/>
       <c r="W322" s="12" t="n"/>
       <c r="X322" s="18">
-        <f>IF($E322="","",IF(AND($B322&lt;&gt;"",ISNA(MATCH($B322,机构表,0))),"※机构不在【资料】里",IF(AND($D322&lt;&gt;"",ISNA(MATCH($D322,状态表,0))),"※状态不在【资料】里",IF(N($M322)&gt;N($L322),"※已还本金大于典当金额",IF(AND($I322&lt;&gt;"",$J322&lt;&gt;"",$J322&lt;$I322),"※到期日早于当票日期",IF(AND($H322&lt;&gt;"",COUNTIF($H$4:$H$403,$H322)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L322&lt;&gt;"",$E322=""),"※有金额没写客户","")))))</f>
+        <f>IF($E322="","",IF(AND($B322&lt;&gt;"",ISNA(MATCH($B322,机构表,0))),"※机构不在【资料】里",IF(AND($D322&lt;&gt;"",ISNA(MATCH($D322,状态表,0))),"※状态不在【资料】里",IF(N($M322)&gt;N($L322),"※已还本金大于典当金额",IF(AND($I322&lt;&gt;"",$J322&lt;&gt;"",$J322&lt;$I322),"※到期日早于当票日期",IF(AND($H322&lt;&gt;"",COUNTIF($H$4:$H$403,$H322)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L322&lt;&gt;"",$E322=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29244,7 +29307,7 @@
       <c r="V323" s="12" t="n"/>
       <c r="W323" s="12" t="n"/>
       <c r="X323" s="18">
-        <f>IF($E323="","",IF(AND($B323&lt;&gt;"",ISNA(MATCH($B323,机构表,0))),"※机构不在【资料】里",IF(AND($D323&lt;&gt;"",ISNA(MATCH($D323,状态表,0))),"※状态不在【资料】里",IF(N($M323)&gt;N($L323),"※已还本金大于典当金额",IF(AND($I323&lt;&gt;"",$J323&lt;&gt;"",$J323&lt;$I323),"※到期日早于当票日期",IF(AND($H323&lt;&gt;"",COUNTIF($H$4:$H$403,$H323)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L323&lt;&gt;"",$E323=""),"※有金额没写客户","")))))</f>
+        <f>IF($E323="","",IF(AND($B323&lt;&gt;"",ISNA(MATCH($B323,机构表,0))),"※机构不在【资料】里",IF(AND($D323&lt;&gt;"",ISNA(MATCH($D323,状态表,0))),"※状态不在【资料】里",IF(N($M323)&gt;N($L323),"※已还本金大于典当金额",IF(AND($I323&lt;&gt;"",$J323&lt;&gt;"",$J323&lt;$I323),"※到期日早于当票日期",IF(AND($H323&lt;&gt;"",COUNTIF($H$4:$H$403,$H323)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L323&lt;&gt;"",$E323=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29279,7 +29342,7 @@
       <c r="V324" s="12" t="n"/>
       <c r="W324" s="12" t="n"/>
       <c r="X324" s="18">
-        <f>IF($E324="","",IF(AND($B324&lt;&gt;"",ISNA(MATCH($B324,机构表,0))),"※机构不在【资料】里",IF(AND($D324&lt;&gt;"",ISNA(MATCH($D324,状态表,0))),"※状态不在【资料】里",IF(N($M324)&gt;N($L324),"※已还本金大于典当金额",IF(AND($I324&lt;&gt;"",$J324&lt;&gt;"",$J324&lt;$I324),"※到期日早于当票日期",IF(AND($H324&lt;&gt;"",COUNTIF($H$4:$H$403,$H324)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L324&lt;&gt;"",$E324=""),"※有金额没写客户","")))))</f>
+        <f>IF($E324="","",IF(AND($B324&lt;&gt;"",ISNA(MATCH($B324,机构表,0))),"※机构不在【资料】里",IF(AND($D324&lt;&gt;"",ISNA(MATCH($D324,状态表,0))),"※状态不在【资料】里",IF(N($M324)&gt;N($L324),"※已还本金大于典当金额",IF(AND($I324&lt;&gt;"",$J324&lt;&gt;"",$J324&lt;$I324),"※到期日早于当票日期",IF(AND($H324&lt;&gt;"",COUNTIF($H$4:$H$403,$H324)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L324&lt;&gt;"",$E324=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29314,7 +29377,7 @@
       <c r="V325" s="12" t="n"/>
       <c r="W325" s="12" t="n"/>
       <c r="X325" s="18">
-        <f>IF($E325="","",IF(AND($B325&lt;&gt;"",ISNA(MATCH($B325,机构表,0))),"※机构不在【资料】里",IF(AND($D325&lt;&gt;"",ISNA(MATCH($D325,状态表,0))),"※状态不在【资料】里",IF(N($M325)&gt;N($L325),"※已还本金大于典当金额",IF(AND($I325&lt;&gt;"",$J325&lt;&gt;"",$J325&lt;$I325),"※到期日早于当票日期",IF(AND($H325&lt;&gt;"",COUNTIF($H$4:$H$403,$H325)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L325&lt;&gt;"",$E325=""),"※有金额没写客户","")))))</f>
+        <f>IF($E325="","",IF(AND($B325&lt;&gt;"",ISNA(MATCH($B325,机构表,0))),"※机构不在【资料】里",IF(AND($D325&lt;&gt;"",ISNA(MATCH($D325,状态表,0))),"※状态不在【资料】里",IF(N($M325)&gt;N($L325),"※已还本金大于典当金额",IF(AND($I325&lt;&gt;"",$J325&lt;&gt;"",$J325&lt;$I325),"※到期日早于当票日期",IF(AND($H325&lt;&gt;"",COUNTIF($H$4:$H$403,$H325)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L325&lt;&gt;"",$E325=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29349,7 +29412,7 @@
       <c r="V326" s="12" t="n"/>
       <c r="W326" s="12" t="n"/>
       <c r="X326" s="18">
-        <f>IF($E326="","",IF(AND($B326&lt;&gt;"",ISNA(MATCH($B326,机构表,0))),"※机构不在【资料】里",IF(AND($D326&lt;&gt;"",ISNA(MATCH($D326,状态表,0))),"※状态不在【资料】里",IF(N($M326)&gt;N($L326),"※已还本金大于典当金额",IF(AND($I326&lt;&gt;"",$J326&lt;&gt;"",$J326&lt;$I326),"※到期日早于当票日期",IF(AND($H326&lt;&gt;"",COUNTIF($H$4:$H$403,$H326)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L326&lt;&gt;"",$E326=""),"※有金额没写客户","")))))</f>
+        <f>IF($E326="","",IF(AND($B326&lt;&gt;"",ISNA(MATCH($B326,机构表,0))),"※机构不在【资料】里",IF(AND($D326&lt;&gt;"",ISNA(MATCH($D326,状态表,0))),"※状态不在【资料】里",IF(N($M326)&gt;N($L326),"※已还本金大于典当金额",IF(AND($I326&lt;&gt;"",$J326&lt;&gt;"",$J326&lt;$I326),"※到期日早于当票日期",IF(AND($H326&lt;&gt;"",COUNTIF($H$4:$H$403,$H326)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L326&lt;&gt;"",$E326=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29384,7 +29447,7 @@
       <c r="V327" s="12" t="n"/>
       <c r="W327" s="12" t="n"/>
       <c r="X327" s="18">
-        <f>IF($E327="","",IF(AND($B327&lt;&gt;"",ISNA(MATCH($B327,机构表,0))),"※机构不在【资料】里",IF(AND($D327&lt;&gt;"",ISNA(MATCH($D327,状态表,0))),"※状态不在【资料】里",IF(N($M327)&gt;N($L327),"※已还本金大于典当金额",IF(AND($I327&lt;&gt;"",$J327&lt;&gt;"",$J327&lt;$I327),"※到期日早于当票日期",IF(AND($H327&lt;&gt;"",COUNTIF($H$4:$H$403,$H327)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L327&lt;&gt;"",$E327=""),"※有金额没写客户","")))))</f>
+        <f>IF($E327="","",IF(AND($B327&lt;&gt;"",ISNA(MATCH($B327,机构表,0))),"※机构不在【资料】里",IF(AND($D327&lt;&gt;"",ISNA(MATCH($D327,状态表,0))),"※状态不在【资料】里",IF(N($M327)&gt;N($L327),"※已还本金大于典当金额",IF(AND($I327&lt;&gt;"",$J327&lt;&gt;"",$J327&lt;$I327),"※到期日早于当票日期",IF(AND($H327&lt;&gt;"",COUNTIF($H$4:$H$403,$H327)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L327&lt;&gt;"",$E327=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29419,7 +29482,7 @@
       <c r="V328" s="12" t="n"/>
       <c r="W328" s="12" t="n"/>
       <c r="X328" s="18">
-        <f>IF($E328="","",IF(AND($B328&lt;&gt;"",ISNA(MATCH($B328,机构表,0))),"※机构不在【资料】里",IF(AND($D328&lt;&gt;"",ISNA(MATCH($D328,状态表,0))),"※状态不在【资料】里",IF(N($M328)&gt;N($L328),"※已还本金大于典当金额",IF(AND($I328&lt;&gt;"",$J328&lt;&gt;"",$J328&lt;$I328),"※到期日早于当票日期",IF(AND($H328&lt;&gt;"",COUNTIF($H$4:$H$403,$H328)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L328&lt;&gt;"",$E328=""),"※有金额没写客户","")))))</f>
+        <f>IF($E328="","",IF(AND($B328&lt;&gt;"",ISNA(MATCH($B328,机构表,0))),"※机构不在【资料】里",IF(AND($D328&lt;&gt;"",ISNA(MATCH($D328,状态表,0))),"※状态不在【资料】里",IF(N($M328)&gt;N($L328),"※已还本金大于典当金额",IF(AND($I328&lt;&gt;"",$J328&lt;&gt;"",$J328&lt;$I328),"※到期日早于当票日期",IF(AND($H328&lt;&gt;"",COUNTIF($H$4:$H$403,$H328)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L328&lt;&gt;"",$E328=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29454,7 +29517,7 @@
       <c r="V329" s="12" t="n"/>
       <c r="W329" s="12" t="n"/>
       <c r="X329" s="18">
-        <f>IF($E329="","",IF(AND($B329&lt;&gt;"",ISNA(MATCH($B329,机构表,0))),"※机构不在【资料】里",IF(AND($D329&lt;&gt;"",ISNA(MATCH($D329,状态表,0))),"※状态不在【资料】里",IF(N($M329)&gt;N($L329),"※已还本金大于典当金额",IF(AND($I329&lt;&gt;"",$J329&lt;&gt;"",$J329&lt;$I329),"※到期日早于当票日期",IF(AND($H329&lt;&gt;"",COUNTIF($H$4:$H$403,$H329)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L329&lt;&gt;"",$E329=""),"※有金额没写客户","")))))</f>
+        <f>IF($E329="","",IF(AND($B329&lt;&gt;"",ISNA(MATCH($B329,机构表,0))),"※机构不在【资料】里",IF(AND($D329&lt;&gt;"",ISNA(MATCH($D329,状态表,0))),"※状态不在【资料】里",IF(N($M329)&gt;N($L329),"※已还本金大于典当金额",IF(AND($I329&lt;&gt;"",$J329&lt;&gt;"",$J329&lt;$I329),"※到期日早于当票日期",IF(AND($H329&lt;&gt;"",COUNTIF($H$4:$H$403,$H329)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L329&lt;&gt;"",$E329=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29489,7 +29552,7 @@
       <c r="V330" s="12" t="n"/>
       <c r="W330" s="12" t="n"/>
       <c r="X330" s="18">
-        <f>IF($E330="","",IF(AND($B330&lt;&gt;"",ISNA(MATCH($B330,机构表,0))),"※机构不在【资料】里",IF(AND($D330&lt;&gt;"",ISNA(MATCH($D330,状态表,0))),"※状态不在【资料】里",IF(N($M330)&gt;N($L330),"※已还本金大于典当金额",IF(AND($I330&lt;&gt;"",$J330&lt;&gt;"",$J330&lt;$I330),"※到期日早于当票日期",IF(AND($H330&lt;&gt;"",COUNTIF($H$4:$H$403,$H330)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L330&lt;&gt;"",$E330=""),"※有金额没写客户","")))))</f>
+        <f>IF($E330="","",IF(AND($B330&lt;&gt;"",ISNA(MATCH($B330,机构表,0))),"※机构不在【资料】里",IF(AND($D330&lt;&gt;"",ISNA(MATCH($D330,状态表,0))),"※状态不在【资料】里",IF(N($M330)&gt;N($L330),"※已还本金大于典当金额",IF(AND($I330&lt;&gt;"",$J330&lt;&gt;"",$J330&lt;$I330),"※到期日早于当票日期",IF(AND($H330&lt;&gt;"",COUNTIF($H$4:$H$403,$H330)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L330&lt;&gt;"",$E330=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29524,7 +29587,7 @@
       <c r="V331" s="12" t="n"/>
       <c r="W331" s="12" t="n"/>
       <c r="X331" s="18">
-        <f>IF($E331="","",IF(AND($B331&lt;&gt;"",ISNA(MATCH($B331,机构表,0))),"※机构不在【资料】里",IF(AND($D331&lt;&gt;"",ISNA(MATCH($D331,状态表,0))),"※状态不在【资料】里",IF(N($M331)&gt;N($L331),"※已还本金大于典当金额",IF(AND($I331&lt;&gt;"",$J331&lt;&gt;"",$J331&lt;$I331),"※到期日早于当票日期",IF(AND($H331&lt;&gt;"",COUNTIF($H$4:$H$403,$H331)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L331&lt;&gt;"",$E331=""),"※有金额没写客户","")))))</f>
+        <f>IF($E331="","",IF(AND($B331&lt;&gt;"",ISNA(MATCH($B331,机构表,0))),"※机构不在【资料】里",IF(AND($D331&lt;&gt;"",ISNA(MATCH($D331,状态表,0))),"※状态不在【资料】里",IF(N($M331)&gt;N($L331),"※已还本金大于典当金额",IF(AND($I331&lt;&gt;"",$J331&lt;&gt;"",$J331&lt;$I331),"※到期日早于当票日期",IF(AND($H331&lt;&gt;"",COUNTIF($H$4:$H$403,$H331)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L331&lt;&gt;"",$E331=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29559,7 +29622,7 @@
       <c r="V332" s="12" t="n"/>
       <c r="W332" s="12" t="n"/>
       <c r="X332" s="18">
-        <f>IF($E332="","",IF(AND($B332&lt;&gt;"",ISNA(MATCH($B332,机构表,0))),"※机构不在【资料】里",IF(AND($D332&lt;&gt;"",ISNA(MATCH($D332,状态表,0))),"※状态不在【资料】里",IF(N($M332)&gt;N($L332),"※已还本金大于典当金额",IF(AND($I332&lt;&gt;"",$J332&lt;&gt;"",$J332&lt;$I332),"※到期日早于当票日期",IF(AND($H332&lt;&gt;"",COUNTIF($H$4:$H$403,$H332)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L332&lt;&gt;"",$E332=""),"※有金额没写客户","")))))</f>
+        <f>IF($E332="","",IF(AND($B332&lt;&gt;"",ISNA(MATCH($B332,机构表,0))),"※机构不在【资料】里",IF(AND($D332&lt;&gt;"",ISNA(MATCH($D332,状态表,0))),"※状态不在【资料】里",IF(N($M332)&gt;N($L332),"※已还本金大于典当金额",IF(AND($I332&lt;&gt;"",$J332&lt;&gt;"",$J332&lt;$I332),"※到期日早于当票日期",IF(AND($H332&lt;&gt;"",COUNTIF($H$4:$H$403,$H332)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L332&lt;&gt;"",$E332=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29594,7 +29657,7 @@
       <c r="V333" s="12" t="n"/>
       <c r="W333" s="12" t="n"/>
       <c r="X333" s="18">
-        <f>IF($E333="","",IF(AND($B333&lt;&gt;"",ISNA(MATCH($B333,机构表,0))),"※机构不在【资料】里",IF(AND($D333&lt;&gt;"",ISNA(MATCH($D333,状态表,0))),"※状态不在【资料】里",IF(N($M333)&gt;N($L333),"※已还本金大于典当金额",IF(AND($I333&lt;&gt;"",$J333&lt;&gt;"",$J333&lt;$I333),"※到期日早于当票日期",IF(AND($H333&lt;&gt;"",COUNTIF($H$4:$H$403,$H333)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L333&lt;&gt;"",$E333=""),"※有金额没写客户","")))))</f>
+        <f>IF($E333="","",IF(AND($B333&lt;&gt;"",ISNA(MATCH($B333,机构表,0))),"※机构不在【资料】里",IF(AND($D333&lt;&gt;"",ISNA(MATCH($D333,状态表,0))),"※状态不在【资料】里",IF(N($M333)&gt;N($L333),"※已还本金大于典当金额",IF(AND($I333&lt;&gt;"",$J333&lt;&gt;"",$J333&lt;$I333),"※到期日早于当票日期",IF(AND($H333&lt;&gt;"",COUNTIF($H$4:$H$403,$H333)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L333&lt;&gt;"",$E333=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29629,7 +29692,7 @@
       <c r="V334" s="12" t="n"/>
       <c r="W334" s="12" t="n"/>
       <c r="X334" s="18">
-        <f>IF($E334="","",IF(AND($B334&lt;&gt;"",ISNA(MATCH($B334,机构表,0))),"※机构不在【资料】里",IF(AND($D334&lt;&gt;"",ISNA(MATCH($D334,状态表,0))),"※状态不在【资料】里",IF(N($M334)&gt;N($L334),"※已还本金大于典当金额",IF(AND($I334&lt;&gt;"",$J334&lt;&gt;"",$J334&lt;$I334),"※到期日早于当票日期",IF(AND($H334&lt;&gt;"",COUNTIF($H$4:$H$403,$H334)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L334&lt;&gt;"",$E334=""),"※有金额没写客户","")))))</f>
+        <f>IF($E334="","",IF(AND($B334&lt;&gt;"",ISNA(MATCH($B334,机构表,0))),"※机构不在【资料】里",IF(AND($D334&lt;&gt;"",ISNA(MATCH($D334,状态表,0))),"※状态不在【资料】里",IF(N($M334)&gt;N($L334),"※已还本金大于典当金额",IF(AND($I334&lt;&gt;"",$J334&lt;&gt;"",$J334&lt;$I334),"※到期日早于当票日期",IF(AND($H334&lt;&gt;"",COUNTIF($H$4:$H$403,$H334)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L334&lt;&gt;"",$E334=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29664,7 +29727,7 @@
       <c r="V335" s="12" t="n"/>
       <c r="W335" s="12" t="n"/>
       <c r="X335" s="18">
-        <f>IF($E335="","",IF(AND($B335&lt;&gt;"",ISNA(MATCH($B335,机构表,0))),"※机构不在【资料】里",IF(AND($D335&lt;&gt;"",ISNA(MATCH($D335,状态表,0))),"※状态不在【资料】里",IF(N($M335)&gt;N($L335),"※已还本金大于典当金额",IF(AND($I335&lt;&gt;"",$J335&lt;&gt;"",$J335&lt;$I335),"※到期日早于当票日期",IF(AND($H335&lt;&gt;"",COUNTIF($H$4:$H$403,$H335)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L335&lt;&gt;"",$E335=""),"※有金额没写客户","")))))</f>
+        <f>IF($E335="","",IF(AND($B335&lt;&gt;"",ISNA(MATCH($B335,机构表,0))),"※机构不在【资料】里",IF(AND($D335&lt;&gt;"",ISNA(MATCH($D335,状态表,0))),"※状态不在【资料】里",IF(N($M335)&gt;N($L335),"※已还本金大于典当金额",IF(AND($I335&lt;&gt;"",$J335&lt;&gt;"",$J335&lt;$I335),"※到期日早于当票日期",IF(AND($H335&lt;&gt;"",COUNTIF($H$4:$H$403,$H335)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L335&lt;&gt;"",$E335=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29699,7 +29762,7 @@
       <c r="V336" s="12" t="n"/>
       <c r="W336" s="12" t="n"/>
       <c r="X336" s="18">
-        <f>IF($E336="","",IF(AND($B336&lt;&gt;"",ISNA(MATCH($B336,机构表,0))),"※机构不在【资料】里",IF(AND($D336&lt;&gt;"",ISNA(MATCH($D336,状态表,0))),"※状态不在【资料】里",IF(N($M336)&gt;N($L336),"※已还本金大于典当金额",IF(AND($I336&lt;&gt;"",$J336&lt;&gt;"",$J336&lt;$I336),"※到期日早于当票日期",IF(AND($H336&lt;&gt;"",COUNTIF($H$4:$H$403,$H336)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L336&lt;&gt;"",$E336=""),"※有金额没写客户","")))))</f>
+        <f>IF($E336="","",IF(AND($B336&lt;&gt;"",ISNA(MATCH($B336,机构表,0))),"※机构不在【资料】里",IF(AND($D336&lt;&gt;"",ISNA(MATCH($D336,状态表,0))),"※状态不在【资料】里",IF(N($M336)&gt;N($L336),"※已还本金大于典当金额",IF(AND($I336&lt;&gt;"",$J336&lt;&gt;"",$J336&lt;$I336),"※到期日早于当票日期",IF(AND($H336&lt;&gt;"",COUNTIF($H$4:$H$403,$H336)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L336&lt;&gt;"",$E336=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29734,7 +29797,7 @@
       <c r="V337" s="12" t="n"/>
       <c r="W337" s="12" t="n"/>
       <c r="X337" s="18">
-        <f>IF($E337="","",IF(AND($B337&lt;&gt;"",ISNA(MATCH($B337,机构表,0))),"※机构不在【资料】里",IF(AND($D337&lt;&gt;"",ISNA(MATCH($D337,状态表,0))),"※状态不在【资料】里",IF(N($M337)&gt;N($L337),"※已还本金大于典当金额",IF(AND($I337&lt;&gt;"",$J337&lt;&gt;"",$J337&lt;$I337),"※到期日早于当票日期",IF(AND($H337&lt;&gt;"",COUNTIF($H$4:$H$403,$H337)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L337&lt;&gt;"",$E337=""),"※有金额没写客户","")))))</f>
+        <f>IF($E337="","",IF(AND($B337&lt;&gt;"",ISNA(MATCH($B337,机构表,0))),"※机构不在【资料】里",IF(AND($D337&lt;&gt;"",ISNA(MATCH($D337,状态表,0))),"※状态不在【资料】里",IF(N($M337)&gt;N($L337),"※已还本金大于典当金额",IF(AND($I337&lt;&gt;"",$J337&lt;&gt;"",$J337&lt;$I337),"※到期日早于当票日期",IF(AND($H337&lt;&gt;"",COUNTIF($H$4:$H$403,$H337)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L337&lt;&gt;"",$E337=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29769,7 +29832,7 @@
       <c r="V338" s="12" t="n"/>
       <c r="W338" s="12" t="n"/>
       <c r="X338" s="18">
-        <f>IF($E338="","",IF(AND($B338&lt;&gt;"",ISNA(MATCH($B338,机构表,0))),"※机构不在【资料】里",IF(AND($D338&lt;&gt;"",ISNA(MATCH($D338,状态表,0))),"※状态不在【资料】里",IF(N($M338)&gt;N($L338),"※已还本金大于典当金额",IF(AND($I338&lt;&gt;"",$J338&lt;&gt;"",$J338&lt;$I338),"※到期日早于当票日期",IF(AND($H338&lt;&gt;"",COUNTIF($H$4:$H$403,$H338)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L338&lt;&gt;"",$E338=""),"※有金额没写客户","")))))</f>
+        <f>IF($E338="","",IF(AND($B338&lt;&gt;"",ISNA(MATCH($B338,机构表,0))),"※机构不在【资料】里",IF(AND($D338&lt;&gt;"",ISNA(MATCH($D338,状态表,0))),"※状态不在【资料】里",IF(N($M338)&gt;N($L338),"※已还本金大于典当金额",IF(AND($I338&lt;&gt;"",$J338&lt;&gt;"",$J338&lt;$I338),"※到期日早于当票日期",IF(AND($H338&lt;&gt;"",COUNTIF($H$4:$H$403,$H338)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L338&lt;&gt;"",$E338=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29804,7 +29867,7 @@
       <c r="V339" s="12" t="n"/>
       <c r="W339" s="12" t="n"/>
       <c r="X339" s="18">
-        <f>IF($E339="","",IF(AND($B339&lt;&gt;"",ISNA(MATCH($B339,机构表,0))),"※机构不在【资料】里",IF(AND($D339&lt;&gt;"",ISNA(MATCH($D339,状态表,0))),"※状态不在【资料】里",IF(N($M339)&gt;N($L339),"※已还本金大于典当金额",IF(AND($I339&lt;&gt;"",$J339&lt;&gt;"",$J339&lt;$I339),"※到期日早于当票日期",IF(AND($H339&lt;&gt;"",COUNTIF($H$4:$H$403,$H339)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L339&lt;&gt;"",$E339=""),"※有金额没写客户","")))))</f>
+        <f>IF($E339="","",IF(AND($B339&lt;&gt;"",ISNA(MATCH($B339,机构表,0))),"※机构不在【资料】里",IF(AND($D339&lt;&gt;"",ISNA(MATCH($D339,状态表,0))),"※状态不在【资料】里",IF(N($M339)&gt;N($L339),"※已还本金大于典当金额",IF(AND($I339&lt;&gt;"",$J339&lt;&gt;"",$J339&lt;$I339),"※到期日早于当票日期",IF(AND($H339&lt;&gt;"",COUNTIF($H$4:$H$403,$H339)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L339&lt;&gt;"",$E339=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29839,7 +29902,7 @@
       <c r="V340" s="12" t="n"/>
       <c r="W340" s="12" t="n"/>
       <c r="X340" s="18">
-        <f>IF($E340="","",IF(AND($B340&lt;&gt;"",ISNA(MATCH($B340,机构表,0))),"※机构不在【资料】里",IF(AND($D340&lt;&gt;"",ISNA(MATCH($D340,状态表,0))),"※状态不在【资料】里",IF(N($M340)&gt;N($L340),"※已还本金大于典当金额",IF(AND($I340&lt;&gt;"",$J340&lt;&gt;"",$J340&lt;$I340),"※到期日早于当票日期",IF(AND($H340&lt;&gt;"",COUNTIF($H$4:$H$403,$H340)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L340&lt;&gt;"",$E340=""),"※有金额没写客户","")))))</f>
+        <f>IF($E340="","",IF(AND($B340&lt;&gt;"",ISNA(MATCH($B340,机构表,0))),"※机构不在【资料】里",IF(AND($D340&lt;&gt;"",ISNA(MATCH($D340,状态表,0))),"※状态不在【资料】里",IF(N($M340)&gt;N($L340),"※已还本金大于典当金额",IF(AND($I340&lt;&gt;"",$J340&lt;&gt;"",$J340&lt;$I340),"※到期日早于当票日期",IF(AND($H340&lt;&gt;"",COUNTIF($H$4:$H$403,$H340)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L340&lt;&gt;"",$E340=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29874,7 +29937,7 @@
       <c r="V341" s="12" t="n"/>
       <c r="W341" s="12" t="n"/>
       <c r="X341" s="18">
-        <f>IF($E341="","",IF(AND($B341&lt;&gt;"",ISNA(MATCH($B341,机构表,0))),"※机构不在【资料】里",IF(AND($D341&lt;&gt;"",ISNA(MATCH($D341,状态表,0))),"※状态不在【资料】里",IF(N($M341)&gt;N($L341),"※已还本金大于典当金额",IF(AND($I341&lt;&gt;"",$J341&lt;&gt;"",$J341&lt;$I341),"※到期日早于当票日期",IF(AND($H341&lt;&gt;"",COUNTIF($H$4:$H$403,$H341)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L341&lt;&gt;"",$E341=""),"※有金额没写客户","")))))</f>
+        <f>IF($E341="","",IF(AND($B341&lt;&gt;"",ISNA(MATCH($B341,机构表,0))),"※机构不在【资料】里",IF(AND($D341&lt;&gt;"",ISNA(MATCH($D341,状态表,0))),"※状态不在【资料】里",IF(N($M341)&gt;N($L341),"※已还本金大于典当金额",IF(AND($I341&lt;&gt;"",$J341&lt;&gt;"",$J341&lt;$I341),"※到期日早于当票日期",IF(AND($H341&lt;&gt;"",COUNTIF($H$4:$H$403,$H341)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L341&lt;&gt;"",$E341=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29909,7 +29972,7 @@
       <c r="V342" s="12" t="n"/>
       <c r="W342" s="12" t="n"/>
       <c r="X342" s="18">
-        <f>IF($E342="","",IF(AND($B342&lt;&gt;"",ISNA(MATCH($B342,机构表,0))),"※机构不在【资料】里",IF(AND($D342&lt;&gt;"",ISNA(MATCH($D342,状态表,0))),"※状态不在【资料】里",IF(N($M342)&gt;N($L342),"※已还本金大于典当金额",IF(AND($I342&lt;&gt;"",$J342&lt;&gt;"",$J342&lt;$I342),"※到期日早于当票日期",IF(AND($H342&lt;&gt;"",COUNTIF($H$4:$H$403,$H342)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L342&lt;&gt;"",$E342=""),"※有金额没写客户","")))))</f>
+        <f>IF($E342="","",IF(AND($B342&lt;&gt;"",ISNA(MATCH($B342,机构表,0))),"※机构不在【资料】里",IF(AND($D342&lt;&gt;"",ISNA(MATCH($D342,状态表,0))),"※状态不在【资料】里",IF(N($M342)&gt;N($L342),"※已还本金大于典当金额",IF(AND($I342&lt;&gt;"",$J342&lt;&gt;"",$J342&lt;$I342),"※到期日早于当票日期",IF(AND($H342&lt;&gt;"",COUNTIF($H$4:$H$403,$H342)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L342&lt;&gt;"",$E342=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29944,7 +30007,7 @@
       <c r="V343" s="12" t="n"/>
       <c r="W343" s="12" t="n"/>
       <c r="X343" s="18">
-        <f>IF($E343="","",IF(AND($B343&lt;&gt;"",ISNA(MATCH($B343,机构表,0))),"※机构不在【资料】里",IF(AND($D343&lt;&gt;"",ISNA(MATCH($D343,状态表,0))),"※状态不在【资料】里",IF(N($M343)&gt;N($L343),"※已还本金大于典当金额",IF(AND($I343&lt;&gt;"",$J343&lt;&gt;"",$J343&lt;$I343),"※到期日早于当票日期",IF(AND($H343&lt;&gt;"",COUNTIF($H$4:$H$403,$H343)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L343&lt;&gt;"",$E343=""),"※有金额没写客户","")))))</f>
+        <f>IF($E343="","",IF(AND($B343&lt;&gt;"",ISNA(MATCH($B343,机构表,0))),"※机构不在【资料】里",IF(AND($D343&lt;&gt;"",ISNA(MATCH($D343,状态表,0))),"※状态不在【资料】里",IF(N($M343)&gt;N($L343),"※已还本金大于典当金额",IF(AND($I343&lt;&gt;"",$J343&lt;&gt;"",$J343&lt;$I343),"※到期日早于当票日期",IF(AND($H343&lt;&gt;"",COUNTIF($H$4:$H$403,$H343)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L343&lt;&gt;"",$E343=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -29979,7 +30042,7 @@
       <c r="V344" s="12" t="n"/>
       <c r="W344" s="12" t="n"/>
       <c r="X344" s="18">
-        <f>IF($E344="","",IF(AND($B344&lt;&gt;"",ISNA(MATCH($B344,机构表,0))),"※机构不在【资料】里",IF(AND($D344&lt;&gt;"",ISNA(MATCH($D344,状态表,0))),"※状态不在【资料】里",IF(N($M344)&gt;N($L344),"※已还本金大于典当金额",IF(AND($I344&lt;&gt;"",$J344&lt;&gt;"",$J344&lt;$I344),"※到期日早于当票日期",IF(AND($H344&lt;&gt;"",COUNTIF($H$4:$H$403,$H344)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L344&lt;&gt;"",$E344=""),"※有金额没写客户","")))))</f>
+        <f>IF($E344="","",IF(AND($B344&lt;&gt;"",ISNA(MATCH($B344,机构表,0))),"※机构不在【资料】里",IF(AND($D344&lt;&gt;"",ISNA(MATCH($D344,状态表,0))),"※状态不在【资料】里",IF(N($M344)&gt;N($L344),"※已还本金大于典当金额",IF(AND($I344&lt;&gt;"",$J344&lt;&gt;"",$J344&lt;$I344),"※到期日早于当票日期",IF(AND($H344&lt;&gt;"",COUNTIF($H$4:$H$403,$H344)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L344&lt;&gt;"",$E344=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30014,7 +30077,7 @@
       <c r="V345" s="12" t="n"/>
       <c r="W345" s="12" t="n"/>
       <c r="X345" s="18">
-        <f>IF($E345="","",IF(AND($B345&lt;&gt;"",ISNA(MATCH($B345,机构表,0))),"※机构不在【资料】里",IF(AND($D345&lt;&gt;"",ISNA(MATCH($D345,状态表,0))),"※状态不在【资料】里",IF(N($M345)&gt;N($L345),"※已还本金大于典当金额",IF(AND($I345&lt;&gt;"",$J345&lt;&gt;"",$J345&lt;$I345),"※到期日早于当票日期",IF(AND($H345&lt;&gt;"",COUNTIF($H$4:$H$403,$H345)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L345&lt;&gt;"",$E345=""),"※有金额没写客户","")))))</f>
+        <f>IF($E345="","",IF(AND($B345&lt;&gt;"",ISNA(MATCH($B345,机构表,0))),"※机构不在【资料】里",IF(AND($D345&lt;&gt;"",ISNA(MATCH($D345,状态表,0))),"※状态不在【资料】里",IF(N($M345)&gt;N($L345),"※已还本金大于典当金额",IF(AND($I345&lt;&gt;"",$J345&lt;&gt;"",$J345&lt;$I345),"※到期日早于当票日期",IF(AND($H345&lt;&gt;"",COUNTIF($H$4:$H$403,$H345)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L345&lt;&gt;"",$E345=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30049,7 +30112,7 @@
       <c r="V346" s="12" t="n"/>
       <c r="W346" s="12" t="n"/>
       <c r="X346" s="18">
-        <f>IF($E346="","",IF(AND($B346&lt;&gt;"",ISNA(MATCH($B346,机构表,0))),"※机构不在【资料】里",IF(AND($D346&lt;&gt;"",ISNA(MATCH($D346,状态表,0))),"※状态不在【资料】里",IF(N($M346)&gt;N($L346),"※已还本金大于典当金额",IF(AND($I346&lt;&gt;"",$J346&lt;&gt;"",$J346&lt;$I346),"※到期日早于当票日期",IF(AND($H346&lt;&gt;"",COUNTIF($H$4:$H$403,$H346)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L346&lt;&gt;"",$E346=""),"※有金额没写客户","")))))</f>
+        <f>IF($E346="","",IF(AND($B346&lt;&gt;"",ISNA(MATCH($B346,机构表,0))),"※机构不在【资料】里",IF(AND($D346&lt;&gt;"",ISNA(MATCH($D346,状态表,0))),"※状态不在【资料】里",IF(N($M346)&gt;N($L346),"※已还本金大于典当金额",IF(AND($I346&lt;&gt;"",$J346&lt;&gt;"",$J346&lt;$I346),"※到期日早于当票日期",IF(AND($H346&lt;&gt;"",COUNTIF($H$4:$H$403,$H346)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L346&lt;&gt;"",$E346=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30084,7 +30147,7 @@
       <c r="V347" s="12" t="n"/>
       <c r="W347" s="12" t="n"/>
       <c r="X347" s="18">
-        <f>IF($E347="","",IF(AND($B347&lt;&gt;"",ISNA(MATCH($B347,机构表,0))),"※机构不在【资料】里",IF(AND($D347&lt;&gt;"",ISNA(MATCH($D347,状态表,0))),"※状态不在【资料】里",IF(N($M347)&gt;N($L347),"※已还本金大于典当金额",IF(AND($I347&lt;&gt;"",$J347&lt;&gt;"",$J347&lt;$I347),"※到期日早于当票日期",IF(AND($H347&lt;&gt;"",COUNTIF($H$4:$H$403,$H347)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L347&lt;&gt;"",$E347=""),"※有金额没写客户","")))))</f>
+        <f>IF($E347="","",IF(AND($B347&lt;&gt;"",ISNA(MATCH($B347,机构表,0))),"※机构不在【资料】里",IF(AND($D347&lt;&gt;"",ISNA(MATCH($D347,状态表,0))),"※状态不在【资料】里",IF(N($M347)&gt;N($L347),"※已还本金大于典当金额",IF(AND($I347&lt;&gt;"",$J347&lt;&gt;"",$J347&lt;$I347),"※到期日早于当票日期",IF(AND($H347&lt;&gt;"",COUNTIF($H$4:$H$403,$H347)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L347&lt;&gt;"",$E347=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30119,7 +30182,7 @@
       <c r="V348" s="12" t="n"/>
       <c r="W348" s="12" t="n"/>
       <c r="X348" s="18">
-        <f>IF($E348="","",IF(AND($B348&lt;&gt;"",ISNA(MATCH($B348,机构表,0))),"※机构不在【资料】里",IF(AND($D348&lt;&gt;"",ISNA(MATCH($D348,状态表,0))),"※状态不在【资料】里",IF(N($M348)&gt;N($L348),"※已还本金大于典当金额",IF(AND($I348&lt;&gt;"",$J348&lt;&gt;"",$J348&lt;$I348),"※到期日早于当票日期",IF(AND($H348&lt;&gt;"",COUNTIF($H$4:$H$403,$H348)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L348&lt;&gt;"",$E348=""),"※有金额没写客户","")))))</f>
+        <f>IF($E348="","",IF(AND($B348&lt;&gt;"",ISNA(MATCH($B348,机构表,0))),"※机构不在【资料】里",IF(AND($D348&lt;&gt;"",ISNA(MATCH($D348,状态表,0))),"※状态不在【资料】里",IF(N($M348)&gt;N($L348),"※已还本金大于典当金额",IF(AND($I348&lt;&gt;"",$J348&lt;&gt;"",$J348&lt;$I348),"※到期日早于当票日期",IF(AND($H348&lt;&gt;"",COUNTIF($H$4:$H$403,$H348)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L348&lt;&gt;"",$E348=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30154,7 +30217,7 @@
       <c r="V349" s="12" t="n"/>
       <c r="W349" s="12" t="n"/>
       <c r="X349" s="18">
-        <f>IF($E349="","",IF(AND($B349&lt;&gt;"",ISNA(MATCH($B349,机构表,0))),"※机构不在【资料】里",IF(AND($D349&lt;&gt;"",ISNA(MATCH($D349,状态表,0))),"※状态不在【资料】里",IF(N($M349)&gt;N($L349),"※已还本金大于典当金额",IF(AND($I349&lt;&gt;"",$J349&lt;&gt;"",$J349&lt;$I349),"※到期日早于当票日期",IF(AND($H349&lt;&gt;"",COUNTIF($H$4:$H$403,$H349)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L349&lt;&gt;"",$E349=""),"※有金额没写客户","")))))</f>
+        <f>IF($E349="","",IF(AND($B349&lt;&gt;"",ISNA(MATCH($B349,机构表,0))),"※机构不在【资料】里",IF(AND($D349&lt;&gt;"",ISNA(MATCH($D349,状态表,0))),"※状态不在【资料】里",IF(N($M349)&gt;N($L349),"※已还本金大于典当金额",IF(AND($I349&lt;&gt;"",$J349&lt;&gt;"",$J349&lt;$I349),"※到期日早于当票日期",IF(AND($H349&lt;&gt;"",COUNTIF($H$4:$H$403,$H349)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L349&lt;&gt;"",$E349=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30189,7 +30252,7 @@
       <c r="V350" s="12" t="n"/>
       <c r="W350" s="12" t="n"/>
       <c r="X350" s="18">
-        <f>IF($E350="","",IF(AND($B350&lt;&gt;"",ISNA(MATCH($B350,机构表,0))),"※机构不在【资料】里",IF(AND($D350&lt;&gt;"",ISNA(MATCH($D350,状态表,0))),"※状态不在【资料】里",IF(N($M350)&gt;N($L350),"※已还本金大于典当金额",IF(AND($I350&lt;&gt;"",$J350&lt;&gt;"",$J350&lt;$I350),"※到期日早于当票日期",IF(AND($H350&lt;&gt;"",COUNTIF($H$4:$H$403,$H350)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L350&lt;&gt;"",$E350=""),"※有金额没写客户","")))))</f>
+        <f>IF($E350="","",IF(AND($B350&lt;&gt;"",ISNA(MATCH($B350,机构表,0))),"※机构不在【资料】里",IF(AND($D350&lt;&gt;"",ISNA(MATCH($D350,状态表,0))),"※状态不在【资料】里",IF(N($M350)&gt;N($L350),"※已还本金大于典当金额",IF(AND($I350&lt;&gt;"",$J350&lt;&gt;"",$J350&lt;$I350),"※到期日早于当票日期",IF(AND($H350&lt;&gt;"",COUNTIF($H$4:$H$403,$H350)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L350&lt;&gt;"",$E350=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30224,7 +30287,7 @@
       <c r="V351" s="12" t="n"/>
       <c r="W351" s="12" t="n"/>
       <c r="X351" s="18">
-        <f>IF($E351="","",IF(AND($B351&lt;&gt;"",ISNA(MATCH($B351,机构表,0))),"※机构不在【资料】里",IF(AND($D351&lt;&gt;"",ISNA(MATCH($D351,状态表,0))),"※状态不在【资料】里",IF(N($M351)&gt;N($L351),"※已还本金大于典当金额",IF(AND($I351&lt;&gt;"",$J351&lt;&gt;"",$J351&lt;$I351),"※到期日早于当票日期",IF(AND($H351&lt;&gt;"",COUNTIF($H$4:$H$403,$H351)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L351&lt;&gt;"",$E351=""),"※有金额没写客户","")))))</f>
+        <f>IF($E351="","",IF(AND($B351&lt;&gt;"",ISNA(MATCH($B351,机构表,0))),"※机构不在【资料】里",IF(AND($D351&lt;&gt;"",ISNA(MATCH($D351,状态表,0))),"※状态不在【资料】里",IF(N($M351)&gt;N($L351),"※已还本金大于典当金额",IF(AND($I351&lt;&gt;"",$J351&lt;&gt;"",$J351&lt;$I351),"※到期日早于当票日期",IF(AND($H351&lt;&gt;"",COUNTIF($H$4:$H$403,$H351)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L351&lt;&gt;"",$E351=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30259,7 +30322,7 @@
       <c r="V352" s="12" t="n"/>
       <c r="W352" s="12" t="n"/>
       <c r="X352" s="18">
-        <f>IF($E352="","",IF(AND($B352&lt;&gt;"",ISNA(MATCH($B352,机构表,0))),"※机构不在【资料】里",IF(AND($D352&lt;&gt;"",ISNA(MATCH($D352,状态表,0))),"※状态不在【资料】里",IF(N($M352)&gt;N($L352),"※已还本金大于典当金额",IF(AND($I352&lt;&gt;"",$J352&lt;&gt;"",$J352&lt;$I352),"※到期日早于当票日期",IF(AND($H352&lt;&gt;"",COUNTIF($H$4:$H$403,$H352)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L352&lt;&gt;"",$E352=""),"※有金额没写客户","")))))</f>
+        <f>IF($E352="","",IF(AND($B352&lt;&gt;"",ISNA(MATCH($B352,机构表,0))),"※机构不在【资料】里",IF(AND($D352&lt;&gt;"",ISNA(MATCH($D352,状态表,0))),"※状态不在【资料】里",IF(N($M352)&gt;N($L352),"※已还本金大于典当金额",IF(AND($I352&lt;&gt;"",$J352&lt;&gt;"",$J352&lt;$I352),"※到期日早于当票日期",IF(AND($H352&lt;&gt;"",COUNTIF($H$4:$H$403,$H352)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L352&lt;&gt;"",$E352=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30294,7 +30357,7 @@
       <c r="V353" s="12" t="n"/>
       <c r="W353" s="12" t="n"/>
       <c r="X353" s="18">
-        <f>IF($E353="","",IF(AND($B353&lt;&gt;"",ISNA(MATCH($B353,机构表,0))),"※机构不在【资料】里",IF(AND($D353&lt;&gt;"",ISNA(MATCH($D353,状态表,0))),"※状态不在【资料】里",IF(N($M353)&gt;N($L353),"※已还本金大于典当金额",IF(AND($I353&lt;&gt;"",$J353&lt;&gt;"",$J353&lt;$I353),"※到期日早于当票日期",IF(AND($H353&lt;&gt;"",COUNTIF($H$4:$H$403,$H353)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L353&lt;&gt;"",$E353=""),"※有金额没写客户","")))))</f>
+        <f>IF($E353="","",IF(AND($B353&lt;&gt;"",ISNA(MATCH($B353,机构表,0))),"※机构不在【资料】里",IF(AND($D353&lt;&gt;"",ISNA(MATCH($D353,状态表,0))),"※状态不在【资料】里",IF(N($M353)&gt;N($L353),"※已还本金大于典当金额",IF(AND($I353&lt;&gt;"",$J353&lt;&gt;"",$J353&lt;$I353),"※到期日早于当票日期",IF(AND($H353&lt;&gt;"",COUNTIF($H$4:$H$403,$H353)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L353&lt;&gt;"",$E353=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30329,7 +30392,7 @@
       <c r="V354" s="12" t="n"/>
       <c r="W354" s="12" t="n"/>
       <c r="X354" s="18">
-        <f>IF($E354="","",IF(AND($B354&lt;&gt;"",ISNA(MATCH($B354,机构表,0))),"※机构不在【资料】里",IF(AND($D354&lt;&gt;"",ISNA(MATCH($D354,状态表,0))),"※状态不在【资料】里",IF(N($M354)&gt;N($L354),"※已还本金大于典当金额",IF(AND($I354&lt;&gt;"",$J354&lt;&gt;"",$J354&lt;$I354),"※到期日早于当票日期",IF(AND($H354&lt;&gt;"",COUNTIF($H$4:$H$403,$H354)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L354&lt;&gt;"",$E354=""),"※有金额没写客户","")))))</f>
+        <f>IF($E354="","",IF(AND($B354&lt;&gt;"",ISNA(MATCH($B354,机构表,0))),"※机构不在【资料】里",IF(AND($D354&lt;&gt;"",ISNA(MATCH($D354,状态表,0))),"※状态不在【资料】里",IF(N($M354)&gt;N($L354),"※已还本金大于典当金额",IF(AND($I354&lt;&gt;"",$J354&lt;&gt;"",$J354&lt;$I354),"※到期日早于当票日期",IF(AND($H354&lt;&gt;"",COUNTIF($H$4:$H$403,$H354)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L354&lt;&gt;"",$E354=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30364,7 +30427,7 @@
       <c r="V355" s="12" t="n"/>
       <c r="W355" s="12" t="n"/>
       <c r="X355" s="18">
-        <f>IF($E355="","",IF(AND($B355&lt;&gt;"",ISNA(MATCH($B355,机构表,0))),"※机构不在【资料】里",IF(AND($D355&lt;&gt;"",ISNA(MATCH($D355,状态表,0))),"※状态不在【资料】里",IF(N($M355)&gt;N($L355),"※已还本金大于典当金额",IF(AND($I355&lt;&gt;"",$J355&lt;&gt;"",$J355&lt;$I355),"※到期日早于当票日期",IF(AND($H355&lt;&gt;"",COUNTIF($H$4:$H$403,$H355)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L355&lt;&gt;"",$E355=""),"※有金额没写客户","")))))</f>
+        <f>IF($E355="","",IF(AND($B355&lt;&gt;"",ISNA(MATCH($B355,机构表,0))),"※机构不在【资料】里",IF(AND($D355&lt;&gt;"",ISNA(MATCH($D355,状态表,0))),"※状态不在【资料】里",IF(N($M355)&gt;N($L355),"※已还本金大于典当金额",IF(AND($I355&lt;&gt;"",$J355&lt;&gt;"",$J355&lt;$I355),"※到期日早于当票日期",IF(AND($H355&lt;&gt;"",COUNTIF($H$4:$H$403,$H355)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L355&lt;&gt;"",$E355=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30399,7 +30462,7 @@
       <c r="V356" s="12" t="n"/>
       <c r="W356" s="12" t="n"/>
       <c r="X356" s="18">
-        <f>IF($E356="","",IF(AND($B356&lt;&gt;"",ISNA(MATCH($B356,机构表,0))),"※机构不在【资料】里",IF(AND($D356&lt;&gt;"",ISNA(MATCH($D356,状态表,0))),"※状态不在【资料】里",IF(N($M356)&gt;N($L356),"※已还本金大于典当金额",IF(AND($I356&lt;&gt;"",$J356&lt;&gt;"",$J356&lt;$I356),"※到期日早于当票日期",IF(AND($H356&lt;&gt;"",COUNTIF($H$4:$H$403,$H356)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L356&lt;&gt;"",$E356=""),"※有金额没写客户","")))))</f>
+        <f>IF($E356="","",IF(AND($B356&lt;&gt;"",ISNA(MATCH($B356,机构表,0))),"※机构不在【资料】里",IF(AND($D356&lt;&gt;"",ISNA(MATCH($D356,状态表,0))),"※状态不在【资料】里",IF(N($M356)&gt;N($L356),"※已还本金大于典当金额",IF(AND($I356&lt;&gt;"",$J356&lt;&gt;"",$J356&lt;$I356),"※到期日早于当票日期",IF(AND($H356&lt;&gt;"",COUNTIF($H$4:$H$403,$H356)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L356&lt;&gt;"",$E356=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30434,7 +30497,7 @@
       <c r="V357" s="12" t="n"/>
       <c r="W357" s="12" t="n"/>
       <c r="X357" s="18">
-        <f>IF($E357="","",IF(AND($B357&lt;&gt;"",ISNA(MATCH($B357,机构表,0))),"※机构不在【资料】里",IF(AND($D357&lt;&gt;"",ISNA(MATCH($D357,状态表,0))),"※状态不在【资料】里",IF(N($M357)&gt;N($L357),"※已还本金大于典当金额",IF(AND($I357&lt;&gt;"",$J357&lt;&gt;"",$J357&lt;$I357),"※到期日早于当票日期",IF(AND($H357&lt;&gt;"",COUNTIF($H$4:$H$403,$H357)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L357&lt;&gt;"",$E357=""),"※有金额没写客户","")))))</f>
+        <f>IF($E357="","",IF(AND($B357&lt;&gt;"",ISNA(MATCH($B357,机构表,0))),"※机构不在【资料】里",IF(AND($D357&lt;&gt;"",ISNA(MATCH($D357,状态表,0))),"※状态不在【资料】里",IF(N($M357)&gt;N($L357),"※已还本金大于典当金额",IF(AND($I357&lt;&gt;"",$J357&lt;&gt;"",$J357&lt;$I357),"※到期日早于当票日期",IF(AND($H357&lt;&gt;"",COUNTIF($H$4:$H$403,$H357)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L357&lt;&gt;"",$E357=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30469,7 +30532,7 @@
       <c r="V358" s="12" t="n"/>
       <c r="W358" s="12" t="n"/>
       <c r="X358" s="18">
-        <f>IF($E358="","",IF(AND($B358&lt;&gt;"",ISNA(MATCH($B358,机构表,0))),"※机构不在【资料】里",IF(AND($D358&lt;&gt;"",ISNA(MATCH($D358,状态表,0))),"※状态不在【资料】里",IF(N($M358)&gt;N($L358),"※已还本金大于典当金额",IF(AND($I358&lt;&gt;"",$J358&lt;&gt;"",$J358&lt;$I358),"※到期日早于当票日期",IF(AND($H358&lt;&gt;"",COUNTIF($H$4:$H$403,$H358)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L358&lt;&gt;"",$E358=""),"※有金额没写客户","")))))</f>
+        <f>IF($E358="","",IF(AND($B358&lt;&gt;"",ISNA(MATCH($B358,机构表,0))),"※机构不在【资料】里",IF(AND($D358&lt;&gt;"",ISNA(MATCH($D358,状态表,0))),"※状态不在【资料】里",IF(N($M358)&gt;N($L358),"※已还本金大于典当金额",IF(AND($I358&lt;&gt;"",$J358&lt;&gt;"",$J358&lt;$I358),"※到期日早于当票日期",IF(AND($H358&lt;&gt;"",COUNTIF($H$4:$H$403,$H358)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L358&lt;&gt;"",$E358=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30504,7 +30567,7 @@
       <c r="V359" s="12" t="n"/>
       <c r="W359" s="12" t="n"/>
       <c r="X359" s="18">
-        <f>IF($E359="","",IF(AND($B359&lt;&gt;"",ISNA(MATCH($B359,机构表,0))),"※机构不在【资料】里",IF(AND($D359&lt;&gt;"",ISNA(MATCH($D359,状态表,0))),"※状态不在【资料】里",IF(N($M359)&gt;N($L359),"※已还本金大于典当金额",IF(AND($I359&lt;&gt;"",$J359&lt;&gt;"",$J359&lt;$I359),"※到期日早于当票日期",IF(AND($H359&lt;&gt;"",COUNTIF($H$4:$H$403,$H359)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L359&lt;&gt;"",$E359=""),"※有金额没写客户","")))))</f>
+        <f>IF($E359="","",IF(AND($B359&lt;&gt;"",ISNA(MATCH($B359,机构表,0))),"※机构不在【资料】里",IF(AND($D359&lt;&gt;"",ISNA(MATCH($D359,状态表,0))),"※状态不在【资料】里",IF(N($M359)&gt;N($L359),"※已还本金大于典当金额",IF(AND($I359&lt;&gt;"",$J359&lt;&gt;"",$J359&lt;$I359),"※到期日早于当票日期",IF(AND($H359&lt;&gt;"",COUNTIF($H$4:$H$403,$H359)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L359&lt;&gt;"",$E359=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30539,7 +30602,7 @@
       <c r="V360" s="12" t="n"/>
       <c r="W360" s="12" t="n"/>
       <c r="X360" s="18">
-        <f>IF($E360="","",IF(AND($B360&lt;&gt;"",ISNA(MATCH($B360,机构表,0))),"※机构不在【资料】里",IF(AND($D360&lt;&gt;"",ISNA(MATCH($D360,状态表,0))),"※状态不在【资料】里",IF(N($M360)&gt;N($L360),"※已还本金大于典当金额",IF(AND($I360&lt;&gt;"",$J360&lt;&gt;"",$J360&lt;$I360),"※到期日早于当票日期",IF(AND($H360&lt;&gt;"",COUNTIF($H$4:$H$403,$H360)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L360&lt;&gt;"",$E360=""),"※有金额没写客户","")))))</f>
+        <f>IF($E360="","",IF(AND($B360&lt;&gt;"",ISNA(MATCH($B360,机构表,0))),"※机构不在【资料】里",IF(AND($D360&lt;&gt;"",ISNA(MATCH($D360,状态表,0))),"※状态不在【资料】里",IF(N($M360)&gt;N($L360),"※已还本金大于典当金额",IF(AND($I360&lt;&gt;"",$J360&lt;&gt;"",$J360&lt;$I360),"※到期日早于当票日期",IF(AND($H360&lt;&gt;"",COUNTIF($H$4:$H$403,$H360)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L360&lt;&gt;"",$E360=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30574,7 +30637,7 @@
       <c r="V361" s="12" t="n"/>
       <c r="W361" s="12" t="n"/>
       <c r="X361" s="18">
-        <f>IF($E361="","",IF(AND($B361&lt;&gt;"",ISNA(MATCH($B361,机构表,0))),"※机构不在【资料】里",IF(AND($D361&lt;&gt;"",ISNA(MATCH($D361,状态表,0))),"※状态不在【资料】里",IF(N($M361)&gt;N($L361),"※已还本金大于典当金额",IF(AND($I361&lt;&gt;"",$J361&lt;&gt;"",$J361&lt;$I361),"※到期日早于当票日期",IF(AND($H361&lt;&gt;"",COUNTIF($H$4:$H$403,$H361)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L361&lt;&gt;"",$E361=""),"※有金额没写客户","")))))</f>
+        <f>IF($E361="","",IF(AND($B361&lt;&gt;"",ISNA(MATCH($B361,机构表,0))),"※机构不在【资料】里",IF(AND($D361&lt;&gt;"",ISNA(MATCH($D361,状态表,0))),"※状态不在【资料】里",IF(N($M361)&gt;N($L361),"※已还本金大于典当金额",IF(AND($I361&lt;&gt;"",$J361&lt;&gt;"",$J361&lt;$I361),"※到期日早于当票日期",IF(AND($H361&lt;&gt;"",COUNTIF($H$4:$H$403,$H361)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L361&lt;&gt;"",$E361=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30609,7 +30672,7 @@
       <c r="V362" s="12" t="n"/>
       <c r="W362" s="12" t="n"/>
       <c r="X362" s="18">
-        <f>IF($E362="","",IF(AND($B362&lt;&gt;"",ISNA(MATCH($B362,机构表,0))),"※机构不在【资料】里",IF(AND($D362&lt;&gt;"",ISNA(MATCH($D362,状态表,0))),"※状态不在【资料】里",IF(N($M362)&gt;N($L362),"※已还本金大于典当金额",IF(AND($I362&lt;&gt;"",$J362&lt;&gt;"",$J362&lt;$I362),"※到期日早于当票日期",IF(AND($H362&lt;&gt;"",COUNTIF($H$4:$H$403,$H362)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L362&lt;&gt;"",$E362=""),"※有金额没写客户","")))))</f>
+        <f>IF($E362="","",IF(AND($B362&lt;&gt;"",ISNA(MATCH($B362,机构表,0))),"※机构不在【资料】里",IF(AND($D362&lt;&gt;"",ISNA(MATCH($D362,状态表,0))),"※状态不在【资料】里",IF(N($M362)&gt;N($L362),"※已还本金大于典当金额",IF(AND($I362&lt;&gt;"",$J362&lt;&gt;"",$J362&lt;$I362),"※到期日早于当票日期",IF(AND($H362&lt;&gt;"",COUNTIF($H$4:$H$403,$H362)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L362&lt;&gt;"",$E362=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30644,7 +30707,7 @@
       <c r="V363" s="12" t="n"/>
       <c r="W363" s="12" t="n"/>
       <c r="X363" s="18">
-        <f>IF($E363="","",IF(AND($B363&lt;&gt;"",ISNA(MATCH($B363,机构表,0))),"※机构不在【资料】里",IF(AND($D363&lt;&gt;"",ISNA(MATCH($D363,状态表,0))),"※状态不在【资料】里",IF(N($M363)&gt;N($L363),"※已还本金大于典当金额",IF(AND($I363&lt;&gt;"",$J363&lt;&gt;"",$J363&lt;$I363),"※到期日早于当票日期",IF(AND($H363&lt;&gt;"",COUNTIF($H$4:$H$403,$H363)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L363&lt;&gt;"",$E363=""),"※有金额没写客户","")))))</f>
+        <f>IF($E363="","",IF(AND($B363&lt;&gt;"",ISNA(MATCH($B363,机构表,0))),"※机构不在【资料】里",IF(AND($D363&lt;&gt;"",ISNA(MATCH($D363,状态表,0))),"※状态不在【资料】里",IF(N($M363)&gt;N($L363),"※已还本金大于典当金额",IF(AND($I363&lt;&gt;"",$J363&lt;&gt;"",$J363&lt;$I363),"※到期日早于当票日期",IF(AND($H363&lt;&gt;"",COUNTIF($H$4:$H$403,$H363)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L363&lt;&gt;"",$E363=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30679,7 +30742,7 @@
       <c r="V364" s="12" t="n"/>
       <c r="W364" s="12" t="n"/>
       <c r="X364" s="18">
-        <f>IF($E364="","",IF(AND($B364&lt;&gt;"",ISNA(MATCH($B364,机构表,0))),"※机构不在【资料】里",IF(AND($D364&lt;&gt;"",ISNA(MATCH($D364,状态表,0))),"※状态不在【资料】里",IF(N($M364)&gt;N($L364),"※已还本金大于典当金额",IF(AND($I364&lt;&gt;"",$J364&lt;&gt;"",$J364&lt;$I364),"※到期日早于当票日期",IF(AND($H364&lt;&gt;"",COUNTIF($H$4:$H$403,$H364)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L364&lt;&gt;"",$E364=""),"※有金额没写客户","")))))</f>
+        <f>IF($E364="","",IF(AND($B364&lt;&gt;"",ISNA(MATCH($B364,机构表,0))),"※机构不在【资料】里",IF(AND($D364&lt;&gt;"",ISNA(MATCH($D364,状态表,0))),"※状态不在【资料】里",IF(N($M364)&gt;N($L364),"※已还本金大于典当金额",IF(AND($I364&lt;&gt;"",$J364&lt;&gt;"",$J364&lt;$I364),"※到期日早于当票日期",IF(AND($H364&lt;&gt;"",COUNTIF($H$4:$H$403,$H364)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L364&lt;&gt;"",$E364=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30714,7 +30777,7 @@
       <c r="V365" s="12" t="n"/>
       <c r="W365" s="12" t="n"/>
       <c r="X365" s="18">
-        <f>IF($E365="","",IF(AND($B365&lt;&gt;"",ISNA(MATCH($B365,机构表,0))),"※机构不在【资料】里",IF(AND($D365&lt;&gt;"",ISNA(MATCH($D365,状态表,0))),"※状态不在【资料】里",IF(N($M365)&gt;N($L365),"※已还本金大于典当金额",IF(AND($I365&lt;&gt;"",$J365&lt;&gt;"",$J365&lt;$I365),"※到期日早于当票日期",IF(AND($H365&lt;&gt;"",COUNTIF($H$4:$H$403,$H365)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L365&lt;&gt;"",$E365=""),"※有金额没写客户","")))))</f>
+        <f>IF($E365="","",IF(AND($B365&lt;&gt;"",ISNA(MATCH($B365,机构表,0))),"※机构不在【资料】里",IF(AND($D365&lt;&gt;"",ISNA(MATCH($D365,状态表,0))),"※状态不在【资料】里",IF(N($M365)&gt;N($L365),"※已还本金大于典当金额",IF(AND($I365&lt;&gt;"",$J365&lt;&gt;"",$J365&lt;$I365),"※到期日早于当票日期",IF(AND($H365&lt;&gt;"",COUNTIF($H$4:$H$403,$H365)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L365&lt;&gt;"",$E365=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30749,7 +30812,7 @@
       <c r="V366" s="12" t="n"/>
       <c r="W366" s="12" t="n"/>
       <c r="X366" s="18">
-        <f>IF($E366="","",IF(AND($B366&lt;&gt;"",ISNA(MATCH($B366,机构表,0))),"※机构不在【资料】里",IF(AND($D366&lt;&gt;"",ISNA(MATCH($D366,状态表,0))),"※状态不在【资料】里",IF(N($M366)&gt;N($L366),"※已还本金大于典当金额",IF(AND($I366&lt;&gt;"",$J366&lt;&gt;"",$J366&lt;$I366),"※到期日早于当票日期",IF(AND($H366&lt;&gt;"",COUNTIF($H$4:$H$403,$H366)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L366&lt;&gt;"",$E366=""),"※有金额没写客户","")))))</f>
+        <f>IF($E366="","",IF(AND($B366&lt;&gt;"",ISNA(MATCH($B366,机构表,0))),"※机构不在【资料】里",IF(AND($D366&lt;&gt;"",ISNA(MATCH($D366,状态表,0))),"※状态不在【资料】里",IF(N($M366)&gt;N($L366),"※已还本金大于典当金额",IF(AND($I366&lt;&gt;"",$J366&lt;&gt;"",$J366&lt;$I366),"※到期日早于当票日期",IF(AND($H366&lt;&gt;"",COUNTIF($H$4:$H$403,$H366)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L366&lt;&gt;"",$E366=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30784,7 +30847,7 @@
       <c r="V367" s="12" t="n"/>
       <c r="W367" s="12" t="n"/>
       <c r="X367" s="18">
-        <f>IF($E367="","",IF(AND($B367&lt;&gt;"",ISNA(MATCH($B367,机构表,0))),"※机构不在【资料】里",IF(AND($D367&lt;&gt;"",ISNA(MATCH($D367,状态表,0))),"※状态不在【资料】里",IF(N($M367)&gt;N($L367),"※已还本金大于典当金额",IF(AND($I367&lt;&gt;"",$J367&lt;&gt;"",$J367&lt;$I367),"※到期日早于当票日期",IF(AND($H367&lt;&gt;"",COUNTIF($H$4:$H$403,$H367)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L367&lt;&gt;"",$E367=""),"※有金额没写客户","")))))</f>
+        <f>IF($E367="","",IF(AND($B367&lt;&gt;"",ISNA(MATCH($B367,机构表,0))),"※机构不在【资料】里",IF(AND($D367&lt;&gt;"",ISNA(MATCH($D367,状态表,0))),"※状态不在【资料】里",IF(N($M367)&gt;N($L367),"※已还本金大于典当金额",IF(AND($I367&lt;&gt;"",$J367&lt;&gt;"",$J367&lt;$I367),"※到期日早于当票日期",IF(AND($H367&lt;&gt;"",COUNTIF($H$4:$H$403,$H367)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L367&lt;&gt;"",$E367=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30819,7 +30882,7 @@
       <c r="V368" s="12" t="n"/>
       <c r="W368" s="12" t="n"/>
       <c r="X368" s="18">
-        <f>IF($E368="","",IF(AND($B368&lt;&gt;"",ISNA(MATCH($B368,机构表,0))),"※机构不在【资料】里",IF(AND($D368&lt;&gt;"",ISNA(MATCH($D368,状态表,0))),"※状态不在【资料】里",IF(N($M368)&gt;N($L368),"※已还本金大于典当金额",IF(AND($I368&lt;&gt;"",$J368&lt;&gt;"",$J368&lt;$I368),"※到期日早于当票日期",IF(AND($H368&lt;&gt;"",COUNTIF($H$4:$H$403,$H368)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L368&lt;&gt;"",$E368=""),"※有金额没写客户","")))))</f>
+        <f>IF($E368="","",IF(AND($B368&lt;&gt;"",ISNA(MATCH($B368,机构表,0))),"※机构不在【资料】里",IF(AND($D368&lt;&gt;"",ISNA(MATCH($D368,状态表,0))),"※状态不在【资料】里",IF(N($M368)&gt;N($L368),"※已还本金大于典当金额",IF(AND($I368&lt;&gt;"",$J368&lt;&gt;"",$J368&lt;$I368),"※到期日早于当票日期",IF(AND($H368&lt;&gt;"",COUNTIF($H$4:$H$403,$H368)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L368&lt;&gt;"",$E368=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30854,7 +30917,7 @@
       <c r="V369" s="12" t="n"/>
       <c r="W369" s="12" t="n"/>
       <c r="X369" s="18">
-        <f>IF($E369="","",IF(AND($B369&lt;&gt;"",ISNA(MATCH($B369,机构表,0))),"※机构不在【资料】里",IF(AND($D369&lt;&gt;"",ISNA(MATCH($D369,状态表,0))),"※状态不在【资料】里",IF(N($M369)&gt;N($L369),"※已还本金大于典当金额",IF(AND($I369&lt;&gt;"",$J369&lt;&gt;"",$J369&lt;$I369),"※到期日早于当票日期",IF(AND($H369&lt;&gt;"",COUNTIF($H$4:$H$403,$H369)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L369&lt;&gt;"",$E369=""),"※有金额没写客户","")))))</f>
+        <f>IF($E369="","",IF(AND($B369&lt;&gt;"",ISNA(MATCH($B369,机构表,0))),"※机构不在【资料】里",IF(AND($D369&lt;&gt;"",ISNA(MATCH($D369,状态表,0))),"※状态不在【资料】里",IF(N($M369)&gt;N($L369),"※已还本金大于典当金额",IF(AND($I369&lt;&gt;"",$J369&lt;&gt;"",$J369&lt;$I369),"※到期日早于当票日期",IF(AND($H369&lt;&gt;"",COUNTIF($H$4:$H$403,$H369)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L369&lt;&gt;"",$E369=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30889,7 +30952,7 @@
       <c r="V370" s="12" t="n"/>
       <c r="W370" s="12" t="n"/>
       <c r="X370" s="18">
-        <f>IF($E370="","",IF(AND($B370&lt;&gt;"",ISNA(MATCH($B370,机构表,0))),"※机构不在【资料】里",IF(AND($D370&lt;&gt;"",ISNA(MATCH($D370,状态表,0))),"※状态不在【资料】里",IF(N($M370)&gt;N($L370),"※已还本金大于典当金额",IF(AND($I370&lt;&gt;"",$J370&lt;&gt;"",$J370&lt;$I370),"※到期日早于当票日期",IF(AND($H370&lt;&gt;"",COUNTIF($H$4:$H$403,$H370)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L370&lt;&gt;"",$E370=""),"※有金额没写客户","")))))</f>
+        <f>IF($E370="","",IF(AND($B370&lt;&gt;"",ISNA(MATCH($B370,机构表,0))),"※机构不在【资料】里",IF(AND($D370&lt;&gt;"",ISNA(MATCH($D370,状态表,0))),"※状态不在【资料】里",IF(N($M370)&gt;N($L370),"※已还本金大于典当金额",IF(AND($I370&lt;&gt;"",$J370&lt;&gt;"",$J370&lt;$I370),"※到期日早于当票日期",IF(AND($H370&lt;&gt;"",COUNTIF($H$4:$H$403,$H370)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L370&lt;&gt;"",$E370=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30924,7 +30987,7 @@
       <c r="V371" s="12" t="n"/>
       <c r="W371" s="12" t="n"/>
       <c r="X371" s="18">
-        <f>IF($E371="","",IF(AND($B371&lt;&gt;"",ISNA(MATCH($B371,机构表,0))),"※机构不在【资料】里",IF(AND($D371&lt;&gt;"",ISNA(MATCH($D371,状态表,0))),"※状态不在【资料】里",IF(N($M371)&gt;N($L371),"※已还本金大于典当金额",IF(AND($I371&lt;&gt;"",$J371&lt;&gt;"",$J371&lt;$I371),"※到期日早于当票日期",IF(AND($H371&lt;&gt;"",COUNTIF($H$4:$H$403,$H371)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L371&lt;&gt;"",$E371=""),"※有金额没写客户","")))))</f>
+        <f>IF($E371="","",IF(AND($B371&lt;&gt;"",ISNA(MATCH($B371,机构表,0))),"※机构不在【资料】里",IF(AND($D371&lt;&gt;"",ISNA(MATCH($D371,状态表,0))),"※状态不在【资料】里",IF(N($M371)&gt;N($L371),"※已还本金大于典当金额",IF(AND($I371&lt;&gt;"",$J371&lt;&gt;"",$J371&lt;$I371),"※到期日早于当票日期",IF(AND($H371&lt;&gt;"",COUNTIF($H$4:$H$403,$H371)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L371&lt;&gt;"",$E371=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30959,7 +31022,7 @@
       <c r="V372" s="12" t="n"/>
       <c r="W372" s="12" t="n"/>
       <c r="X372" s="18">
-        <f>IF($E372="","",IF(AND($B372&lt;&gt;"",ISNA(MATCH($B372,机构表,0))),"※机构不在【资料】里",IF(AND($D372&lt;&gt;"",ISNA(MATCH($D372,状态表,0))),"※状态不在【资料】里",IF(N($M372)&gt;N($L372),"※已还本金大于典当金额",IF(AND($I372&lt;&gt;"",$J372&lt;&gt;"",$J372&lt;$I372),"※到期日早于当票日期",IF(AND($H372&lt;&gt;"",COUNTIF($H$4:$H$403,$H372)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L372&lt;&gt;"",$E372=""),"※有金额没写客户","")))))</f>
+        <f>IF($E372="","",IF(AND($B372&lt;&gt;"",ISNA(MATCH($B372,机构表,0))),"※机构不在【资料】里",IF(AND($D372&lt;&gt;"",ISNA(MATCH($D372,状态表,0))),"※状态不在【资料】里",IF(N($M372)&gt;N($L372),"※已还本金大于典当金额",IF(AND($I372&lt;&gt;"",$J372&lt;&gt;"",$J372&lt;$I372),"※到期日早于当票日期",IF(AND($H372&lt;&gt;"",COUNTIF($H$4:$H$403,$H372)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L372&lt;&gt;"",$E372=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -30994,7 +31057,7 @@
       <c r="V373" s="12" t="n"/>
       <c r="W373" s="12" t="n"/>
       <c r="X373" s="18">
-        <f>IF($E373="","",IF(AND($B373&lt;&gt;"",ISNA(MATCH($B373,机构表,0))),"※机构不在【资料】里",IF(AND($D373&lt;&gt;"",ISNA(MATCH($D373,状态表,0))),"※状态不在【资料】里",IF(N($M373)&gt;N($L373),"※已还本金大于典当金额",IF(AND($I373&lt;&gt;"",$J373&lt;&gt;"",$J373&lt;$I373),"※到期日早于当票日期",IF(AND($H373&lt;&gt;"",COUNTIF($H$4:$H$403,$H373)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L373&lt;&gt;"",$E373=""),"※有金额没写客户","")))))</f>
+        <f>IF($E373="","",IF(AND($B373&lt;&gt;"",ISNA(MATCH($B373,机构表,0))),"※机构不在【资料】里",IF(AND($D373&lt;&gt;"",ISNA(MATCH($D373,状态表,0))),"※状态不在【资料】里",IF(N($M373)&gt;N($L373),"※已还本金大于典当金额",IF(AND($I373&lt;&gt;"",$J373&lt;&gt;"",$J373&lt;$I373),"※到期日早于当票日期",IF(AND($H373&lt;&gt;"",COUNTIF($H$4:$H$403,$H373)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L373&lt;&gt;"",$E373=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31029,7 +31092,7 @@
       <c r="V374" s="12" t="n"/>
       <c r="W374" s="12" t="n"/>
       <c r="X374" s="18">
-        <f>IF($E374="","",IF(AND($B374&lt;&gt;"",ISNA(MATCH($B374,机构表,0))),"※机构不在【资料】里",IF(AND($D374&lt;&gt;"",ISNA(MATCH($D374,状态表,0))),"※状态不在【资料】里",IF(N($M374)&gt;N($L374),"※已还本金大于典当金额",IF(AND($I374&lt;&gt;"",$J374&lt;&gt;"",$J374&lt;$I374),"※到期日早于当票日期",IF(AND($H374&lt;&gt;"",COUNTIF($H$4:$H$403,$H374)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L374&lt;&gt;"",$E374=""),"※有金额没写客户","")))))</f>
+        <f>IF($E374="","",IF(AND($B374&lt;&gt;"",ISNA(MATCH($B374,机构表,0))),"※机构不在【资料】里",IF(AND($D374&lt;&gt;"",ISNA(MATCH($D374,状态表,0))),"※状态不在【资料】里",IF(N($M374)&gt;N($L374),"※已还本金大于典当金额",IF(AND($I374&lt;&gt;"",$J374&lt;&gt;"",$J374&lt;$I374),"※到期日早于当票日期",IF(AND($H374&lt;&gt;"",COUNTIF($H$4:$H$403,$H374)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L374&lt;&gt;"",$E374=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31064,7 +31127,7 @@
       <c r="V375" s="12" t="n"/>
       <c r="W375" s="12" t="n"/>
       <c r="X375" s="18">
-        <f>IF($E375="","",IF(AND($B375&lt;&gt;"",ISNA(MATCH($B375,机构表,0))),"※机构不在【资料】里",IF(AND($D375&lt;&gt;"",ISNA(MATCH($D375,状态表,0))),"※状态不在【资料】里",IF(N($M375)&gt;N($L375),"※已还本金大于典当金额",IF(AND($I375&lt;&gt;"",$J375&lt;&gt;"",$J375&lt;$I375),"※到期日早于当票日期",IF(AND($H375&lt;&gt;"",COUNTIF($H$4:$H$403,$H375)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L375&lt;&gt;"",$E375=""),"※有金额没写客户","")))))</f>
+        <f>IF($E375="","",IF(AND($B375&lt;&gt;"",ISNA(MATCH($B375,机构表,0))),"※机构不在【资料】里",IF(AND($D375&lt;&gt;"",ISNA(MATCH($D375,状态表,0))),"※状态不在【资料】里",IF(N($M375)&gt;N($L375),"※已还本金大于典当金额",IF(AND($I375&lt;&gt;"",$J375&lt;&gt;"",$J375&lt;$I375),"※到期日早于当票日期",IF(AND($H375&lt;&gt;"",COUNTIF($H$4:$H$403,$H375)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L375&lt;&gt;"",$E375=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31099,7 +31162,7 @@
       <c r="V376" s="12" t="n"/>
       <c r="W376" s="12" t="n"/>
       <c r="X376" s="18">
-        <f>IF($E376="","",IF(AND($B376&lt;&gt;"",ISNA(MATCH($B376,机构表,0))),"※机构不在【资料】里",IF(AND($D376&lt;&gt;"",ISNA(MATCH($D376,状态表,0))),"※状态不在【资料】里",IF(N($M376)&gt;N($L376),"※已还本金大于典当金额",IF(AND($I376&lt;&gt;"",$J376&lt;&gt;"",$J376&lt;$I376),"※到期日早于当票日期",IF(AND($H376&lt;&gt;"",COUNTIF($H$4:$H$403,$H376)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L376&lt;&gt;"",$E376=""),"※有金额没写客户","")))))</f>
+        <f>IF($E376="","",IF(AND($B376&lt;&gt;"",ISNA(MATCH($B376,机构表,0))),"※机构不在【资料】里",IF(AND($D376&lt;&gt;"",ISNA(MATCH($D376,状态表,0))),"※状态不在【资料】里",IF(N($M376)&gt;N($L376),"※已还本金大于典当金额",IF(AND($I376&lt;&gt;"",$J376&lt;&gt;"",$J376&lt;$I376),"※到期日早于当票日期",IF(AND($H376&lt;&gt;"",COUNTIF($H$4:$H$403,$H376)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L376&lt;&gt;"",$E376=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31134,7 +31197,7 @@
       <c r="V377" s="12" t="n"/>
       <c r="W377" s="12" t="n"/>
       <c r="X377" s="18">
-        <f>IF($E377="","",IF(AND($B377&lt;&gt;"",ISNA(MATCH($B377,机构表,0))),"※机构不在【资料】里",IF(AND($D377&lt;&gt;"",ISNA(MATCH($D377,状态表,0))),"※状态不在【资料】里",IF(N($M377)&gt;N($L377),"※已还本金大于典当金额",IF(AND($I377&lt;&gt;"",$J377&lt;&gt;"",$J377&lt;$I377),"※到期日早于当票日期",IF(AND($H377&lt;&gt;"",COUNTIF($H$4:$H$403,$H377)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L377&lt;&gt;"",$E377=""),"※有金额没写客户","")))))</f>
+        <f>IF($E377="","",IF(AND($B377&lt;&gt;"",ISNA(MATCH($B377,机构表,0))),"※机构不在【资料】里",IF(AND($D377&lt;&gt;"",ISNA(MATCH($D377,状态表,0))),"※状态不在【资料】里",IF(N($M377)&gt;N($L377),"※已还本金大于典当金额",IF(AND($I377&lt;&gt;"",$J377&lt;&gt;"",$J377&lt;$I377),"※到期日早于当票日期",IF(AND($H377&lt;&gt;"",COUNTIF($H$4:$H$403,$H377)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L377&lt;&gt;"",$E377=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31169,7 +31232,7 @@
       <c r="V378" s="12" t="n"/>
       <c r="W378" s="12" t="n"/>
       <c r="X378" s="18">
-        <f>IF($E378="","",IF(AND($B378&lt;&gt;"",ISNA(MATCH($B378,机构表,0))),"※机构不在【资料】里",IF(AND($D378&lt;&gt;"",ISNA(MATCH($D378,状态表,0))),"※状态不在【资料】里",IF(N($M378)&gt;N($L378),"※已还本金大于典当金额",IF(AND($I378&lt;&gt;"",$J378&lt;&gt;"",$J378&lt;$I378),"※到期日早于当票日期",IF(AND($H378&lt;&gt;"",COUNTIF($H$4:$H$403,$H378)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L378&lt;&gt;"",$E378=""),"※有金额没写客户","")))))</f>
+        <f>IF($E378="","",IF(AND($B378&lt;&gt;"",ISNA(MATCH($B378,机构表,0))),"※机构不在【资料】里",IF(AND($D378&lt;&gt;"",ISNA(MATCH($D378,状态表,0))),"※状态不在【资料】里",IF(N($M378)&gt;N($L378),"※已还本金大于典当金额",IF(AND($I378&lt;&gt;"",$J378&lt;&gt;"",$J378&lt;$I378),"※到期日早于当票日期",IF(AND($H378&lt;&gt;"",COUNTIF($H$4:$H$403,$H378)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L378&lt;&gt;"",$E378=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31204,7 +31267,7 @@
       <c r="V379" s="12" t="n"/>
       <c r="W379" s="12" t="n"/>
       <c r="X379" s="18">
-        <f>IF($E379="","",IF(AND($B379&lt;&gt;"",ISNA(MATCH($B379,机构表,0))),"※机构不在【资料】里",IF(AND($D379&lt;&gt;"",ISNA(MATCH($D379,状态表,0))),"※状态不在【资料】里",IF(N($M379)&gt;N($L379),"※已还本金大于典当金额",IF(AND($I379&lt;&gt;"",$J379&lt;&gt;"",$J379&lt;$I379),"※到期日早于当票日期",IF(AND($H379&lt;&gt;"",COUNTIF($H$4:$H$403,$H379)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L379&lt;&gt;"",$E379=""),"※有金额没写客户","")))))</f>
+        <f>IF($E379="","",IF(AND($B379&lt;&gt;"",ISNA(MATCH($B379,机构表,0))),"※机构不在【资料】里",IF(AND($D379&lt;&gt;"",ISNA(MATCH($D379,状态表,0))),"※状态不在【资料】里",IF(N($M379)&gt;N($L379),"※已还本金大于典当金额",IF(AND($I379&lt;&gt;"",$J379&lt;&gt;"",$J379&lt;$I379),"※到期日早于当票日期",IF(AND($H379&lt;&gt;"",COUNTIF($H$4:$H$403,$H379)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L379&lt;&gt;"",$E379=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31239,7 +31302,7 @@
       <c r="V380" s="12" t="n"/>
       <c r="W380" s="12" t="n"/>
       <c r="X380" s="18">
-        <f>IF($E380="","",IF(AND($B380&lt;&gt;"",ISNA(MATCH($B380,机构表,0))),"※机构不在【资料】里",IF(AND($D380&lt;&gt;"",ISNA(MATCH($D380,状态表,0))),"※状态不在【资料】里",IF(N($M380)&gt;N($L380),"※已还本金大于典当金额",IF(AND($I380&lt;&gt;"",$J380&lt;&gt;"",$J380&lt;$I380),"※到期日早于当票日期",IF(AND($H380&lt;&gt;"",COUNTIF($H$4:$H$403,$H380)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L380&lt;&gt;"",$E380=""),"※有金额没写客户","")))))</f>
+        <f>IF($E380="","",IF(AND($B380&lt;&gt;"",ISNA(MATCH($B380,机构表,0))),"※机构不在【资料】里",IF(AND($D380&lt;&gt;"",ISNA(MATCH($D380,状态表,0))),"※状态不在【资料】里",IF(N($M380)&gt;N($L380),"※已还本金大于典当金额",IF(AND($I380&lt;&gt;"",$J380&lt;&gt;"",$J380&lt;$I380),"※到期日早于当票日期",IF(AND($H380&lt;&gt;"",COUNTIF($H$4:$H$403,$H380)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L380&lt;&gt;"",$E380=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31274,7 +31337,7 @@
       <c r="V381" s="12" t="n"/>
       <c r="W381" s="12" t="n"/>
       <c r="X381" s="18">
-        <f>IF($E381="","",IF(AND($B381&lt;&gt;"",ISNA(MATCH($B381,机构表,0))),"※机构不在【资料】里",IF(AND($D381&lt;&gt;"",ISNA(MATCH($D381,状态表,0))),"※状态不在【资料】里",IF(N($M381)&gt;N($L381),"※已还本金大于典当金额",IF(AND($I381&lt;&gt;"",$J381&lt;&gt;"",$J381&lt;$I381),"※到期日早于当票日期",IF(AND($H381&lt;&gt;"",COUNTIF($H$4:$H$403,$H381)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L381&lt;&gt;"",$E381=""),"※有金额没写客户","")))))</f>
+        <f>IF($E381="","",IF(AND($B381&lt;&gt;"",ISNA(MATCH($B381,机构表,0))),"※机构不在【资料】里",IF(AND($D381&lt;&gt;"",ISNA(MATCH($D381,状态表,0))),"※状态不在【资料】里",IF(N($M381)&gt;N($L381),"※已还本金大于典当金额",IF(AND($I381&lt;&gt;"",$J381&lt;&gt;"",$J381&lt;$I381),"※到期日早于当票日期",IF(AND($H381&lt;&gt;"",COUNTIF($H$4:$H$403,$H381)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L381&lt;&gt;"",$E381=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31309,7 +31372,7 @@
       <c r="V382" s="12" t="n"/>
       <c r="W382" s="12" t="n"/>
       <c r="X382" s="18">
-        <f>IF($E382="","",IF(AND($B382&lt;&gt;"",ISNA(MATCH($B382,机构表,0))),"※机构不在【资料】里",IF(AND($D382&lt;&gt;"",ISNA(MATCH($D382,状态表,0))),"※状态不在【资料】里",IF(N($M382)&gt;N($L382),"※已还本金大于典当金额",IF(AND($I382&lt;&gt;"",$J382&lt;&gt;"",$J382&lt;$I382),"※到期日早于当票日期",IF(AND($H382&lt;&gt;"",COUNTIF($H$4:$H$403,$H382)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L382&lt;&gt;"",$E382=""),"※有金额没写客户","")))))</f>
+        <f>IF($E382="","",IF(AND($B382&lt;&gt;"",ISNA(MATCH($B382,机构表,0))),"※机构不在【资料】里",IF(AND($D382&lt;&gt;"",ISNA(MATCH($D382,状态表,0))),"※状态不在【资料】里",IF(N($M382)&gt;N($L382),"※已还本金大于典当金额",IF(AND($I382&lt;&gt;"",$J382&lt;&gt;"",$J382&lt;$I382),"※到期日早于当票日期",IF(AND($H382&lt;&gt;"",COUNTIF($H$4:$H$403,$H382)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L382&lt;&gt;"",$E382=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31344,7 +31407,7 @@
       <c r="V383" s="12" t="n"/>
       <c r="W383" s="12" t="n"/>
       <c r="X383" s="18">
-        <f>IF($E383="","",IF(AND($B383&lt;&gt;"",ISNA(MATCH($B383,机构表,0))),"※机构不在【资料】里",IF(AND($D383&lt;&gt;"",ISNA(MATCH($D383,状态表,0))),"※状态不在【资料】里",IF(N($M383)&gt;N($L383),"※已还本金大于典当金额",IF(AND($I383&lt;&gt;"",$J383&lt;&gt;"",$J383&lt;$I383),"※到期日早于当票日期",IF(AND($H383&lt;&gt;"",COUNTIF($H$4:$H$403,$H383)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L383&lt;&gt;"",$E383=""),"※有金额没写客户","")))))</f>
+        <f>IF($E383="","",IF(AND($B383&lt;&gt;"",ISNA(MATCH($B383,机构表,0))),"※机构不在【资料】里",IF(AND($D383&lt;&gt;"",ISNA(MATCH($D383,状态表,0))),"※状态不在【资料】里",IF(N($M383)&gt;N($L383),"※已还本金大于典当金额",IF(AND($I383&lt;&gt;"",$J383&lt;&gt;"",$J383&lt;$I383),"※到期日早于当票日期",IF(AND($H383&lt;&gt;"",COUNTIF($H$4:$H$403,$H383)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L383&lt;&gt;"",$E383=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31379,7 +31442,7 @@
       <c r="V384" s="12" t="n"/>
       <c r="W384" s="12" t="n"/>
       <c r="X384" s="18">
-        <f>IF($E384="","",IF(AND($B384&lt;&gt;"",ISNA(MATCH($B384,机构表,0))),"※机构不在【资料】里",IF(AND($D384&lt;&gt;"",ISNA(MATCH($D384,状态表,0))),"※状态不在【资料】里",IF(N($M384)&gt;N($L384),"※已还本金大于典当金额",IF(AND($I384&lt;&gt;"",$J384&lt;&gt;"",$J384&lt;$I384),"※到期日早于当票日期",IF(AND($H384&lt;&gt;"",COUNTIF($H$4:$H$403,$H384)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L384&lt;&gt;"",$E384=""),"※有金额没写客户","")))))</f>
+        <f>IF($E384="","",IF(AND($B384&lt;&gt;"",ISNA(MATCH($B384,机构表,0))),"※机构不在【资料】里",IF(AND($D384&lt;&gt;"",ISNA(MATCH($D384,状态表,0))),"※状态不在【资料】里",IF(N($M384)&gt;N($L384),"※已还本金大于典当金额",IF(AND($I384&lt;&gt;"",$J384&lt;&gt;"",$J384&lt;$I384),"※到期日早于当票日期",IF(AND($H384&lt;&gt;"",COUNTIF($H$4:$H$403,$H384)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L384&lt;&gt;"",$E384=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31414,7 +31477,7 @@
       <c r="V385" s="12" t="n"/>
       <c r="W385" s="12" t="n"/>
       <c r="X385" s="18">
-        <f>IF($E385="","",IF(AND($B385&lt;&gt;"",ISNA(MATCH($B385,机构表,0))),"※机构不在【资料】里",IF(AND($D385&lt;&gt;"",ISNA(MATCH($D385,状态表,0))),"※状态不在【资料】里",IF(N($M385)&gt;N($L385),"※已还本金大于典当金额",IF(AND($I385&lt;&gt;"",$J385&lt;&gt;"",$J385&lt;$I385),"※到期日早于当票日期",IF(AND($H385&lt;&gt;"",COUNTIF($H$4:$H$403,$H385)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L385&lt;&gt;"",$E385=""),"※有金额没写客户","")))))</f>
+        <f>IF($E385="","",IF(AND($B385&lt;&gt;"",ISNA(MATCH($B385,机构表,0))),"※机构不在【资料】里",IF(AND($D385&lt;&gt;"",ISNA(MATCH($D385,状态表,0))),"※状态不在【资料】里",IF(N($M385)&gt;N($L385),"※已还本金大于典当金额",IF(AND($I385&lt;&gt;"",$J385&lt;&gt;"",$J385&lt;$I385),"※到期日早于当票日期",IF(AND($H385&lt;&gt;"",COUNTIF($H$4:$H$403,$H385)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L385&lt;&gt;"",$E385=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31449,7 +31512,7 @@
       <c r="V386" s="12" t="n"/>
       <c r="W386" s="12" t="n"/>
       <c r="X386" s="18">
-        <f>IF($E386="","",IF(AND($B386&lt;&gt;"",ISNA(MATCH($B386,机构表,0))),"※机构不在【资料】里",IF(AND($D386&lt;&gt;"",ISNA(MATCH($D386,状态表,0))),"※状态不在【资料】里",IF(N($M386)&gt;N($L386),"※已还本金大于典当金额",IF(AND($I386&lt;&gt;"",$J386&lt;&gt;"",$J386&lt;$I386),"※到期日早于当票日期",IF(AND($H386&lt;&gt;"",COUNTIF($H$4:$H$403,$H386)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L386&lt;&gt;"",$E386=""),"※有金额没写客户","")))))</f>
+        <f>IF($E386="","",IF(AND($B386&lt;&gt;"",ISNA(MATCH($B386,机构表,0))),"※机构不在【资料】里",IF(AND($D386&lt;&gt;"",ISNA(MATCH($D386,状态表,0))),"※状态不在【资料】里",IF(N($M386)&gt;N($L386),"※已还本金大于典当金额",IF(AND($I386&lt;&gt;"",$J386&lt;&gt;"",$J386&lt;$I386),"※到期日早于当票日期",IF(AND($H386&lt;&gt;"",COUNTIF($H$4:$H$403,$H386)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L386&lt;&gt;"",$E386=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31484,7 +31547,7 @@
       <c r="V387" s="12" t="n"/>
       <c r="W387" s="12" t="n"/>
       <c r="X387" s="18">
-        <f>IF($E387="","",IF(AND($B387&lt;&gt;"",ISNA(MATCH($B387,机构表,0))),"※机构不在【资料】里",IF(AND($D387&lt;&gt;"",ISNA(MATCH($D387,状态表,0))),"※状态不在【资料】里",IF(N($M387)&gt;N($L387),"※已还本金大于典当金额",IF(AND($I387&lt;&gt;"",$J387&lt;&gt;"",$J387&lt;$I387),"※到期日早于当票日期",IF(AND($H387&lt;&gt;"",COUNTIF($H$4:$H$403,$H387)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L387&lt;&gt;"",$E387=""),"※有金额没写客户","")))))</f>
+        <f>IF($E387="","",IF(AND($B387&lt;&gt;"",ISNA(MATCH($B387,机构表,0))),"※机构不在【资料】里",IF(AND($D387&lt;&gt;"",ISNA(MATCH($D387,状态表,0))),"※状态不在【资料】里",IF(N($M387)&gt;N($L387),"※已还本金大于典当金额",IF(AND($I387&lt;&gt;"",$J387&lt;&gt;"",$J387&lt;$I387),"※到期日早于当票日期",IF(AND($H387&lt;&gt;"",COUNTIF($H$4:$H$403,$H387)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L387&lt;&gt;"",$E387=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31519,7 +31582,7 @@
       <c r="V388" s="12" t="n"/>
       <c r="W388" s="12" t="n"/>
       <c r="X388" s="18">
-        <f>IF($E388="","",IF(AND($B388&lt;&gt;"",ISNA(MATCH($B388,机构表,0))),"※机构不在【资料】里",IF(AND($D388&lt;&gt;"",ISNA(MATCH($D388,状态表,0))),"※状态不在【资料】里",IF(N($M388)&gt;N($L388),"※已还本金大于典当金额",IF(AND($I388&lt;&gt;"",$J388&lt;&gt;"",$J388&lt;$I388),"※到期日早于当票日期",IF(AND($H388&lt;&gt;"",COUNTIF($H$4:$H$403,$H388)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L388&lt;&gt;"",$E388=""),"※有金额没写客户","")))))</f>
+        <f>IF($E388="","",IF(AND($B388&lt;&gt;"",ISNA(MATCH($B388,机构表,0))),"※机构不在【资料】里",IF(AND($D388&lt;&gt;"",ISNA(MATCH($D388,状态表,0))),"※状态不在【资料】里",IF(N($M388)&gt;N($L388),"※已还本金大于典当金额",IF(AND($I388&lt;&gt;"",$J388&lt;&gt;"",$J388&lt;$I388),"※到期日早于当票日期",IF(AND($H388&lt;&gt;"",COUNTIF($H$4:$H$403,$H388)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L388&lt;&gt;"",$E388=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31554,7 +31617,7 @@
       <c r="V389" s="12" t="n"/>
       <c r="W389" s="12" t="n"/>
       <c r="X389" s="18">
-        <f>IF($E389="","",IF(AND($B389&lt;&gt;"",ISNA(MATCH($B389,机构表,0))),"※机构不在【资料】里",IF(AND($D389&lt;&gt;"",ISNA(MATCH($D389,状态表,0))),"※状态不在【资料】里",IF(N($M389)&gt;N($L389),"※已还本金大于典当金额",IF(AND($I389&lt;&gt;"",$J389&lt;&gt;"",$J389&lt;$I389),"※到期日早于当票日期",IF(AND($H389&lt;&gt;"",COUNTIF($H$4:$H$403,$H389)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L389&lt;&gt;"",$E389=""),"※有金额没写客户","")))))</f>
+        <f>IF($E389="","",IF(AND($B389&lt;&gt;"",ISNA(MATCH($B389,机构表,0))),"※机构不在【资料】里",IF(AND($D389&lt;&gt;"",ISNA(MATCH($D389,状态表,0))),"※状态不在【资料】里",IF(N($M389)&gt;N($L389),"※已还本金大于典当金额",IF(AND($I389&lt;&gt;"",$J389&lt;&gt;"",$J389&lt;$I389),"※到期日早于当票日期",IF(AND($H389&lt;&gt;"",COUNTIF($H$4:$H$403,$H389)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L389&lt;&gt;"",$E389=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31589,7 +31652,7 @@
       <c r="V390" s="12" t="n"/>
       <c r="W390" s="12" t="n"/>
       <c r="X390" s="18">
-        <f>IF($E390="","",IF(AND($B390&lt;&gt;"",ISNA(MATCH($B390,机构表,0))),"※机构不在【资料】里",IF(AND($D390&lt;&gt;"",ISNA(MATCH($D390,状态表,0))),"※状态不在【资料】里",IF(N($M390)&gt;N($L390),"※已还本金大于典当金额",IF(AND($I390&lt;&gt;"",$J390&lt;&gt;"",$J390&lt;$I390),"※到期日早于当票日期",IF(AND($H390&lt;&gt;"",COUNTIF($H$4:$H$403,$H390)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L390&lt;&gt;"",$E390=""),"※有金额没写客户","")))))</f>
+        <f>IF($E390="","",IF(AND($B390&lt;&gt;"",ISNA(MATCH($B390,机构表,0))),"※机构不在【资料】里",IF(AND($D390&lt;&gt;"",ISNA(MATCH($D390,状态表,0))),"※状态不在【资料】里",IF(N($M390)&gt;N($L390),"※已还本金大于典当金额",IF(AND($I390&lt;&gt;"",$J390&lt;&gt;"",$J390&lt;$I390),"※到期日早于当票日期",IF(AND($H390&lt;&gt;"",COUNTIF($H$4:$H$403,$H390)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L390&lt;&gt;"",$E390=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31624,7 +31687,7 @@
       <c r="V391" s="12" t="n"/>
       <c r="W391" s="12" t="n"/>
       <c r="X391" s="18">
-        <f>IF($E391="","",IF(AND($B391&lt;&gt;"",ISNA(MATCH($B391,机构表,0))),"※机构不在【资料】里",IF(AND($D391&lt;&gt;"",ISNA(MATCH($D391,状态表,0))),"※状态不在【资料】里",IF(N($M391)&gt;N($L391),"※已还本金大于典当金额",IF(AND($I391&lt;&gt;"",$J391&lt;&gt;"",$J391&lt;$I391),"※到期日早于当票日期",IF(AND($H391&lt;&gt;"",COUNTIF($H$4:$H$403,$H391)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L391&lt;&gt;"",$E391=""),"※有金额没写客户","")))))</f>
+        <f>IF($E391="","",IF(AND($B391&lt;&gt;"",ISNA(MATCH($B391,机构表,0))),"※机构不在【资料】里",IF(AND($D391&lt;&gt;"",ISNA(MATCH($D391,状态表,0))),"※状态不在【资料】里",IF(N($M391)&gt;N($L391),"※已还本金大于典当金额",IF(AND($I391&lt;&gt;"",$J391&lt;&gt;"",$J391&lt;$I391),"※到期日早于当票日期",IF(AND($H391&lt;&gt;"",COUNTIF($H$4:$H$403,$H391)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L391&lt;&gt;"",$E391=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31659,7 +31722,7 @@
       <c r="V392" s="12" t="n"/>
       <c r="W392" s="12" t="n"/>
       <c r="X392" s="18">
-        <f>IF($E392="","",IF(AND($B392&lt;&gt;"",ISNA(MATCH($B392,机构表,0))),"※机构不在【资料】里",IF(AND($D392&lt;&gt;"",ISNA(MATCH($D392,状态表,0))),"※状态不在【资料】里",IF(N($M392)&gt;N($L392),"※已还本金大于典当金额",IF(AND($I392&lt;&gt;"",$J392&lt;&gt;"",$J392&lt;$I392),"※到期日早于当票日期",IF(AND($H392&lt;&gt;"",COUNTIF($H$4:$H$403,$H392)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L392&lt;&gt;"",$E392=""),"※有金额没写客户","")))))</f>
+        <f>IF($E392="","",IF(AND($B392&lt;&gt;"",ISNA(MATCH($B392,机构表,0))),"※机构不在【资料】里",IF(AND($D392&lt;&gt;"",ISNA(MATCH($D392,状态表,0))),"※状态不在【资料】里",IF(N($M392)&gt;N($L392),"※已还本金大于典当金额",IF(AND($I392&lt;&gt;"",$J392&lt;&gt;"",$J392&lt;$I392),"※到期日早于当票日期",IF(AND($H392&lt;&gt;"",COUNTIF($H$4:$H$403,$H392)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L392&lt;&gt;"",$E392=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31694,7 +31757,7 @@
       <c r="V393" s="12" t="n"/>
       <c r="W393" s="12" t="n"/>
       <c r="X393" s="18">
-        <f>IF($E393="","",IF(AND($B393&lt;&gt;"",ISNA(MATCH($B393,机构表,0))),"※机构不在【资料】里",IF(AND($D393&lt;&gt;"",ISNA(MATCH($D393,状态表,0))),"※状态不在【资料】里",IF(N($M393)&gt;N($L393),"※已还本金大于典当金额",IF(AND($I393&lt;&gt;"",$J393&lt;&gt;"",$J393&lt;$I393),"※到期日早于当票日期",IF(AND($H393&lt;&gt;"",COUNTIF($H$4:$H$403,$H393)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L393&lt;&gt;"",$E393=""),"※有金额没写客户","")))))</f>
+        <f>IF($E393="","",IF(AND($B393&lt;&gt;"",ISNA(MATCH($B393,机构表,0))),"※机构不在【资料】里",IF(AND($D393&lt;&gt;"",ISNA(MATCH($D393,状态表,0))),"※状态不在【资料】里",IF(N($M393)&gt;N($L393),"※已还本金大于典当金额",IF(AND($I393&lt;&gt;"",$J393&lt;&gt;"",$J393&lt;$I393),"※到期日早于当票日期",IF(AND($H393&lt;&gt;"",COUNTIF($H$4:$H$403,$H393)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L393&lt;&gt;"",$E393=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31729,7 +31792,7 @@
       <c r="V394" s="12" t="n"/>
       <c r="W394" s="12" t="n"/>
       <c r="X394" s="18">
-        <f>IF($E394="","",IF(AND($B394&lt;&gt;"",ISNA(MATCH($B394,机构表,0))),"※机构不在【资料】里",IF(AND($D394&lt;&gt;"",ISNA(MATCH($D394,状态表,0))),"※状态不在【资料】里",IF(N($M394)&gt;N($L394),"※已还本金大于典当金额",IF(AND($I394&lt;&gt;"",$J394&lt;&gt;"",$J394&lt;$I394),"※到期日早于当票日期",IF(AND($H394&lt;&gt;"",COUNTIF($H$4:$H$403,$H394)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L394&lt;&gt;"",$E394=""),"※有金额没写客户","")))))</f>
+        <f>IF($E394="","",IF(AND($B394&lt;&gt;"",ISNA(MATCH($B394,机构表,0))),"※机构不在【资料】里",IF(AND($D394&lt;&gt;"",ISNA(MATCH($D394,状态表,0))),"※状态不在【资料】里",IF(N($M394)&gt;N($L394),"※已还本金大于典当金额",IF(AND($I394&lt;&gt;"",$J394&lt;&gt;"",$J394&lt;$I394),"※到期日早于当票日期",IF(AND($H394&lt;&gt;"",COUNTIF($H$4:$H$403,$H394)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L394&lt;&gt;"",$E394=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31764,7 +31827,7 @@
       <c r="V395" s="12" t="n"/>
       <c r="W395" s="12" t="n"/>
       <c r="X395" s="18">
-        <f>IF($E395="","",IF(AND($B395&lt;&gt;"",ISNA(MATCH($B395,机构表,0))),"※机构不在【资料】里",IF(AND($D395&lt;&gt;"",ISNA(MATCH($D395,状态表,0))),"※状态不在【资料】里",IF(N($M395)&gt;N($L395),"※已还本金大于典当金额",IF(AND($I395&lt;&gt;"",$J395&lt;&gt;"",$J395&lt;$I395),"※到期日早于当票日期",IF(AND($H395&lt;&gt;"",COUNTIF($H$4:$H$403,$H395)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L395&lt;&gt;"",$E395=""),"※有金额没写客户","")))))</f>
+        <f>IF($E395="","",IF(AND($B395&lt;&gt;"",ISNA(MATCH($B395,机构表,0))),"※机构不在【资料】里",IF(AND($D395&lt;&gt;"",ISNA(MATCH($D395,状态表,0))),"※状态不在【资料】里",IF(N($M395)&gt;N($L395),"※已还本金大于典当金额",IF(AND($I395&lt;&gt;"",$J395&lt;&gt;"",$J395&lt;$I395),"※到期日早于当票日期",IF(AND($H395&lt;&gt;"",COUNTIF($H$4:$H$403,$H395)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L395&lt;&gt;"",$E395=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31799,7 +31862,7 @@
       <c r="V396" s="12" t="n"/>
       <c r="W396" s="12" t="n"/>
       <c r="X396" s="18">
-        <f>IF($E396="","",IF(AND($B396&lt;&gt;"",ISNA(MATCH($B396,机构表,0))),"※机构不在【资料】里",IF(AND($D396&lt;&gt;"",ISNA(MATCH($D396,状态表,0))),"※状态不在【资料】里",IF(N($M396)&gt;N($L396),"※已还本金大于典当金额",IF(AND($I396&lt;&gt;"",$J396&lt;&gt;"",$J396&lt;$I396),"※到期日早于当票日期",IF(AND($H396&lt;&gt;"",COUNTIF($H$4:$H$403,$H396)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L396&lt;&gt;"",$E396=""),"※有金额没写客户","")))))</f>
+        <f>IF($E396="","",IF(AND($B396&lt;&gt;"",ISNA(MATCH($B396,机构表,0))),"※机构不在【资料】里",IF(AND($D396&lt;&gt;"",ISNA(MATCH($D396,状态表,0))),"※状态不在【资料】里",IF(N($M396)&gt;N($L396),"※已还本金大于典当金额",IF(AND($I396&lt;&gt;"",$J396&lt;&gt;"",$J396&lt;$I396),"※到期日早于当票日期",IF(AND($H396&lt;&gt;"",COUNTIF($H$4:$H$403,$H396)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L396&lt;&gt;"",$E396=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31834,7 +31897,7 @@
       <c r="V397" s="12" t="n"/>
       <c r="W397" s="12" t="n"/>
       <c r="X397" s="18">
-        <f>IF($E397="","",IF(AND($B397&lt;&gt;"",ISNA(MATCH($B397,机构表,0))),"※机构不在【资料】里",IF(AND($D397&lt;&gt;"",ISNA(MATCH($D397,状态表,0))),"※状态不在【资料】里",IF(N($M397)&gt;N($L397),"※已还本金大于典当金额",IF(AND($I397&lt;&gt;"",$J397&lt;&gt;"",$J397&lt;$I397),"※到期日早于当票日期",IF(AND($H397&lt;&gt;"",COUNTIF($H$4:$H$403,$H397)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L397&lt;&gt;"",$E397=""),"※有金额没写客户","")))))</f>
+        <f>IF($E397="","",IF(AND($B397&lt;&gt;"",ISNA(MATCH($B397,机构表,0))),"※机构不在【资料】里",IF(AND($D397&lt;&gt;"",ISNA(MATCH($D397,状态表,0))),"※状态不在【资料】里",IF(N($M397)&gt;N($L397),"※已还本金大于典当金额",IF(AND($I397&lt;&gt;"",$J397&lt;&gt;"",$J397&lt;$I397),"※到期日早于当票日期",IF(AND($H397&lt;&gt;"",COUNTIF($H$4:$H$403,$H397)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L397&lt;&gt;"",$E397=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31869,7 +31932,7 @@
       <c r="V398" s="12" t="n"/>
       <c r="W398" s="12" t="n"/>
       <c r="X398" s="18">
-        <f>IF($E398="","",IF(AND($B398&lt;&gt;"",ISNA(MATCH($B398,机构表,0))),"※机构不在【资料】里",IF(AND($D398&lt;&gt;"",ISNA(MATCH($D398,状态表,0))),"※状态不在【资料】里",IF(N($M398)&gt;N($L398),"※已还本金大于典当金额",IF(AND($I398&lt;&gt;"",$J398&lt;&gt;"",$J398&lt;$I398),"※到期日早于当票日期",IF(AND($H398&lt;&gt;"",COUNTIF($H$4:$H$403,$H398)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L398&lt;&gt;"",$E398=""),"※有金额没写客户","")))))</f>
+        <f>IF($E398="","",IF(AND($B398&lt;&gt;"",ISNA(MATCH($B398,机构表,0))),"※机构不在【资料】里",IF(AND($D398&lt;&gt;"",ISNA(MATCH($D398,状态表,0))),"※状态不在【资料】里",IF(N($M398)&gt;N($L398),"※已还本金大于典当金额",IF(AND($I398&lt;&gt;"",$J398&lt;&gt;"",$J398&lt;$I398),"※到期日早于当票日期",IF(AND($H398&lt;&gt;"",COUNTIF($H$4:$H$403,$H398)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L398&lt;&gt;"",$E398=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31904,7 +31967,7 @@
       <c r="V399" s="12" t="n"/>
       <c r="W399" s="12" t="n"/>
       <c r="X399" s="18">
-        <f>IF($E399="","",IF(AND($B399&lt;&gt;"",ISNA(MATCH($B399,机构表,0))),"※机构不在【资料】里",IF(AND($D399&lt;&gt;"",ISNA(MATCH($D399,状态表,0))),"※状态不在【资料】里",IF(N($M399)&gt;N($L399),"※已还本金大于典当金额",IF(AND($I399&lt;&gt;"",$J399&lt;&gt;"",$J399&lt;$I399),"※到期日早于当票日期",IF(AND($H399&lt;&gt;"",COUNTIF($H$4:$H$403,$H399)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L399&lt;&gt;"",$E399=""),"※有金额没写客户","")))))</f>
+        <f>IF($E399="","",IF(AND($B399&lt;&gt;"",ISNA(MATCH($B399,机构表,0))),"※机构不在【资料】里",IF(AND($D399&lt;&gt;"",ISNA(MATCH($D399,状态表,0))),"※状态不在【资料】里",IF(N($M399)&gt;N($L399),"※已还本金大于典当金额",IF(AND($I399&lt;&gt;"",$J399&lt;&gt;"",$J399&lt;$I399),"※到期日早于当票日期",IF(AND($H399&lt;&gt;"",COUNTIF($H$4:$H$403,$H399)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L399&lt;&gt;"",$E399=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31939,7 +32002,7 @@
       <c r="V400" s="12" t="n"/>
       <c r="W400" s="12" t="n"/>
       <c r="X400" s="18">
-        <f>IF($E400="","",IF(AND($B400&lt;&gt;"",ISNA(MATCH($B400,机构表,0))),"※机构不在【资料】里",IF(AND($D400&lt;&gt;"",ISNA(MATCH($D400,状态表,0))),"※状态不在【资料】里",IF(N($M400)&gt;N($L400),"※已还本金大于典当金额",IF(AND($I400&lt;&gt;"",$J400&lt;&gt;"",$J400&lt;$I400),"※到期日早于当票日期",IF(AND($H400&lt;&gt;"",COUNTIF($H$4:$H$403,$H400)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L400&lt;&gt;"",$E400=""),"※有金额没写客户","")))))</f>
+        <f>IF($E400="","",IF(AND($B400&lt;&gt;"",ISNA(MATCH($B400,机构表,0))),"※机构不在【资料】里",IF(AND($D400&lt;&gt;"",ISNA(MATCH($D400,状态表,0))),"※状态不在【资料】里",IF(N($M400)&gt;N($L400),"※已还本金大于典当金额",IF(AND($I400&lt;&gt;"",$J400&lt;&gt;"",$J400&lt;$I400),"※到期日早于当票日期",IF(AND($H400&lt;&gt;"",COUNTIF($H$4:$H$403,$H400)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L400&lt;&gt;"",$E400=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -31974,7 +32037,7 @@
       <c r="V401" s="12" t="n"/>
       <c r="W401" s="12" t="n"/>
       <c r="X401" s="18">
-        <f>IF($E401="","",IF(AND($B401&lt;&gt;"",ISNA(MATCH($B401,机构表,0))),"※机构不在【资料】里",IF(AND($D401&lt;&gt;"",ISNA(MATCH($D401,状态表,0))),"※状态不在【资料】里",IF(N($M401)&gt;N($L401),"※已还本金大于典当金额",IF(AND($I401&lt;&gt;"",$J401&lt;&gt;"",$J401&lt;$I401),"※到期日早于当票日期",IF(AND($H401&lt;&gt;"",COUNTIF($H$4:$H$403,$H401)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L401&lt;&gt;"",$E401=""),"※有金额没写客户","")))))</f>
+        <f>IF($E401="","",IF(AND($B401&lt;&gt;"",ISNA(MATCH($B401,机构表,0))),"※机构不在【资料】里",IF(AND($D401&lt;&gt;"",ISNA(MATCH($D401,状态表,0))),"※状态不在【资料】里",IF(N($M401)&gt;N($L401),"※已还本金大于典当金额",IF(AND($I401&lt;&gt;"",$J401&lt;&gt;"",$J401&lt;$I401),"※到期日早于当票日期",IF(AND($H401&lt;&gt;"",COUNTIF($H$4:$H$403,$H401)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L401&lt;&gt;"",$E401=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -32009,7 +32072,7 @@
       <c r="V402" s="12" t="n"/>
       <c r="W402" s="12" t="n"/>
       <c r="X402" s="18">
-        <f>IF($E402="","",IF(AND($B402&lt;&gt;"",ISNA(MATCH($B402,机构表,0))),"※机构不在【资料】里",IF(AND($D402&lt;&gt;"",ISNA(MATCH($D402,状态表,0))),"※状态不在【资料】里",IF(N($M402)&gt;N($L402),"※已还本金大于典当金额",IF(AND($I402&lt;&gt;"",$J402&lt;&gt;"",$J402&lt;$I402),"※到期日早于当票日期",IF(AND($H402&lt;&gt;"",COUNTIF($H$4:$H$403,$H402)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L402&lt;&gt;"",$E402=""),"※有金额没写客户","")))))</f>
+        <f>IF($E402="","",IF(AND($B402&lt;&gt;"",ISNA(MATCH($B402,机构表,0))),"※机构不在【资料】里",IF(AND($D402&lt;&gt;"",ISNA(MATCH($D402,状态表,0))),"※状态不在【资料】里",IF(N($M402)&gt;N($L402),"※已还本金大于典当金额",IF(AND($I402&lt;&gt;"",$J402&lt;&gt;"",$J402&lt;$I402),"※到期日早于当票日期",IF(AND($H402&lt;&gt;"",COUNTIF($H$4:$H$403,$H402)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L402&lt;&gt;"",$E402=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -32044,7 +32107,7 @@
       <c r="V403" s="12" t="n"/>
       <c r="W403" s="12" t="n"/>
       <c r="X403" s="18">
-        <f>IF($E403="","",IF(AND($B403&lt;&gt;"",ISNA(MATCH($B403,机构表,0))),"※机构不在【资料】里",IF(AND($D403&lt;&gt;"",ISNA(MATCH($D403,状态表,0))),"※状态不在【资料】里",IF(N($M403)&gt;N($L403),"※已还本金大于典当金额",IF(AND($I403&lt;&gt;"",$J403&lt;&gt;"",$J403&lt;$I403),"※到期日早于当票日期",IF(AND($H403&lt;&gt;"",COUNTIF($H$4:$H$403,$H403)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L403&lt;&gt;"",$E403=""),"※有金额没写客户","")))))</f>
+        <f>IF($E403="","",IF(AND($B403&lt;&gt;"",ISNA(MATCH($B403,机构表,0))),"※机构不在【资料】里",IF(AND($D403&lt;&gt;"",ISNA(MATCH($D403,状态表,0))),"※状态不在【资料】里",IF(N($M403)&gt;N($L403),"※已还本金大于典当金额",IF(AND($I403&lt;&gt;"",$J403&lt;&gt;"",$J403&lt;$I403),"※到期日早于当票日期",IF(AND($H403&lt;&gt;"",COUNTIF($H$4:$H$403,$H403)&gt;1),"※当票号在本表里出现了不止一次",IF(AND($L403&lt;&gt;"",$E403=""),"※有金额没写客户","")))))))</f>
         <v/>
       </c>
     </row>
@@ -32348,7 +32411,7 @@
     </row>
     <row r="4">
       <c r="A4" s="18" cm="1">
-        <f t="array" ref="A4:X203">_xlfn._xlws.FILTER(表2客户典当登记!$A$4:$X$403,表2客户典当登记!$B$4:$B$403=$B$2,"这个机构还没有记录")</f>
+        <f t="array" ref="A4:X203">_xlfn._xlws.FILTER(IF(表2客户典当登记!$A$4:$X$403="","",表2客户典当登记!$A$4:$X$403),表2客户典当登记!$B$4:$B$403=$B$2,"这个机构还没有记录")</f>
         <v/>
       </c>
       <c r="B4" s="18" t="n"/>
@@ -37829,7 +37892,7 @@
     </row>
     <row r="4">
       <c r="A4" s="18" cm="1">
-        <f t="array" ref="A4:X203">_xlfn._xlws.FILTER(表2客户典当登记!$A$4:$X$403,表2客户典当登记!$B$4:$B$403=$B$2,"这个机构还没有记录")</f>
+        <f t="array" ref="A4:X203">_xlfn._xlws.FILTER(IF(表2客户典当登记!$A$4:$X$403="","",表2客户典当登记!$A$4:$X$403),表2客户典当登记!$B$4:$B$403=$B$2,"这个机构还没有记录")</f>
         <v/>
       </c>
       <c r="B4" s="18" t="n"/>
@@ -43310,7 +43373,7 @@
     </row>
     <row r="4">
       <c r="A4" s="18" cm="1">
-        <f t="array" ref="A4:X203">_xlfn._xlws.FILTER(表2客户典当登记!$A$4:$X$403,表2客户典当登记!$B$4:$B$403=$B$2,"这个机构还没有记录")</f>
+        <f t="array" ref="A4:X203">_xlfn._xlws.FILTER(IF(表2客户典当登记!$A$4:$X$403="","",表2客户典当登记!$A$4:$X$403),表2客户典当登记!$B$4:$B$403=$B$2,"这个机构还没有记录")</f>
         <v/>
       </c>
       <c r="B4" s="18" t="n"/>
@@ -48521,6 +48584,1693 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00375623"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:T67"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6.6" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="13" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="8" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="2.2" customWidth="1" min="13" max="13"/>
+    <col width="6.6" customWidth="1" min="14" max="14"/>
+    <col width="11" customWidth="1" min="15" max="15"/>
+    <col width="12" customWidth="1" min="16" max="16"/>
+    <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="30" customWidth="1" min="18" max="18"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="20" max="20"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="32" t="inlineStr">
+        <is>
+          <t>客户姓名</t>
+        </is>
+      </c>
+      <c r="B1" s="33" t="inlineStr">
+        <is>
+          <t>严为志</t>
+        </is>
+      </c>
+      <c r="C1" s="3" t="n"/>
+      <c r="D1" s="32" t="inlineStr">
+        <is>
+          <t>身份证号</t>
+        </is>
+      </c>
+      <c r="E1" s="34" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="26">
+        <f>IF($B$1="","← 先选客户姓名。身份证号只有碰到同名客户时才要填。",IF($E$1&lt;&gt;"","已按【姓名+身份证】筛选，典当命中 "&amp;COUNTIFS(表2客户典当登记!$E$4:$E$403,$B$1,表2客户典当登记!$F$4:$F$403,$E$1)&amp;" 笔。（不动产和资金台账没有身份证号这一列，那两块仍然只能按姓名查）",IF(IFERROR(SUMPRODUCT((表2客户典当登记!$E$4:$E$403=$B$1)*(表2客户典当登记!$F$4:$F$403&lt;&gt;"")/(COUNTIFS(表2客户典当登记!$E$4:$E$403,$B$1,表2客户典当登记!$F$4:$F$403,表2客户典当登记!$F$4:$F$403&amp;"")+(表2客户典当登记!$E$4:$E$403&lt;&gt;$B$1))),0)&gt;1,"※这个姓名下登了 "&amp;IFERROR(SUMPRODUCT((表2客户典当登记!$E$4:$E$403=$B$1)*(表2客户典当登记!$F$4:$F$403&lt;&gt;"")/(COUNTIFS(表2客户典当登记!$E$4:$E$403,$B$1,表2客户典当登记!$F$4:$F$403,表2客户典当登记!$F$4:$F$403&amp;"")+(表2客户典当登记!$E$4:$E$403&lt;&gt;$B$1))),0)&amp;" 个不同的身份证号，请把身份证号填到左边 E1 再查。","按姓名查，典当 "&amp;COUNTIF(表2客户典当登记!$E$4:$E$403,$B$1)&amp;" 笔。"&amp;IF(SUMPRODUCT((表2客户典当登记!$E$4:$E$403=$B$1)*(表2客户典当登记!$F$4:$F$403&lt;&gt;""))=0,"（这个客户还没登身份证号，没有同名就不用管）",""))))</f>
+        <v/>
+      </c>
+      <c r="H1" s="2" t="n"/>
+      <c r="I1" s="2" t="n"/>
+      <c r="J1" s="2" t="n"/>
+      <c r="K1" s="2" t="n"/>
+      <c r="L1" s="3" t="n"/>
+      <c r="N1" s="26" t="inlineStr">
+        <is>
+          <t>※ 右边这块取的是《A061_资金台账.xlsx》，查的时候那个文件要一起打开。</t>
+        </is>
+      </c>
+      <c r="O1" s="2" t="n"/>
+      <c r="P1" s="2" t="n"/>
+      <c r="Q1" s="2" t="n"/>
+      <c r="R1" s="2" t="n"/>
+      <c r="S1" s="2" t="n"/>
+      <c r="T1" s="3" t="n"/>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="35" t="inlineStr">
+        <is>
+          <t>典当笔数</t>
+        </is>
+      </c>
+      <c r="B2" s="16">
+        <f>IF($B$1="","",IF($E$1="",COUNTIF(表2客户典当登记!$E$4:$E$403,$B$1),COUNTIFS(表2客户典当登记!$E$4:$E$403,$B$1,表2客户典当登记!$F$4:$F$403,$E$1)))</f>
+        <v/>
+      </c>
+      <c r="C2" s="35" t="inlineStr">
+        <is>
+          <t>典当金额</t>
+        </is>
+      </c>
+      <c r="D2" s="29">
+        <f>IF($B$1="","",ROUND(IF($E$1="",SUMIF(表2客户典当登记!$E$4:$E$403,$B$1,表2客户典当登记!$L$4:$L$403),SUMIFS(表2客户典当登记!$L$4:$L$403,表2客户典当登记!$E$4:$E$403,$B$1,表2客户典当登记!$F$4:$F$403,$E$1)),2))</f>
+        <v/>
+      </c>
+      <c r="E2" s="35" t="inlineStr">
+        <is>
+          <t>已还本金</t>
+        </is>
+      </c>
+      <c r="F2" s="29">
+        <f>IF($B$1="","",ROUND(IF($E$1="",SUMIF(表2客户典当登记!$E$4:$E$403,$B$1,表2客户典当登记!$M$4:$M$403),SUMIFS(表2客户典当登记!$M$4:$M$403,表2客户典当登记!$E$4:$E$403,$B$1,表2客户典当登记!$F$4:$F$403,$E$1)),2))</f>
+        <v/>
+      </c>
+      <c r="G2" s="35" t="inlineStr">
+        <is>
+          <t>当前在当</t>
+        </is>
+      </c>
+      <c r="H2" s="29">
+        <f>IF($B$1="","",ROUND(IF($E$1="",SUMIF(表2客户典当登记!$E$4:$E$403,$B$1,表2客户典当登记!$N$4:$N$403),SUMIFS(表2客户典当登记!$N$4:$N$403,表2客户典当登记!$E$4:$E$403,$B$1,表2客户典当登记!$F$4:$F$403,$E$1)),2))</f>
+        <v/>
+      </c>
+      <c r="I2" s="35" t="inlineStr">
+        <is>
+          <t>应收利息</t>
+        </is>
+      </c>
+      <c r="J2" s="29">
+        <f>IF($B$1="","",ROUND(IF($E$1="",SUMIF(表2客户典当登记!$E$4:$E$403,$B$1,表2客户典当登记!$P$4:$P$403),SUMIFS(表2客户典当登记!$P$4:$P$403,表2客户典当登记!$E$4:$E$403,$B$1,表2客户典当登记!$F$4:$F$403,$E$1)),2))</f>
+        <v/>
+      </c>
+      <c r="K2" s="35" t="inlineStr">
+        <is>
+          <t>不动产金额</t>
+        </is>
+      </c>
+      <c r="L2" s="29">
+        <f>IF($B$1="","",ROUND(SUMIF(表1不动产登记!$D$4:$D$123,$B$1,表1不动产登记!$J$4:$J$123),2))</f>
+        <v/>
+      </c>
+      <c r="N2" s="35" t="inlineStr">
+        <is>
+          <t>资金·收到</t>
+        </is>
+      </c>
+      <c r="O2" s="29">
+        <f>IF($B$1="","",IFERROR(ROUND(SUMIF([1]数据录入!$I$19:$I$5078,$B$1,[1]数据录入!$F$19:$F$5078)+SUMIF([1]数据录入!$J$19:$J$5078,$B$1,[1]数据录入!$F$19:$F$5078),2),"—"))</f>
+        <v/>
+      </c>
+      <c r="P2" s="35" t="inlineStr">
+        <is>
+          <t>资金·付出</t>
+        </is>
+      </c>
+      <c r="Q2" s="29">
+        <f>IF($B$1="","",IFERROR(ROUND(SUMIF([1]数据录入!$I$19:$I$5078,$B$1,[1]数据录入!$G$19:$G$5078)+SUMIF([1]数据录入!$J$19:$J$5078,$B$1,[1]数据录入!$G$19:$G$5078),2),"—"))</f>
+        <v/>
+      </c>
+      <c r="R2" s="35" t="inlineStr">
+        <is>
+          <t>资金笔数</t>
+        </is>
+      </c>
+      <c r="S2" s="16">
+        <f>IF($B$1="","",IFERROR(COUNTIF([1]数据录入!$I$19:$I$5078,$B$1)+COUNTIF([1]数据录入!$J$19:$J$5078,$B$1),"—"))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="36">
+        <f>IF($B$1="","一、典当记录（表2）　← 先选客户姓名","一、典当记录（表2）　共 "&amp;IF($E$1="",COUNTIF(表2客户典当登记!$E$4:$E$403,$B$1),COUNTIFS(表2客户典当登记!$E$4:$E$403,$B$1,表2客户典当登记!$F$4:$F$403,$E$1))&amp;" 笔"&amp;IF(IF($E$1="",COUNTIF(表2客户典当登记!$E$4:$E$403,$B$1),COUNTIFS(表2客户典当登记!$E$4:$E$403,$B$1,表2客户典当登记!$F$4:$F$403,$E$1))&gt;40,"　※超过预留的 40 行了，告诉我加行",""))</f>
+        <v/>
+      </c>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="3" t="n"/>
+      <c r="N3" s="36">
+        <f>IF($B$1="","二、资金收付流水（《A061_资金台账.xlsx》数据录入）　← 先选客户姓名",IFERROR("二、资金收付流水（《A061_资金台账.xlsx》数据录入）　共 "&amp;COUNTIF([1]数据录入!$I$19:$I$5078,$B$1)+COUNTIF([1]数据录入!$J$19:$J$5078,$B$1)&amp;" 笔"&amp;IF(COUNTIF([1]数据录入!$I$19:$I$5078,$B$1)+COUNTIF([1]数据录入!$J$19:$J$5078,$B$1)&gt;60,"　※超过预留的 60 行了，告诉我加行",""),"二、资金收付流水（《A061_资金台账.xlsx》数据录入）　← 取不到数：请把《A061_资金台账.xlsx》一起打开"))</f>
+        <v/>
+      </c>
+      <c r="O3" s="2" t="n"/>
+      <c r="P3" s="2" t="n"/>
+      <c r="Q3" s="2" t="n"/>
+      <c r="R3" s="2" t="n"/>
+      <c r="S3" s="2" t="n"/>
+      <c r="T3" s="3" t="n"/>
+    </row>
+    <row r="4" ht="28" customHeight="1">
+      <c r="A4" s="37" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B4" s="37" t="inlineStr">
+        <is>
+          <t>抵押机构</t>
+        </is>
+      </c>
+      <c r="C4" s="37" t="inlineStr">
+        <is>
+          <t>抵押物品</t>
+        </is>
+      </c>
+      <c r="D4" s="37" t="inlineStr">
+        <is>
+          <t>状 态</t>
+        </is>
+      </c>
+      <c r="E4" s="37" t="inlineStr">
+        <is>
+          <t>当票号</t>
+        </is>
+      </c>
+      <c r="F4" s="37" t="inlineStr">
+        <is>
+          <t>出款日期</t>
+        </is>
+      </c>
+      <c r="G4" s="37" t="inlineStr">
+        <is>
+          <t>典当金额</t>
+        </is>
+      </c>
+      <c r="H4" s="37" t="inlineStr">
+        <is>
+          <t>已还本金</t>
+        </is>
+      </c>
+      <c r="I4" s="37" t="inlineStr">
+        <is>
+          <t>当前在当</t>
+        </is>
+      </c>
+      <c r="J4" s="37" t="inlineStr">
+        <is>
+          <t>应收利息</t>
+        </is>
+      </c>
+      <c r="K4" s="37" t="inlineStr">
+        <is>
+          <t>利息日</t>
+        </is>
+      </c>
+      <c r="L4" s="37" t="inlineStr">
+        <is>
+          <t>详情/备注</t>
+        </is>
+      </c>
+      <c r="N4" s="37" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="O4" s="37" t="inlineStr">
+        <is>
+          <t>日 期</t>
+        </is>
+      </c>
+      <c r="P4" s="37" t="inlineStr">
+        <is>
+          <t>公司账户</t>
+        </is>
+      </c>
+      <c r="Q4" s="37" t="inlineStr">
+        <is>
+          <t>收/支项目类别</t>
+        </is>
+      </c>
+      <c r="R4" s="37" t="inlineStr">
+        <is>
+          <t>摘  要</t>
+        </is>
+      </c>
+      <c r="S4" s="37" t="inlineStr">
+        <is>
+          <t>收入金额</t>
+        </is>
+      </c>
+      <c r="T4" s="37" t="inlineStr">
+        <is>
+          <t>支出金额</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="18" cm="1">
+        <f t="array" ref="A5:D44">IF($B$1="","",IFERROR(_xlfn._xlws.FILTER(IF(表2客户典当登记!$A$4:$D$403="","",表2客户典当登记!$A$4:$D$403),(表2客户典当登记!$E$4:$E$403=$B$1)*IF($E$1="",1,(表2客户典当登记!$F$4:$F$403&amp;"")=($E$1&amp;"")),""),""))</f>
+        <v/>
+      </c>
+      <c r="B5" s="18" t="n"/>
+      <c r="C5" s="18" t="n"/>
+      <c r="D5" s="18" t="n"/>
+      <c r="E5" s="18" cm="1">
+        <f t="array" ref="E5:E44">IF($B$1="","",IFERROR(_xlfn._xlws.FILTER(IF(表2客户典当登记!$H$4:$H$403="","",表2客户典当登记!$H$4:$H$403),(表2客户典当登记!$E$4:$E$403=$B$1)*IF($E$1="",1,(表2客户典当登记!$F$4:$F$403&amp;"")=($E$1&amp;"")),""),""))</f>
+        <v/>
+      </c>
+      <c r="F5" s="30" cm="1">
+        <f t="array" ref="F5:I44">IF($B$1="","",IFERROR(_xlfn._xlws.FILTER(IF(表2客户典当登记!$K$4:$N$403="","",表2客户典当登记!$K$4:$N$403),(表2客户典当登记!$E$4:$E$403=$B$1)*IF($E$1="",1,(表2客户典当登记!$F$4:$F$403&amp;"")=($E$1&amp;"")),""),""))</f>
+        <v/>
+      </c>
+      <c r="G5" s="22" t="n"/>
+      <c r="H5" s="22" t="n"/>
+      <c r="I5" s="22" t="n"/>
+      <c r="J5" s="22" cm="1">
+        <f t="array" ref="J5:K44">IF($B$1="","",IFERROR(_xlfn._xlws.FILTER(IF(表2客户典当登记!$P$4:$Q$403="","",表2客户典当登记!$P$4:$Q$403),(表2客户典当登记!$E$4:$E$403=$B$1)*IF($E$1="",1,(表2客户典当登记!$F$4:$F$403&amp;"")=($E$1&amp;"")),""),""))</f>
+        <v/>
+      </c>
+      <c r="K5" s="18" t="n"/>
+      <c r="L5" s="18" cm="1">
+        <f t="array" ref="L5:L44">IF($B$1="","",IFERROR(_xlfn._xlws.FILTER(IF(表2客户典当登记!$W$4:$W$403="","",表2客户典当登记!$W$4:$W$403),(表2客户典当登记!$E$4:$E$403=$B$1)*IF($E$1="",1,(表2客户典当登记!$F$4:$F$403&amp;"")=($E$1&amp;"")),""),""))</f>
+        <v/>
+      </c>
+      <c r="N5" s="18" cm="1">
+        <f t="array" ref="N5:T64">IF($B$1="","",IFERROR(_xlfn._xlws.FILTER(IF([1]数据录入!$A$19:$G$5078="","",[1]数据录入!$A$19:$G$5078),(([1]数据录入!$I$19:$I$5078=$B$1)+([1]数据录入!$J$19:$J$5078=$B$1))&gt;0,""),""))</f>
+        <v/>
+      </c>
+      <c r="O5" s="30" t="n"/>
+      <c r="P5" s="18" t="n"/>
+      <c r="Q5" s="18" t="n"/>
+      <c r="R5" s="18" t="n"/>
+      <c r="S5" s="22" t="n"/>
+      <c r="T5" s="22" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="18" t="n"/>
+      <c r="B6" s="18" t="n"/>
+      <c r="C6" s="18" t="n"/>
+      <c r="D6" s="18" t="n"/>
+      <c r="E6" s="18" t="n"/>
+      <c r="F6" s="30" t="n"/>
+      <c r="G6" s="22" t="n"/>
+      <c r="H6" s="22" t="n"/>
+      <c r="I6" s="22" t="n"/>
+      <c r="J6" s="22" t="n"/>
+      <c r="K6" s="18" t="n"/>
+      <c r="L6" s="18" t="n"/>
+      <c r="N6" s="18" t="n"/>
+      <c r="O6" s="30" t="n"/>
+      <c r="P6" s="18" t="n"/>
+      <c r="Q6" s="18" t="n"/>
+      <c r="R6" s="18" t="n"/>
+      <c r="S6" s="22" t="n"/>
+      <c r="T6" s="22" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="18" t="n"/>
+      <c r="B7" s="18" t="n"/>
+      <c r="C7" s="18" t="n"/>
+      <c r="D7" s="18" t="n"/>
+      <c r="E7" s="18" t="n"/>
+      <c r="F7" s="30" t="n"/>
+      <c r="G7" s="22" t="n"/>
+      <c r="H7" s="22" t="n"/>
+      <c r="I7" s="22" t="n"/>
+      <c r="J7" s="22" t="n"/>
+      <c r="K7" s="18" t="n"/>
+      <c r="L7" s="18" t="n"/>
+      <c r="N7" s="18" t="n"/>
+      <c r="O7" s="30" t="n"/>
+      <c r="P7" s="18" t="n"/>
+      <c r="Q7" s="18" t="n"/>
+      <c r="R7" s="18" t="n"/>
+      <c r="S7" s="22" t="n"/>
+      <c r="T7" s="22" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="18" t="n"/>
+      <c r="B8" s="18" t="n"/>
+      <c r="C8" s="18" t="n"/>
+      <c r="D8" s="18" t="n"/>
+      <c r="E8" s="18" t="n"/>
+      <c r="F8" s="30" t="n"/>
+      <c r="G8" s="22" t="n"/>
+      <c r="H8" s="22" t="n"/>
+      <c r="I8" s="22" t="n"/>
+      <c r="J8" s="22" t="n"/>
+      <c r="K8" s="18" t="n"/>
+      <c r="L8" s="18" t="n"/>
+      <c r="N8" s="18" t="n"/>
+      <c r="O8" s="30" t="n"/>
+      <c r="P8" s="18" t="n"/>
+      <c r="Q8" s="18" t="n"/>
+      <c r="R8" s="18" t="n"/>
+      <c r="S8" s="22" t="n"/>
+      <c r="T8" s="22" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="18" t="n"/>
+      <c r="B9" s="18" t="n"/>
+      <c r="C9" s="18" t="n"/>
+      <c r="D9" s="18" t="n"/>
+      <c r="E9" s="18" t="n"/>
+      <c r="F9" s="30" t="n"/>
+      <c r="G9" s="22" t="n"/>
+      <c r="H9" s="22" t="n"/>
+      <c r="I9" s="22" t="n"/>
+      <c r="J9" s="22" t="n"/>
+      <c r="K9" s="18" t="n"/>
+      <c r="L9" s="18" t="n"/>
+      <c r="N9" s="18" t="n"/>
+      <c r="O9" s="30" t="n"/>
+      <c r="P9" s="18" t="n"/>
+      <c r="Q9" s="18" t="n"/>
+      <c r="R9" s="18" t="n"/>
+      <c r="S9" s="22" t="n"/>
+      <c r="T9" s="22" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="18" t="n"/>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="30" t="n"/>
+      <c r="G10" s="22" t="n"/>
+      <c r="H10" s="22" t="n"/>
+      <c r="I10" s="22" t="n"/>
+      <c r="J10" s="22" t="n"/>
+      <c r="K10" s="18" t="n"/>
+      <c r="L10" s="18" t="n"/>
+      <c r="N10" s="18" t="n"/>
+      <c r="O10" s="30" t="n"/>
+      <c r="P10" s="18" t="n"/>
+      <c r="Q10" s="18" t="n"/>
+      <c r="R10" s="18" t="n"/>
+      <c r="S10" s="22" t="n"/>
+      <c r="T10" s="22" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="18" t="n"/>
+      <c r="B11" s="18" t="n"/>
+      <c r="C11" s="18" t="n"/>
+      <c r="D11" s="18" t="n"/>
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="30" t="n"/>
+      <c r="G11" s="22" t="n"/>
+      <c r="H11" s="22" t="n"/>
+      <c r="I11" s="22" t="n"/>
+      <c r="J11" s="22" t="n"/>
+      <c r="K11" s="18" t="n"/>
+      <c r="L11" s="18" t="n"/>
+      <c r="N11" s="18" t="n"/>
+      <c r="O11" s="30" t="n"/>
+      <c r="P11" s="18" t="n"/>
+      <c r="Q11" s="18" t="n"/>
+      <c r="R11" s="18" t="n"/>
+      <c r="S11" s="22" t="n"/>
+      <c r="T11" s="22" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="18" t="n"/>
+      <c r="B12" s="18" t="n"/>
+      <c r="C12" s="18" t="n"/>
+      <c r="D12" s="18" t="n"/>
+      <c r="E12" s="18" t="n"/>
+      <c r="F12" s="30" t="n"/>
+      <c r="G12" s="22" t="n"/>
+      <c r="H12" s="22" t="n"/>
+      <c r="I12" s="22" t="n"/>
+      <c r="J12" s="22" t="n"/>
+      <c r="K12" s="18" t="n"/>
+      <c r="L12" s="18" t="n"/>
+      <c r="N12" s="18" t="n"/>
+      <c r="O12" s="30" t="n"/>
+      <c r="P12" s="18" t="n"/>
+      <c r="Q12" s="18" t="n"/>
+      <c r="R12" s="18" t="n"/>
+      <c r="S12" s="22" t="n"/>
+      <c r="T12" s="22" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="18" t="n"/>
+      <c r="B13" s="18" t="n"/>
+      <c r="C13" s="18" t="n"/>
+      <c r="D13" s="18" t="n"/>
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="30" t="n"/>
+      <c r="G13" s="22" t="n"/>
+      <c r="H13" s="22" t="n"/>
+      <c r="I13" s="22" t="n"/>
+      <c r="J13" s="22" t="n"/>
+      <c r="K13" s="18" t="n"/>
+      <c r="L13" s="18" t="n"/>
+      <c r="N13" s="18" t="n"/>
+      <c r="O13" s="30" t="n"/>
+      <c r="P13" s="18" t="n"/>
+      <c r="Q13" s="18" t="n"/>
+      <c r="R13" s="18" t="n"/>
+      <c r="S13" s="22" t="n"/>
+      <c r="T13" s="22" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="18" t="n"/>
+      <c r="B14" s="18" t="n"/>
+      <c r="C14" s="18" t="n"/>
+      <c r="D14" s="18" t="n"/>
+      <c r="E14" s="18" t="n"/>
+      <c r="F14" s="30" t="n"/>
+      <c r="G14" s="22" t="n"/>
+      <c r="H14" s="22" t="n"/>
+      <c r="I14" s="22" t="n"/>
+      <c r="J14" s="22" t="n"/>
+      <c r="K14" s="18" t="n"/>
+      <c r="L14" s="18" t="n"/>
+      <c r="N14" s="18" t="n"/>
+      <c r="O14" s="30" t="n"/>
+      <c r="P14" s="18" t="n"/>
+      <c r="Q14" s="18" t="n"/>
+      <c r="R14" s="18" t="n"/>
+      <c r="S14" s="22" t="n"/>
+      <c r="T14" s="22" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="18" t="n"/>
+      <c r="B15" s="18" t="n"/>
+      <c r="C15" s="18" t="n"/>
+      <c r="D15" s="18" t="n"/>
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="30" t="n"/>
+      <c r="G15" s="22" t="n"/>
+      <c r="H15" s="22" t="n"/>
+      <c r="I15" s="22" t="n"/>
+      <c r="J15" s="22" t="n"/>
+      <c r="K15" s="18" t="n"/>
+      <c r="L15" s="18" t="n"/>
+      <c r="N15" s="18" t="n"/>
+      <c r="O15" s="30" t="n"/>
+      <c r="P15" s="18" t="n"/>
+      <c r="Q15" s="18" t="n"/>
+      <c r="R15" s="18" t="n"/>
+      <c r="S15" s="22" t="n"/>
+      <c r="T15" s="22" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="18" t="n"/>
+      <c r="B16" s="18" t="n"/>
+      <c r="C16" s="18" t="n"/>
+      <c r="D16" s="18" t="n"/>
+      <c r="E16" s="18" t="n"/>
+      <c r="F16" s="30" t="n"/>
+      <c r="G16" s="22" t="n"/>
+      <c r="H16" s="22" t="n"/>
+      <c r="I16" s="22" t="n"/>
+      <c r="J16" s="22" t="n"/>
+      <c r="K16" s="18" t="n"/>
+      <c r="L16" s="18" t="n"/>
+      <c r="N16" s="18" t="n"/>
+      <c r="O16" s="30" t="n"/>
+      <c r="P16" s="18" t="n"/>
+      <c r="Q16" s="18" t="n"/>
+      <c r="R16" s="18" t="n"/>
+      <c r="S16" s="22" t="n"/>
+      <c r="T16" s="22" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="18" t="n"/>
+      <c r="B17" s="18" t="n"/>
+      <c r="C17" s="18" t="n"/>
+      <c r="D17" s="18" t="n"/>
+      <c r="E17" s="18" t="n"/>
+      <c r="F17" s="30" t="n"/>
+      <c r="G17" s="22" t="n"/>
+      <c r="H17" s="22" t="n"/>
+      <c r="I17" s="22" t="n"/>
+      <c r="J17" s="22" t="n"/>
+      <c r="K17" s="18" t="n"/>
+      <c r="L17" s="18" t="n"/>
+      <c r="N17" s="18" t="n"/>
+      <c r="O17" s="30" t="n"/>
+      <c r="P17" s="18" t="n"/>
+      <c r="Q17" s="18" t="n"/>
+      <c r="R17" s="18" t="n"/>
+      <c r="S17" s="22" t="n"/>
+      <c r="T17" s="22" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="18" t="n"/>
+      <c r="B18" s="18" t="n"/>
+      <c r="C18" s="18" t="n"/>
+      <c r="D18" s="18" t="n"/>
+      <c r="E18" s="18" t="n"/>
+      <c r="F18" s="30" t="n"/>
+      <c r="G18" s="22" t="n"/>
+      <c r="H18" s="22" t="n"/>
+      <c r="I18" s="22" t="n"/>
+      <c r="J18" s="22" t="n"/>
+      <c r="K18" s="18" t="n"/>
+      <c r="L18" s="18" t="n"/>
+      <c r="N18" s="18" t="n"/>
+      <c r="O18" s="30" t="n"/>
+      <c r="P18" s="18" t="n"/>
+      <c r="Q18" s="18" t="n"/>
+      <c r="R18" s="18" t="n"/>
+      <c r="S18" s="22" t="n"/>
+      <c r="T18" s="22" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="18" t="n"/>
+      <c r="B19" s="18" t="n"/>
+      <c r="C19" s="18" t="n"/>
+      <c r="D19" s="18" t="n"/>
+      <c r="E19" s="18" t="n"/>
+      <c r="F19" s="30" t="n"/>
+      <c r="G19" s="22" t="n"/>
+      <c r="H19" s="22" t="n"/>
+      <c r="I19" s="22" t="n"/>
+      <c r="J19" s="22" t="n"/>
+      <c r="K19" s="18" t="n"/>
+      <c r="L19" s="18" t="n"/>
+      <c r="N19" s="18" t="n"/>
+      <c r="O19" s="30" t="n"/>
+      <c r="P19" s="18" t="n"/>
+      <c r="Q19" s="18" t="n"/>
+      <c r="R19" s="18" t="n"/>
+      <c r="S19" s="22" t="n"/>
+      <c r="T19" s="22" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="18" t="n"/>
+      <c r="B20" s="18" t="n"/>
+      <c r="C20" s="18" t="n"/>
+      <c r="D20" s="18" t="n"/>
+      <c r="E20" s="18" t="n"/>
+      <c r="F20" s="30" t="n"/>
+      <c r="G20" s="22" t="n"/>
+      <c r="H20" s="22" t="n"/>
+      <c r="I20" s="22" t="n"/>
+      <c r="J20" s="22" t="n"/>
+      <c r="K20" s="18" t="n"/>
+      <c r="L20" s="18" t="n"/>
+      <c r="N20" s="18" t="n"/>
+      <c r="O20" s="30" t="n"/>
+      <c r="P20" s="18" t="n"/>
+      <c r="Q20" s="18" t="n"/>
+      <c r="R20" s="18" t="n"/>
+      <c r="S20" s="22" t="n"/>
+      <c r="T20" s="22" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="18" t="n"/>
+      <c r="B21" s="18" t="n"/>
+      <c r="C21" s="18" t="n"/>
+      <c r="D21" s="18" t="n"/>
+      <c r="E21" s="18" t="n"/>
+      <c r="F21" s="30" t="n"/>
+      <c r="G21" s="22" t="n"/>
+      <c r="H21" s="22" t="n"/>
+      <c r="I21" s="22" t="n"/>
+      <c r="J21" s="22" t="n"/>
+      <c r="K21" s="18" t="n"/>
+      <c r="L21" s="18" t="n"/>
+      <c r="N21" s="18" t="n"/>
+      <c r="O21" s="30" t="n"/>
+      <c r="P21" s="18" t="n"/>
+      <c r="Q21" s="18" t="n"/>
+      <c r="R21" s="18" t="n"/>
+      <c r="S21" s="22" t="n"/>
+      <c r="T21" s="22" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="18" t="n"/>
+      <c r="B22" s="18" t="n"/>
+      <c r="C22" s="18" t="n"/>
+      <c r="D22" s="18" t="n"/>
+      <c r="E22" s="18" t="n"/>
+      <c r="F22" s="30" t="n"/>
+      <c r="G22" s="22" t="n"/>
+      <c r="H22" s="22" t="n"/>
+      <c r="I22" s="22" t="n"/>
+      <c r="J22" s="22" t="n"/>
+      <c r="K22" s="18" t="n"/>
+      <c r="L22" s="18" t="n"/>
+      <c r="N22" s="18" t="n"/>
+      <c r="O22" s="30" t="n"/>
+      <c r="P22" s="18" t="n"/>
+      <c r="Q22" s="18" t="n"/>
+      <c r="R22" s="18" t="n"/>
+      <c r="S22" s="22" t="n"/>
+      <c r="T22" s="22" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="18" t="n"/>
+      <c r="B23" s="18" t="n"/>
+      <c r="C23" s="18" t="n"/>
+      <c r="D23" s="18" t="n"/>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="30" t="n"/>
+      <c r="G23" s="22" t="n"/>
+      <c r="H23" s="22" t="n"/>
+      <c r="I23" s="22" t="n"/>
+      <c r="J23" s="22" t="n"/>
+      <c r="K23" s="18" t="n"/>
+      <c r="L23" s="18" t="n"/>
+      <c r="N23" s="18" t="n"/>
+      <c r="O23" s="30" t="n"/>
+      <c r="P23" s="18" t="n"/>
+      <c r="Q23" s="18" t="n"/>
+      <c r="R23" s="18" t="n"/>
+      <c r="S23" s="22" t="n"/>
+      <c r="T23" s="22" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="18" t="n"/>
+      <c r="B24" s="18" t="n"/>
+      <c r="C24" s="18" t="n"/>
+      <c r="D24" s="18" t="n"/>
+      <c r="E24" s="18" t="n"/>
+      <c r="F24" s="30" t="n"/>
+      <c r="G24" s="22" t="n"/>
+      <c r="H24" s="22" t="n"/>
+      <c r="I24" s="22" t="n"/>
+      <c r="J24" s="22" t="n"/>
+      <c r="K24" s="18" t="n"/>
+      <c r="L24" s="18" t="n"/>
+      <c r="N24" s="18" t="n"/>
+      <c r="O24" s="30" t="n"/>
+      <c r="P24" s="18" t="n"/>
+      <c r="Q24" s="18" t="n"/>
+      <c r="R24" s="18" t="n"/>
+      <c r="S24" s="22" t="n"/>
+      <c r="T24" s="22" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="18" t="n"/>
+      <c r="B25" s="18" t="n"/>
+      <c r="C25" s="18" t="n"/>
+      <c r="D25" s="18" t="n"/>
+      <c r="E25" s="18" t="n"/>
+      <c r="F25" s="30" t="n"/>
+      <c r="G25" s="22" t="n"/>
+      <c r="H25" s="22" t="n"/>
+      <c r="I25" s="22" t="n"/>
+      <c r="J25" s="22" t="n"/>
+      <c r="K25" s="18" t="n"/>
+      <c r="L25" s="18" t="n"/>
+      <c r="N25" s="18" t="n"/>
+      <c r="O25" s="30" t="n"/>
+      <c r="P25" s="18" t="n"/>
+      <c r="Q25" s="18" t="n"/>
+      <c r="R25" s="18" t="n"/>
+      <c r="S25" s="22" t="n"/>
+      <c r="T25" s="22" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="18" t="n"/>
+      <c r="B26" s="18" t="n"/>
+      <c r="C26" s="18" t="n"/>
+      <c r="D26" s="18" t="n"/>
+      <c r="E26" s="18" t="n"/>
+      <c r="F26" s="30" t="n"/>
+      <c r="G26" s="22" t="n"/>
+      <c r="H26" s="22" t="n"/>
+      <c r="I26" s="22" t="n"/>
+      <c r="J26" s="22" t="n"/>
+      <c r="K26" s="18" t="n"/>
+      <c r="L26" s="18" t="n"/>
+      <c r="N26" s="18" t="n"/>
+      <c r="O26" s="30" t="n"/>
+      <c r="P26" s="18" t="n"/>
+      <c r="Q26" s="18" t="n"/>
+      <c r="R26" s="18" t="n"/>
+      <c r="S26" s="22" t="n"/>
+      <c r="T26" s="22" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="18" t="n"/>
+      <c r="B27" s="18" t="n"/>
+      <c r="C27" s="18" t="n"/>
+      <c r="D27" s="18" t="n"/>
+      <c r="E27" s="18" t="n"/>
+      <c r="F27" s="30" t="n"/>
+      <c r="G27" s="22" t="n"/>
+      <c r="H27" s="22" t="n"/>
+      <c r="I27" s="22" t="n"/>
+      <c r="J27" s="22" t="n"/>
+      <c r="K27" s="18" t="n"/>
+      <c r="L27" s="18" t="n"/>
+      <c r="N27" s="18" t="n"/>
+      <c r="O27" s="30" t="n"/>
+      <c r="P27" s="18" t="n"/>
+      <c r="Q27" s="18" t="n"/>
+      <c r="R27" s="18" t="n"/>
+      <c r="S27" s="22" t="n"/>
+      <c r="T27" s="22" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="18" t="n"/>
+      <c r="B28" s="18" t="n"/>
+      <c r="C28" s="18" t="n"/>
+      <c r="D28" s="18" t="n"/>
+      <c r="E28" s="18" t="n"/>
+      <c r="F28" s="30" t="n"/>
+      <c r="G28" s="22" t="n"/>
+      <c r="H28" s="22" t="n"/>
+      <c r="I28" s="22" t="n"/>
+      <c r="J28" s="22" t="n"/>
+      <c r="K28" s="18" t="n"/>
+      <c r="L28" s="18" t="n"/>
+      <c r="N28" s="18" t="n"/>
+      <c r="O28" s="30" t="n"/>
+      <c r="P28" s="18" t="n"/>
+      <c r="Q28" s="18" t="n"/>
+      <c r="R28" s="18" t="n"/>
+      <c r="S28" s="22" t="n"/>
+      <c r="T28" s="22" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="18" t="n"/>
+      <c r="B29" s="18" t="n"/>
+      <c r="C29" s="18" t="n"/>
+      <c r="D29" s="18" t="n"/>
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="30" t="n"/>
+      <c r="G29" s="22" t="n"/>
+      <c r="H29" s="22" t="n"/>
+      <c r="I29" s="22" t="n"/>
+      <c r="J29" s="22" t="n"/>
+      <c r="K29" s="18" t="n"/>
+      <c r="L29" s="18" t="n"/>
+      <c r="N29" s="18" t="n"/>
+      <c r="O29" s="30" t="n"/>
+      <c r="P29" s="18" t="n"/>
+      <c r="Q29" s="18" t="n"/>
+      <c r="R29" s="18" t="n"/>
+      <c r="S29" s="22" t="n"/>
+      <c r="T29" s="22" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="18" t="n"/>
+      <c r="B30" s="18" t="n"/>
+      <c r="C30" s="18" t="n"/>
+      <c r="D30" s="18" t="n"/>
+      <c r="E30" s="18" t="n"/>
+      <c r="F30" s="30" t="n"/>
+      <c r="G30" s="22" t="n"/>
+      <c r="H30" s="22" t="n"/>
+      <c r="I30" s="22" t="n"/>
+      <c r="J30" s="22" t="n"/>
+      <c r="K30" s="18" t="n"/>
+      <c r="L30" s="18" t="n"/>
+      <c r="N30" s="18" t="n"/>
+      <c r="O30" s="30" t="n"/>
+      <c r="P30" s="18" t="n"/>
+      <c r="Q30" s="18" t="n"/>
+      <c r="R30" s="18" t="n"/>
+      <c r="S30" s="22" t="n"/>
+      <c r="T30" s="22" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="18" t="n"/>
+      <c r="B31" s="18" t="n"/>
+      <c r="C31" s="18" t="n"/>
+      <c r="D31" s="18" t="n"/>
+      <c r="E31" s="18" t="n"/>
+      <c r="F31" s="30" t="n"/>
+      <c r="G31" s="22" t="n"/>
+      <c r="H31" s="22" t="n"/>
+      <c r="I31" s="22" t="n"/>
+      <c r="J31" s="22" t="n"/>
+      <c r="K31" s="18" t="n"/>
+      <c r="L31" s="18" t="n"/>
+      <c r="N31" s="18" t="n"/>
+      <c r="O31" s="30" t="n"/>
+      <c r="P31" s="18" t="n"/>
+      <c r="Q31" s="18" t="n"/>
+      <c r="R31" s="18" t="n"/>
+      <c r="S31" s="22" t="n"/>
+      <c r="T31" s="22" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="18" t="n"/>
+      <c r="B32" s="18" t="n"/>
+      <c r="C32" s="18" t="n"/>
+      <c r="D32" s="18" t="n"/>
+      <c r="E32" s="18" t="n"/>
+      <c r="F32" s="30" t="n"/>
+      <c r="G32" s="22" t="n"/>
+      <c r="H32" s="22" t="n"/>
+      <c r="I32" s="22" t="n"/>
+      <c r="J32" s="22" t="n"/>
+      <c r="K32" s="18" t="n"/>
+      <c r="L32" s="18" t="n"/>
+      <c r="N32" s="18" t="n"/>
+      <c r="O32" s="30" t="n"/>
+      <c r="P32" s="18" t="n"/>
+      <c r="Q32" s="18" t="n"/>
+      <c r="R32" s="18" t="n"/>
+      <c r="S32" s="22" t="n"/>
+      <c r="T32" s="22" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="18" t="n"/>
+      <c r="B33" s="18" t="n"/>
+      <c r="C33" s="18" t="n"/>
+      <c r="D33" s="18" t="n"/>
+      <c r="E33" s="18" t="n"/>
+      <c r="F33" s="30" t="n"/>
+      <c r="G33" s="22" t="n"/>
+      <c r="H33" s="22" t="n"/>
+      <c r="I33" s="22" t="n"/>
+      <c r="J33" s="22" t="n"/>
+      <c r="K33" s="18" t="n"/>
+      <c r="L33" s="18" t="n"/>
+      <c r="N33" s="18" t="n"/>
+      <c r="O33" s="30" t="n"/>
+      <c r="P33" s="18" t="n"/>
+      <c r="Q33" s="18" t="n"/>
+      <c r="R33" s="18" t="n"/>
+      <c r="S33" s="22" t="n"/>
+      <c r="T33" s="22" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="18" t="n"/>
+      <c r="B34" s="18" t="n"/>
+      <c r="C34" s="18" t="n"/>
+      <c r="D34" s="18" t="n"/>
+      <c r="E34" s="18" t="n"/>
+      <c r="F34" s="30" t="n"/>
+      <c r="G34" s="22" t="n"/>
+      <c r="H34" s="22" t="n"/>
+      <c r="I34" s="22" t="n"/>
+      <c r="J34" s="22" t="n"/>
+      <c r="K34" s="18" t="n"/>
+      <c r="L34" s="18" t="n"/>
+      <c r="N34" s="18" t="n"/>
+      <c r="O34" s="30" t="n"/>
+      <c r="P34" s="18" t="n"/>
+      <c r="Q34" s="18" t="n"/>
+      <c r="R34" s="18" t="n"/>
+      <c r="S34" s="22" t="n"/>
+      <c r="T34" s="22" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="18" t="n"/>
+      <c r="B35" s="18" t="n"/>
+      <c r="C35" s="18" t="n"/>
+      <c r="D35" s="18" t="n"/>
+      <c r="E35" s="18" t="n"/>
+      <c r="F35" s="30" t="n"/>
+      <c r="G35" s="22" t="n"/>
+      <c r="H35" s="22" t="n"/>
+      <c r="I35" s="22" t="n"/>
+      <c r="J35" s="22" t="n"/>
+      <c r="K35" s="18" t="n"/>
+      <c r="L35" s="18" t="n"/>
+      <c r="N35" s="18" t="n"/>
+      <c r="O35" s="30" t="n"/>
+      <c r="P35" s="18" t="n"/>
+      <c r="Q35" s="18" t="n"/>
+      <c r="R35" s="18" t="n"/>
+      <c r="S35" s="22" t="n"/>
+      <c r="T35" s="22" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="18" t="n"/>
+      <c r="B36" s="18" t="n"/>
+      <c r="C36" s="18" t="n"/>
+      <c r="D36" s="18" t="n"/>
+      <c r="E36" s="18" t="n"/>
+      <c r="F36" s="30" t="n"/>
+      <c r="G36" s="22" t="n"/>
+      <c r="H36" s="22" t="n"/>
+      <c r="I36" s="22" t="n"/>
+      <c r="J36" s="22" t="n"/>
+      <c r="K36" s="18" t="n"/>
+      <c r="L36" s="18" t="n"/>
+      <c r="N36" s="18" t="n"/>
+      <c r="O36" s="30" t="n"/>
+      <c r="P36" s="18" t="n"/>
+      <c r="Q36" s="18" t="n"/>
+      <c r="R36" s="18" t="n"/>
+      <c r="S36" s="22" t="n"/>
+      <c r="T36" s="22" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="18" t="n"/>
+      <c r="B37" s="18" t="n"/>
+      <c r="C37" s="18" t="n"/>
+      <c r="D37" s="18" t="n"/>
+      <c r="E37" s="18" t="n"/>
+      <c r="F37" s="30" t="n"/>
+      <c r="G37" s="22" t="n"/>
+      <c r="H37" s="22" t="n"/>
+      <c r="I37" s="22" t="n"/>
+      <c r="J37" s="22" t="n"/>
+      <c r="K37" s="18" t="n"/>
+      <c r="L37" s="18" t="n"/>
+      <c r="N37" s="18" t="n"/>
+      <c r="O37" s="30" t="n"/>
+      <c r="P37" s="18" t="n"/>
+      <c r="Q37" s="18" t="n"/>
+      <c r="R37" s="18" t="n"/>
+      <c r="S37" s="22" t="n"/>
+      <c r="T37" s="22" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="18" t="n"/>
+      <c r="B38" s="18" t="n"/>
+      <c r="C38" s="18" t="n"/>
+      <c r="D38" s="18" t="n"/>
+      <c r="E38" s="18" t="n"/>
+      <c r="F38" s="30" t="n"/>
+      <c r="G38" s="22" t="n"/>
+      <c r="H38" s="22" t="n"/>
+      <c r="I38" s="22" t="n"/>
+      <c r="J38" s="22" t="n"/>
+      <c r="K38" s="18" t="n"/>
+      <c r="L38" s="18" t="n"/>
+      <c r="N38" s="18" t="n"/>
+      <c r="O38" s="30" t="n"/>
+      <c r="P38" s="18" t="n"/>
+      <c r="Q38" s="18" t="n"/>
+      <c r="R38" s="18" t="n"/>
+      <c r="S38" s="22" t="n"/>
+      <c r="T38" s="22" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="18" t="n"/>
+      <c r="B39" s="18" t="n"/>
+      <c r="C39" s="18" t="n"/>
+      <c r="D39" s="18" t="n"/>
+      <c r="E39" s="18" t="n"/>
+      <c r="F39" s="30" t="n"/>
+      <c r="G39" s="22" t="n"/>
+      <c r="H39" s="22" t="n"/>
+      <c r="I39" s="22" t="n"/>
+      <c r="J39" s="22" t="n"/>
+      <c r="K39" s="18" t="n"/>
+      <c r="L39" s="18" t="n"/>
+      <c r="N39" s="18" t="n"/>
+      <c r="O39" s="30" t="n"/>
+      <c r="P39" s="18" t="n"/>
+      <c r="Q39" s="18" t="n"/>
+      <c r="R39" s="18" t="n"/>
+      <c r="S39" s="22" t="n"/>
+      <c r="T39" s="22" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="18" t="n"/>
+      <c r="B40" s="18" t="n"/>
+      <c r="C40" s="18" t="n"/>
+      <c r="D40" s="18" t="n"/>
+      <c r="E40" s="18" t="n"/>
+      <c r="F40" s="30" t="n"/>
+      <c r="G40" s="22" t="n"/>
+      <c r="H40" s="22" t="n"/>
+      <c r="I40" s="22" t="n"/>
+      <c r="J40" s="22" t="n"/>
+      <c r="K40" s="18" t="n"/>
+      <c r="L40" s="18" t="n"/>
+      <c r="N40" s="18" t="n"/>
+      <c r="O40" s="30" t="n"/>
+      <c r="P40" s="18" t="n"/>
+      <c r="Q40" s="18" t="n"/>
+      <c r="R40" s="18" t="n"/>
+      <c r="S40" s="22" t="n"/>
+      <c r="T40" s="22" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="18" t="n"/>
+      <c r="B41" s="18" t="n"/>
+      <c r="C41" s="18" t="n"/>
+      <c r="D41" s="18" t="n"/>
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="30" t="n"/>
+      <c r="G41" s="22" t="n"/>
+      <c r="H41" s="22" t="n"/>
+      <c r="I41" s="22" t="n"/>
+      <c r="J41" s="22" t="n"/>
+      <c r="K41" s="18" t="n"/>
+      <c r="L41" s="18" t="n"/>
+      <c r="N41" s="18" t="n"/>
+      <c r="O41" s="30" t="n"/>
+      <c r="P41" s="18" t="n"/>
+      <c r="Q41" s="18" t="n"/>
+      <c r="R41" s="18" t="n"/>
+      <c r="S41" s="22" t="n"/>
+      <c r="T41" s="22" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="18" t="n"/>
+      <c r="B42" s="18" t="n"/>
+      <c r="C42" s="18" t="n"/>
+      <c r="D42" s="18" t="n"/>
+      <c r="E42" s="18" t="n"/>
+      <c r="F42" s="30" t="n"/>
+      <c r="G42" s="22" t="n"/>
+      <c r="H42" s="22" t="n"/>
+      <c r="I42" s="22" t="n"/>
+      <c r="J42" s="22" t="n"/>
+      <c r="K42" s="18" t="n"/>
+      <c r="L42" s="18" t="n"/>
+      <c r="N42" s="18" t="n"/>
+      <c r="O42" s="30" t="n"/>
+      <c r="P42" s="18" t="n"/>
+      <c r="Q42" s="18" t="n"/>
+      <c r="R42" s="18" t="n"/>
+      <c r="S42" s="22" t="n"/>
+      <c r="T42" s="22" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="18" t="n"/>
+      <c r="B43" s="18" t="n"/>
+      <c r="C43" s="18" t="n"/>
+      <c r="D43" s="18" t="n"/>
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="30" t="n"/>
+      <c r="G43" s="22" t="n"/>
+      <c r="H43" s="22" t="n"/>
+      <c r="I43" s="22" t="n"/>
+      <c r="J43" s="22" t="n"/>
+      <c r="K43" s="18" t="n"/>
+      <c r="L43" s="18" t="n"/>
+      <c r="N43" s="18" t="n"/>
+      <c r="O43" s="30" t="n"/>
+      <c r="P43" s="18" t="n"/>
+      <c r="Q43" s="18" t="n"/>
+      <c r="R43" s="18" t="n"/>
+      <c r="S43" s="22" t="n"/>
+      <c r="T43" s="22" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="18" t="n"/>
+      <c r="B44" s="18" t="n"/>
+      <c r="C44" s="18" t="n"/>
+      <c r="D44" s="18" t="n"/>
+      <c r="E44" s="18" t="n"/>
+      <c r="F44" s="30" t="n"/>
+      <c r="G44" s="22" t="n"/>
+      <c r="H44" s="22" t="n"/>
+      <c r="I44" s="22" t="n"/>
+      <c r="J44" s="22" t="n"/>
+      <c r="K44" s="18" t="n"/>
+      <c r="L44" s="18" t="n"/>
+      <c r="N44" s="18" t="n"/>
+      <c r="O44" s="30" t="n"/>
+      <c r="P44" s="18" t="n"/>
+      <c r="Q44" s="18" t="n"/>
+      <c r="R44" s="18" t="n"/>
+      <c r="S44" s="22" t="n"/>
+      <c r="T44" s="22" t="n"/>
+    </row>
+    <row r="45">
+      <c r="N45" s="18" t="n"/>
+      <c r="O45" s="30" t="n"/>
+      <c r="P45" s="18" t="n"/>
+      <c r="Q45" s="18" t="n"/>
+      <c r="R45" s="18" t="n"/>
+      <c r="S45" s="22" t="n"/>
+      <c r="T45" s="22" t="n"/>
+    </row>
+    <row r="46" ht="20" customHeight="1">
+      <c r="A46" s="36">
+        <f>IF($B$1="","三、不动产记录（表1 · 就是上面金辉典当那几笔的收款明细，别跟上面相加）　← 先选客户姓名","三、不动产记录（表1 · 就是上面金辉典当那几笔的收款明细，别跟上面相加）　共 "&amp;COUNTIF(表1不动产登记!$D$4:$D$123,$B$1)&amp;" 笔"&amp;IF(COUNTIF(表1不动产登记!$D$4:$D$123,$B$1)&gt;20,"　※超过预留的 20 行了，告诉我加行",""))</f>
+        <v/>
+      </c>
+      <c r="B46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n"/>
+      <c r="E46" s="2" t="n"/>
+      <c r="F46" s="2" t="n"/>
+      <c r="G46" s="2" t="n"/>
+      <c r="H46" s="2" t="n"/>
+      <c r="I46" s="2" t="n"/>
+      <c r="J46" s="2" t="n"/>
+      <c r="K46" s="2" t="n"/>
+      <c r="L46" s="3" t="n"/>
+      <c r="N46" s="18" t="n"/>
+      <c r="O46" s="30" t="n"/>
+      <c r="P46" s="18" t="n"/>
+      <c r="Q46" s="18" t="n"/>
+      <c r="R46" s="18" t="n"/>
+      <c r="S46" s="22" t="n"/>
+      <c r="T46" s="22" t="n"/>
+    </row>
+    <row r="47" ht="28" customHeight="1">
+      <c r="A47" s="37" t="inlineStr">
+        <is>
+          <t>序号</t>
+        </is>
+      </c>
+      <c r="B47" s="37" t="inlineStr">
+        <is>
+          <t>抵押物品</t>
+        </is>
+      </c>
+      <c r="C47" s="37" t="inlineStr">
+        <is>
+          <t>状 态</t>
+        </is>
+      </c>
+      <c r="D47" s="37" t="inlineStr">
+        <is>
+          <t>当票号</t>
+        </is>
+      </c>
+      <c r="E47" s="37" t="inlineStr">
+        <is>
+          <t>当票日期</t>
+        </is>
+      </c>
+      <c r="F47" s="37" t="inlineStr">
+        <is>
+          <t>到期日</t>
+        </is>
+      </c>
+      <c r="G47" s="37" t="inlineStr">
+        <is>
+          <t>出款日期</t>
+        </is>
+      </c>
+      <c r="H47" s="37" t="inlineStr">
+        <is>
+          <t>典当金额</t>
+        </is>
+      </c>
+      <c r="I47" s="37" t="inlineStr">
+        <is>
+          <t>应收利息</t>
+        </is>
+      </c>
+      <c r="J47" s="37" t="inlineStr">
+        <is>
+          <t>合计收款</t>
+        </is>
+      </c>
+      <c r="K47" s="37" t="inlineStr">
+        <is>
+          <t>逾期天数</t>
+        </is>
+      </c>
+      <c r="L47" s="37" t="inlineStr">
+        <is>
+          <t>应收滞纳金</t>
+        </is>
+      </c>
+      <c r="N47" s="18" t="n"/>
+      <c r="O47" s="30" t="n"/>
+      <c r="P47" s="18" t="n"/>
+      <c r="Q47" s="18" t="n"/>
+      <c r="R47" s="18" t="n"/>
+      <c r="S47" s="22" t="n"/>
+      <c r="T47" s="22" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="18" cm="1">
+        <f t="array" ref="A48:C67">IF($B$1="","",IFERROR(_xlfn._xlws.FILTER(IF(表1不动产登记!$A$4:$C$123="","",表1不动产登记!$A$4:$C$123),表1不动产登记!$D$4:$D$123=$B$1,""),""))</f>
+        <v/>
+      </c>
+      <c r="B48" s="18" t="n"/>
+      <c r="C48" s="18" t="n"/>
+      <c r="D48" s="18" cm="1">
+        <f t="array" ref="D48:H67">IF($B$1="","",IFERROR(_xlfn._xlws.FILTER(IF(表1不动产登记!$F$4:$J$123="","",表1不动产登记!$F$4:$J$123),表1不动产登记!$D$4:$D$123=$B$1,""),""))</f>
+        <v/>
+      </c>
+      <c r="E48" s="30" t="n"/>
+      <c r="F48" s="30" t="n"/>
+      <c r="G48" s="30" t="n"/>
+      <c r="H48" s="22" t="n"/>
+      <c r="I48" s="22" cm="1">
+        <f t="array" ref="I48:I67">IF($B$1="","",IFERROR(_xlfn._xlws.FILTER(IF(表1不动产登记!$L$4:$L$123="","",表1不动产登记!$L$4:$L$123),表1不动产登记!$D$4:$D$123=$B$1,""),""))</f>
+        <v/>
+      </c>
+      <c r="J48" s="22" cm="1">
+        <f t="array" ref="J48:J67">IF($B$1="","",IFERROR(_xlfn._xlws.FILTER(IF(表1不动产登记!$S$4:$S$123="","",表1不动产登记!$S$4:$S$123),表1不动产登记!$D$4:$D$123=$B$1,""),""))</f>
+        <v/>
+      </c>
+      <c r="K48" s="23" cm="1">
+        <f t="array" ref="K48:L67">IF($B$1="","",IFERROR(_xlfn._xlws.FILTER(IF(表1不动产登记!$V$4:$W$123="","",表1不动产登记!$V$4:$W$123),表1不动产登记!$D$4:$D$123=$B$1,""),""))</f>
+        <v/>
+      </c>
+      <c r="L48" s="22" t="n"/>
+      <c r="N48" s="18" t="n"/>
+      <c r="O48" s="30" t="n"/>
+      <c r="P48" s="18" t="n"/>
+      <c r="Q48" s="18" t="n"/>
+      <c r="R48" s="18" t="n"/>
+      <c r="S48" s="22" t="n"/>
+      <c r="T48" s="22" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="18" t="n"/>
+      <c r="B49" s="18" t="n"/>
+      <c r="C49" s="18" t="n"/>
+      <c r="D49" s="18" t="n"/>
+      <c r="E49" s="30" t="n"/>
+      <c r="F49" s="30" t="n"/>
+      <c r="G49" s="30" t="n"/>
+      <c r="H49" s="22" t="n"/>
+      <c r="I49" s="22" t="n"/>
+      <c r="J49" s="22" t="n"/>
+      <c r="K49" s="23" t="n"/>
+      <c r="L49" s="22" t="n"/>
+      <c r="N49" s="18" t="n"/>
+      <c r="O49" s="30" t="n"/>
+      <c r="P49" s="18" t="n"/>
+      <c r="Q49" s="18" t="n"/>
+      <c r="R49" s="18" t="n"/>
+      <c r="S49" s="22" t="n"/>
+      <c r="T49" s="22" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="18" t="n"/>
+      <c r="B50" s="18" t="n"/>
+      <c r="C50" s="18" t="n"/>
+      <c r="D50" s="18" t="n"/>
+      <c r="E50" s="30" t="n"/>
+      <c r="F50" s="30" t="n"/>
+      <c r="G50" s="30" t="n"/>
+      <c r="H50" s="22" t="n"/>
+      <c r="I50" s="22" t="n"/>
+      <c r="J50" s="22" t="n"/>
+      <c r="K50" s="23" t="n"/>
+      <c r="L50" s="22" t="n"/>
+      <c r="N50" s="18" t="n"/>
+      <c r="O50" s="30" t="n"/>
+      <c r="P50" s="18" t="n"/>
+      <c r="Q50" s="18" t="n"/>
+      <c r="R50" s="18" t="n"/>
+      <c r="S50" s="22" t="n"/>
+      <c r="T50" s="22" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="18" t="n"/>
+      <c r="B51" s="18" t="n"/>
+      <c r="C51" s="18" t="n"/>
+      <c r="D51" s="18" t="n"/>
+      <c r="E51" s="30" t="n"/>
+      <c r="F51" s="30" t="n"/>
+      <c r="G51" s="30" t="n"/>
+      <c r="H51" s="22" t="n"/>
+      <c r="I51" s="22" t="n"/>
+      <c r="J51" s="22" t="n"/>
+      <c r="K51" s="23" t="n"/>
+      <c r="L51" s="22" t="n"/>
+      <c r="N51" s="18" t="n"/>
+      <c r="O51" s="30" t="n"/>
+      <c r="P51" s="18" t="n"/>
+      <c r="Q51" s="18" t="n"/>
+      <c r="R51" s="18" t="n"/>
+      <c r="S51" s="22" t="n"/>
+      <c r="T51" s="22" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="18" t="n"/>
+      <c r="B52" s="18" t="n"/>
+      <c r="C52" s="18" t="n"/>
+      <c r="D52" s="18" t="n"/>
+      <c r="E52" s="30" t="n"/>
+      <c r="F52" s="30" t="n"/>
+      <c r="G52" s="30" t="n"/>
+      <c r="H52" s="22" t="n"/>
+      <c r="I52" s="22" t="n"/>
+      <c r="J52" s="22" t="n"/>
+      <c r="K52" s="23" t="n"/>
+      <c r="L52" s="22" t="n"/>
+      <c r="N52" s="18" t="n"/>
+      <c r="O52" s="30" t="n"/>
+      <c r="P52" s="18" t="n"/>
+      <c r="Q52" s="18" t="n"/>
+      <c r="R52" s="18" t="n"/>
+      <c r="S52" s="22" t="n"/>
+      <c r="T52" s="22" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="18" t="n"/>
+      <c r="B53" s="18" t="n"/>
+      <c r="C53" s="18" t="n"/>
+      <c r="D53" s="18" t="n"/>
+      <c r="E53" s="30" t="n"/>
+      <c r="F53" s="30" t="n"/>
+      <c r="G53" s="30" t="n"/>
+      <c r="H53" s="22" t="n"/>
+      <c r="I53" s="22" t="n"/>
+      <c r="J53" s="22" t="n"/>
+      <c r="K53" s="23" t="n"/>
+      <c r="L53" s="22" t="n"/>
+      <c r="N53" s="18" t="n"/>
+      <c r="O53" s="30" t="n"/>
+      <c r="P53" s="18" t="n"/>
+      <c r="Q53" s="18" t="n"/>
+      <c r="R53" s="18" t="n"/>
+      <c r="S53" s="22" t="n"/>
+      <c r="T53" s="22" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="18" t="n"/>
+      <c r="B54" s="18" t="n"/>
+      <c r="C54" s="18" t="n"/>
+      <c r="D54" s="18" t="n"/>
+      <c r="E54" s="30" t="n"/>
+      <c r="F54" s="30" t="n"/>
+      <c r="G54" s="30" t="n"/>
+      <c r="H54" s="22" t="n"/>
+      <c r="I54" s="22" t="n"/>
+      <c r="J54" s="22" t="n"/>
+      <c r="K54" s="23" t="n"/>
+      <c r="L54" s="22" t="n"/>
+      <c r="N54" s="18" t="n"/>
+      <c r="O54" s="30" t="n"/>
+      <c r="P54" s="18" t="n"/>
+      <c r="Q54" s="18" t="n"/>
+      <c r="R54" s="18" t="n"/>
+      <c r="S54" s="22" t="n"/>
+      <c r="T54" s="22" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="18" t="n"/>
+      <c r="B55" s="18" t="n"/>
+      <c r="C55" s="18" t="n"/>
+      <c r="D55" s="18" t="n"/>
+      <c r="E55" s="30" t="n"/>
+      <c r="F55" s="30" t="n"/>
+      <c r="G55" s="30" t="n"/>
+      <c r="H55" s="22" t="n"/>
+      <c r="I55" s="22" t="n"/>
+      <c r="J55" s="22" t="n"/>
+      <c r="K55" s="23" t="n"/>
+      <c r="L55" s="22" t="n"/>
+      <c r="N55" s="18" t="n"/>
+      <c r="O55" s="30" t="n"/>
+      <c r="P55" s="18" t="n"/>
+      <c r="Q55" s="18" t="n"/>
+      <c r="R55" s="18" t="n"/>
+      <c r="S55" s="22" t="n"/>
+      <c r="T55" s="22" t="n"/>
+    </row>
+    <row r="56">
+      <c r="A56" s="18" t="n"/>
+      <c r="B56" s="18" t="n"/>
+      <c r="C56" s="18" t="n"/>
+      <c r="D56" s="18" t="n"/>
+      <c r="E56" s="30" t="n"/>
+      <c r="F56" s="30" t="n"/>
+      <c r="G56" s="30" t="n"/>
+      <c r="H56" s="22" t="n"/>
+      <c r="I56" s="22" t="n"/>
+      <c r="J56" s="22" t="n"/>
+      <c r="K56" s="23" t="n"/>
+      <c r="L56" s="22" t="n"/>
+      <c r="N56" s="18" t="n"/>
+      <c r="O56" s="30" t="n"/>
+      <c r="P56" s="18" t="n"/>
+      <c r="Q56" s="18" t="n"/>
+      <c r="R56" s="18" t="n"/>
+      <c r="S56" s="22" t="n"/>
+      <c r="T56" s="22" t="n"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="18" t="n"/>
+      <c r="B57" s="18" t="n"/>
+      <c r="C57" s="18" t="n"/>
+      <c r="D57" s="18" t="n"/>
+      <c r="E57" s="30" t="n"/>
+      <c r="F57" s="30" t="n"/>
+      <c r="G57" s="30" t="n"/>
+      <c r="H57" s="22" t="n"/>
+      <c r="I57" s="22" t="n"/>
+      <c r="J57" s="22" t="n"/>
+      <c r="K57" s="23" t="n"/>
+      <c r="L57" s="22" t="n"/>
+      <c r="N57" s="18" t="n"/>
+      <c r="O57" s="30" t="n"/>
+      <c r="P57" s="18" t="n"/>
+      <c r="Q57" s="18" t="n"/>
+      <c r="R57" s="18" t="n"/>
+      <c r="S57" s="22" t="n"/>
+      <c r="T57" s="22" t="n"/>
+    </row>
+    <row r="58">
+      <c r="A58" s="18" t="n"/>
+      <c r="B58" s="18" t="n"/>
+      <c r="C58" s="18" t="n"/>
+      <c r="D58" s="18" t="n"/>
+      <c r="E58" s="30" t="n"/>
+      <c r="F58" s="30" t="n"/>
+      <c r="G58" s="30" t="n"/>
+      <c r="H58" s="22" t="n"/>
+      <c r="I58" s="22" t="n"/>
+      <c r="J58" s="22" t="n"/>
+      <c r="K58" s="23" t="n"/>
+      <c r="L58" s="22" t="n"/>
+      <c r="N58" s="18" t="n"/>
+      <c r="O58" s="30" t="n"/>
+      <c r="P58" s="18" t="n"/>
+      <c r="Q58" s="18" t="n"/>
+      <c r="R58" s="18" t="n"/>
+      <c r="S58" s="22" t="n"/>
+      <c r="T58" s="22" t="n"/>
+    </row>
+    <row r="59">
+      <c r="A59" s="18" t="n"/>
+      <c r="B59" s="18" t="n"/>
+      <c r="C59" s="18" t="n"/>
+      <c r="D59" s="18" t="n"/>
+      <c r="E59" s="30" t="n"/>
+      <c r="F59" s="30" t="n"/>
+      <c r="G59" s="30" t="n"/>
+      <c r="H59" s="22" t="n"/>
+      <c r="I59" s="22" t="n"/>
+      <c r="J59" s="22" t="n"/>
+      <c r="K59" s="23" t="n"/>
+      <c r="L59" s="22" t="n"/>
+      <c r="N59" s="18" t="n"/>
+      <c r="O59" s="30" t="n"/>
+      <c r="P59" s="18" t="n"/>
+      <c r="Q59" s="18" t="n"/>
+      <c r="R59" s="18" t="n"/>
+      <c r="S59" s="22" t="n"/>
+      <c r="T59" s="22" t="n"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="18" t="n"/>
+      <c r="B60" s="18" t="n"/>
+      <c r="C60" s="18" t="n"/>
+      <c r="D60" s="18" t="n"/>
+      <c r="E60" s="30" t="n"/>
+      <c r="F60" s="30" t="n"/>
+      <c r="G60" s="30" t="n"/>
+      <c r="H60" s="22" t="n"/>
+      <c r="I60" s="22" t="n"/>
+      <c r="J60" s="22" t="n"/>
+      <c r="K60" s="23" t="n"/>
+      <c r="L60" s="22" t="n"/>
+      <c r="N60" s="18" t="n"/>
+      <c r="O60" s="30" t="n"/>
+      <c r="P60" s="18" t="n"/>
+      <c r="Q60" s="18" t="n"/>
+      <c r="R60" s="18" t="n"/>
+      <c r="S60" s="22" t="n"/>
+      <c r="T60" s="22" t="n"/>
+    </row>
+    <row r="61">
+      <c r="A61" s="18" t="n"/>
+      <c r="B61" s="18" t="n"/>
+      <c r="C61" s="18" t="n"/>
+      <c r="D61" s="18" t="n"/>
+      <c r="E61" s="30" t="n"/>
+      <c r="F61" s="30" t="n"/>
+      <c r="G61" s="30" t="n"/>
+      <c r="H61" s="22" t="n"/>
+      <c r="I61" s="22" t="n"/>
+      <c r="J61" s="22" t="n"/>
+      <c r="K61" s="23" t="n"/>
+      <c r="L61" s="22" t="n"/>
+      <c r="N61" s="18" t="n"/>
+      <c r="O61" s="30" t="n"/>
+      <c r="P61" s="18" t="n"/>
+      <c r="Q61" s="18" t="n"/>
+      <c r="R61" s="18" t="n"/>
+      <c r="S61" s="22" t="n"/>
+      <c r="T61" s="22" t="n"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="18" t="n"/>
+      <c r="B62" s="18" t="n"/>
+      <c r="C62" s="18" t="n"/>
+      <c r="D62" s="18" t="n"/>
+      <c r="E62" s="30" t="n"/>
+      <c r="F62" s="30" t="n"/>
+      <c r="G62" s="30" t="n"/>
+      <c r="H62" s="22" t="n"/>
+      <c r="I62" s="22" t="n"/>
+      <c r="J62" s="22" t="n"/>
+      <c r="K62" s="23" t="n"/>
+      <c r="L62" s="22" t="n"/>
+      <c r="N62" s="18" t="n"/>
+      <c r="O62" s="30" t="n"/>
+      <c r="P62" s="18" t="n"/>
+      <c r="Q62" s="18" t="n"/>
+      <c r="R62" s="18" t="n"/>
+      <c r="S62" s="22" t="n"/>
+      <c r="T62" s="22" t="n"/>
+    </row>
+    <row r="63">
+      <c r="A63" s="18" t="n"/>
+      <c r="B63" s="18" t="n"/>
+      <c r="C63" s="18" t="n"/>
+      <c r="D63" s="18" t="n"/>
+      <c r="E63" s="30" t="n"/>
+      <c r="F63" s="30" t="n"/>
+      <c r="G63" s="30" t="n"/>
+      <c r="H63" s="22" t="n"/>
+      <c r="I63" s="22" t="n"/>
+      <c r="J63" s="22" t="n"/>
+      <c r="K63" s="23" t="n"/>
+      <c r="L63" s="22" t="n"/>
+      <c r="N63" s="18" t="n"/>
+      <c r="O63" s="30" t="n"/>
+      <c r="P63" s="18" t="n"/>
+      <c r="Q63" s="18" t="n"/>
+      <c r="R63" s="18" t="n"/>
+      <c r="S63" s="22" t="n"/>
+      <c r="T63" s="22" t="n"/>
+    </row>
+    <row r="64">
+      <c r="A64" s="18" t="n"/>
+      <c r="B64" s="18" t="n"/>
+      <c r="C64" s="18" t="n"/>
+      <c r="D64" s="18" t="n"/>
+      <c r="E64" s="30" t="n"/>
+      <c r="F64" s="30" t="n"/>
+      <c r="G64" s="30" t="n"/>
+      <c r="H64" s="22" t="n"/>
+      <c r="I64" s="22" t="n"/>
+      <c r="J64" s="22" t="n"/>
+      <c r="K64" s="23" t="n"/>
+      <c r="L64" s="22" t="n"/>
+      <c r="N64" s="18" t="n"/>
+      <c r="O64" s="30" t="n"/>
+      <c r="P64" s="18" t="n"/>
+      <c r="Q64" s="18" t="n"/>
+      <c r="R64" s="18" t="n"/>
+      <c r="S64" s="22" t="n"/>
+      <c r="T64" s="22" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="18" t="n"/>
+      <c r="B65" s="18" t="n"/>
+      <c r="C65" s="18" t="n"/>
+      <c r="D65" s="18" t="n"/>
+      <c r="E65" s="30" t="n"/>
+      <c r="F65" s="30" t="n"/>
+      <c r="G65" s="30" t="n"/>
+      <c r="H65" s="22" t="n"/>
+      <c r="I65" s="22" t="n"/>
+      <c r="J65" s="22" t="n"/>
+      <c r="K65" s="23" t="n"/>
+      <c r="L65" s="22" t="n"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="18" t="n"/>
+      <c r="B66" s="18" t="n"/>
+      <c r="C66" s="18" t="n"/>
+      <c r="D66" s="18" t="n"/>
+      <c r="E66" s="30" t="n"/>
+      <c r="F66" s="30" t="n"/>
+      <c r="G66" s="30" t="n"/>
+      <c r="H66" s="22" t="n"/>
+      <c r="I66" s="22" t="n"/>
+      <c r="J66" s="22" t="n"/>
+      <c r="K66" s="23" t="n"/>
+      <c r="L66" s="22" t="n"/>
+    </row>
+    <row r="67">
+      <c r="A67" s="18" t="n"/>
+      <c r="B67" s="18" t="n"/>
+      <c r="C67" s="18" t="n"/>
+      <c r="D67" s="18" t="n"/>
+      <c r="E67" s="30" t="n"/>
+      <c r="F67" s="30" t="n"/>
+      <c r="G67" s="30" t="n"/>
+      <c r="H67" s="22" t="n"/>
+      <c r="I67" s="22" t="n"/>
+      <c r="J67" s="22" t="n"/>
+      <c r="K67" s="23" t="n"/>
+      <c r="L67" s="22" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="7">
+    <mergeCell ref="G1:L1"/>
+    <mergeCell ref="N1:T1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="A46:L46"/>
+    <mergeCell ref="A3:L3"/>
+    <mergeCell ref="N3:T3"/>
+    <mergeCell ref="B1:C1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A3">
+    <cfRule type="expression" priority="1" dxfId="2">
+      <formula>ISNUMBER(SEARCH("※",A3))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="N3">
+    <cfRule type="expression" priority="2" dxfId="2">
+      <formula>ISNUMBER(SEARCH("※",N3))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="A46">
+    <cfRule type="expression" priority="3" dxfId="2">
+      <formula>ISNUMBER(SEARCH("※",A46))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="B1" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="不在名单里" error="先去【资料】把它加上，或者选一个已有的。" type="list" errorStyle="warning">
+      <formula1>=客户名单</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00375623"/>
@@ -48553,7 +50303,7 @@
     <row r="1" ht="30" customHeight="1">
       <c r="A1" s="9" t="inlineStr">
         <is>
-          <t>查询表 · 输入客户姓名，一次看全他的典当和资金往来</t>
+          <t>查询表（旧版·竖着排，保留备用）· 输入客户姓名，一次看全他的典当和资金往来</t>
         </is>
       </c>
     </row>
@@ -48565,7 +50315,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="32" t="inlineStr">
+      <c r="A3" s="38" t="inlineStr">
         <is>
           <t>客户姓名 →</t>
         </is>
@@ -48576,7 +50326,7 @@
         </is>
       </c>
       <c r="C3" s="3" t="n"/>
-      <c r="D3" s="34" t="inlineStr">
+      <c r="D3" s="32" t="inlineStr">
         <is>
           <t>身份证号</t>
         </is>
@@ -48586,7 +50336,7 @@
         <v/>
       </c>
       <c r="F3" s="3" t="n"/>
-      <c r="G3" s="34" t="inlineStr">
+      <c r="G3" s="32" t="inlineStr">
         <is>
           <t>客户电话</t>
         </is>
@@ -48681,7 +50431,7 @@
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="36" t="inlineStr">
+      <c r="A8" s="39" t="inlineStr">
         <is>
           <t>一、典当记录（来自【表2客户典当登记】·所有机构）</t>
         </is>
@@ -48703,98 +50453,98 @@
       <c r="P8" s="2" t="n"/>
       <c r="Q8" s="2" t="n"/>
       <c r="R8" s="3" t="n"/>
-      <c r="T8" s="37">
+      <c r="T8" s="40">
         <f>IF(COUNTIF(表2客户典当登记!$E$4:$E$403,$B$3)&gt;40,"※记录超过预留的 40 行，会显示 #SPILL!，告诉我加行","")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1">
-      <c r="A9" s="38" t="inlineStr">
+      <c r="A9" s="37" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B9" s="38" t="inlineStr">
+      <c r="B9" s="37" t="inlineStr">
         <is>
           <t>抵押机构 ★</t>
         </is>
       </c>
-      <c r="C9" s="38" t="inlineStr">
+      <c r="C9" s="37" t="inlineStr">
         <is>
           <t>抵押物品 ★</t>
         </is>
       </c>
-      <c r="D9" s="38" t="inlineStr">
+      <c r="D9" s="37" t="inlineStr">
         <is>
           <t>状态 ★</t>
         </is>
       </c>
-      <c r="E9" s="38" t="inlineStr">
+      <c r="E9" s="37" t="inlineStr">
         <is>
           <t>客户姓名 ★</t>
         </is>
       </c>
-      <c r="F9" s="38" t="inlineStr">
+      <c r="F9" s="37" t="inlineStr">
         <is>
           <t>身份证号</t>
         </is>
       </c>
-      <c r="G9" s="38" t="inlineStr">
+      <c r="G9" s="37" t="inlineStr">
         <is>
           <t>客户电话</t>
         </is>
       </c>
-      <c r="H9" s="38" t="inlineStr">
+      <c r="H9" s="37" t="inlineStr">
         <is>
           <t>当票号</t>
         </is>
       </c>
-      <c r="I9" s="38" t="inlineStr">
+      <c r="I9" s="37" t="inlineStr">
         <is>
           <t>当票日期</t>
         </is>
       </c>
-      <c r="J9" s="38" t="inlineStr">
+      <c r="J9" s="37" t="inlineStr">
         <is>
           <t>当票到期日</t>
         </is>
       </c>
-      <c r="K9" s="38" t="inlineStr">
+      <c r="K9" s="37" t="inlineStr">
         <is>
           <t>出款日期</t>
         </is>
       </c>
-      <c r="L9" s="38" t="inlineStr">
+      <c r="L9" s="37" t="inlineStr">
         <is>
           <t>典当金额 ★</t>
         </is>
       </c>
-      <c r="M9" s="38" t="inlineStr">
+      <c r="M9" s="37" t="inlineStr">
         <is>
           <t>已还本金</t>
         </is>
       </c>
-      <c r="N9" s="38" t="inlineStr">
+      <c r="N9" s="37" t="inlineStr">
         <is>
           <t>当前在当</t>
         </is>
       </c>
-      <c r="O9" s="38" t="inlineStr">
+      <c r="O9" s="37" t="inlineStr">
         <is>
           <t>典当系统费率</t>
         </is>
       </c>
-      <c r="P9" s="38" t="inlineStr">
+      <c r="P9" s="37" t="inlineStr">
         <is>
           <t>应收利息</t>
         </is>
       </c>
-      <c r="Q9" s="38" t="inlineStr">
+      <c r="Q9" s="37" t="inlineStr">
         <is>
           <t>利息日</t>
         </is>
       </c>
-      <c r="R9" s="38" t="inlineStr">
+      <c r="R9" s="37" t="inlineStr">
         <is>
           <t>应付利息日</t>
         </is>
@@ -48802,7 +50552,7 @@
     </row>
     <row r="10">
       <c r="A10" s="18" cm="1">
-        <f t="array" ref="A10:R49">_xlfn._xlws.FILTER(表2客户典当登记!$A$4:$R$403,表2客户典当登记!$E$4:$E$403=$B$3,"这个客户在表2里没有典当记录")</f>
+        <f t="array" ref="A10:R49">_xlfn._xlws.FILTER(IF(表2客户典当登记!$A$4:$R$403="","",表2客户典当登记!$A$4:$R$403),表2客户典当登记!$E$4:$E$403=$B$3,"这个客户在表2里没有典当记录")</f>
         <v/>
       </c>
       <c r="B10" s="18" t="n"/>
@@ -49604,7 +51354,7 @@
       <c r="R49" s="30" t="n"/>
     </row>
     <row r="52" ht="22" customHeight="1">
-      <c r="A52" s="36" t="inlineStr">
+      <c r="A52" s="39" t="inlineStr">
         <is>
           <t>二、不动产记录（来自【表1不动产登记】·就是上面金辉典当那几笔的收款明细，别跟上面相加）</t>
         </is>
@@ -49621,73 +51371,73 @@
       <c r="K52" s="2" t="n"/>
       <c r="L52" s="2" t="n"/>
       <c r="M52" s="3" t="n"/>
-      <c r="O52" s="37">
+      <c r="O52" s="40">
         <f>IF(COUNTIF(表1不动产登记!$D$4:$D$123,$B$3)&gt;20,"※记录超过预留的 20 行，会显示 #SPILL!，告诉我加行","")</f>
         <v/>
       </c>
     </row>
     <row r="53" ht="32" customHeight="1">
-      <c r="A53" s="38" t="inlineStr">
+      <c r="A53" s="37" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B53" s="38" t="inlineStr">
+      <c r="B53" s="37" t="inlineStr">
         <is>
           <t>抵押物品 ★</t>
         </is>
       </c>
-      <c r="C53" s="38" t="inlineStr">
+      <c r="C53" s="37" t="inlineStr">
         <is>
           <t>状态 ★</t>
         </is>
       </c>
-      <c r="D53" s="38" t="inlineStr">
+      <c r="D53" s="37" t="inlineStr">
         <is>
           <t>客户姓名 ★</t>
         </is>
       </c>
-      <c r="E53" s="38" t="inlineStr">
+      <c r="E53" s="37" t="inlineStr">
         <is>
           <t>客户电话</t>
         </is>
       </c>
-      <c r="F53" s="38" t="inlineStr">
+      <c r="F53" s="37" t="inlineStr">
         <is>
           <t>当票号</t>
         </is>
       </c>
-      <c r="G53" s="38" t="inlineStr">
+      <c r="G53" s="37" t="inlineStr">
         <is>
           <t>当票日期</t>
         </is>
       </c>
-      <c r="H53" s="38" t="inlineStr">
+      <c r="H53" s="37" t="inlineStr">
         <is>
           <t>当票到期日</t>
         </is>
       </c>
-      <c r="I53" s="38" t="inlineStr">
+      <c r="I53" s="37" t="inlineStr">
         <is>
           <t>出款日期</t>
         </is>
       </c>
-      <c r="J53" s="38" t="inlineStr">
+      <c r="J53" s="37" t="inlineStr">
         <is>
           <t>典当金额 ★</t>
         </is>
       </c>
-      <c r="K53" s="38" t="inlineStr">
+      <c r="K53" s="37" t="inlineStr">
         <is>
           <t>典当系统费率</t>
         </is>
       </c>
-      <c r="L53" s="38" t="inlineStr">
+      <c r="L53" s="37" t="inlineStr">
         <is>
           <t>应收金额(利息)</t>
         </is>
       </c>
-      <c r="M53" s="38" t="inlineStr">
+      <c r="M53" s="37" t="inlineStr">
         <is>
           <t>开票金额</t>
         </is>
@@ -49695,7 +51445,7 @@
     </row>
     <row r="54">
       <c r="A54" s="18" cm="1">
-        <f t="array" ref="A54:M73">_xlfn._xlws.FILTER(表1不动产登记!$A$4:$M$123,表1不动产登记!$D$4:$D$123=$B$3,"这个客户在表1里没有不动产记录")</f>
+        <f t="array" ref="A54:M73">_xlfn._xlws.FILTER(IF(表1不动产登记!$A$4:$M$123="","",表1不动产登记!$A$4:$M$123),表1不动产登记!$D$4:$D$123=$B$3,"这个客户在表1里没有不动产记录")</f>
         <v/>
       </c>
       <c r="B54" s="18" t="n"/>
@@ -49997,7 +51747,7 @@
       <c r="M73" s="22" t="n"/>
     </row>
     <row r="76" ht="22" customHeight="1">
-      <c r="A76" s="36" t="inlineStr">
+      <c r="A76" s="39" t="inlineStr">
         <is>
           <t>三、资金收付流水（来自《A061_资金台账.xlsx》的「数据录入」，要同时打开那个文件）</t>
         </is>
@@ -50012,63 +51762,63 @@
       <c r="I76" s="2" t="n"/>
       <c r="J76" s="2" t="n"/>
       <c r="K76" s="3" t="n"/>
-      <c r="M76" s="37">
+      <c r="M76" s="40">
         <f>IF(COUNTIF([1]数据录入!$I$19:$I$5078,$B$3)&gt;80,"※记录超过预留的 80 行，会显示 #SPILL!，告诉我加行","")</f>
         <v/>
       </c>
     </row>
     <row r="77" ht="32" customHeight="1">
-      <c r="A77" s="38" t="inlineStr">
+      <c r="A77" s="37" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B77" s="38" t="inlineStr">
+      <c r="B77" s="37" t="inlineStr">
         <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="C77" s="38" t="inlineStr">
+      <c r="C77" s="37" t="inlineStr">
         <is>
           <t>公司账户</t>
         </is>
       </c>
-      <c r="D77" s="38" t="inlineStr">
+      <c r="D77" s="37" t="inlineStr">
         <is>
           <t>收/支项目类别</t>
         </is>
       </c>
-      <c r="E77" s="38" t="inlineStr">
+      <c r="E77" s="37" t="inlineStr">
         <is>
           <t>摘要内容</t>
         </is>
       </c>
-      <c r="F77" s="38" t="inlineStr">
+      <c r="F77" s="37" t="inlineStr">
         <is>
           <t>收入</t>
         </is>
       </c>
-      <c r="G77" s="38" t="inlineStr">
+      <c r="G77" s="37" t="inlineStr">
         <is>
           <t>支出</t>
         </is>
       </c>
-      <c r="H77" s="38" t="inlineStr">
+      <c r="H77" s="37" t="inlineStr">
         <is>
           <t>账户余额</t>
         </is>
       </c>
-      <c r="I77" s="38" t="inlineStr">
+      <c r="I77" s="37" t="inlineStr">
         <is>
           <t>客户</t>
         </is>
       </c>
-      <c r="J77" s="38" t="inlineStr">
+      <c r="J77" s="37" t="inlineStr">
         <is>
           <t>供应商</t>
         </is>
       </c>
-      <c r="K77" s="38" t="inlineStr">
+      <c r="K77" s="37" t="inlineStr">
         <is>
           <t>月份</t>
         </is>
@@ -50076,7 +51826,7 @@
     </row>
     <row r="78">
       <c r="A78" s="18" cm="1">
-        <f t="array" ref="A78:K157">_xlfn._xlws.FILTER([1]数据录入!$A$19:$K$5078,[1]数据录入!$I$19:$I$5078=$B$3,"这个客户在资金台账里没有流水，或者《A061_资金台账.xlsx》没打开")</f>
+        <f t="array" ref="A78:K157">_xlfn._xlws.FILTER(IF([1]数据录入!$A$19:$K$5078="","",[1]数据录入!$A$19:$K$5078),[1]数据录入!$I$19:$I$5078=$B$3,"这个客户在资金台账里没有流水，或者《A061_资金台账.xlsx》没打开")</f>
         <v/>
       </c>
       <c r="B78" s="30" t="n"/>
